--- a/cotacao-cristofer-reveillon.xlsx
+++ b/cotacao-cristofer-reveillon.xlsx
@@ -1101,7 +1101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P52"/>
+  <dimension ref="A1:P59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="D6" s="23" t="inlineStr">
         <is>
-          <t>GRU → VIE (04/01, 1 conexão) + CDG → GRU (12/01, mesmo voo da família)</t>
+          <t>AF453 GRU 04/01 14:40 → CDG 05/01 06:05 · AF1138 CDG 10:00 → VIE 12:00 (conexão 3h55) · AF1139 VIE 10/01 12:55 → CDG 15:10 · AF454 CDG 12/01 23:20 → GRU 13/01 07:20 · econômica</t>
         </is>
       </c>
       <c r="E6" s="23" t="inlineStr">
@@ -1313,13 +1313,19 @@
       <c r="F6" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="25" t="inlineStr"/>
+      <c r="G6" s="25" t="inlineStr">
+        <is>
+          <t>Air France (consolidador)</t>
+        </is>
+      </c>
       <c r="H6" s="25" t="inlineStr">
         <is>
           <t>BRL</t>
         </is>
       </c>
-      <c r="I6" s="26" t="n"/>
+      <c r="I6" s="26" t="n">
+        <v>11607.25</v>
+      </c>
       <c r="J6" s="25" t="n">
         <v>1</v>
       </c>
@@ -1339,12 +1345,12 @@
       </c>
       <c r="O6" s="25" t="inlineStr">
         <is>
-          <t>A cotar</t>
+          <t>Cotado</t>
         </is>
       </c>
       <c r="P6" s="30" t="inlineStr">
         <is>
-          <t>Mesma cia da família. Menor de 18 viajando só: autorização de viagem obrigatória.</t>
+          <t>Cotação recebida em 20/09: R$ 11.607,25 (USD 2.250,56). RECOTAR: o 3º trecho saiu de Viena, mas em 10/01 o filho está em Praga com a família — precisa ser PRG → CDG (ideal AF1183 09:50, o mesmo dos 4). A volta CDG → GRU está no AF454 23:20, e a família no LA8133 12:05: alinhar num só voo, ou trocar todos para o noturno e ganhar o dia 12 inteiro em Paris.</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1412,7 @@
       </c>
       <c r="P7" s="30" t="inlineStr">
         <is>
-          <t>Se o bilhete do filho vier como multitrecho GRU→VIE / PRG→CDG / CDG→GRU, marcar esta linha como Não.</t>
+          <t>Aguardando recotação do bilhete do filho com PRG → CDG. Se o trecho entrar no multitrecho dele, marcar esta linha como Não.</t>
         </is>
       </c>
     </row>
@@ -3850,6 +3856,7 @@
       </c>
       <c r="P47" s="30" t="inlineStr"/>
     </row>
+    <row r="48"/>
     <row r="49">
       <c r="C49" s="21" t="inlineStr">
         <is>
@@ -3904,6 +3911,13 @@
         </is>
       </c>
     </row>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
   </sheetData>
   <autoFilter ref="A4:P47"/>
   <dataValidations count="3">

--- a/cotacao-cristofer-reveillon.xlsx
+++ b/cotacao-cristofer-reveillon.xlsx
@@ -1302,7 +1302,7 @@
       </c>
       <c r="D6" s="23" t="inlineStr">
         <is>
-          <t>AF453 GRU 04/01 14:40 → CDG 05/01 06:05 · AF1138 CDG 10:00 → VIE 12:00 (conexão 3h55) · AF1139 VIE 10/01 12:55 → CDG 15:10 · AF454 CDG 12/01 23:20 → GRU 13/01 07:20 · econômica</t>
+          <t>AF453 GRU 04/01 14:40 → CDG 05/01 06:05 · AF1138 CDG 10:00 → VIE 12:00 (conexão 3h55) · AF1383 PRG 10/01 12:10 → CDG 14:05 · AF454 CDG 12/01 23:20 → GRU 13/01 07:20 · econômica</t>
         </is>
       </c>
       <c r="E6" s="23" t="inlineStr">
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c r="I6" s="26" t="n">
-        <v>11607.25</v>
+        <v>12056.63</v>
       </c>
       <c r="J6" s="25" t="n">
         <v>1</v>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="P6" s="30" t="inlineStr">
         <is>
-          <t>Cotação recebida em 20/09: R$ 11.607,25 (USD 2.250,56). RECOTAR: o 3º trecho saiu de Viena, mas em 10/01 o filho está em Praga com a família — precisa ser PRG → CDG (ideal AF1183 09:50, o mesmo dos 4). A volta CDG → GRU está no AF454 23:20, e a família no LA8133 12:05: alinhar num só voo, ou trocar todos para o noturno e ganhar o dia 12 inteiro em Paris.</t>
+          <t>Recotação de 20/09: R$ 12.056,63 (USD 2.337,69), com PRG → CDG correto. Ainda em voos diferentes da família em 10/01 (AF1383 12:10 vs AF1183 09:50) e em 12/01 (AF454 23:20 vs LA8133 12:05). Decisão pendente: alinhar os 4 ao filho (recotar os 4 com AF1383 + AF454, ganha o dia 12 em Paris) ou aceitar as duas separações.</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1398,7 @@
       <c r="L7" s="28" t="inlineStr"/>
       <c r="M7" s="25" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="N7" s="29">
@@ -1407,12 +1407,12 @@
       </c>
       <c r="O7" s="25" t="inlineStr">
         <is>
-          <t>A cotar</t>
+          <t>Descartado</t>
         </is>
       </c>
       <c r="P7" s="30" t="inlineStr">
         <is>
-          <t>Aguardando recotação do bilhete do filho com PRG → CDG. Se o trecho entrar no multitrecho dele, marcar esta linha como Não.</t>
+          <t>Incluído no multitrecho do filho (AF1383). Não cotar à parte.</t>
         </is>
       </c>
     </row>

--- a/cotacao-cristofer-reveillon.xlsx
+++ b/cotacao-cristofer-reveillon.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Cotação" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Cotação'!$A$4:$P$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Cotação'!$A$4:$P$48</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -625,19 +625,19 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$47,A5)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$48,A5)</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$47,A5,Cotação!$O$5:$O$47,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$48,A5,Cotação!$O$5:$O$48,"A cotar")</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$47,A5,Cotação!$O$5:$O$47,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$48,A5,Cotação!$O$5:$O$48,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E5" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$47,A5,Cotação!$N$5:$N$47)</f>
+        <f>SUMIF(Cotação!$B$5:$B$48,A5,Cotação!$N$5:$N$48)</f>
         <v/>
       </c>
     </row>
@@ -648,19 +648,19 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$47,A6)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$48,A6)</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$47,A6,Cotação!$O$5:$O$47,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$48,A6,Cotação!$O$5:$O$48,"A cotar")</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$47,A6,Cotação!$O$5:$O$47,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$48,A6,Cotação!$O$5:$O$48,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E6" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$47,A6,Cotação!$N$5:$N$47)</f>
+        <f>SUMIF(Cotação!$B$5:$B$48,A6,Cotação!$N$5:$N$48)</f>
         <v/>
       </c>
     </row>
@@ -671,19 +671,19 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$47,A7)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$48,A7)</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$47,A7,Cotação!$O$5:$O$47,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$48,A7,Cotação!$O$5:$O$48,"A cotar")</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$47,A7,Cotação!$O$5:$O$47,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$48,A7,Cotação!$O$5:$O$48,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E7" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$47,A7,Cotação!$N$5:$N$47)</f>
+        <f>SUMIF(Cotação!$B$5:$B$48,A7,Cotação!$N$5:$N$48)</f>
         <v/>
       </c>
     </row>
@@ -694,19 +694,19 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$47,A8)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$48,A8)</f>
         <v/>
       </c>
       <c r="C8" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$47,A8,Cotação!$O$5:$O$47,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$48,A8,Cotação!$O$5:$O$48,"A cotar")</f>
         <v/>
       </c>
       <c r="D8" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$47,A8,Cotação!$O$5:$O$47,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$48,A8,Cotação!$O$5:$O$48,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E8" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$47,A8,Cotação!$N$5:$N$47)</f>
+        <f>SUMIF(Cotação!$B$5:$B$48,A8,Cotação!$N$5:$N$48)</f>
         <v/>
       </c>
     </row>
@@ -717,19 +717,19 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$47,A9)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$48,A9)</f>
         <v/>
       </c>
       <c r="C9" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$47,A9,Cotação!$O$5:$O$47,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$48,A9,Cotação!$O$5:$O$48,"A cotar")</f>
         <v/>
       </c>
       <c r="D9" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$47,A9,Cotação!$O$5:$O$47,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$48,A9,Cotação!$O$5:$O$48,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E9" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$47,A9,Cotação!$N$5:$N$47)</f>
+        <f>SUMIF(Cotação!$B$5:$B$48,A9,Cotação!$N$5:$N$48)</f>
         <v/>
       </c>
     </row>
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$47,A10)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$48,A10)</f>
         <v/>
       </c>
       <c r="C10" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$47,A10,Cotação!$O$5:$O$47,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$48,A10,Cotação!$O$5:$O$48,"A cotar")</f>
         <v/>
       </c>
       <c r="D10" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$47,A10,Cotação!$O$5:$O$47,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$48,A10,Cotação!$O$5:$O$48,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$47,A10,Cotação!$N$5:$N$47)</f>
+        <f>SUMIF(Cotação!$B$5:$B$48,A10,Cotação!$N$5:$N$48)</f>
         <v/>
       </c>
     </row>
@@ -763,19 +763,19 @@
         </is>
       </c>
       <c r="B11" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$47,A11)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$48,A11)</f>
         <v/>
       </c>
       <c r="C11" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$47,A11,Cotação!$O$5:$O$47,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$48,A11,Cotação!$O$5:$O$48,"A cotar")</f>
         <v/>
       </c>
       <c r="D11" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$47,A11,Cotação!$O$5:$O$47,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$48,A11,Cotação!$O$5:$O$48,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E11" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$47,A11,Cotação!$N$5:$N$47)</f>
+        <f>SUMIF(Cotação!$B$5:$B$48,A11,Cotação!$N$5:$N$48)</f>
         <v/>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P59"/>
+  <dimension ref="A1:P80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1489,12 +1489,12 @@
       </c>
       <c r="C9" s="24" t="inlineStr">
         <is>
-          <t>Budapeste · Opção 1 · InterContinental Budapest 5★</t>
+          <t>Budapeste · Opção 1 · Barceló Budapest 4★</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
         <is>
-          <t>Margem do Danúbio, vista para o Castelo · 2 quartos duplos · café da manhã · 4 noites</t>
+          <t>Király utca, Terézváros, a 5 min da Basílica · 2 quartos Superior Double · café da manhã · 4 noites</t>
         </is>
       </c>
       <c r="E9" s="23" t="inlineStr">
@@ -1505,15 +1505,21 @@
       <c r="F9" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="G9" s="25" t="inlineStr"/>
+      <c r="G9" s="25" t="inlineStr">
+        <is>
+          <t>Consolidador (a nomear)</t>
+        </is>
+      </c>
       <c r="H9" s="25" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="I9" s="26" t="n"/>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="I9" s="26" t="n">
+        <v>16800</v>
+      </c>
       <c r="J9" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K9" s="27">
         <f>IF(I9="","",I9*J9)</f>
@@ -1521,7 +1527,7 @@
       </c>
       <c r="L9" s="28" t="inlineStr">
         <is>
-          <t>€ 2.398 · 4 noites · 2 quartos · 2 adultos + 2 crianças</t>
+          <t>Booking 20/09: R$ 15.136 pelas 2 quartos/4 noites no mesmo hotel · InterContinental 5★ € 2.398 · Corinthia 5★ € 2.939</t>
         </is>
       </c>
       <c r="M9" s="25" t="inlineStr">
@@ -1535,12 +1541,12 @@
       </c>
       <c r="O9" s="25" t="inlineStr">
         <is>
-          <t>A cotar</t>
+          <t>Cotado</t>
         </is>
       </c>
       <c r="P9" s="30" t="inlineStr">
         <is>
-          <t>Valor unitário = diária dos 2 quartos somados. Mínimo de noites no Réveillon: confirmar.</t>
+          <t>Cotação de 21/09: R$ 16.800 por quarto pelas 4 noites (R$ 4.200/noite) = R$ 33.600. ALERTA: mais que o dobro do Booking para o mesmo hotel e datas (R$ 15.136 pelos 2 quartos). Confirmar se o valor é por quarto ou pelos dois, e o que a tarifa inclui (cancelamento flexível? pacote de Réveillon?).</t>
         </is>
       </c>
     </row>
@@ -1555,12 +1561,12 @@
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>Budapeste · Opção 2 · Corinthia Budapest 5★</t>
+          <t>Budapeste · Opção 2 · (aguardando)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
         <is>
-          <t>Erzsébet körút, spa e piscina coberta, quartos para família · 2 quartos · café · 4 noites</t>
+          <t>2 quartos · café da manhã · 4 noites</t>
         </is>
       </c>
       <c r="E10" s="23" t="inlineStr">
@@ -1571,25 +1577,21 @@
       <c r="F10" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="G10" s="25" t="inlineStr"/>
+      <c r="G10" s="25" t="n"/>
       <c r="H10" s="25" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>BRL</t>
         </is>
       </c>
       <c r="I10" s="26" t="n"/>
       <c r="J10" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K10" s="27">
         <f>IF(I10="","",I10*J10)</f>
         <v/>
       </c>
-      <c r="L10" s="28" t="inlineStr">
-        <is>
-          <t>€ 2.939 · 4 noites · 2 quartos · 2 adultos + 2 crianças</t>
-        </is>
-      </c>
+      <c r="L10" s="28" t="n"/>
       <c r="M10" s="25" t="inlineStr">
         <is>
           <t>Não</t>
@@ -1604,11 +1606,7 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P10" s="30" t="inlineStr">
-        <is>
-          <t>Alternativa com spa próprio, bom para o dia 01/01.</t>
-        </is>
-      </c>
+      <c r="P10" s="30" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="23" t="n">
@@ -1621,44 +1619,40 @@
       </c>
       <c r="C11" s="24" t="inlineStr">
         <is>
-          <t>Viena · Opção 1 · Steigenberger Icon Herrenhof 5★</t>
+          <t>Budapeste · Opção 3 · (aguardando)</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
         <is>
-          <t>Herrengasse, Innere Stadt, a 5 min do Hofburg · 2 quartos · café · 4 noites</t>
+          <t>2 quartos · café da manhã · 4 noites</t>
         </is>
       </c>
       <c r="E11" s="23" t="inlineStr">
         <is>
-          <t>03/01 → 07/01</t>
+          <t>30/12 → 03/01</t>
         </is>
       </c>
       <c r="F11" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="G11" s="25" t="inlineStr"/>
+      <c r="G11" s="25" t="n"/>
       <c r="H11" s="25" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>BRL</t>
         </is>
       </c>
       <c r="I11" s="26" t="n"/>
       <c r="J11" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K11" s="27">
         <f>IF(I11="","",I11*J11)</f>
         <v/>
       </c>
-      <c r="L11" s="28" t="inlineStr">
-        <is>
-          <t>€ 1.862 · 4 noites · 2 quartos · 2 adultos + 2 crianças</t>
-        </is>
-      </c>
+      <c r="L11" s="28" t="n"/>
       <c r="M11" s="25" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="N11" s="29">
@@ -1670,11 +1664,7 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P11" s="30" t="inlineStr">
-        <is>
-          <t>Cotar também cama extra ou 3º quarto de 05 a 07/01 (linha própria abaixo).</t>
-        </is>
-      </c>
+      <c r="P11" s="30" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="23" t="n">
@@ -1687,12 +1677,12 @@
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>Viena · Opção 2 · Hotel Sacher Wien 5★</t>
+          <t>Viena · Opção 1 · Steigenberger Icon Herrenhof 5★</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
         <is>
-          <t>Ao lado da Ópera, o hotel da Sachertorte · 2 quartos · café · 4 noites</t>
+          <t>Herrengasse, Innere Stadt, a 5 min do Hofburg · 2 quartos · café · 4 noites</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">
@@ -1719,12 +1709,12 @@
       </c>
       <c r="L12" s="28" t="inlineStr">
         <is>
-          <t>€ 4.350 · 4 noites · 2 quartos · 2 adultos + 2 crianças</t>
+          <t>€ 1.862 · 4 noites · 2 quartos · 2 adultos + 2 crianças</t>
         </is>
       </c>
       <c r="M12" s="25" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="N12" s="29">
@@ -1738,7 +1728,7 @@
       </c>
       <c r="P12" s="30" t="inlineStr">
         <is>
-          <t>Opção icônica. Preço bem acima da Opção 1.</t>
+          <t>Cotar também cama extra ou 3º quarto de 05 a 07/01 (linha própria abaixo).</t>
         </is>
       </c>
     </row>
@@ -1753,21 +1743,21 @@
       </c>
       <c r="C13" s="24" t="inlineStr">
         <is>
-          <t>Viena · cama extra ou 3º quarto para o filho</t>
+          <t>Viena · Opção 2 · Hotel Sacher Wien 5★</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
         <is>
-          <t>2 noites, a partir da chegada em 05/01, no hotel escolhido</t>
+          <t>Ao lado da Ópera, o hotel da Sachertorte · 2 quartos · café · 4 noites</t>
         </is>
       </c>
       <c r="E13" s="23" t="inlineStr">
         <is>
-          <t>05/01 → 07/01</t>
+          <t>03/01 → 07/01</t>
         </is>
       </c>
       <c r="F13" s="23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G13" s="25" t="inlineStr"/>
       <c r="H13" s="25" t="inlineStr">
@@ -1777,16 +1767,20 @@
       </c>
       <c r="I13" s="26" t="n"/>
       <c r="J13" s="25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K13" s="27">
         <f>IF(I13="","",I13*J13)</f>
         <v/>
       </c>
-      <c r="L13" s="28" t="inlineStr"/>
+      <c r="L13" s="28" t="inlineStr">
+        <is>
+          <t>€ 4.350 · 4 noites · 2 quartos · 2 adultos + 2 crianças</t>
+        </is>
+      </c>
       <c r="M13" s="25" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="N13" s="29">
@@ -1800,7 +1794,7 @@
       </c>
       <c r="P13" s="30" t="inlineStr">
         <is>
-          <t>Valor unitário = diária. Se o hotel oferecer triplo, ajustar a Opção escolhida em vez desta linha.</t>
+          <t>Opção icônica. Preço bem acima da Opção 1.</t>
         </is>
       </c>
     </row>
@@ -1815,21 +1809,21 @@
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>Praga · Opção 1 · Art Nouveau Palace Hotel 5★</t>
+          <t>Viena · cama extra ou 3º quarto para o filho</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
         <is>
-          <t>Panská, Cidade Nova, a 5 min da Praça da Cidade Velha · 2 quartos (5 pax) · café · 3 noites</t>
+          <t>2 noites, a partir da chegada em 05/01, no hotel escolhido</t>
         </is>
       </c>
       <c r="E14" s="23" t="inlineStr">
         <is>
-          <t>07/01 → 10/01</t>
+          <t>05/01 → 07/01</t>
         </is>
       </c>
       <c r="F14" s="23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G14" s="25" t="inlineStr"/>
       <c r="H14" s="25" t="inlineStr">
@@ -1839,17 +1833,13 @@
       </c>
       <c r="I14" s="26" t="n"/>
       <c r="J14" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K14" s="27">
         <f>IF(I14="","",I14*J14)</f>
         <v/>
       </c>
-      <c r="L14" s="28" t="inlineStr">
-        <is>
-          <t>€ 812 · 3 noites · 2 quartos · 3 adultos + 2 crianças</t>
-        </is>
-      </c>
+      <c r="L14" s="28" t="inlineStr"/>
       <c r="M14" s="25" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1866,7 +1856,7 @@
       </c>
       <c r="P14" s="30" t="inlineStr">
         <is>
-          <t>Valor unitário = diária dos 2 quartos somados, já com 5 pax.</t>
+          <t>Valor unitário = diária. Se o hotel oferecer triplo, ajustar a Opção escolhida em vez desta linha.</t>
         </is>
       </c>
     </row>
@@ -1881,12 +1871,12 @@
       </c>
       <c r="C15" s="24" t="inlineStr">
         <is>
-          <t>Praga · Opção 2 · Hilton Prague Old Town 5★</t>
+          <t>Praga · Opção 1 · Art Nouveau Palace Hotel 5★</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
         <is>
-          <t>V Celnici, junto à Praça da República, piscina coberta · 2 quartos (5 pax) · café · 3 noites</t>
+          <t>Panská, Cidade Nova, a 5 min da Praça da Cidade Velha · 2 quartos (5 pax) · café · 3 noites</t>
         </is>
       </c>
       <c r="E15" s="23" t="inlineStr">
@@ -1913,12 +1903,12 @@
       </c>
       <c r="L15" s="28" t="inlineStr">
         <is>
-          <t>€ 1.041 · 3 noites · 2 quartos · 3 adultos + 2 crianças</t>
+          <t>€ 812 · 3 noites · 2 quartos · 3 adultos + 2 crianças</t>
         </is>
       </c>
       <c r="M15" s="25" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="N15" s="29">
@@ -1930,7 +1920,11 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P15" s="30" t="inlineStr"/>
+      <c r="P15" s="30" t="inlineStr">
+        <is>
+          <t>Valor unitário = diária dos 2 quartos somados, já com 5 pax.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="23" t="n">
@@ -1943,17 +1937,17 @@
       </c>
       <c r="C16" s="24" t="inlineStr">
         <is>
-          <t>Paris · Opção 1 · Castille Paris 5★</t>
+          <t>Praga · Opção 2 · Hilton Prague Old Town 5★</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
         <is>
-          <t>Rue Cambon, 1º arr., entre Louvre e Madeleine · 2 quartos (5 pax) · café · 2 noites</t>
+          <t>V Celnici, junto à Praça da República, piscina coberta · 2 quartos (5 pax) · café · 3 noites</t>
         </is>
       </c>
       <c r="E16" s="23" t="inlineStr">
         <is>
-          <t>10/01 → 12/01</t>
+          <t>07/01 → 10/01</t>
         </is>
       </c>
       <c r="F16" s="23" t="n">
@@ -1967,7 +1961,7 @@
       </c>
       <c r="I16" s="26" t="n"/>
       <c r="J16" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K16" s="27">
         <f>IF(I16="","",I16*J16)</f>
@@ -1975,12 +1969,12 @@
       </c>
       <c r="L16" s="28" t="inlineStr">
         <is>
-          <t>€ 1.509 · 2 noites · 2 quartos · 3 adultos + 2 crianças</t>
+          <t>€ 1.041 · 3 noites · 2 quartos · 3 adultos + 2 crianças</t>
         </is>
       </c>
       <c r="M16" s="25" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="N16" s="29">
@@ -1992,11 +1986,7 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P16" s="30" t="inlineStr">
-        <is>
-          <t>Valor unitário = diária dos 2 quartos somados.</t>
-        </is>
-      </c>
+      <c r="P16" s="30" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="23" t="n">
@@ -2009,12 +1999,12 @@
       </c>
       <c r="C17" s="24" t="inlineStr">
         <is>
-          <t>Paris · Opção 2 · Hôtel Napoleon Paris 5★</t>
+          <t>Paris · Opção 1 · Castille Paris 5★</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
         <is>
-          <t>Av. de Friedland, 8º arr., a 100 m do Arco do Triunfo · 2 quartos (5 pax) · café · 2 noites</t>
+          <t>Rue Cambon, 1º arr., entre Louvre e Madeleine · 2 quartos (5 pax) · café · 2 noites</t>
         </is>
       </c>
       <c r="E17" s="23" t="inlineStr">
@@ -2041,12 +2031,12 @@
       </c>
       <c r="L17" s="28" t="inlineStr">
         <is>
-          <t>€ 1.593 · 2 noites · 2 quartos · 3 adultos + 2 crianças</t>
+          <t>€ 1.509 · 2 noites · 2 quartos · 3 adultos + 2 crianças</t>
         </is>
       </c>
       <c r="M17" s="25" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="N17" s="29">
@@ -2058,7 +2048,11 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P17" s="30" t="inlineStr"/>
+      <c r="P17" s="30" t="inlineStr">
+        <is>
+          <t>Valor unitário = diária dos 2 quartos somados.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="23" t="n">
@@ -2066,26 +2060,26 @@
       </c>
       <c r="B18" s="23" t="inlineStr">
         <is>
-          <t>Trem</t>
+          <t>Hotel</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
         <is>
-          <t>Railjet Budapeste → Viena · 4 pax</t>
+          <t>Paris · Opção 2 · Hôtel Napoleon Paris 5★</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
         <is>
-          <t>Budapest-Keleti → Wien Hbf · 2h40 · 1ª classe · assentos marcados</t>
+          <t>Av. de Friedland, 8º arr., a 100 m do Arco do Triunfo · 2 quartos (5 pax) · café · 2 noites</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">
         <is>
-          <t>03/01</t>
+          <t>10/01 → 12/01</t>
         </is>
       </c>
       <c r="F18" s="23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G18" s="25" t="inlineStr"/>
       <c r="H18" s="25" t="inlineStr">
@@ -2095,16 +2089,20 @@
       </c>
       <c r="I18" s="26" t="n"/>
       <c r="J18" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K18" s="27">
         <f>IF(I18="","",I18*J18)</f>
         <v/>
       </c>
-      <c r="L18" s="28" t="inlineStr"/>
+      <c r="L18" s="28" t="inlineStr">
+        <is>
+          <t>€ 1.593 · 2 noites · 2 quartos · 3 adultos + 2 crianças</t>
+        </is>
+      </c>
       <c r="M18" s="25" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="N18" s="29">
@@ -2116,11 +2114,7 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P18" s="30" t="inlineStr">
-        <is>
-          <t>Valor unitário = por passageiro. Abre venda ~180 dias antes; tarifa Sparschiene é a mais barata.</t>
-        </is>
-      </c>
+      <c r="P18" s="30" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="23" t="n">
@@ -2133,21 +2127,21 @@
       </c>
       <c r="C19" s="24" t="inlineStr">
         <is>
-          <t>Railjet Viena → Praga · 5 pax</t>
+          <t>Railjet Budapeste → Viena · 4 pax</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
         <is>
-          <t>Wien Hbf → Praha hl.n. · 4h · 1ª classe · assentos marcados</t>
+          <t>Budapest-Keleti → Wien Hbf · 2h40 · 1ª classe · assentos marcados</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
         <is>
-          <t>07/01</t>
+          <t>03/01</t>
         </is>
       </c>
       <c r="F19" s="23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G19" s="25" t="inlineStr"/>
       <c r="H19" s="25" t="inlineStr">
@@ -2157,7 +2151,7 @@
       </c>
       <c r="I19" s="26" t="n"/>
       <c r="J19" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K19" s="27">
         <f>IF(I19="","",I19*J19)</f>
@@ -2180,7 +2174,7 @@
       </c>
       <c r="P19" s="30" t="inlineStr">
         <is>
-          <t>Valor unitário = por passageiro.</t>
+          <t>Valor unitário = por passageiro. Abre venda ~180 dias antes; tarifa Sparschiene é a mais barata.</t>
         </is>
       </c>
     </row>
@@ -2190,26 +2184,26 @@
       </c>
       <c r="B20" s="23" t="inlineStr">
         <is>
-          <t>Transfer</t>
+          <t>Trem</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
         <is>
-          <t>Budapeste · aeroporto → hotel · 4 pax</t>
+          <t>Railjet Viena → Praga · 5 pax</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
         <is>
-          <t>Van privativa com recepção no desembarque</t>
+          <t>Wien Hbf → Praha hl.n. · 4h · 1ª classe · assentos marcados</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
         <is>
-          <t>30/12</t>
+          <t>07/01</t>
         </is>
       </c>
       <c r="F20" s="23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G20" s="25" t="inlineStr"/>
       <c r="H20" s="25" t="inlineStr">
@@ -2219,7 +2213,7 @@
       </c>
       <c r="I20" s="26" t="n"/>
       <c r="J20" s="25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K20" s="27">
         <f>IF(I20="","",I20*J20)</f>
@@ -2242,7 +2236,7 @@
       </c>
       <c r="P20" s="30" t="inlineStr">
         <is>
-          <t>Valor unitário = por veículo.</t>
+          <t>Valor unitário = por passageiro.</t>
         </is>
       </c>
     </row>
@@ -2257,17 +2251,17 @@
       </c>
       <c r="C21" s="24" t="inlineStr">
         <is>
-          <t>Budapeste · hotel → estação Keleti · 4 pax</t>
+          <t>Budapeste · aeroporto → hotel · 4 pax</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
         <is>
-          <t>Carro ou van privativa</t>
+          <t>Van privativa com recepção no desembarque</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
         <is>
-          <t>03/01</t>
+          <t>30/12</t>
         </is>
       </c>
       <c r="F21" s="23" t="n">
@@ -2302,7 +2296,11 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P21" s="30" t="inlineStr"/>
+      <c r="P21" s="30" t="inlineStr">
+        <is>
+          <t>Valor unitário = por veículo.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="23" t="n">
@@ -2315,7 +2313,7 @@
       </c>
       <c r="C22" s="24" t="inlineStr">
         <is>
-          <t>Viena · estação Hbf → hotel · 4 pax</t>
+          <t>Budapeste · hotel → estação Keleti · 4 pax</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
@@ -2373,21 +2371,21 @@
       </c>
       <c r="C23" s="24" t="inlineStr">
         <is>
-          <t>Viena · aeroporto → hotel · filho · 1 pax</t>
+          <t>Viena · estação Hbf → hotel · 4 pax</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
         <is>
-          <t>Motorista com placa no desembarque · reforçar: menor viajando só</t>
+          <t>Carro ou van privativa</t>
         </is>
       </c>
       <c r="E23" s="23" t="inlineStr">
         <is>
-          <t>05/01</t>
+          <t>03/01</t>
         </is>
       </c>
       <c r="F23" s="23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G23" s="25" t="inlineStr"/>
       <c r="H23" s="25" t="inlineStr">
@@ -2431,21 +2429,21 @@
       </c>
       <c r="C24" s="24" t="inlineStr">
         <is>
-          <t>Viena · hotel → estação Hbf · 5 pax</t>
+          <t>Viena · aeroporto → hotel · filho · 1 pax</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
         <is>
-          <t>Van privativa</t>
+          <t>Motorista com placa no desembarque · reforçar: menor viajando só</t>
         </is>
       </c>
       <c r="E24" s="23" t="inlineStr">
         <is>
-          <t>07/01</t>
+          <t>05/01</t>
         </is>
       </c>
       <c r="F24" s="23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G24" s="25" t="inlineStr"/>
       <c r="H24" s="25" t="inlineStr">
@@ -2489,7 +2487,7 @@
       </c>
       <c r="C25" s="24" t="inlineStr">
         <is>
-          <t>Praga · estação hl.n. → hotel · 5 pax</t>
+          <t>Viena · hotel → estação Hbf · 5 pax</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
@@ -2547,7 +2545,7 @@
       </c>
       <c r="C26" s="24" t="inlineStr">
         <is>
-          <t>Praga · hotel → aeroporto · 5 pax</t>
+          <t>Praga · estação hl.n. → hotel · 5 pax</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
@@ -2557,7 +2555,7 @@
       </c>
       <c r="E26" s="23" t="inlineStr">
         <is>
-          <t>10/01</t>
+          <t>07/01</t>
         </is>
       </c>
       <c r="F26" s="23" t="n">
@@ -2605,7 +2603,7 @@
       </c>
       <c r="C27" s="24" t="inlineStr">
         <is>
-          <t>Paris · CDG → hotel · 5 pax</t>
+          <t>Praga · hotel → aeroporto · 5 pax</t>
         </is>
       </c>
       <c r="D27" s="23" t="inlineStr">
@@ -2663,7 +2661,7 @@
       </c>
       <c r="C28" s="24" t="inlineStr">
         <is>
-          <t>Paris · hotel → CDG · 5 pax</t>
+          <t>Paris · CDG → hotel · 5 pax</t>
         </is>
       </c>
       <c r="D28" s="23" t="inlineStr">
@@ -2673,7 +2671,7 @@
       </c>
       <c r="E28" s="23" t="inlineStr">
         <is>
-          <t>12/01</t>
+          <t>10/01</t>
         </is>
       </c>
       <c r="F28" s="23" t="n">
@@ -2716,26 +2714,26 @@
       </c>
       <c r="B29" s="23" t="inlineStr">
         <is>
-          <t>Experiência</t>
+          <t>Transfer</t>
         </is>
       </c>
       <c r="C29" s="24" t="inlineStr">
         <is>
-          <t>Réveillon · jantar de gala em cruzeiro no Danúbio · 4 pax</t>
+          <t>Paris · hotel → CDG · 5 pax</t>
         </is>
       </c>
       <c r="D29" s="23" t="inlineStr">
         <is>
-          <t>Embarque ~22h, jantar de vários pratos, música ao vivo, brinde à meia-noite, desembarque ~1h–2h</t>
+          <t>Van privativa</t>
         </is>
       </c>
       <c r="E29" s="23" t="inlineStr">
         <is>
-          <t>31/12</t>
+          <t>12/01</t>
         </is>
       </c>
       <c r="F29" s="23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G29" s="25" t="inlineStr"/>
       <c r="H29" s="25" t="inlineStr">
@@ -2745,7 +2743,7 @@
       </c>
       <c r="I29" s="26" t="n"/>
       <c r="J29" s="25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K29" s="27">
         <f>IF(I29="","",I29*J29)</f>
@@ -2766,11 +2764,7 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P29" s="30" t="inlineStr">
-        <is>
-          <t>Valor unitário = por pessoa. Esgota em novembro. Confirmar menu para adolescentes.</t>
-        </is>
-      </c>
+      <c r="P29" s="30" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="23" t="n">
@@ -2783,17 +2777,17 @@
       </c>
       <c r="C30" s="24" t="inlineStr">
         <is>
-          <t>Tokaj · motorista-guia privativo · dia inteiro · 4 pax</t>
+          <t>Réveillon · jantar de gala em cruzeiro no Danúbio · 4 pax</t>
         </is>
       </c>
       <c r="D30" s="23" t="inlineStr">
         <is>
-          <t>Saída 8h de Budapeste, Oremus (Tolcsva) + segunda vinícola + almoço em Mád/Tarcal, retorno ~19h</t>
+          <t>Embarque ~22h, jantar de vários pratos, música ao vivo, brinde à meia-noite, desembarque ~1h–2h</t>
         </is>
       </c>
       <c r="E30" s="23" t="inlineStr">
         <is>
-          <t>02/01</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="F30" s="23" t="n">
@@ -2807,7 +2801,7 @@
       </c>
       <c r="I30" s="26" t="n"/>
       <c r="J30" s="25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K30" s="27">
         <f>IF(I30="","",I30*J30)</f>
@@ -2830,7 +2824,7 @@
       </c>
       <c r="P30" s="30" t="inlineStr">
         <is>
-          <t>Valor unitário = por veículo/dia. Motorista não bebe: tolerância zero na Hungria.</t>
+          <t>Valor unitário = por pessoa. Esgota em novembro. Confirmar menu para adolescentes.</t>
         </is>
       </c>
     </row>
@@ -2845,12 +2839,12 @@
       </c>
       <c r="C31" s="24" t="inlineStr">
         <is>
-          <t>Oremus · visita à adega e prova · 2 adultos</t>
+          <t>Tokaj · motorista-guia privativo · dia inteiro · 4 pax</t>
         </is>
       </c>
       <c r="D31" s="23" t="inlineStr">
         <is>
-          <t>Agendamento por e-mail · ~1h · adolescentes acompanham sem álcool</t>
+          <t>Saída 8h de Budapeste, Oremus (Tolcsva) + segunda vinícola + almoço em Mád/Tarcal, retorno ~19h</t>
         </is>
       </c>
       <c r="E31" s="23" t="inlineStr">
@@ -2859,7 +2853,7 @@
         </is>
       </c>
       <c r="F31" s="23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G31" s="25" t="inlineStr"/>
       <c r="H31" s="25" t="inlineStr">
@@ -2869,7 +2863,7 @@
       </c>
       <c r="I31" s="26" t="n"/>
       <c r="J31" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K31" s="27">
         <f>IF(I31="","",I31*J31)</f>
@@ -2892,7 +2886,7 @@
       </c>
       <c r="P31" s="30" t="inlineStr">
         <is>
-          <t>Valor unitário = por pessoa. Confirmar recepção no sábado 02/01. Plano B: segunda 04/01.</t>
+          <t>Valor unitário = por veículo/dia. Motorista não bebe: tolerância zero na Hungria.</t>
         </is>
       </c>
     </row>
@@ -2907,12 +2901,12 @@
       </c>
       <c r="C32" s="24" t="inlineStr">
         <is>
-          <t>Almoço em vinícola ou restaurante em Tokaj · 4 pax</t>
+          <t>Oremus · visita à adega e prova · 2 adultos</t>
         </is>
       </c>
       <c r="D32" s="23" t="inlineStr">
         <is>
-          <t>Mád ou Tarcal</t>
+          <t>Agendamento por e-mail · ~1h · adolescentes acompanham sem álcool</t>
         </is>
       </c>
       <c r="E32" s="23" t="inlineStr">
@@ -2921,7 +2915,7 @@
         </is>
       </c>
       <c r="F32" s="23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G32" s="25" t="inlineStr"/>
       <c r="H32" s="25" t="inlineStr">
@@ -2931,7 +2925,7 @@
       </c>
       <c r="I32" s="26" t="n"/>
       <c r="J32" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K32" s="27">
         <f>IF(I32="","",I32*J32)</f>
@@ -2954,7 +2948,7 @@
       </c>
       <c r="P32" s="30" t="inlineStr">
         <is>
-          <t>Pode vir incluído no pacote do motorista-guia.</t>
+          <t>Valor unitário = por pessoa. Confirmar recepção no sábado 02/01. Plano B: segunda 04/01.</t>
         </is>
       </c>
     </row>
@@ -2969,17 +2963,17 @@
       </c>
       <c r="C33" s="24" t="inlineStr">
         <is>
-          <t>Termas Széchenyi · 4 pax</t>
+          <t>Almoço em vinícola ou restaurante em Tokaj · 4 pax</t>
         </is>
       </c>
       <c r="D33" s="23" t="inlineStr">
         <is>
-          <t>Ingresso dia inteiro com cabine · aberto em 01/01</t>
+          <t>Mád ou Tarcal</t>
         </is>
       </c>
       <c r="E33" s="23" t="inlineStr">
         <is>
-          <t>01/01</t>
+          <t>02/01</t>
         </is>
       </c>
       <c r="F33" s="23" t="n">
@@ -3014,7 +3008,11 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P33" s="30" t="inlineStr"/>
+      <c r="P33" s="30" t="inlineStr">
+        <is>
+          <t>Pode vir incluído no pacote do motorista-guia.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="23" t="n">
@@ -3027,17 +3025,17 @@
       </c>
       <c r="C34" s="24" t="inlineStr">
         <is>
-          <t>Schönbrunn · Grand Tour · 4 pax</t>
+          <t>Termas Széchenyi · 4 pax</t>
         </is>
       </c>
       <c r="D34" s="23" t="inlineStr">
         <is>
-          <t>Entrada com hora marcada · mercado de Ano Novo no pátio até 06/01</t>
+          <t>Ingresso dia inteiro com cabine · aberto em 01/01</t>
         </is>
       </c>
       <c r="E34" s="23" t="inlineStr">
         <is>
-          <t>04/01</t>
+          <t>01/01</t>
         </is>
       </c>
       <c r="F34" s="23" t="n">
@@ -3085,12 +3083,12 @@
       </c>
       <c r="C35" s="24" t="inlineStr">
         <is>
-          <t>Concerto Orquestra do Hofburg ou Musikverein · 4 pax</t>
+          <t>Schönbrunn · Grand Tour · 4 pax</t>
         </is>
       </c>
       <c r="D35" s="23" t="inlineStr">
         <is>
-          <t>Strauss e Mozart · categoria de assento a definir</t>
+          <t>Entrada com hora marcada · mercado de Ano Novo no pátio até 06/01</t>
         </is>
       </c>
       <c r="E35" s="23" t="inlineStr">
@@ -3130,11 +3128,7 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P35" s="30" t="inlineStr">
-        <is>
-          <t>Concerto de Ano Novo da Filarmônica (01/01) é por sorteio já encerrado.</t>
-        </is>
-      </c>
+      <c r="P35" s="30" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="23" t="n">
@@ -3147,21 +3141,21 @@
       </c>
       <c r="C36" s="24" t="inlineStr">
         <is>
-          <t>Prater · Roda Gigante · 5 pax</t>
+          <t>Concerto Orquestra do Hofburg ou Musikverein · 4 pax</t>
         </is>
       </c>
       <c r="D36" s="23" t="inlineStr">
         <is>
-          <t>Ingresso · mercado de inverno na praça até 06/01</t>
+          <t>Strauss e Mozart · categoria de assento a definir</t>
         </is>
       </c>
       <c r="E36" s="23" t="inlineStr">
         <is>
-          <t>05/01</t>
+          <t>04/01</t>
         </is>
       </c>
       <c r="F36" s="23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G36" s="25" t="inlineStr"/>
       <c r="H36" s="25" t="inlineStr">
@@ -3171,7 +3165,7 @@
       </c>
       <c r="I36" s="26" t="n"/>
       <c r="J36" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K36" s="27">
         <f>IF(I36="","",I36*J36)</f>
@@ -3192,7 +3186,11 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P36" s="30" t="inlineStr"/>
+      <c r="P36" s="30" t="inlineStr">
+        <is>
+          <t>Concerto de Ano Novo da Filarmônica (01/01) é por sorteio já encerrado.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="23" t="n">
@@ -3205,17 +3203,17 @@
       </c>
       <c r="C37" s="24" t="inlineStr">
         <is>
-          <t>Belvedere Superior · 5 pax</t>
+          <t>Prater · Roda Gigante · 5 pax</t>
         </is>
       </c>
       <c r="D37" s="23" t="inlineStr">
         <is>
-          <t>Ingresso · O Beijo de Klimt</t>
+          <t>Ingresso · mercado de inverno na praça até 06/01</t>
         </is>
       </c>
       <c r="E37" s="23" t="inlineStr">
         <is>
-          <t>06/01</t>
+          <t>05/01</t>
         </is>
       </c>
       <c r="F37" s="23" t="n">
@@ -3263,12 +3261,12 @@
       </c>
       <c r="C38" s="24" t="inlineStr">
         <is>
-          <t>Opcional · Ópera Estatal de Viena · 5 pax</t>
+          <t>Belvedere Superior · 5 pax</t>
         </is>
       </c>
       <c r="D38" s="23" t="inlineStr">
         <is>
-          <t>Récita da noite · verificar programa de 06/01</t>
+          <t>Ingresso · O Beijo de Klimt</t>
         </is>
       </c>
       <c r="E38" s="23" t="inlineStr">
@@ -3296,7 +3294,7 @@
       <c r="L38" s="28" t="inlineStr"/>
       <c r="M38" s="25" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="N38" s="29">
@@ -3308,11 +3306,7 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P38" s="30" t="inlineStr">
-        <is>
-          <t>Só entra se o cliente pedir.</t>
-        </is>
-      </c>
+      <c r="P38" s="30" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="23" t="n">
@@ -3325,17 +3319,17 @@
       </c>
       <c r="C39" s="24" t="inlineStr">
         <is>
-          <t>Castelo de Praga · circuito B · 5 pax</t>
+          <t>Opcional · Ópera Estatal de Viena · 5 pax</t>
         </is>
       </c>
       <c r="D39" s="23" t="inlineStr">
         <is>
-          <t>Catedral de São Vito, Palácio Real Antigo, Ruela Dourada</t>
+          <t>Récita da noite · verificar programa de 06/01</t>
         </is>
       </c>
       <c r="E39" s="23" t="inlineStr">
         <is>
-          <t>08/01</t>
+          <t>06/01</t>
         </is>
       </c>
       <c r="F39" s="23" t="n">
@@ -3358,7 +3352,7 @@
       <c r="L39" s="28" t="inlineStr"/>
       <c r="M39" s="25" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="N39" s="29">
@@ -3370,7 +3364,11 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P39" s="30" t="inlineStr"/>
+      <c r="P39" s="30" t="inlineStr">
+        <is>
+          <t>Só entra se o cliente pedir.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="23" t="n">
@@ -3383,12 +3381,12 @@
       </c>
       <c r="C40" s="24" t="inlineStr">
         <is>
-          <t>Teatro de luz negra · 5 pax</t>
+          <t>Castelo de Praga · circuito B · 5 pax</t>
         </is>
       </c>
       <c r="D40" s="23" t="inlineStr">
         <is>
-          <t>Sessão da noite</t>
+          <t>Catedral de São Vito, Palácio Real Antigo, Ruela Dourada</t>
         </is>
       </c>
       <c r="E40" s="23" t="inlineStr">
@@ -3441,17 +3439,17 @@
       </c>
       <c r="C41" s="24" t="inlineStr">
         <is>
-          <t>Torre Eiffel · topo · 5 pax</t>
+          <t>Teatro de luz negra · 5 pax</t>
         </is>
       </c>
       <c r="D41" s="23" t="inlineStr">
         <is>
-          <t>Entrada com hora marcada · abre venda 60 dias antes</t>
+          <t>Sessão da noite</t>
         </is>
       </c>
       <c r="E41" s="23" t="inlineStr">
         <is>
-          <t>10/01</t>
+          <t>08/01</t>
         </is>
       </c>
       <c r="F41" s="23" t="n">
@@ -3486,11 +3484,7 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P41" s="30" t="inlineStr">
-        <is>
-          <t>Reservar exatamente em 11/11 para garantir horário.</t>
-        </is>
-      </c>
+      <c r="P41" s="30" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="23" t="n">
@@ -3503,17 +3497,17 @@
       </c>
       <c r="C42" s="24" t="inlineStr">
         <is>
-          <t>Louvre · 5 pax</t>
+          <t>Torre Eiffel · topo · 5 pax</t>
         </is>
       </c>
       <c r="D42" s="23" t="inlineStr">
         <is>
-          <t>Entrada com hora marcada · menores de 18 gratuitos</t>
+          <t>Entrada com hora marcada · abre venda 60 dias antes</t>
         </is>
       </c>
       <c r="E42" s="23" t="inlineStr">
         <is>
-          <t>11/01</t>
+          <t>10/01</t>
         </is>
       </c>
       <c r="F42" s="23" t="n">
@@ -3527,7 +3521,7 @@
       </c>
       <c r="I42" s="26" t="n"/>
       <c r="J42" s="25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K42" s="27">
         <f>IF(I42="","",I42*J42)</f>
@@ -3550,7 +3544,7 @@
       </c>
       <c r="P42" s="30" t="inlineStr">
         <is>
-          <t>Qtd = 2 adultos pagantes.</t>
+          <t>Reservar exatamente em 11/11 para garantir horário.</t>
         </is>
       </c>
     </row>
@@ -3565,12 +3559,12 @@
       </c>
       <c r="C43" s="24" t="inlineStr">
         <is>
-          <t>Cruzeiro no Sena com jantar · 5 pax</t>
+          <t>Louvre · 5 pax</t>
         </is>
       </c>
       <c r="D43" s="23" t="inlineStr">
         <is>
-          <t>Bateaux Parisiens ou Bateaux-Mouches · jantar da noite</t>
+          <t>Entrada com hora marcada · menores de 18 gratuitos</t>
         </is>
       </c>
       <c r="E43" s="23" t="inlineStr">
@@ -3589,7 +3583,7 @@
       </c>
       <c r="I43" s="26" t="n"/>
       <c r="J43" s="25" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K43" s="27">
         <f>IF(I43="","",I43*J43)</f>
@@ -3610,7 +3604,11 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P43" s="30" t="inlineStr"/>
+      <c r="P43" s="30" t="inlineStr">
+        <is>
+          <t>Qtd = 2 adultos pagantes.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="23" t="n">
@@ -3618,22 +3616,22 @@
       </c>
       <c r="B44" s="23" t="inlineStr">
         <is>
-          <t>Seguro/Docs</t>
+          <t>Experiência</t>
         </is>
       </c>
       <c r="C44" s="24" t="inlineStr">
         <is>
-          <t>Seguro viagem · 5 pax · 15 dias</t>
+          <t>Cruzeiro no Sena com jantar · 5 pax</t>
         </is>
       </c>
       <c r="D44" s="23" t="inlineStr">
         <is>
-          <t>Cobertura médica mínima € 30.000 (Schengen) · bagagem · cancelamento</t>
+          <t>Bateaux Parisiens ou Bateaux-Mouches · jantar da noite</t>
         </is>
       </c>
       <c r="E44" s="23" t="inlineStr">
         <is>
-          <t>29/12 → 12/01</t>
+          <t>11/01</t>
         </is>
       </c>
       <c r="F44" s="23" t="n">
@@ -3642,7 +3640,7 @@
       <c r="G44" s="25" t="inlineStr"/>
       <c r="H44" s="25" t="inlineStr">
         <is>
-          <t>BRL</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="I44" s="26" t="n"/>
@@ -3668,11 +3666,7 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P44" s="30" t="inlineStr">
-        <is>
-          <t>Valor unitário = por pessoa. Filho com vigência a partir de 04/01 pode sair mais barato.</t>
-        </is>
-      </c>
+      <c r="P44" s="30" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="23" t="n">
@@ -3685,31 +3679,31 @@
       </c>
       <c r="C45" s="24" t="inlineStr">
         <is>
-          <t>ETIAS · 2 adultos</t>
+          <t>Seguro viagem · 5 pax · 15 dias</t>
         </is>
       </c>
       <c r="D45" s="23" t="inlineStr">
         <is>
-          <t>€ 20 por adulto · menores de 18 isentos · previsto para o 4º trimestre de 2026</t>
+          <t>Cobertura médica mínima € 30.000 (Schengen) · bagagem · cancelamento</t>
         </is>
       </c>
       <c r="E45" s="23" t="inlineStr">
         <is>
-          <t>antes de 29/12</t>
+          <t>29/12 → 12/01</t>
         </is>
       </c>
       <c r="F45" s="23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G45" s="25" t="inlineStr"/>
       <c r="H45" s="25" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>BRL</t>
         </is>
       </c>
       <c r="I45" s="26" t="n"/>
       <c r="J45" s="25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K45" s="27">
         <f>IF(I45="","",I45*J45)</f>
@@ -3732,7 +3726,7 @@
       </c>
       <c r="P45" s="30" t="inlineStr">
         <is>
-          <t>Confirmar se já estará em vigor na data do embarque.</t>
+          <t>Valor unitário = por pessoa. Filho com vigência a partir de 04/01 pode sair mais barato.</t>
         </is>
       </c>
     </row>
@@ -3747,12 +3741,12 @@
       </c>
       <c r="C46" s="24" t="inlineStr">
         <is>
-          <t>Autorização de viagem do menor · cartório</t>
+          <t>ETIAS · 2 adultos</t>
         </is>
       </c>
       <c r="D46" s="23" t="inlineStr">
         <is>
-          <t>Reconhecimento de firma dos dois pais, 2 vias · assinar antes de 29/12</t>
+          <t>€ 20 por adulto · menores de 18 isentos · previsto para o 4º trimestre de 2026</t>
         </is>
       </c>
       <c r="E46" s="23" t="inlineStr">
@@ -3761,17 +3755,17 @@
         </is>
       </c>
       <c r="F46" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G46" s="25" t="inlineStr"/>
       <c r="H46" s="25" t="inlineStr">
         <is>
-          <t>BRL</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="I46" s="26" t="n"/>
       <c r="J46" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K46" s="27">
         <f>IF(I46="","",I46*J46)</f>
@@ -3794,7 +3788,7 @@
       </c>
       <c r="P46" s="30" t="inlineStr">
         <is>
-          <t>Custo de cartório, pago pelo cliente. Registrar aqui só para controle.</t>
+          <t>Confirmar se já estará em vigor na data do embarque.</t>
         </is>
       </c>
     </row>
@@ -3804,26 +3798,26 @@
       </c>
       <c r="B47" s="23" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Seguro/Docs</t>
         </is>
       </c>
       <c r="C47" s="24" t="inlineStr">
         <is>
-          <t>eSIM Europa · 5 linhas · 15 dias</t>
+          <t>Autorização de viagem do menor · cartório</t>
         </is>
       </c>
       <c r="D47" s="23" t="inlineStr">
         <is>
-          <t>Dados para os cinco</t>
+          <t>Reconhecimento de firma dos dois pais, 2 vias · assinar antes de 29/12</t>
         </is>
       </c>
       <c r="E47" s="23" t="inlineStr">
         <is>
-          <t>29/12 → 12/01</t>
+          <t>antes de 29/12</t>
         </is>
       </c>
       <c r="F47" s="23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G47" s="25" t="inlineStr"/>
       <c r="H47" s="25" t="inlineStr">
@@ -3833,7 +3827,7 @@
       </c>
       <c r="I47" s="26" t="n"/>
       <c r="J47" s="25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K47" s="27">
         <f>IF(I47="","",I47*J47)</f>
@@ -3854,80 +3848,162 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P47" s="30" t="inlineStr"/>
-    </row>
-    <row r="48"/>
-    <row r="49">
-      <c r="C49" s="21" t="inlineStr">
+      <c r="P47" s="30" t="inlineStr">
+        <is>
+          <t>Custo de cartório, pago pelo cliente. Registrar aqui só para controle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="23" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" s="23" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="C48" s="24" t="inlineStr">
+        <is>
+          <t>eSIM Europa · 5 linhas · 15 dias</t>
+        </is>
+      </c>
+      <c r="D48" s="23" t="inlineStr">
+        <is>
+          <t>Dados para os cinco</t>
+        </is>
+      </c>
+      <c r="E48" s="23" t="inlineStr">
+        <is>
+          <t>29/12 → 12/01</t>
+        </is>
+      </c>
+      <c r="F48" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="G48" s="25" t="inlineStr"/>
+      <c r="H48" s="25" t="inlineStr">
+        <is>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="I48" s="26" t="n"/>
+      <c r="J48" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="K48" s="27">
+        <f>IF(I48="","",I48*J48)</f>
+        <v/>
+      </c>
+      <c r="L48" s="28" t="inlineStr"/>
+      <c r="M48" s="25" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="N48" s="29">
+        <f>IF(OR(M48&lt;&gt;"Sim",I48=""),0,K48*IF(H48="BRL",1,IF(H48="EUR",Parâmetros!$B$4,IF(H48="USD",Parâmetros!$B$5,1))))</f>
+        <v/>
+      </c>
+      <c r="O48" s="25" t="inlineStr">
+        <is>
+          <t>A cotar</t>
+        </is>
+      </c>
+      <c r="P48" s="30" t="inlineStr"/>
+    </row>
+    <row r="49"/>
+    <row r="50">
+      <c r="C50" s="21" t="inlineStr">
         <is>
           <t>SUBTOTAL EM R$ (itens marcados como Sim)</t>
         </is>
       </c>
-      <c r="N49" s="31">
-        <f>SUM(N5:N47)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="C50" s="12" t="inlineStr">
+      <c r="N50" s="31">
+        <f>SUM(N5:N48)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" s="12" t="inlineStr">
         <is>
           <t>Taxa de serviço LusaTravel</t>
         </is>
       </c>
-      <c r="N50" s="13">
-        <f>N49*Parâmetros!$B$10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="32" t="n"/>
-      <c r="B51" s="32" t="n"/>
-      <c r="C51" s="33" t="inlineStr">
+      <c r="N51" s="13">
+        <f>N50*Parâmetros!$B$10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="32" t="n"/>
+      <c r="B52" s="32" t="n"/>
+      <c r="C52" s="33" t="inlineStr">
         <is>
           <t>TOTAL PARA O CLIENTE</t>
         </is>
       </c>
-      <c r="D51" s="32" t="n"/>
-      <c r="E51" s="32" t="n"/>
-      <c r="F51" s="32" t="n"/>
-      <c r="G51" s="32" t="n"/>
-      <c r="H51" s="32" t="n"/>
-      <c r="I51" s="32" t="n"/>
-      <c r="J51" s="32" t="n"/>
-      <c r="K51" s="32" t="n"/>
-      <c r="L51" s="32" t="n"/>
-      <c r="M51" s="32" t="n"/>
-      <c r="N51" s="34">
-        <f>N49+N50</f>
-        <v/>
-      </c>
-      <c r="O51" s="32" t="n"/>
-      <c r="P51" s="32" t="n"/>
-    </row>
-    <row r="52">
-      <c r="C52" s="2" t="inlineStr">
+      <c r="D52" s="32" t="n"/>
+      <c r="E52" s="32" t="n"/>
+      <c r="F52" s="32" t="n"/>
+      <c r="G52" s="32" t="n"/>
+      <c r="H52" s="32" t="n"/>
+      <c r="I52" s="32" t="n"/>
+      <c r="J52" s="32" t="n"/>
+      <c r="K52" s="32" t="n"/>
+      <c r="L52" s="32" t="n"/>
+      <c r="M52" s="32" t="n"/>
+      <c r="N52" s="34">
+        <f>N50+N51</f>
+        <v/>
+      </c>
+      <c r="O52" s="32" t="n"/>
+      <c r="P52" s="32" t="n"/>
+    </row>
+    <row r="53">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>*Nada reservado, apenas cotado.</t>
         </is>
       </c>
     </row>
-    <row r="53"/>
     <row r="54"/>
     <row r="55"/>
     <row r="56"/>
     <row r="57"/>
     <row r="58"/>
     <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
   </sheetData>
-  <autoFilter ref="A4:P47"/>
+  <autoFilter ref="A4:P48"/>
   <dataValidations count="3">
-    <dataValidation sqref="O5:O47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O5:O48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"A cotar,Cotado,Aprovado pelo cliente,Reservado,Descartado"</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="M5:M48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="H5:H48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"BRL,EUR,USD"</formula1>
     </dataValidation>
   </dataValidations>

--- a/cotacao-cristofer-reveillon.xlsx
+++ b/cotacao-cristofer-reveillon.xlsx
@@ -1101,7 +1101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P80"/>
+  <dimension ref="A1:P79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1561,12 +1561,12 @@
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>Budapeste · Opção 2 · (aguardando)</t>
+          <t>Budapeste · Opção 2 · Mercure Budapest City Center 4★</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
         <is>
-          <t>2 quartos · café da manhã · 4 noites</t>
+          <t>Váci utca, coração de Pest, pedestre · 2 quartos Superior · café da manhã · 4 noites</t>
         </is>
       </c>
       <c r="E10" s="23" t="inlineStr">
@@ -1577,13 +1577,19 @@
       <c r="F10" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="G10" s="25" t="n"/>
+      <c r="G10" s="25" t="inlineStr">
+        <is>
+          <t>Consolidador (a nomear)</t>
+        </is>
+      </c>
       <c r="H10" s="25" t="inlineStr">
         <is>
           <t>BRL</t>
         </is>
       </c>
-      <c r="I10" s="26" t="n"/>
+      <c r="I10" s="26" t="n">
+        <v>6700</v>
+      </c>
       <c r="J10" s="25" t="n">
         <v>2</v>
       </c>
@@ -1591,7 +1597,11 @@
         <f>IF(I10="","",I10*J10)</f>
         <v/>
       </c>
-      <c r="L10" s="28" t="n"/>
+      <c r="L10" s="28" t="inlineStr">
+        <is>
+          <t>Booking 20/09: R$ 11.016 pelos 2 quartos/4 noites no mesmo hotel</t>
+        </is>
+      </c>
       <c r="M10" s="25" t="inlineStr">
         <is>
           <t>Não</t>
@@ -1603,10 +1613,14 @@
       </c>
       <c r="O10" s="25" t="inlineStr">
         <is>
-          <t>A cotar</t>
-        </is>
-      </c>
-      <c r="P10" s="30" t="n"/>
+          <t>Cotado</t>
+        </is>
+      </c>
+      <c r="P10" s="30" t="inlineStr">
+        <is>
+          <t>Cotação de 21/09: '2x Superior Room 13.400' — lido como R$ 13.400 pelos 2 quartos (R$ 6.700 por quarto, R$ 1.675/noite). Se for por quarto, o total é R$ 26.800. Confirmar. Com café da manhã.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="23" t="n">
@@ -3993,7 +4007,6 @@
     <row r="77"/>
     <row r="78"/>
     <row r="79"/>
-    <row r="80"/>
   </sheetData>
   <autoFilter ref="A4:P48"/>
   <dataValidations count="3">

--- a/cotacao-cristofer-reveillon.xlsx
+++ b/cotacao-cristofer-reveillon.xlsx
@@ -1532,7 +1532,7 @@
       </c>
       <c r="M9" s="25" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="N9" s="29">
@@ -1633,12 +1633,12 @@
       </c>
       <c r="C11" s="24" t="inlineStr">
         <is>
-          <t>Budapeste · Opção 3 · (aguardando)</t>
+          <t>Budapeste · Opção 3 · InterContinental Budapest 5★</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
         <is>
-          <t>2 quartos · café da manhã · 4 noites</t>
+          <t>Margem do Danúbio, vista para o Castelo e a Ponte das Correntes · 2 quartos Classic · café da manhã · 4 noites</t>
         </is>
       </c>
       <c r="E11" s="23" t="inlineStr">
@@ -1649,13 +1649,19 @@
       <c r="F11" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="G11" s="25" t="n"/>
+      <c r="G11" s="25" t="inlineStr">
+        <is>
+          <t>Consolidador (a nomear)</t>
+        </is>
+      </c>
       <c r="H11" s="25" t="inlineStr">
         <is>
           <t>BRL</t>
         </is>
       </c>
-      <c r="I11" s="26" t="n"/>
+      <c r="I11" s="26" t="n">
+        <v>8690</v>
+      </c>
       <c r="J11" s="25" t="n">
         <v>2</v>
       </c>
@@ -1663,10 +1669,14 @@
         <f>IF(I11="","",I11*J11)</f>
         <v/>
       </c>
-      <c r="L11" s="28" t="n"/>
+      <c r="L11" s="28" t="inlineStr">
+        <is>
+          <t>Booking 20/09: € 2.398 (≈ R$ 14.172) pelos 2 quartos/4 noites no mesmo hotel, tarifa mais barata</t>
+        </is>
+      </c>
       <c r="M11" s="25" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="N11" s="29">
@@ -1675,10 +1685,14 @@
       </c>
       <c r="O11" s="25" t="inlineStr">
         <is>
-          <t>A cotar</t>
-        </is>
-      </c>
-      <c r="P11" s="30" t="n"/>
+          <t>Cotado</t>
+        </is>
+      </c>
+      <c r="P11" s="30" t="inlineStr">
+        <is>
+          <t>Cotação de 21/09: '2x Classic Room 17.380' — R$ 17.380 pelos 2 quartos (R$ 8.690 por quarto, R$ 2.172/noite). Escolhida para o total: único 5★ das três, à beira do rio, por R$ 3.980 a mais que o Mercure.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="23" t="n">

--- a/cotacao-cristofer-reveillon.xlsx
+++ b/cotacao-cristofer-reveillon.xlsx
@@ -1710,7 +1710,7 @@
       </c>
       <c r="D12" s="23" t="inlineStr">
         <is>
-          <t>Herrengasse, Innere Stadt, a 5 min do Hofburg · 2 quartos · café · 4 noites</t>
+          <t>Herrengasse, Innere Stadt, a 5 min do Hofburg · 1 Junior Suite + 1 Superior Room · café da manhã · 4 noites</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">
@@ -1721,13 +1721,19 @@
       <c r="F12" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="G12" s="25" t="inlineStr"/>
+      <c r="G12" s="25" t="inlineStr">
+        <is>
+          <t>Consolidador (a nomear)</t>
+        </is>
+      </c>
       <c r="H12" s="25" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="I12" s="26" t="n"/>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="I12" s="26" t="n">
+        <v>5910</v>
+      </c>
       <c r="J12" s="25" t="n">
         <v>4</v>
       </c>
@@ -1737,7 +1743,7 @@
       </c>
       <c r="L12" s="28" t="inlineStr">
         <is>
-          <t>€ 1.862 · 4 noites · 2 quartos · 2 adultos + 2 crianças</t>
+          <t>Booking 20/09: € 1.862 (≈ R$ 11.004) por 2 quartos standard/4 noites no mesmo hotel</t>
         </is>
       </c>
       <c r="M12" s="25" t="inlineStr">
@@ -1751,12 +1757,12 @@
       </c>
       <c r="O12" s="25" t="inlineStr">
         <is>
-          <t>A cotar</t>
+          <t>Cotado</t>
         </is>
       </c>
       <c r="P12" s="30" t="inlineStr">
         <is>
-          <t>Cotar também cama extra ou 3º quarto de 05 a 07/01 (linha própria abaixo).</t>
+          <t>Cotação de 21/09: Junior Suite R$ 15.300 + Superior Room R$ 8.340 = R$ 23.640 pelas 4 noites (R$ 5.910/noite). A Junior Suite custa quase o dobro do Superior: perguntar ao consolidador se ela comporta 3 pessoas (sofá-cama) — se sim, resolve o filho a partir de 05/01 e a linha de cama extra sai. Pedir também o preço com 2 Superior.</t>
         </is>
       </c>
     </row>

--- a/cotacao-cristofer-reveillon.xlsx
+++ b/cotacao-cristofer-reveillon.xlsx
@@ -1777,12 +1777,12 @@
       </c>
       <c r="C13" s="24" t="inlineStr">
         <is>
-          <t>Viena · Opção 2 · Hotel Sacher Wien 5★</t>
+          <t>Viena · Opção 2 · Radisson Blu Style Hotel 5★</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
         <is>
-          <t>Ao lado da Ópera, o hotel da Sachertorte · 2 quartos · café · 4 noites</t>
+          <t>Herrengasse 12, Innere Stadt, design, a 3 min do Hofburg · 1 Junior Suite + 1 Superior Room · café da manhã · 4 noites</t>
         </is>
       </c>
       <c r="E13" s="23" t="inlineStr">
@@ -1793,13 +1793,19 @@
       <c r="F13" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="G13" s="25" t="inlineStr"/>
+      <c r="G13" s="25" t="inlineStr">
+        <is>
+          <t>Consolidador (a nomear)</t>
+        </is>
+      </c>
       <c r="H13" s="25" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="I13" s="26" t="n"/>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="I13" s="26" t="n">
+        <v>4768</v>
+      </c>
       <c r="J13" s="25" t="n">
         <v>4</v>
       </c>
@@ -1809,7 +1815,7 @@
       </c>
       <c r="L13" s="28" t="inlineStr">
         <is>
-          <t>€ 4.350 · 4 noites · 2 quartos · 2 adultos + 2 crianças</t>
+          <t>Booking 20/09: R$ 12.034 por 2 quartos standard/4 noites no mesmo hotel</t>
         </is>
       </c>
       <c r="M13" s="25" t="inlineStr">
@@ -1823,12 +1829,12 @@
       </c>
       <c r="O13" s="25" t="inlineStr">
         <is>
-          <t>A cotar</t>
+          <t>Cotado</t>
         </is>
       </c>
       <c r="P13" s="30" t="inlineStr">
         <is>
-          <t>Opção icônica. Preço bem acima da Opção 1.</t>
+          <t>Cotação de 21/09: Junior Suite R$ 11.042 + Superior Room R$ 8.030 = R$ 19.072 pelas 4 noites (R$ 4.768/noite). R$ 4.568 mais barato que o Herrenhof na mesma configuração e na mesma rua. Mesma pergunta: a Junior Suite comporta 3?</t>
         </is>
       </c>
     </row>

--- a/cotacao-cristofer-reveillon.xlsx
+++ b/cotacao-cristofer-reveillon.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Cotação" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Cotação'!$A$4:$P$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Cotação'!$A$4:$P$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -625,19 +625,19 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$48,A5)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$45,A5)</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$48,A5,Cotação!$O$5:$O$48,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$45,A5,Cotação!$O$5:$O$45,"A cotar")</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$48,A5,Cotação!$O$5:$O$48,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$45,A5,Cotação!$O$5:$O$45,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E5" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$48,A5,Cotação!$N$5:$N$48)</f>
+        <f>SUMIF(Cotação!$B$5:$B$45,A5,Cotação!$N$5:$N$45)</f>
         <v/>
       </c>
     </row>
@@ -648,19 +648,19 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$48,A6)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$45,A6)</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$48,A6,Cotação!$O$5:$O$48,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$45,A6,Cotação!$O$5:$O$45,"A cotar")</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$48,A6,Cotação!$O$5:$O$48,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$45,A6,Cotação!$O$5:$O$45,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E6" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$48,A6,Cotação!$N$5:$N$48)</f>
+        <f>SUMIF(Cotação!$B$5:$B$45,A6,Cotação!$N$5:$N$45)</f>
         <v/>
       </c>
     </row>
@@ -671,19 +671,19 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$48,A7)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$45,A7)</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$48,A7,Cotação!$O$5:$O$48,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$45,A7,Cotação!$O$5:$O$45,"A cotar")</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$48,A7,Cotação!$O$5:$O$48,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$45,A7,Cotação!$O$5:$O$45,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E7" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$48,A7,Cotação!$N$5:$N$48)</f>
+        <f>SUMIF(Cotação!$B$5:$B$45,A7,Cotação!$N$5:$N$45)</f>
         <v/>
       </c>
     </row>
@@ -694,19 +694,19 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$48,A8)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$45,A8)</f>
         <v/>
       </c>
       <c r="C8" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$48,A8,Cotação!$O$5:$O$48,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$45,A8,Cotação!$O$5:$O$45,"A cotar")</f>
         <v/>
       </c>
       <c r="D8" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$48,A8,Cotação!$O$5:$O$48,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$45,A8,Cotação!$O$5:$O$45,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E8" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$48,A8,Cotação!$N$5:$N$48)</f>
+        <f>SUMIF(Cotação!$B$5:$B$45,A8,Cotação!$N$5:$N$45)</f>
         <v/>
       </c>
     </row>
@@ -717,19 +717,19 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$48,A9)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$45,A9)</f>
         <v/>
       </c>
       <c r="C9" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$48,A9,Cotação!$O$5:$O$48,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$45,A9,Cotação!$O$5:$O$45,"A cotar")</f>
         <v/>
       </c>
       <c r="D9" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$48,A9,Cotação!$O$5:$O$48,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$45,A9,Cotação!$O$5:$O$45,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E9" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$48,A9,Cotação!$N$5:$N$48)</f>
+        <f>SUMIF(Cotação!$B$5:$B$45,A9,Cotação!$N$5:$N$45)</f>
         <v/>
       </c>
     </row>
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$48,A10)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$45,A10)</f>
         <v/>
       </c>
       <c r="C10" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$48,A10,Cotação!$O$5:$O$48,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$45,A10,Cotação!$O$5:$O$45,"A cotar")</f>
         <v/>
       </c>
       <c r="D10" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$48,A10,Cotação!$O$5:$O$48,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$45,A10,Cotação!$O$5:$O$45,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$48,A10,Cotação!$N$5:$N$48)</f>
+        <f>SUMIF(Cotação!$B$5:$B$45,A10,Cotação!$N$5:$N$45)</f>
         <v/>
       </c>
     </row>
@@ -763,19 +763,19 @@
         </is>
       </c>
       <c r="B11" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$48,A11)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$45,A11)</f>
         <v/>
       </c>
       <c r="C11" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$48,A11,Cotação!$O$5:$O$48,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$45,A11,Cotação!$O$5:$O$45,"A cotar")</f>
         <v/>
       </c>
       <c r="D11" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$48,A11,Cotação!$O$5:$O$48,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$45,A11,Cotação!$O$5:$O$45,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E11" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$48,A11,Cotação!$N$5:$N$48)</f>
+        <f>SUMIF(Cotação!$B$5:$B$45,A11,Cotação!$N$5:$N$45)</f>
         <v/>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P79"/>
+  <dimension ref="A1:P86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3770,243 +3770,64 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="23" t="n">
-        <v>42</v>
-      </c>
-      <c r="B46" s="23" t="inlineStr">
-        <is>
-          <t>Seguro/Docs</t>
-        </is>
-      </c>
-      <c r="C46" s="24" t="inlineStr">
-        <is>
-          <t>ETIAS · 2 adultos</t>
-        </is>
-      </c>
-      <c r="D46" s="23" t="inlineStr">
-        <is>
-          <t>€ 20 por adulto · menores de 18 isentos · previsto para o 4º trimestre de 2026</t>
-        </is>
-      </c>
-      <c r="E46" s="23" t="inlineStr">
-        <is>
-          <t>antes de 29/12</t>
-        </is>
-      </c>
-      <c r="F46" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="G46" s="25" t="inlineStr"/>
-      <c r="H46" s="25" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="I46" s="26" t="n"/>
-      <c r="J46" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="K46" s="27">
-        <f>IF(I46="","",I46*J46)</f>
-        <v/>
-      </c>
-      <c r="L46" s="28" t="inlineStr"/>
-      <c r="M46" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="N46" s="29">
-        <f>IF(OR(M46&lt;&gt;"Sim",I46=""),0,K46*IF(H46="BRL",1,IF(H46="EUR",Parâmetros!$B$4,IF(H46="USD",Parâmetros!$B$5,1))))</f>
-        <v/>
-      </c>
-      <c r="O46" s="25" t="inlineStr">
-        <is>
-          <t>A cotar</t>
-        </is>
-      </c>
-      <c r="P46" s="30" t="inlineStr">
-        <is>
-          <t>Confirmar se já estará em vigor na data do embarque.</t>
-        </is>
-      </c>
-    </row>
+    <row r="46"/>
     <row r="47">
-      <c r="A47" s="23" t="n">
-        <v>43</v>
-      </c>
-      <c r="B47" s="23" t="inlineStr">
-        <is>
-          <t>Seguro/Docs</t>
-        </is>
-      </c>
-      <c r="C47" s="24" t="inlineStr">
-        <is>
-          <t>Autorização de viagem do menor · cartório</t>
-        </is>
-      </c>
-      <c r="D47" s="23" t="inlineStr">
-        <is>
-          <t>Reconhecimento de firma dos dois pais, 2 vias · assinar antes de 29/12</t>
-        </is>
-      </c>
-      <c r="E47" s="23" t="inlineStr">
-        <is>
-          <t>antes de 29/12</t>
-        </is>
-      </c>
-      <c r="F47" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" s="25" t="inlineStr"/>
-      <c r="H47" s="25" t="inlineStr">
-        <is>
-          <t>BRL</t>
-        </is>
-      </c>
-      <c r="I47" s="26" t="n"/>
-      <c r="J47" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="K47" s="27">
-        <f>IF(I47="","",I47*J47)</f>
-        <v/>
-      </c>
-      <c r="L47" s="28" t="inlineStr"/>
-      <c r="M47" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="N47" s="29">
-        <f>IF(OR(M47&lt;&gt;"Sim",I47=""),0,K47*IF(H47="BRL",1,IF(H47="EUR",Parâmetros!$B$4,IF(H47="USD",Parâmetros!$B$5,1))))</f>
-        <v/>
-      </c>
-      <c r="O47" s="25" t="inlineStr">
-        <is>
-          <t>A cotar</t>
-        </is>
-      </c>
-      <c r="P47" s="30" t="inlineStr">
-        <is>
-          <t>Custo de cartório, pago pelo cliente. Registrar aqui só para controle.</t>
-        </is>
+      <c r="C47" s="21" t="inlineStr">
+        <is>
+          <t>SUBTOTAL EM R$ (itens marcados como Sim)</t>
+        </is>
+      </c>
+      <c r="N47" s="31">
+        <f>SUM(N5:N45)</f>
+        <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="23" t="n">
-        <v>44</v>
-      </c>
-      <c r="B48" s="23" t="inlineStr">
-        <is>
-          <t>Outros</t>
-        </is>
-      </c>
-      <c r="C48" s="24" t="inlineStr">
-        <is>
-          <t>eSIM Europa · 5 linhas · 15 dias</t>
-        </is>
-      </c>
-      <c r="D48" s="23" t="inlineStr">
-        <is>
-          <t>Dados para os cinco</t>
-        </is>
-      </c>
-      <c r="E48" s="23" t="inlineStr">
-        <is>
-          <t>29/12 → 12/01</t>
-        </is>
-      </c>
-      <c r="F48" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="G48" s="25" t="inlineStr"/>
-      <c r="H48" s="25" t="inlineStr">
-        <is>
-          <t>BRL</t>
-        </is>
-      </c>
-      <c r="I48" s="26" t="n"/>
-      <c r="J48" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="K48" s="27">
-        <f>IF(I48="","",I48*J48)</f>
-        <v/>
-      </c>
-      <c r="L48" s="28" t="inlineStr"/>
-      <c r="M48" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="N48" s="29">
-        <f>IF(OR(M48&lt;&gt;"Sim",I48=""),0,K48*IF(H48="BRL",1,IF(H48="EUR",Parâmetros!$B$4,IF(H48="USD",Parâmetros!$B$5,1))))</f>
-        <v/>
-      </c>
-      <c r="O48" s="25" t="inlineStr">
-        <is>
-          <t>A cotar</t>
-        </is>
-      </c>
-      <c r="P48" s="30" t="inlineStr"/>
-    </row>
-    <row r="49"/>
+      <c r="C48" s="12" t="inlineStr">
+        <is>
+          <t>Taxa de serviço LusaTravel</t>
+        </is>
+      </c>
+      <c r="N48" s="13">
+        <f>N47*Parâmetros!$B$10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="32" t="n"/>
+      <c r="B49" s="32" t="n"/>
+      <c r="C49" s="33" t="inlineStr">
+        <is>
+          <t>TOTAL PARA O CLIENTE</t>
+        </is>
+      </c>
+      <c r="D49" s="32" t="n"/>
+      <c r="E49" s="32" t="n"/>
+      <c r="F49" s="32" t="n"/>
+      <c r="G49" s="32" t="n"/>
+      <c r="H49" s="32" t="n"/>
+      <c r="I49" s="32" t="n"/>
+      <c r="J49" s="32" t="n"/>
+      <c r="K49" s="32" t="n"/>
+      <c r="L49" s="32" t="n"/>
+      <c r="M49" s="32" t="n"/>
+      <c r="N49" s="34">
+        <f>N47+N48</f>
+        <v/>
+      </c>
+      <c r="O49" s="32" t="n"/>
+      <c r="P49" s="32" t="n"/>
+    </row>
     <row r="50">
-      <c r="C50" s="21" t="inlineStr">
-        <is>
-          <t>SUBTOTAL EM R$ (itens marcados como Sim)</t>
-        </is>
-      </c>
-      <c r="N50" s="31">
-        <f>SUM(N5:N48)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="C51" s="12" t="inlineStr">
-        <is>
-          <t>Taxa de serviço LusaTravel</t>
-        </is>
-      </c>
-      <c r="N51" s="13">
-        <f>N50*Parâmetros!$B$10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="32" t="n"/>
-      <c r="B52" s="32" t="n"/>
-      <c r="C52" s="33" t="inlineStr">
-        <is>
-          <t>TOTAL PARA O CLIENTE</t>
-        </is>
-      </c>
-      <c r="D52" s="32" t="n"/>
-      <c r="E52" s="32" t="n"/>
-      <c r="F52" s="32" t="n"/>
-      <c r="G52" s="32" t="n"/>
-      <c r="H52" s="32" t="n"/>
-      <c r="I52" s="32" t="n"/>
-      <c r="J52" s="32" t="n"/>
-      <c r="K52" s="32" t="n"/>
-      <c r="L52" s="32" t="n"/>
-      <c r="M52" s="32" t="n"/>
-      <c r="N52" s="34">
-        <f>N50+N51</f>
-        <v/>
-      </c>
-      <c r="O52" s="32" t="n"/>
-      <c r="P52" s="32" t="n"/>
-    </row>
-    <row r="53">
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>*Nada reservado, apenas cotado.</t>
         </is>
       </c>
     </row>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
     <row r="54"/>
     <row r="55"/>
     <row r="56"/>
@@ -4033,16 +3854,23 @@
     <row r="77"/>
     <row r="78"/>
     <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
   </sheetData>
-  <autoFilter ref="A4:P48"/>
+  <autoFilter ref="A4:P45"/>
   <dataValidations count="3">
-    <dataValidation sqref="O5:O48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O5:O45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"A cotar,Cotado,Aprovado pelo cliente,Reservado,Descartado"</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="M5:M45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="H5:H45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"BRL,EUR,USD"</formula1>
     </dataValidation>
   </dataValidations>

--- a/cotacao-cristofer-reveillon.xlsx
+++ b/cotacao-cristofer-reveillon.xlsx
@@ -1101,7 +1101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P86"/>
+  <dimension ref="A1:P79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1911,12 +1911,12 @@
       </c>
       <c r="C15" s="24" t="inlineStr">
         <is>
-          <t>Praga · Opção 1 · Art Nouveau Palace Hotel 5★</t>
+          <t>Praga · Opção 1 · The Emblem Prague Hotel 5★</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
         <is>
-          <t>Panská, Cidade Nova, a 5 min da Praça da Cidade Velha · 2 quartos (5 pax) · café · 3 noites</t>
+          <t>Platnéřská, Cidade Velha, a 2 min da Praça da Cidade Velha, spa na cobertura · 1 Suite Pretender + 1 Queen Room · café da manhã · 3 noites</t>
         </is>
       </c>
       <c r="E15" s="23" t="inlineStr">
@@ -1927,13 +1927,19 @@
       <c r="F15" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="G15" s="25" t="inlineStr"/>
+      <c r="G15" s="25" t="inlineStr">
+        <is>
+          <t>Consolidador (a nomear)</t>
+        </is>
+      </c>
       <c r="H15" s="25" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="I15" s="26" t="n"/>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="I15" s="26" t="n">
+        <v>3335</v>
+      </c>
       <c r="J15" s="25" t="n">
         <v>3</v>
       </c>
@@ -1943,7 +1949,7 @@
       </c>
       <c r="L15" s="28" t="inlineStr">
         <is>
-          <t>€ 812 · 3 noites · 2 quartos · 3 adultos + 2 crianças</t>
+          <t>Booking 20/09, outros hotéis: Art Nouveau Palace 5★ € 812 · Hilton Old Town 5★ € 1.041 por 2 quartos/3 noites (5 pax)</t>
         </is>
       </c>
       <c r="M15" s="25" t="inlineStr">
@@ -1957,12 +1963,12 @@
       </c>
       <c r="O15" s="25" t="inlineStr">
         <is>
-          <t>A cotar</t>
+          <t>Cotado</t>
         </is>
       </c>
       <c r="P15" s="30" t="inlineStr">
         <is>
-          <t>Valor unitário = diária dos 2 quartos somados, já com 5 pax.</t>
+          <t>Cotação de 21/09: Suite Pretender R$ 5.680 + Queen Room R$ 4.325 = R$ 10.005 pelas 3 noites (R$ 3.335/noite). Escolhida para o total: boutique 5★ no coração da Cidade Velha, R$ 1.980 acima da Opção 2. Confirmar que a suíte comporta 3 (pais + filho).</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1983,12 @@
       </c>
       <c r="C16" s="24" t="inlineStr">
         <is>
-          <t>Praga · Opção 2 · Hilton Prague Old Town 5★</t>
+          <t>Praga · Opção 2 · Century Old Town Prague, MGallery 4★</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
         <is>
-          <t>V Celnici, junto à Praça da República, piscina coberta · 2 quartos (5 pax) · café · 3 noites</t>
+          <t>Na Poříčí, prédio onde Kafka trabalhou, a 8 min da Praça da Cidade Velha · 1 Executive + 1 Classic Room · café da manhã · 3 noites</t>
         </is>
       </c>
       <c r="E16" s="23" t="inlineStr">
@@ -1993,13 +1999,19 @@
       <c r="F16" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="G16" s="25" t="inlineStr"/>
+      <c r="G16" s="25" t="inlineStr">
+        <is>
+          <t>Consolidador (a nomear)</t>
+        </is>
+      </c>
       <c r="H16" s="25" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="I16" s="26" t="n"/>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="I16" s="26" t="n">
+        <v>2675</v>
+      </c>
       <c r="J16" s="25" t="n">
         <v>3</v>
       </c>
@@ -2007,11 +2019,7 @@
         <f>IF(I16="","",I16*J16)</f>
         <v/>
       </c>
-      <c r="L16" s="28" t="inlineStr">
-        <is>
-          <t>€ 1.041 · 3 noites · 2 quartos · 3 adultos + 2 crianças</t>
-        </is>
-      </c>
+      <c r="L16" s="28" t="n"/>
       <c r="M16" s="25" t="inlineStr">
         <is>
           <t>Não</t>
@@ -2023,10 +2031,14 @@
       </c>
       <c r="O16" s="25" t="inlineStr">
         <is>
-          <t>A cotar</t>
-        </is>
-      </c>
-      <c r="P16" s="30" t="inlineStr"/>
+          <t>Cotado</t>
+        </is>
+      </c>
+      <c r="P16" s="30" t="inlineStr">
+        <is>
+          <t>Cotação de 21/09: Executive R$ 4.645 + Classic R$ 3.380 = R$ 8.025 pelas 3 noites (R$ 2.675/noite).</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="23" t="n">
@@ -3854,13 +3866,6 @@
     <row r="77"/>
     <row r="78"/>
     <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
   </sheetData>
   <autoFilter ref="A4:P45"/>
   <dataValidations count="3">

--- a/cotacao-cristofer-reveillon.xlsx
+++ b/cotacao-cristofer-reveillon.xlsx
@@ -2184,7 +2184,7 @@
       </c>
       <c r="D19" s="23" t="inlineStr">
         <is>
-          <t>Budapest-Keleti → Wien Hbf · 2h40 · 1ª classe · assentos marcados</t>
+          <t>ÖBB RJX 62 · Budapest-Keleti 09:30 → Wien Hbf 12:20 · 2h50 · direto · assentos marcados</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
@@ -2195,13 +2195,19 @@
       <c r="F19" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="G19" s="25" t="inlineStr"/>
+      <c r="G19" s="25" t="inlineStr">
+        <is>
+          <t>Consolidador (a nomear)</t>
+        </is>
+      </c>
       <c r="H19" s="25" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="I19" s="26" t="n"/>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="I19" s="26" t="n">
+        <v>302.5</v>
+      </c>
       <c r="J19" s="25" t="n">
         <v>4</v>
       </c>
@@ -2221,12 +2227,12 @@
       </c>
       <c r="O19" s="25" t="inlineStr">
         <is>
-          <t>A cotar</t>
+          <t>Cotado</t>
         </is>
       </c>
       <c r="P19" s="30" t="inlineStr">
         <is>
-          <t>Valor unitário = por passageiro. Abre venda ~180 dias antes; tarifa Sparschiene é a mais barata.</t>
+          <t>Cotação de 21/09: R$ 1.210 para 4 pax (R$ 302,50/pax). Confirmar classe (1ª ou 2ª) e se a tarifa permite alteração.</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2252,7 @@
       </c>
       <c r="D20" s="23" t="inlineStr">
         <is>
-          <t>Wien Hbf → Praha hl.n. · 4h · 1ª classe · assentos marcados</t>
+          <t>ÖBB RJ 252 · Wien Hbf 11:10 → Praha hlavní nádraží 15:23 · 4h13 · direto · assentos marcados</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
@@ -2257,13 +2263,19 @@
       <c r="F20" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="G20" s="25" t="inlineStr"/>
+      <c r="G20" s="25" t="inlineStr">
+        <is>
+          <t>Consolidador (a nomear)</t>
+        </is>
+      </c>
       <c r="H20" s="25" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="I20" s="26" t="n"/>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="I20" s="26" t="n">
+        <v>381</v>
+      </c>
       <c r="J20" s="25" t="n">
         <v>5</v>
       </c>
@@ -2283,12 +2295,12 @@
       </c>
       <c r="O20" s="25" t="inlineStr">
         <is>
-          <t>A cotar</t>
+          <t>Cotado</t>
         </is>
       </c>
       <c r="P20" s="30" t="inlineStr">
         <is>
-          <t>Valor unitário = por passageiro.</t>
+          <t>Cotação de 21/09: R$ 1.905 para 5 pax (R$ 381/pax). Confirmar classe (1ª ou 2ª) e se a tarifa permite alteração.</t>
         </is>
       </c>
     </row>

--- a/cotacao-cristofer-reveillon.xlsx
+++ b/cotacao-cristofer-reveillon.xlsx
@@ -916,11 +916,11 @@
         </is>
       </c>
       <c r="B4" s="16" t="n">
-        <v>5.91</v>
+        <v>6.1</v>
       </c>
       <c r="C4" s="17" t="inlineStr">
         <is>
-          <t>Cotação comercial de 19/09/2026 (Remessa Online). Atualizar no dia da cotação formal.</t>
+          <t>Cotação informada pela LusaTravel em 21/09/2026.</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
       </c>
       <c r="B6" s="18" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="C6" s="17" t="inlineStr">
@@ -1101,7 +1101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P79"/>
+  <dimension ref="A1:P50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3794,7 +3794,6 @@
         </is>
       </c>
     </row>
-    <row r="46"/>
     <row r="47">
       <c r="C47" s="21" t="inlineStr">
         <is>
@@ -3849,35 +3848,6 @@
         </is>
       </c>
     </row>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
   </sheetData>
   <autoFilter ref="A4:P45"/>
   <dataValidations count="3">

--- a/cotacao-cristofer-reveillon.xlsx
+++ b/cotacao-cristofer-reveillon.xlsx
@@ -1101,7 +1101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P50"/>
+  <dimension ref="A1:P79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="C32" s="24" t="inlineStr">
         <is>
-          <t>Oremus · visita à adega e prova · 2 adultos</t>
+          <t>Oremus · visita à adega e prova · 2 adultos + 2 filhas</t>
         </is>
       </c>
       <c r="D32" s="23" t="inlineStr">
         <is>
-          <t>Agendamento por e-mail · ~1h · adolescentes acompanham sem álcool</t>
+          <t>Tolcsva · agendamento por e-mail · ~1h · adegas do século XIII · adolescentes acompanham sem álcool</t>
         </is>
       </c>
       <c r="E32" s="23" t="inlineStr">
@@ -2979,17 +2979,23 @@
         </is>
       </c>
       <c r="F32" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="G32" s="25" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G32" s="25" t="inlineStr">
+        <is>
+          <t>Tokaj-Oremus</t>
+        </is>
+      </c>
       <c r="H32" s="25" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="I32" s="26" t="n"/>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="I32" s="26" t="n">
+        <v>315.67</v>
+      </c>
       <c r="J32" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K32" s="27">
         <f>IF(I32="","",I32*J32)</f>
@@ -3007,12 +3013,12 @@
       </c>
       <c r="O32" s="25" t="inlineStr">
         <is>
-          <t>A cotar</t>
+          <t>Cotado</t>
         </is>
       </c>
       <c r="P32" s="30" t="inlineStr">
         <is>
-          <t>Valor unitário = por pessoa. Confirmar recepção no sábado 02/01. Plano B: segunda 04/01.</t>
+          <t>Cotação de 21/09 em reais para a família (2 adultos e 2 filhas). Confirmar recepção no sábado 02/01; plano B: segunda 04/01.</t>
         </is>
       </c>
     </row>
@@ -3794,6 +3800,7 @@
         </is>
       </c>
     </row>
+    <row r="46"/>
     <row r="47">
       <c r="C47" s="21" t="inlineStr">
         <is>
@@ -3848,6 +3855,35 @@
         </is>
       </c>
     </row>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
   </sheetData>
   <autoFilter ref="A4:P45"/>
   <dataValidations count="3">

--- a/cotacao-cristofer-reveillon.xlsx
+++ b/cotacao-cristofer-reveillon.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Cotação" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Cotação'!$A$4:$P$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Cotação'!$A$4:$P$47</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -625,19 +625,19 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$45,A5)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$47,A5)</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$45,A5,Cotação!$O$5:$O$45,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$47,A5,Cotação!$O$5:$O$47,"A cotar")</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$45,A5,Cotação!$O$5:$O$45,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$47,A5,Cotação!$O$5:$O$47,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E5" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$45,A5,Cotação!$N$5:$N$45)</f>
+        <f>SUMIF(Cotação!$B$5:$B$47,A5,Cotação!$N$5:$N$47)</f>
         <v/>
       </c>
     </row>
@@ -648,19 +648,19 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$45,A6)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$47,A6)</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$45,A6,Cotação!$O$5:$O$45,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$47,A6,Cotação!$O$5:$O$47,"A cotar")</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$45,A6,Cotação!$O$5:$O$45,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$47,A6,Cotação!$O$5:$O$47,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E6" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$45,A6,Cotação!$N$5:$N$45)</f>
+        <f>SUMIF(Cotação!$B$5:$B$47,A6,Cotação!$N$5:$N$47)</f>
         <v/>
       </c>
     </row>
@@ -671,19 +671,19 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$45,A7)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$47,A7)</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$45,A7,Cotação!$O$5:$O$45,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$47,A7,Cotação!$O$5:$O$47,"A cotar")</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$45,A7,Cotação!$O$5:$O$45,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$47,A7,Cotação!$O$5:$O$47,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E7" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$45,A7,Cotação!$N$5:$N$45)</f>
+        <f>SUMIF(Cotação!$B$5:$B$47,A7,Cotação!$N$5:$N$47)</f>
         <v/>
       </c>
     </row>
@@ -694,19 +694,19 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$45,A8)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$47,A8)</f>
         <v/>
       </c>
       <c r="C8" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$45,A8,Cotação!$O$5:$O$45,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$47,A8,Cotação!$O$5:$O$47,"A cotar")</f>
         <v/>
       </c>
       <c r="D8" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$45,A8,Cotação!$O$5:$O$45,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$47,A8,Cotação!$O$5:$O$47,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E8" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$45,A8,Cotação!$N$5:$N$45)</f>
+        <f>SUMIF(Cotação!$B$5:$B$47,A8,Cotação!$N$5:$N$47)</f>
         <v/>
       </c>
     </row>
@@ -717,19 +717,19 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$45,A9)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$47,A9)</f>
         <v/>
       </c>
       <c r="C9" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$45,A9,Cotação!$O$5:$O$45,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$47,A9,Cotação!$O$5:$O$47,"A cotar")</f>
         <v/>
       </c>
       <c r="D9" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$45,A9,Cotação!$O$5:$O$45,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$47,A9,Cotação!$O$5:$O$47,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E9" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$45,A9,Cotação!$N$5:$N$45)</f>
+        <f>SUMIF(Cotação!$B$5:$B$47,A9,Cotação!$N$5:$N$47)</f>
         <v/>
       </c>
     </row>
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$45,A10)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$47,A10)</f>
         <v/>
       </c>
       <c r="C10" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$45,A10,Cotação!$O$5:$O$45,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$47,A10,Cotação!$O$5:$O$47,"A cotar")</f>
         <v/>
       </c>
       <c r="D10" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$45,A10,Cotação!$O$5:$O$45,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$47,A10,Cotação!$O$5:$O$47,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$45,A10,Cotação!$N$5:$N$45)</f>
+        <f>SUMIF(Cotação!$B$5:$B$47,A10,Cotação!$N$5:$N$47)</f>
         <v/>
       </c>
     </row>
@@ -763,19 +763,19 @@
         </is>
       </c>
       <c r="B11" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$45,A11)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$47,A11)</f>
         <v/>
       </c>
       <c r="C11" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$45,A11,Cotação!$O$5:$O$45,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$47,A11,Cotação!$O$5:$O$47,"A cotar")</f>
         <v/>
       </c>
       <c r="D11" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$45,A11,Cotação!$O$5:$O$45,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$47,A11,Cotação!$O$5:$O$47,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E11" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$45,A11,Cotação!$N$5:$N$45)</f>
+        <f>SUMIF(Cotação!$B$5:$B$47,A11,Cotação!$N$5:$N$47)</f>
         <v/>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P79"/>
+  <dimension ref="A1:P91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2841,12 +2841,12 @@
       </c>
       <c r="C30" s="24" t="inlineStr">
         <is>
-          <t>Réveillon · jantar de gala em cruzeiro no Danúbio · 4 pax</t>
+          <t>Réveillon · Opção 1 · Silverline · jantar de gala em catamarã · 4 pax</t>
         </is>
       </c>
       <c r="D30" s="23" t="inlineStr">
         <is>
-          <t>Embarque ~22h, jantar de vários pratos, música ao vivo, brinde à meia-noite, desembarque ~1h–2h</t>
+          <t>Cais 11, Ponte Elisabeth · welcome cocktail, jantar de 5 pratos, espumante, show de piano · passa pelo Parlamento iluminado, brinde e fogos à meia-noite</t>
         </is>
       </c>
       <c r="E30" s="23" t="inlineStr">
@@ -2857,13 +2857,19 @@
       <c r="F30" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="G30" s="25" t="inlineStr"/>
+      <c r="G30" s="25" t="inlineStr">
+        <is>
+          <t>Silverline Cruises</t>
+        </is>
+      </c>
       <c r="H30" s="25" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="I30" s="26" t="n"/>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="I30" s="26" t="n">
+        <v>1092.24</v>
+      </c>
       <c r="J30" s="25" t="n">
         <v>4</v>
       </c>
@@ -2871,7 +2877,11 @@
         <f>IF(I30="","",I30*J30)</f>
         <v/>
       </c>
-      <c r="L30" s="28" t="inlineStr"/>
+      <c r="L30" s="28" t="inlineStr">
+        <is>
+          <t>silver-line.hu/product/budapest-new-years-eve-dinner-cruise</t>
+        </is>
+      </c>
       <c r="M30" s="25" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2883,12 +2893,12 @@
       </c>
       <c r="O30" s="25" t="inlineStr">
         <is>
-          <t>A cotar</t>
+          <t>Cotado</t>
         </is>
       </c>
       <c r="P30" s="30" t="inlineStr">
         <is>
-          <t>Valor unitário = por pessoa. Esgota em novembro. Confirmar menu para adolescentes.</t>
+          <t>Valor por pessoa do pacote de bebidas básico (o site tem pacotes até quase o dobro). Preço de criança e horário de embarque a confirmar na página.</t>
         </is>
       </c>
     </row>
@@ -2903,40 +2913,48 @@
       </c>
       <c r="C31" s="24" t="inlineStr">
         <is>
-          <t>Tokaj · motorista-guia privativo · dia inteiro · 4 pax</t>
+          <t>Réveillon · Opção 2 · Budapest River Cruise · NYE Party Cruise · 4 pax</t>
         </is>
       </c>
       <c r="D31" s="23" t="inlineStr">
         <is>
-          <t>Saída 8h de Budapeste, Oremus (Tolcsva) + segunda vinícola + almoço em Mád/Tarcal, retorno ~19h</t>
+          <t>Cais 8/8A, Ponte Elisabeth · jantar, música ao vivo e virada a bordo · detalhes do barco a confirmar</t>
         </is>
       </c>
       <c r="E31" s="23" t="inlineStr">
         <is>
-          <t>02/01</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="F31" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="G31" s="25" t="inlineStr"/>
+      <c r="G31" s="25" t="inlineStr">
+        <is>
+          <t>Budapest River Cruise</t>
+        </is>
+      </c>
       <c r="H31" s="25" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>BRL</t>
         </is>
       </c>
       <c r="I31" s="26" t="n"/>
       <c r="J31" s="25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K31" s="27">
         <f>IF(I31="","",I31*J31)</f>
         <v/>
       </c>
-      <c r="L31" s="28" t="inlineStr"/>
+      <c r="L31" s="28" t="inlineStr">
+        <is>
+          <t>budapestrivercruise.com/budapest-new-years-eve-cruise-party</t>
+        </is>
+      </c>
       <c r="M31" s="25" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="N31" s="29">
@@ -2950,7 +2968,7 @@
       </c>
       <c r="P31" s="30" t="inlineStr">
         <is>
-          <t>Valor unitário = por veículo/dia. Motorista não bebe: tolerância zero na Hungria.</t>
+          <t>Não consegui ler a página. Me mande o preço por adulto e por menor, o horário de embarque e o que inclui, que eu lanço.</t>
         </is>
       </c>
     </row>
@@ -2965,17 +2983,17 @@
       </c>
       <c r="C32" s="24" t="inlineStr">
         <is>
-          <t>Oremus · visita à adega e prova · 2 adultos + 2 filhas</t>
+          <t>Réveillon · Opção 3 · Budapest River Cruise · NYE Boat Party · 4 pax</t>
         </is>
       </c>
       <c r="D32" s="23" t="inlineStr">
         <is>
-          <t>Tolcsva · agendamento por e-mail · ~1h · adegas do século XIII · adolescentes acompanham sem álcool</t>
+          <t>22h à 3h · DJ, open bar, fotógrafo · festa, sem jantar servido</t>
         </is>
       </c>
       <c r="E32" s="23" t="inlineStr">
         <is>
-          <t>02/01</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="F32" s="23" t="n">
@@ -2983,7 +3001,7 @@
       </c>
       <c r="G32" s="25" t="inlineStr">
         <is>
-          <t>Tokaj-Oremus</t>
+          <t>Budapest River Cruise</t>
         </is>
       </c>
       <c r="H32" s="25" t="inlineStr">
@@ -2991,20 +3009,22 @@
           <t>BRL</t>
         </is>
       </c>
-      <c r="I32" s="26" t="n">
-        <v>315.67</v>
-      </c>
+      <c r="I32" s="26" t="n"/>
       <c r="J32" s="25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K32" s="27">
         <f>IF(I32="","",I32*J32)</f>
         <v/>
       </c>
-      <c r="L32" s="28" t="inlineStr"/>
+      <c r="L32" s="28" t="inlineStr">
+        <is>
+          <t>budapestrivercruise.com/budapest-nye-boat-party-cruise</t>
+        </is>
+      </c>
       <c r="M32" s="25" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="N32" s="29">
@@ -3013,12 +3033,12 @@
       </c>
       <c r="O32" s="25" t="inlineStr">
         <is>
-          <t>Cotado</t>
+          <t>Descartado</t>
         </is>
       </c>
       <c r="P32" s="30" t="inlineStr">
         <is>
-          <t>Cotação de 21/09 em reais para a família (2 adultos e 2 filhas). Confirmar recepção no sábado 02/01; plano B: segunda 04/01.</t>
+          <t>Evento restrito a maiores de 18 anos. As filhas de 13 e 16 não embarcam.</t>
         </is>
       </c>
     </row>
@@ -3033,12 +3053,12 @@
       </c>
       <c r="C33" s="24" t="inlineStr">
         <is>
-          <t>Almoço em vinícola ou restaurante em Tokaj · 4 pax</t>
+          <t>Tokaj · motorista-guia privativo · dia inteiro · 4 pax</t>
         </is>
       </c>
       <c r="D33" s="23" t="inlineStr">
         <is>
-          <t>Mád ou Tarcal</t>
+          <t>Saída 8h de Budapeste, Oremus (Tolcsva) + segunda vinícola + almoço em Mád/Tarcal, retorno ~19h</t>
         </is>
       </c>
       <c r="E33" s="23" t="inlineStr">
@@ -3057,7 +3077,7 @@
       </c>
       <c r="I33" s="26" t="n"/>
       <c r="J33" s="25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K33" s="27">
         <f>IF(I33="","",I33*J33)</f>
@@ -3080,7 +3100,7 @@
       </c>
       <c r="P33" s="30" t="inlineStr">
         <is>
-          <t>Pode vir incluído no pacote do motorista-guia.</t>
+          <t>Valor unitário = por veículo/dia. Motorista não bebe: tolerância zero na Hungria.</t>
         </is>
       </c>
     </row>
@@ -3095,31 +3115,37 @@
       </c>
       <c r="C34" s="24" t="inlineStr">
         <is>
-          <t>Termas Széchenyi · 4 pax</t>
+          <t>Oremus · visita à adega e prova · 2 adultos + 2 filhas</t>
         </is>
       </c>
       <c r="D34" s="23" t="inlineStr">
         <is>
-          <t>Ingresso dia inteiro com cabine · aberto em 01/01</t>
+          <t>Tolcsva · agendamento por e-mail · ~1h · adegas do século XIII · adolescentes acompanham sem álcool</t>
         </is>
       </c>
       <c r="E34" s="23" t="inlineStr">
         <is>
-          <t>01/01</t>
+          <t>02/01</t>
         </is>
       </c>
       <c r="F34" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="G34" s="25" t="inlineStr"/>
+      <c r="G34" s="25" t="inlineStr">
+        <is>
+          <t>Tokaj-Oremus</t>
+        </is>
+      </c>
       <c r="H34" s="25" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="I34" s="26" t="n"/>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="I34" s="26" t="n">
+        <v>315.67</v>
+      </c>
       <c r="J34" s="25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K34" s="27">
         <f>IF(I34="","",I34*J34)</f>
@@ -3137,10 +3163,14 @@
       </c>
       <c r="O34" s="25" t="inlineStr">
         <is>
-          <t>A cotar</t>
-        </is>
-      </c>
-      <c r="P34" s="30" t="inlineStr"/>
+          <t>Cotado</t>
+        </is>
+      </c>
+      <c r="P34" s="30" t="inlineStr">
+        <is>
+          <t>Cotação de 21/09 em reais para a família (2 adultos e 2 filhas). Confirmar recepção no sábado 02/01; plano B: segunda 04/01.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="23" t="n">
@@ -3153,17 +3183,17 @@
       </c>
       <c r="C35" s="24" t="inlineStr">
         <is>
-          <t>Schönbrunn · Grand Tour · 4 pax</t>
+          <t>Almoço em vinícola ou restaurante em Tokaj · 4 pax</t>
         </is>
       </c>
       <c r="D35" s="23" t="inlineStr">
         <is>
-          <t>Entrada com hora marcada · mercado de Ano Novo no pátio até 06/01</t>
+          <t>Mád ou Tarcal</t>
         </is>
       </c>
       <c r="E35" s="23" t="inlineStr">
         <is>
-          <t>04/01</t>
+          <t>02/01</t>
         </is>
       </c>
       <c r="F35" s="23" t="n">
@@ -3198,7 +3228,11 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P35" s="30" t="inlineStr"/>
+      <c r="P35" s="30" t="inlineStr">
+        <is>
+          <t>Pode vir incluído no pacote do motorista-guia.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="23" t="n">
@@ -3211,17 +3245,17 @@
       </c>
       <c r="C36" s="24" t="inlineStr">
         <is>
-          <t>Concerto Orquestra do Hofburg ou Musikverein · 4 pax</t>
+          <t>Termas Széchenyi · 4 pax</t>
         </is>
       </c>
       <c r="D36" s="23" t="inlineStr">
         <is>
-          <t>Strauss e Mozart · categoria de assento a definir</t>
+          <t>Ingresso dia inteiro com cabine · aberto em 01/01</t>
         </is>
       </c>
       <c r="E36" s="23" t="inlineStr">
         <is>
-          <t>04/01</t>
+          <t>01/01</t>
         </is>
       </c>
       <c r="F36" s="23" t="n">
@@ -3256,11 +3290,7 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P36" s="30" t="inlineStr">
-        <is>
-          <t>Concerto de Ano Novo da Filarmônica (01/01) é por sorteio já encerrado.</t>
-        </is>
-      </c>
+      <c r="P36" s="30" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="23" t="n">
@@ -3273,21 +3303,21 @@
       </c>
       <c r="C37" s="24" t="inlineStr">
         <is>
-          <t>Prater · Roda Gigante · 5 pax</t>
+          <t>Schönbrunn · Grand Tour · 4 pax</t>
         </is>
       </c>
       <c r="D37" s="23" t="inlineStr">
         <is>
-          <t>Ingresso · mercado de inverno na praça até 06/01</t>
+          <t>Entrada com hora marcada · mercado de Ano Novo no pátio até 06/01</t>
         </is>
       </c>
       <c r="E37" s="23" t="inlineStr">
         <is>
-          <t>05/01</t>
+          <t>04/01</t>
         </is>
       </c>
       <c r="F37" s="23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G37" s="25" t="inlineStr"/>
       <c r="H37" s="25" t="inlineStr">
@@ -3297,7 +3327,7 @@
       </c>
       <c r="I37" s="26" t="n"/>
       <c r="J37" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K37" s="27">
         <f>IF(I37="","",I37*J37)</f>
@@ -3331,21 +3361,21 @@
       </c>
       <c r="C38" s="24" t="inlineStr">
         <is>
-          <t>Belvedere Superior · 5 pax</t>
+          <t>Concerto Orquestra do Hofburg ou Musikverein · 4 pax</t>
         </is>
       </c>
       <c r="D38" s="23" t="inlineStr">
         <is>
-          <t>Ingresso · O Beijo de Klimt</t>
+          <t>Strauss e Mozart · categoria de assento a definir</t>
         </is>
       </c>
       <c r="E38" s="23" t="inlineStr">
         <is>
-          <t>06/01</t>
+          <t>04/01</t>
         </is>
       </c>
       <c r="F38" s="23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G38" s="25" t="inlineStr"/>
       <c r="H38" s="25" t="inlineStr">
@@ -3355,7 +3385,7 @@
       </c>
       <c r="I38" s="26" t="n"/>
       <c r="J38" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K38" s="27">
         <f>IF(I38="","",I38*J38)</f>
@@ -3376,7 +3406,11 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P38" s="30" t="inlineStr"/>
+      <c r="P38" s="30" t="inlineStr">
+        <is>
+          <t>Concerto de Ano Novo da Filarmônica (01/01) é por sorteio já encerrado.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="23" t="n">
@@ -3389,17 +3423,17 @@
       </c>
       <c r="C39" s="24" t="inlineStr">
         <is>
-          <t>Opcional · Ópera Estatal de Viena · 5 pax</t>
+          <t>Prater · Roda Gigante · 5 pax</t>
         </is>
       </c>
       <c r="D39" s="23" t="inlineStr">
         <is>
-          <t>Récita da noite · verificar programa de 06/01</t>
+          <t>Ingresso · mercado de inverno na praça até 06/01</t>
         </is>
       </c>
       <c r="E39" s="23" t="inlineStr">
         <is>
-          <t>06/01</t>
+          <t>05/01</t>
         </is>
       </c>
       <c r="F39" s="23" t="n">
@@ -3422,7 +3456,7 @@
       <c r="L39" s="28" t="inlineStr"/>
       <c r="M39" s="25" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="N39" s="29">
@@ -3434,11 +3468,7 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P39" s="30" t="inlineStr">
-        <is>
-          <t>Só entra se o cliente pedir.</t>
-        </is>
-      </c>
+      <c r="P39" s="30" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="23" t="n">
@@ -3451,17 +3481,17 @@
       </c>
       <c r="C40" s="24" t="inlineStr">
         <is>
-          <t>Castelo de Praga · circuito B · 5 pax</t>
+          <t>Belvedere Superior · 5 pax</t>
         </is>
       </c>
       <c r="D40" s="23" t="inlineStr">
         <is>
-          <t>Catedral de São Vito, Palácio Real Antigo, Ruela Dourada</t>
+          <t>Ingresso · O Beijo de Klimt</t>
         </is>
       </c>
       <c r="E40" s="23" t="inlineStr">
         <is>
-          <t>08/01</t>
+          <t>06/01</t>
         </is>
       </c>
       <c r="F40" s="23" t="n">
@@ -3509,17 +3539,17 @@
       </c>
       <c r="C41" s="24" t="inlineStr">
         <is>
-          <t>Teatro de luz negra · 5 pax</t>
+          <t>Opcional · Ópera Estatal de Viena · 5 pax</t>
         </is>
       </c>
       <c r="D41" s="23" t="inlineStr">
         <is>
-          <t>Sessão da noite</t>
+          <t>Récita da noite · verificar programa de 06/01</t>
         </is>
       </c>
       <c r="E41" s="23" t="inlineStr">
         <is>
-          <t>08/01</t>
+          <t>06/01</t>
         </is>
       </c>
       <c r="F41" s="23" t="n">
@@ -3542,7 +3572,7 @@
       <c r="L41" s="28" t="inlineStr"/>
       <c r="M41" s="25" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="N41" s="29">
@@ -3554,7 +3584,11 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P41" s="30" t="inlineStr"/>
+      <c r="P41" s="30" t="inlineStr">
+        <is>
+          <t>Só entra se o cliente pedir.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="23" t="n">
@@ -3567,17 +3601,17 @@
       </c>
       <c r="C42" s="24" t="inlineStr">
         <is>
-          <t>Torre Eiffel · topo · 5 pax</t>
+          <t>Castelo de Praga · circuito B · 5 pax</t>
         </is>
       </c>
       <c r="D42" s="23" t="inlineStr">
         <is>
-          <t>Entrada com hora marcada · abre venda 60 dias antes</t>
+          <t>Catedral de São Vito, Palácio Real Antigo, Ruela Dourada</t>
         </is>
       </c>
       <c r="E42" s="23" t="inlineStr">
         <is>
-          <t>10/01</t>
+          <t>08/01</t>
         </is>
       </c>
       <c r="F42" s="23" t="n">
@@ -3612,11 +3646,7 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P42" s="30" t="inlineStr">
-        <is>
-          <t>Reservar exatamente em 11/11 para garantir horário.</t>
-        </is>
-      </c>
+      <c r="P42" s="30" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="23" t="n">
@@ -3629,17 +3659,17 @@
       </c>
       <c r="C43" s="24" t="inlineStr">
         <is>
-          <t>Louvre · 5 pax</t>
+          <t>Teatro de luz negra · 5 pax</t>
         </is>
       </c>
       <c r="D43" s="23" t="inlineStr">
         <is>
-          <t>Entrada com hora marcada · menores de 18 gratuitos</t>
+          <t>Sessão da noite</t>
         </is>
       </c>
       <c r="E43" s="23" t="inlineStr">
         <is>
-          <t>11/01</t>
+          <t>08/01</t>
         </is>
       </c>
       <c r="F43" s="23" t="n">
@@ -3653,7 +3683,7 @@
       </c>
       <c r="I43" s="26" t="n"/>
       <c r="J43" s="25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K43" s="27">
         <f>IF(I43="","",I43*J43)</f>
@@ -3674,11 +3704,7 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P43" s="30" t="inlineStr">
-        <is>
-          <t>Qtd = 2 adultos pagantes.</t>
-        </is>
-      </c>
+      <c r="P43" s="30" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="23" t="n">
@@ -3691,17 +3717,17 @@
       </c>
       <c r="C44" s="24" t="inlineStr">
         <is>
-          <t>Cruzeiro no Sena com jantar · 5 pax</t>
+          <t>Torre Eiffel · topo · 5 pax</t>
         </is>
       </c>
       <c r="D44" s="23" t="inlineStr">
         <is>
-          <t>Bateaux Parisiens ou Bateaux-Mouches · jantar da noite</t>
+          <t>Entrada com hora marcada · abre venda 60 dias antes</t>
         </is>
       </c>
       <c r="E44" s="23" t="inlineStr">
         <is>
-          <t>11/01</t>
+          <t>10/01</t>
         </is>
       </c>
       <c r="F44" s="23" t="n">
@@ -3736,7 +3762,11 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P44" s="30" t="inlineStr"/>
+      <c r="P44" s="30" t="inlineStr">
+        <is>
+          <t>Reservar exatamente em 11/11 para garantir horário.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="23" t="n">
@@ -3744,22 +3774,22 @@
       </c>
       <c r="B45" s="23" t="inlineStr">
         <is>
-          <t>Seguro/Docs</t>
+          <t>Experiência</t>
         </is>
       </c>
       <c r="C45" s="24" t="inlineStr">
         <is>
-          <t>Seguro viagem · 5 pax · 15 dias</t>
+          <t>Louvre · 5 pax</t>
         </is>
       </c>
       <c r="D45" s="23" t="inlineStr">
         <is>
-          <t>Cobertura médica mínima € 30.000 (Schengen) · bagagem · cancelamento</t>
+          <t>Entrada com hora marcada · menores de 18 gratuitos</t>
         </is>
       </c>
       <c r="E45" s="23" t="inlineStr">
         <is>
-          <t>29/12 → 12/01</t>
+          <t>11/01</t>
         </is>
       </c>
       <c r="F45" s="23" t="n">
@@ -3768,12 +3798,12 @@
       <c r="G45" s="25" t="inlineStr"/>
       <c r="H45" s="25" t="inlineStr">
         <is>
-          <t>BRL</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="I45" s="26" t="n"/>
       <c r="J45" s="25" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K45" s="27">
         <f>IF(I45="","",I45*J45)</f>
@@ -3796,67 +3826,185 @@
       </c>
       <c r="P45" s="30" t="inlineStr">
         <is>
+          <t>Qtd = 2 adultos pagantes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="23" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" s="23" t="inlineStr">
+        <is>
+          <t>Experiência</t>
+        </is>
+      </c>
+      <c r="C46" s="24" t="inlineStr">
+        <is>
+          <t>Cruzeiro no Sena com jantar · 5 pax</t>
+        </is>
+      </c>
+      <c r="D46" s="23" t="inlineStr">
+        <is>
+          <t>Bateaux Parisiens ou Bateaux-Mouches · jantar da noite</t>
+        </is>
+      </c>
+      <c r="E46" s="23" t="inlineStr">
+        <is>
+          <t>11/01</t>
+        </is>
+      </c>
+      <c r="F46" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="G46" s="25" t="inlineStr"/>
+      <c r="H46" s="25" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I46" s="26" t="n"/>
+      <c r="J46" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="K46" s="27">
+        <f>IF(I46="","",I46*J46)</f>
+        <v/>
+      </c>
+      <c r="L46" s="28" t="inlineStr"/>
+      <c r="M46" s="25" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="N46" s="29">
+        <f>IF(OR(M46&lt;&gt;"Sim",I46=""),0,K46*IF(H46="BRL",1,IF(H46="EUR",Parâmetros!$B$4,IF(H46="USD",Parâmetros!$B$5,1))))</f>
+        <v/>
+      </c>
+      <c r="O46" s="25" t="inlineStr">
+        <is>
+          <t>A cotar</t>
+        </is>
+      </c>
+      <c r="P46" s="30" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="23" t="n">
+        <v>43</v>
+      </c>
+      <c r="B47" s="23" t="inlineStr">
+        <is>
+          <t>Seguro/Docs</t>
+        </is>
+      </c>
+      <c r="C47" s="24" t="inlineStr">
+        <is>
+          <t>Seguro viagem · 5 pax · 15 dias</t>
+        </is>
+      </c>
+      <c r="D47" s="23" t="inlineStr">
+        <is>
+          <t>Cobertura médica mínima € 30.000 (Schengen) · bagagem · cancelamento</t>
+        </is>
+      </c>
+      <c r="E47" s="23" t="inlineStr">
+        <is>
+          <t>29/12 → 12/01</t>
+        </is>
+      </c>
+      <c r="F47" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="G47" s="25" t="inlineStr"/>
+      <c r="H47" s="25" t="inlineStr">
+        <is>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="I47" s="26" t="n"/>
+      <c r="J47" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="K47" s="27">
+        <f>IF(I47="","",I47*J47)</f>
+        <v/>
+      </c>
+      <c r="L47" s="28" t="inlineStr"/>
+      <c r="M47" s="25" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="N47" s="29">
+        <f>IF(OR(M47&lt;&gt;"Sim",I47=""),0,K47*IF(H47="BRL",1,IF(H47="EUR",Parâmetros!$B$4,IF(H47="USD",Parâmetros!$B$5,1))))</f>
+        <v/>
+      </c>
+      <c r="O47" s="25" t="inlineStr">
+        <is>
+          <t>A cotar</t>
+        </is>
+      </c>
+      <c r="P47" s="30" t="inlineStr">
+        <is>
           <t>Valor unitário = por pessoa. Filho com vigência a partir de 04/01 pode sair mais barato.</t>
         </is>
       </c>
     </row>
-    <row r="46"/>
-    <row r="47">
-      <c r="C47" s="21" t="inlineStr">
+    <row r="48"/>
+    <row r="49">
+      <c r="C49" s="21" t="inlineStr">
         <is>
           <t>SUBTOTAL EM R$ (itens marcados como Sim)</t>
         </is>
       </c>
-      <c r="N47" s="31">
-        <f>SUM(N5:N45)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="C48" s="12" t="inlineStr">
+      <c r="N49" s="31">
+        <f>SUM(N5:N47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" s="12" t="inlineStr">
         <is>
           <t>Taxa de serviço LusaTravel</t>
         </is>
       </c>
-      <c r="N48" s="13">
-        <f>N47*Parâmetros!$B$10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="32" t="n"/>
-      <c r="B49" s="32" t="n"/>
-      <c r="C49" s="33" t="inlineStr">
+      <c r="N50" s="13">
+        <f>N49*Parâmetros!$B$10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="32" t="n"/>
+      <c r="B51" s="32" t="n"/>
+      <c r="C51" s="33" t="inlineStr">
         <is>
           <t>TOTAL PARA O CLIENTE</t>
         </is>
       </c>
-      <c r="D49" s="32" t="n"/>
-      <c r="E49" s="32" t="n"/>
-      <c r="F49" s="32" t="n"/>
-      <c r="G49" s="32" t="n"/>
-      <c r="H49" s="32" t="n"/>
-      <c r="I49" s="32" t="n"/>
-      <c r="J49" s="32" t="n"/>
-      <c r="K49" s="32" t="n"/>
-      <c r="L49" s="32" t="n"/>
-      <c r="M49" s="32" t="n"/>
-      <c r="N49" s="34">
-        <f>N47+N48</f>
-        <v/>
-      </c>
-      <c r="O49" s="32" t="n"/>
-      <c r="P49" s="32" t="n"/>
-    </row>
-    <row r="50">
-      <c r="C50" s="2" t="inlineStr">
+      <c r="D51" s="32" t="n"/>
+      <c r="E51" s="32" t="n"/>
+      <c r="F51" s="32" t="n"/>
+      <c r="G51" s="32" t="n"/>
+      <c r="H51" s="32" t="n"/>
+      <c r="I51" s="32" t="n"/>
+      <c r="J51" s="32" t="n"/>
+      <c r="K51" s="32" t="n"/>
+      <c r="L51" s="32" t="n"/>
+      <c r="M51" s="32" t="n"/>
+      <c r="N51" s="34">
+        <f>N49+N50</f>
+        <v/>
+      </c>
+      <c r="O51" s="32" t="n"/>
+      <c r="P51" s="32" t="n"/>
+    </row>
+    <row r="52">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>*Nada reservado, apenas cotado.</t>
         </is>
       </c>
     </row>
-    <row r="51"/>
-    <row r="52"/>
     <row r="53"/>
     <row r="54"/>
     <row r="55"/>
@@ -3884,16 +4032,28 @@
     <row r="77"/>
     <row r="78"/>
     <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
   </sheetData>
-  <autoFilter ref="A4:P45"/>
+  <autoFilter ref="A4:P47"/>
   <dataValidations count="3">
-    <dataValidation sqref="O5:O45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O5:O47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"A cotar,Cotado,Aprovado pelo cliente,Reservado,Descartado"</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="M5:M47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="H5:H47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"BRL,EUR,USD"</formula1>
     </dataValidation>
   </dataValidations>

--- a/cotacao-cristofer-reveillon.xlsx
+++ b/cotacao-cristofer-reveillon.xlsx
@@ -1101,7 +1101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P91"/>
+  <dimension ref="A1:P89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="D31" s="23" t="inlineStr">
         <is>
-          <t>Cais 8/8A, Ponte Elisabeth · jantar, música ao vivo e virada a bordo · detalhes do barco a confirmar</t>
+          <t>Cais 8/8A, Ponte Elisabeth · embarque 19h, retorno 1h · jantar, música ao vivo e virada a bordo</t>
         </is>
       </c>
       <c r="E31" s="23" t="inlineStr">
@@ -2939,7 +2939,9 @@
           <t>BRL</t>
         </is>
       </c>
-      <c r="I31" s="26" t="n"/>
+      <c r="I31" s="26" t="n">
+        <v>2272.86</v>
+      </c>
       <c r="J31" s="25" t="n">
         <v>4</v>
       </c>
@@ -2963,12 +2965,12 @@
       </c>
       <c r="O31" s="25" t="inlineStr">
         <is>
-          <t>A cotar</t>
+          <t>Cotado</t>
         </is>
       </c>
       <c r="P31" s="30" t="inlineStr">
         <is>
-          <t>Não consegui ler a página. Me mande o preço por adulto e por menor, o horário de embarque e o que inclui, que eu lanço.</t>
+          <t>Valor por pessoa, 6 horas a bordo (19h à 1h). Mais que o dobro da Opção 1 por pessoa. Confirmar preço de menor e o que o jantar inclui.</t>
         </is>
       </c>
     </row>
@@ -4042,8 +4044,6 @@
     <row r="87"/>
     <row r="88"/>
     <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
   </sheetData>
   <autoFilter ref="A4:P47"/>
   <dataValidations count="3">

--- a/cotacao-cristofer-reveillon.xlsx
+++ b/cotacao-cristofer-reveillon.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Cotação" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Cotação'!$A$4:$P$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Cotação'!$A$4:$P$46</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -625,19 +625,19 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$47,A5)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$46,A5)</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$47,A5,Cotação!$O$5:$O$47,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$46,A5,Cotação!$O$5:$O$46,"A cotar")</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$47,A5,Cotação!$O$5:$O$47,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$46,A5,Cotação!$O$5:$O$46,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E5" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$47,A5,Cotação!$N$5:$N$47)</f>
+        <f>SUMIF(Cotação!$B$5:$B$46,A5,Cotação!$N$5:$N$46)</f>
         <v/>
       </c>
     </row>
@@ -648,19 +648,19 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$47,A6)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$46,A6)</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$47,A6,Cotação!$O$5:$O$47,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$46,A6,Cotação!$O$5:$O$46,"A cotar")</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$47,A6,Cotação!$O$5:$O$47,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$46,A6,Cotação!$O$5:$O$46,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E6" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$47,A6,Cotação!$N$5:$N$47)</f>
+        <f>SUMIF(Cotação!$B$5:$B$46,A6,Cotação!$N$5:$N$46)</f>
         <v/>
       </c>
     </row>
@@ -671,19 +671,19 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$47,A7)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$46,A7)</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$47,A7,Cotação!$O$5:$O$47,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$46,A7,Cotação!$O$5:$O$46,"A cotar")</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$47,A7,Cotação!$O$5:$O$47,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$46,A7,Cotação!$O$5:$O$46,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E7" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$47,A7,Cotação!$N$5:$N$47)</f>
+        <f>SUMIF(Cotação!$B$5:$B$46,A7,Cotação!$N$5:$N$46)</f>
         <v/>
       </c>
     </row>
@@ -694,19 +694,19 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$47,A8)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$46,A8)</f>
         <v/>
       </c>
       <c r="C8" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$47,A8,Cotação!$O$5:$O$47,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$46,A8,Cotação!$O$5:$O$46,"A cotar")</f>
         <v/>
       </c>
       <c r="D8" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$47,A8,Cotação!$O$5:$O$47,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$46,A8,Cotação!$O$5:$O$46,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E8" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$47,A8,Cotação!$N$5:$N$47)</f>
+        <f>SUMIF(Cotação!$B$5:$B$46,A8,Cotação!$N$5:$N$46)</f>
         <v/>
       </c>
     </row>
@@ -717,19 +717,19 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$47,A9)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$46,A9)</f>
         <v/>
       </c>
       <c r="C9" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$47,A9,Cotação!$O$5:$O$47,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$46,A9,Cotação!$O$5:$O$46,"A cotar")</f>
         <v/>
       </c>
       <c r="D9" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$47,A9,Cotação!$O$5:$O$47,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$46,A9,Cotação!$O$5:$O$46,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E9" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$47,A9,Cotação!$N$5:$N$47)</f>
+        <f>SUMIF(Cotação!$B$5:$B$46,A9,Cotação!$N$5:$N$46)</f>
         <v/>
       </c>
     </row>
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$47,A10)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$46,A10)</f>
         <v/>
       </c>
       <c r="C10" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$47,A10,Cotação!$O$5:$O$47,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$46,A10,Cotação!$O$5:$O$46,"A cotar")</f>
         <v/>
       </c>
       <c r="D10" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$47,A10,Cotação!$O$5:$O$47,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$46,A10,Cotação!$O$5:$O$46,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$47,A10,Cotação!$N$5:$N$47)</f>
+        <f>SUMIF(Cotação!$B$5:$B$46,A10,Cotação!$N$5:$N$46)</f>
         <v/>
       </c>
     </row>
@@ -763,19 +763,19 @@
         </is>
       </c>
       <c r="B11" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$47,A11)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$46,A11)</f>
         <v/>
       </c>
       <c r="C11" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$47,A11,Cotação!$O$5:$O$47,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$46,A11,Cotação!$O$5:$O$46,"A cotar")</f>
         <v/>
       </c>
       <c r="D11" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$47,A11,Cotação!$O$5:$O$47,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$46,A11,Cotação!$O$5:$O$46,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E11" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$47,A11,Cotação!$N$5:$N$47)</f>
+        <f>SUMIF(Cotação!$B$5:$B$46,A11,Cotação!$N$5:$N$46)</f>
         <v/>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P89"/>
+  <dimension ref="A1:P88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2985,48 +2985,40 @@
       </c>
       <c r="C32" s="24" t="inlineStr">
         <is>
-          <t>Réveillon · Opção 3 · Budapest River Cruise · NYE Boat Party · 4 pax</t>
+          <t>Tokaj · motorista-guia privativo · dia inteiro · 4 pax</t>
         </is>
       </c>
       <c r="D32" s="23" t="inlineStr">
         <is>
-          <t>22h à 3h · DJ, open bar, fotógrafo · festa, sem jantar servido</t>
+          <t>Saída 8h de Budapeste, Oremus (Tolcsva) + segunda vinícola + almoço em Mád/Tarcal, retorno ~19h</t>
         </is>
       </c>
       <c r="E32" s="23" t="inlineStr">
         <is>
-          <t>31/12</t>
+          <t>02/01</t>
         </is>
       </c>
       <c r="F32" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="G32" s="25" t="inlineStr">
-        <is>
-          <t>Budapest River Cruise</t>
-        </is>
-      </c>
+      <c r="G32" s="25" t="inlineStr"/>
       <c r="H32" s="25" t="inlineStr">
         <is>
-          <t>BRL</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="I32" s="26" t="n"/>
       <c r="J32" s="25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K32" s="27">
         <f>IF(I32="","",I32*J32)</f>
         <v/>
       </c>
-      <c r="L32" s="28" t="inlineStr">
-        <is>
-          <t>budapestrivercruise.com/budapest-nye-boat-party-cruise</t>
-        </is>
-      </c>
+      <c r="L32" s="28" t="inlineStr"/>
       <c r="M32" s="25" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="N32" s="29">
@@ -3035,12 +3027,12 @@
       </c>
       <c r="O32" s="25" t="inlineStr">
         <is>
-          <t>Descartado</t>
+          <t>A cotar</t>
         </is>
       </c>
       <c r="P32" s="30" t="inlineStr">
         <is>
-          <t>Evento restrito a maiores de 18 anos. As filhas de 13 e 16 não embarcam.</t>
+          <t>Valor unitário = por veículo/dia. Motorista não bebe: tolerância zero na Hungria.</t>
         </is>
       </c>
     </row>
@@ -3055,12 +3047,12 @@
       </c>
       <c r="C33" s="24" t="inlineStr">
         <is>
-          <t>Tokaj · motorista-guia privativo · dia inteiro · 4 pax</t>
+          <t>Oremus · visita à adega e prova · 2 adultos + 2 filhas</t>
         </is>
       </c>
       <c r="D33" s="23" t="inlineStr">
         <is>
-          <t>Saída 8h de Budapeste, Oremus (Tolcsva) + segunda vinícola + almoço em Mád/Tarcal, retorno ~19h</t>
+          <t>Tolcsva · agendamento por e-mail · ~1h · adegas do século XIII · adolescentes acompanham sem álcool</t>
         </is>
       </c>
       <c r="E33" s="23" t="inlineStr">
@@ -3071,13 +3063,19 @@
       <c r="F33" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="G33" s="25" t="inlineStr"/>
+      <c r="G33" s="25" t="inlineStr">
+        <is>
+          <t>Tokaj-Oremus</t>
+        </is>
+      </c>
       <c r="H33" s="25" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="I33" s="26" t="n"/>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="I33" s="26" t="n">
+        <v>315.67</v>
+      </c>
       <c r="J33" s="25" t="n">
         <v>1</v>
       </c>
@@ -3097,12 +3095,12 @@
       </c>
       <c r="O33" s="25" t="inlineStr">
         <is>
-          <t>A cotar</t>
+          <t>Cotado</t>
         </is>
       </c>
       <c r="P33" s="30" t="inlineStr">
         <is>
-          <t>Valor unitário = por veículo/dia. Motorista não bebe: tolerância zero na Hungria.</t>
+          <t>Cotação de 21/09 em reais para a família (2 adultos e 2 filhas). Confirmar recepção no sábado 02/01; plano B: segunda 04/01.</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3115,12 @@
       </c>
       <c r="C34" s="24" t="inlineStr">
         <is>
-          <t>Oremus · visita à adega e prova · 2 adultos + 2 filhas</t>
+          <t>Almoço em vinícola ou restaurante em Tokaj · 4 pax</t>
         </is>
       </c>
       <c r="D34" s="23" t="inlineStr">
         <is>
-          <t>Tolcsva · agendamento por e-mail · ~1h · adegas do século XIII · adolescentes acompanham sem álcool</t>
+          <t>Mád ou Tarcal</t>
         </is>
       </c>
       <c r="E34" s="23" t="inlineStr">
@@ -3133,21 +3131,15 @@
       <c r="F34" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="G34" s="25" t="inlineStr">
-        <is>
-          <t>Tokaj-Oremus</t>
-        </is>
-      </c>
+      <c r="G34" s="25" t="inlineStr"/>
       <c r="H34" s="25" t="inlineStr">
         <is>
-          <t>BRL</t>
-        </is>
-      </c>
-      <c r="I34" s="26" t="n">
-        <v>315.67</v>
-      </c>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I34" s="26" t="n"/>
       <c r="J34" s="25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K34" s="27">
         <f>IF(I34="","",I34*J34)</f>
@@ -3165,12 +3157,12 @@
       </c>
       <c r="O34" s="25" t="inlineStr">
         <is>
-          <t>Cotado</t>
+          <t>A cotar</t>
         </is>
       </c>
       <c r="P34" s="30" t="inlineStr">
         <is>
-          <t>Cotação de 21/09 em reais para a família (2 adultos e 2 filhas). Confirmar recepção no sábado 02/01; plano B: segunda 04/01.</t>
+          <t>Pode vir incluído no pacote do motorista-guia.</t>
         </is>
       </c>
     </row>
@@ -3185,17 +3177,17 @@
       </c>
       <c r="C35" s="24" t="inlineStr">
         <is>
-          <t>Almoço em vinícola ou restaurante em Tokaj · 4 pax</t>
+          <t>Termas Széchenyi · 4 pax</t>
         </is>
       </c>
       <c r="D35" s="23" t="inlineStr">
         <is>
-          <t>Mád ou Tarcal</t>
+          <t>Ingresso dia inteiro com cabine · aberto em 01/01</t>
         </is>
       </c>
       <c r="E35" s="23" t="inlineStr">
         <is>
-          <t>02/01</t>
+          <t>01/01</t>
         </is>
       </c>
       <c r="F35" s="23" t="n">
@@ -3230,11 +3222,7 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P35" s="30" t="inlineStr">
-        <is>
-          <t>Pode vir incluído no pacote do motorista-guia.</t>
-        </is>
-      </c>
+      <c r="P35" s="30" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="23" t="n">
@@ -3247,17 +3235,17 @@
       </c>
       <c r="C36" s="24" t="inlineStr">
         <is>
-          <t>Termas Széchenyi · 4 pax</t>
+          <t>Schönbrunn · Grand Tour · 4 pax</t>
         </is>
       </c>
       <c r="D36" s="23" t="inlineStr">
         <is>
-          <t>Ingresso dia inteiro com cabine · aberto em 01/01</t>
+          <t>Entrada com hora marcada · mercado de Ano Novo no pátio até 06/01</t>
         </is>
       </c>
       <c r="E36" s="23" t="inlineStr">
         <is>
-          <t>01/01</t>
+          <t>04/01</t>
         </is>
       </c>
       <c r="F36" s="23" t="n">
@@ -3305,12 +3293,12 @@
       </c>
       <c r="C37" s="24" t="inlineStr">
         <is>
-          <t>Schönbrunn · Grand Tour · 4 pax</t>
+          <t>Concerto Orquestra do Hofburg ou Musikverein · 4 pax</t>
         </is>
       </c>
       <c r="D37" s="23" t="inlineStr">
         <is>
-          <t>Entrada com hora marcada · mercado de Ano Novo no pátio até 06/01</t>
+          <t>Strauss e Mozart · categoria de assento a definir</t>
         </is>
       </c>
       <c r="E37" s="23" t="inlineStr">
@@ -3350,7 +3338,11 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P37" s="30" t="inlineStr"/>
+      <c r="P37" s="30" t="inlineStr">
+        <is>
+          <t>Concerto de Ano Novo da Filarmônica (01/01) é por sorteio já encerrado.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="23" t="n">
@@ -3363,21 +3355,21 @@
       </c>
       <c r="C38" s="24" t="inlineStr">
         <is>
-          <t>Concerto Orquestra do Hofburg ou Musikverein · 4 pax</t>
+          <t>Prater · Roda Gigante · 5 pax</t>
         </is>
       </c>
       <c r="D38" s="23" t="inlineStr">
         <is>
-          <t>Strauss e Mozart · categoria de assento a definir</t>
+          <t>Ingresso · mercado de inverno na praça até 06/01</t>
         </is>
       </c>
       <c r="E38" s="23" t="inlineStr">
         <is>
-          <t>04/01</t>
+          <t>05/01</t>
         </is>
       </c>
       <c r="F38" s="23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G38" s="25" t="inlineStr"/>
       <c r="H38" s="25" t="inlineStr">
@@ -3387,7 +3379,7 @@
       </c>
       <c r="I38" s="26" t="n"/>
       <c r="J38" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K38" s="27">
         <f>IF(I38="","",I38*J38)</f>
@@ -3408,11 +3400,7 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P38" s="30" t="inlineStr">
-        <is>
-          <t>Concerto de Ano Novo da Filarmônica (01/01) é por sorteio já encerrado.</t>
-        </is>
-      </c>
+      <c r="P38" s="30" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="23" t="n">
@@ -3425,17 +3413,17 @@
       </c>
       <c r="C39" s="24" t="inlineStr">
         <is>
-          <t>Prater · Roda Gigante · 5 pax</t>
+          <t>Belvedere Superior · 5 pax</t>
         </is>
       </c>
       <c r="D39" s="23" t="inlineStr">
         <is>
-          <t>Ingresso · mercado de inverno na praça até 06/01</t>
+          <t>Ingresso · O Beijo de Klimt</t>
         </is>
       </c>
       <c r="E39" s="23" t="inlineStr">
         <is>
-          <t>05/01</t>
+          <t>06/01</t>
         </is>
       </c>
       <c r="F39" s="23" t="n">
@@ -3483,12 +3471,12 @@
       </c>
       <c r="C40" s="24" t="inlineStr">
         <is>
-          <t>Belvedere Superior · 5 pax</t>
+          <t>Opcional · Ópera Estatal de Viena · 5 pax</t>
         </is>
       </c>
       <c r="D40" s="23" t="inlineStr">
         <is>
-          <t>Ingresso · O Beijo de Klimt</t>
+          <t>Récita da noite · verificar programa de 06/01</t>
         </is>
       </c>
       <c r="E40" s="23" t="inlineStr">
@@ -3516,7 +3504,7 @@
       <c r="L40" s="28" t="inlineStr"/>
       <c r="M40" s="25" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="N40" s="29">
@@ -3528,7 +3516,11 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P40" s="30" t="inlineStr"/>
+      <c r="P40" s="30" t="inlineStr">
+        <is>
+          <t>Só entra se o cliente pedir.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="23" t="n">
@@ -3541,17 +3533,17 @@
       </c>
       <c r="C41" s="24" t="inlineStr">
         <is>
-          <t>Opcional · Ópera Estatal de Viena · 5 pax</t>
+          <t>Castelo de Praga · circuito B · 5 pax</t>
         </is>
       </c>
       <c r="D41" s="23" t="inlineStr">
         <is>
-          <t>Récita da noite · verificar programa de 06/01</t>
+          <t>Catedral de São Vito, Palácio Real Antigo, Ruela Dourada</t>
         </is>
       </c>
       <c r="E41" s="23" t="inlineStr">
         <is>
-          <t>06/01</t>
+          <t>08/01</t>
         </is>
       </c>
       <c r="F41" s="23" t="n">
@@ -3574,7 +3566,7 @@
       <c r="L41" s="28" t="inlineStr"/>
       <c r="M41" s="25" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="N41" s="29">
@@ -3586,11 +3578,7 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P41" s="30" t="inlineStr">
-        <is>
-          <t>Só entra se o cliente pedir.</t>
-        </is>
-      </c>
+      <c r="P41" s="30" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="23" t="n">
@@ -3603,12 +3591,12 @@
       </c>
       <c r="C42" s="24" t="inlineStr">
         <is>
-          <t>Castelo de Praga · circuito B · 5 pax</t>
+          <t>Teatro de luz negra · 5 pax</t>
         </is>
       </c>
       <c r="D42" s="23" t="inlineStr">
         <is>
-          <t>Catedral de São Vito, Palácio Real Antigo, Ruela Dourada</t>
+          <t>Sessão da noite</t>
         </is>
       </c>
       <c r="E42" s="23" t="inlineStr">
@@ -3661,17 +3649,17 @@
       </c>
       <c r="C43" s="24" t="inlineStr">
         <is>
-          <t>Teatro de luz negra · 5 pax</t>
+          <t>Torre Eiffel · topo · 5 pax</t>
         </is>
       </c>
       <c r="D43" s="23" t="inlineStr">
         <is>
-          <t>Sessão da noite</t>
+          <t>Entrada com hora marcada · abre venda 60 dias antes</t>
         </is>
       </c>
       <c r="E43" s="23" t="inlineStr">
         <is>
-          <t>08/01</t>
+          <t>10/01</t>
         </is>
       </c>
       <c r="F43" s="23" t="n">
@@ -3706,7 +3694,11 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P43" s="30" t="inlineStr"/>
+      <c r="P43" s="30" t="inlineStr">
+        <is>
+          <t>Reservar exatamente em 11/11 para garantir horário.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="23" t="n">
@@ -3719,17 +3711,17 @@
       </c>
       <c r="C44" s="24" t="inlineStr">
         <is>
-          <t>Torre Eiffel · topo · 5 pax</t>
+          <t>Louvre · 5 pax</t>
         </is>
       </c>
       <c r="D44" s="23" t="inlineStr">
         <is>
-          <t>Entrada com hora marcada · abre venda 60 dias antes</t>
+          <t>Entrada com hora marcada · menores de 18 gratuitos</t>
         </is>
       </c>
       <c r="E44" s="23" t="inlineStr">
         <is>
-          <t>10/01</t>
+          <t>11/01</t>
         </is>
       </c>
       <c r="F44" s="23" t="n">
@@ -3743,7 +3735,7 @@
       </c>
       <c r="I44" s="26" t="n"/>
       <c r="J44" s="25" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K44" s="27">
         <f>IF(I44="","",I44*J44)</f>
@@ -3766,7 +3758,7 @@
       </c>
       <c r="P44" s="30" t="inlineStr">
         <is>
-          <t>Reservar exatamente em 11/11 para garantir horário.</t>
+          <t>Qtd = 2 adultos pagantes.</t>
         </is>
       </c>
     </row>
@@ -3781,12 +3773,12 @@
       </c>
       <c r="C45" s="24" t="inlineStr">
         <is>
-          <t>Louvre · 5 pax</t>
+          <t>Cruzeiro no Sena com jantar · 5 pax</t>
         </is>
       </c>
       <c r="D45" s="23" t="inlineStr">
         <is>
-          <t>Entrada com hora marcada · menores de 18 gratuitos</t>
+          <t>Bateaux Parisiens ou Bateaux-Mouches · jantar da noite</t>
         </is>
       </c>
       <c r="E45" s="23" t="inlineStr">
@@ -3805,7 +3797,7 @@
       </c>
       <c r="I45" s="26" t="n"/>
       <c r="J45" s="25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K45" s="27">
         <f>IF(I45="","",I45*J45)</f>
@@ -3826,11 +3818,7 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P45" s="30" t="inlineStr">
-        <is>
-          <t>Qtd = 2 adultos pagantes.</t>
-        </is>
-      </c>
+      <c r="P45" s="30" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="23" t="n">
@@ -3838,22 +3826,22 @@
       </c>
       <c r="B46" s="23" t="inlineStr">
         <is>
-          <t>Experiência</t>
+          <t>Seguro/Docs</t>
         </is>
       </c>
       <c r="C46" s="24" t="inlineStr">
         <is>
-          <t>Cruzeiro no Sena com jantar · 5 pax</t>
+          <t>Seguro viagem · 5 pax · 15 dias</t>
         </is>
       </c>
       <c r="D46" s="23" t="inlineStr">
         <is>
-          <t>Bateaux Parisiens ou Bateaux-Mouches · jantar da noite</t>
+          <t>Cobertura médica mínima € 30.000 (Schengen) · bagagem · cancelamento</t>
         </is>
       </c>
       <c r="E46" s="23" t="inlineStr">
         <is>
-          <t>11/01</t>
+          <t>29/12 → 12/01</t>
         </is>
       </c>
       <c r="F46" s="23" t="n">
@@ -3862,7 +3850,7 @@
       <c r="G46" s="25" t="inlineStr"/>
       <c r="H46" s="25" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>BRL</t>
         </is>
       </c>
       <c r="I46" s="26" t="n"/>
@@ -3888,125 +3876,68 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P46" s="30" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="23" t="n">
-        <v>43</v>
-      </c>
-      <c r="B47" s="23" t="inlineStr">
-        <is>
-          <t>Seguro/Docs</t>
-        </is>
-      </c>
-      <c r="C47" s="24" t="inlineStr">
-        <is>
-          <t>Seguro viagem · 5 pax · 15 dias</t>
-        </is>
-      </c>
-      <c r="D47" s="23" t="inlineStr">
-        <is>
-          <t>Cobertura médica mínima € 30.000 (Schengen) · bagagem · cancelamento</t>
-        </is>
-      </c>
-      <c r="E47" s="23" t="inlineStr">
-        <is>
-          <t>29/12 → 12/01</t>
-        </is>
-      </c>
-      <c r="F47" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="G47" s="25" t="inlineStr"/>
-      <c r="H47" s="25" t="inlineStr">
-        <is>
-          <t>BRL</t>
-        </is>
-      </c>
-      <c r="I47" s="26" t="n"/>
-      <c r="J47" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="K47" s="27">
-        <f>IF(I47="","",I47*J47)</f>
-        <v/>
-      </c>
-      <c r="L47" s="28" t="inlineStr"/>
-      <c r="M47" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="N47" s="29">
-        <f>IF(OR(M47&lt;&gt;"Sim",I47=""),0,K47*IF(H47="BRL",1,IF(H47="EUR",Parâmetros!$B$4,IF(H47="USD",Parâmetros!$B$5,1))))</f>
-        <v/>
-      </c>
-      <c r="O47" s="25" t="inlineStr">
-        <is>
-          <t>A cotar</t>
-        </is>
-      </c>
-      <c r="P47" s="30" t="inlineStr">
+      <c r="P46" s="30" t="inlineStr">
         <is>
           <t>Valor unitário = por pessoa. Filho com vigência a partir de 04/01 pode sair mais barato.</t>
         </is>
       </c>
     </row>
-    <row r="48"/>
+    <row r="47"/>
+    <row r="48">
+      <c r="C48" s="21" t="inlineStr">
+        <is>
+          <t>SUBTOTAL EM R$ (itens marcados como Sim)</t>
+        </is>
+      </c>
+      <c r="N48" s="31">
+        <f>SUM(N5:N46)</f>
+        <v/>
+      </c>
+    </row>
     <row r="49">
-      <c r="C49" s="21" t="inlineStr">
-        <is>
-          <t>SUBTOTAL EM R$ (itens marcados como Sim)</t>
-        </is>
-      </c>
-      <c r="N49" s="31">
-        <f>SUM(N5:N47)</f>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>Taxa de serviço LusaTravel</t>
+        </is>
+      </c>
+      <c r="N49" s="13">
+        <f>N48*Parâmetros!$B$10</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="C50" s="12" t="inlineStr">
-        <is>
-          <t>Taxa de serviço LusaTravel</t>
-        </is>
-      </c>
-      <c r="N50" s="13">
-        <f>N49*Parâmetros!$B$10</f>
-        <v/>
-      </c>
+      <c r="A50" s="32" t="n"/>
+      <c r="B50" s="32" t="n"/>
+      <c r="C50" s="33" t="inlineStr">
+        <is>
+          <t>TOTAL PARA O CLIENTE</t>
+        </is>
+      </c>
+      <c r="D50" s="32" t="n"/>
+      <c r="E50" s="32" t="n"/>
+      <c r="F50" s="32" t="n"/>
+      <c r="G50" s="32" t="n"/>
+      <c r="H50" s="32" t="n"/>
+      <c r="I50" s="32" t="n"/>
+      <c r="J50" s="32" t="n"/>
+      <c r="K50" s="32" t="n"/>
+      <c r="L50" s="32" t="n"/>
+      <c r="M50" s="32" t="n"/>
+      <c r="N50" s="34">
+        <f>N48+N49</f>
+        <v/>
+      </c>
+      <c r="O50" s="32" t="n"/>
+      <c r="P50" s="32" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="32" t="n"/>
-      <c r="B51" s="32" t="n"/>
-      <c r="C51" s="33" t="inlineStr">
-        <is>
-          <t>TOTAL PARA O CLIENTE</t>
-        </is>
-      </c>
-      <c r="D51" s="32" t="n"/>
-      <c r="E51" s="32" t="n"/>
-      <c r="F51" s="32" t="n"/>
-      <c r="G51" s="32" t="n"/>
-      <c r="H51" s="32" t="n"/>
-      <c r="I51" s="32" t="n"/>
-      <c r="J51" s="32" t="n"/>
-      <c r="K51" s="32" t="n"/>
-      <c r="L51" s="32" t="n"/>
-      <c r="M51" s="32" t="n"/>
-      <c r="N51" s="34">
-        <f>N49+N50</f>
-        <v/>
-      </c>
-      <c r="O51" s="32" t="n"/>
-      <c r="P51" s="32" t="n"/>
-    </row>
-    <row r="52">
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>*Nada reservado, apenas cotado.</t>
         </is>
       </c>
     </row>
+    <row r="52"/>
     <row r="53"/>
     <row r="54"/>
     <row r="55"/>
@@ -4043,17 +3974,16 @@
     <row r="86"/>
     <row r="87"/>
     <row r="88"/>
-    <row r="89"/>
   </sheetData>
-  <autoFilter ref="A4:P47"/>
+  <autoFilter ref="A4:P46"/>
   <dataValidations count="3">
-    <dataValidation sqref="O5:O47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O5:O46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"A cotar,Cotado,Aprovado pelo cliente,Reservado,Descartado"</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="M5:M46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="H5:H46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"BRL,EUR,USD"</formula1>
     </dataValidation>
   </dataValidations>

--- a/cotacao-cristofer-reveillon.xlsx
+++ b/cotacao-cristofer-reveillon.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Cotação" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Cotação'!$A$4:$P$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Cotação'!$A$4:$P$47</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -625,19 +625,19 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$46,A5)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$47,A5)</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$46,A5,Cotação!$O$5:$O$46,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$47,A5,Cotação!$O$5:$O$47,"A cotar")</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$46,A5,Cotação!$O$5:$O$46,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$47,A5,Cotação!$O$5:$O$47,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E5" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$46,A5,Cotação!$N$5:$N$46)</f>
+        <f>SUMIF(Cotação!$B$5:$B$47,A5,Cotação!$N$5:$N$47)</f>
         <v/>
       </c>
     </row>
@@ -648,19 +648,19 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$46,A6)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$47,A6)</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$46,A6,Cotação!$O$5:$O$46,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$47,A6,Cotação!$O$5:$O$47,"A cotar")</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$46,A6,Cotação!$O$5:$O$46,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$47,A6,Cotação!$O$5:$O$47,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E6" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$46,A6,Cotação!$N$5:$N$46)</f>
+        <f>SUMIF(Cotação!$B$5:$B$47,A6,Cotação!$N$5:$N$47)</f>
         <v/>
       </c>
     </row>
@@ -671,19 +671,19 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$46,A7)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$47,A7)</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$46,A7,Cotação!$O$5:$O$46,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$47,A7,Cotação!$O$5:$O$47,"A cotar")</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$46,A7,Cotação!$O$5:$O$46,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$47,A7,Cotação!$O$5:$O$47,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E7" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$46,A7,Cotação!$N$5:$N$46)</f>
+        <f>SUMIF(Cotação!$B$5:$B$47,A7,Cotação!$N$5:$N$47)</f>
         <v/>
       </c>
     </row>
@@ -694,19 +694,19 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$46,A8)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$47,A8)</f>
         <v/>
       </c>
       <c r="C8" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$46,A8,Cotação!$O$5:$O$46,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$47,A8,Cotação!$O$5:$O$47,"A cotar")</f>
         <v/>
       </c>
       <c r="D8" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$46,A8,Cotação!$O$5:$O$46,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$47,A8,Cotação!$O$5:$O$47,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E8" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$46,A8,Cotação!$N$5:$N$46)</f>
+        <f>SUMIF(Cotação!$B$5:$B$47,A8,Cotação!$N$5:$N$47)</f>
         <v/>
       </c>
     </row>
@@ -717,19 +717,19 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$46,A9)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$47,A9)</f>
         <v/>
       </c>
       <c r="C9" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$46,A9,Cotação!$O$5:$O$46,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$47,A9,Cotação!$O$5:$O$47,"A cotar")</f>
         <v/>
       </c>
       <c r="D9" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$46,A9,Cotação!$O$5:$O$46,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$47,A9,Cotação!$O$5:$O$47,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E9" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$46,A9,Cotação!$N$5:$N$46)</f>
+        <f>SUMIF(Cotação!$B$5:$B$47,A9,Cotação!$N$5:$N$47)</f>
         <v/>
       </c>
     </row>
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$46,A10)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$47,A10)</f>
         <v/>
       </c>
       <c r="C10" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$46,A10,Cotação!$O$5:$O$46,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$47,A10,Cotação!$O$5:$O$47,"A cotar")</f>
         <v/>
       </c>
       <c r="D10" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$46,A10,Cotação!$O$5:$O$46,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$47,A10,Cotação!$O$5:$O$47,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$46,A10,Cotação!$N$5:$N$46)</f>
+        <f>SUMIF(Cotação!$B$5:$B$47,A10,Cotação!$N$5:$N$47)</f>
         <v/>
       </c>
     </row>
@@ -763,19 +763,19 @@
         </is>
       </c>
       <c r="B11" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$46,A11)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$47,A11)</f>
         <v/>
       </c>
       <c r="C11" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$46,A11,Cotação!$O$5:$O$46,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$47,A11,Cotação!$O$5:$O$47,"A cotar")</f>
         <v/>
       </c>
       <c r="D11" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$46,A11,Cotação!$O$5:$O$46,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$47,A11,Cotação!$O$5:$O$47,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E11" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$46,A11,Cotação!$N$5:$N$46)</f>
+        <f>SUMIF(Cotação!$B$5:$B$47,A11,Cotação!$N$5:$N$47)</f>
         <v/>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P88"/>
+  <dimension ref="A1:P52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="C5" s="24" t="inlineStr">
         <is>
-          <t>Aéreo internacional · 4 pax</t>
+          <t>Aéreo internacional · 4 pax · Opção A · volta 12/01 12:05</t>
         </is>
       </c>
       <c r="D5" s="23" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="P5" s="30" t="inlineStr">
         <is>
-          <t>Cotação recebida em 20/09: R$ 41.637,56 total (USD 8.073,20) para 4 pax = R$ 10.409,39 por pax. Inclui o trecho Praga → Paris. Chegada em Budapeste às 10:30 de 30/12. Conferir o alerta (⚠) no voo LA1579 no sistema.</t>
+          <t>Cotação de 20/09: R$ 41.637,56 total (USD 8.073,20) = R$ 10.409,39 por pax. Inclui Praga → Paris. Nesta opção o filho viaja em voos diferentes em 10/01 e 12/01 (chega ao Brasil em 13/01 de manhã).</t>
         </is>
       </c>
     </row>
@@ -1297,46 +1297,40 @@
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>Aéreo do filho · 1 pax</t>
+          <t>Aéreo internacional · 4 pax · Opção B · volta 12/01 23:20, junto com o filho</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
         <is>
-          <t>AF453 GRU 04/01 14:40 → CDG 05/01 06:05 · AF1138 CDG 10:00 → VIE 12:00 (conexão 3h55) · AF1383 PRG 10/01 12:10 → CDG 14:05 · AF454 CDG 12/01 23:20 → GRU 13/01 07:20 · econômica</t>
+          <t>Mesma ida (LA1579 + IB869) · AF1383 PRG 10/01 12:10 → CDG 14:05 · AF454 CDG 12/01 23:20 → GRU 13/01 07:20 · os cinco nos mesmos voos em 10/01 e 12/01 · dia 12 inteiro em Paris</t>
         </is>
       </c>
       <c r="E6" s="23" t="inlineStr">
         <is>
-          <t>04/01 e 12/01</t>
+          <t>29/12 e 12/01</t>
         </is>
       </c>
       <c r="F6" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="25" t="inlineStr">
-        <is>
-          <t>Air France (consolidador)</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G6" s="25" t="n"/>
       <c r="H6" s="25" t="inlineStr">
         <is>
           <t>BRL</t>
         </is>
       </c>
-      <c r="I6" s="26" t="n">
-        <v>12056.63</v>
-      </c>
+      <c r="I6" s="26" t="n"/>
       <c r="J6" s="25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K6" s="27">
         <f>IF(I6="","",I6*J6)</f>
         <v/>
       </c>
-      <c r="L6" s="28" t="inlineStr"/>
+      <c r="L6" s="28" t="n"/>
       <c r="M6" s="25" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="N6" s="29">
@@ -1345,12 +1339,12 @@
       </c>
       <c r="O6" s="25" t="inlineStr">
         <is>
-          <t>Cotado</t>
+          <t>A cotar</t>
         </is>
       </c>
       <c r="P6" s="30" t="inlineStr">
         <is>
-          <t>Recotação de 20/09: R$ 12.056,63 (USD 2.337,69), com PRG → CDG correto. Ainda em voos diferentes da família em 10/01 (AF1383 12:10 vs AF1183 09:50) e em 12/01 (AF454 23:20 vs LA8133 12:05). Decisão pendente: alinhar os 4 ao filho (recotar os 4 com AF1383 + AF454, ganha o dia 12 em Paris) ou aceitar as duas separações.</t>
+          <t>A recotar com o consolidador. Decisão do cliente: chegar ao Brasil na noite de 12/01 separado do filho, ou na manhã de 13/01 com ele.</t>
         </is>
       </c>
     </row>
@@ -1365,29 +1359,35 @@
       </c>
       <c r="C7" s="24" t="inlineStr">
         <is>
-          <t>Voo Praga → Paris · filho · 1 pax</t>
+          <t>Aéreo do filho · 1 pax</t>
         </is>
       </c>
       <c r="D7" s="23" t="inlineStr">
         <is>
-          <t>PRG → CDG 10/01 · os 4 já estão no bilhete internacional (AF1183) · ideal: mesmo voo AF1183 09:50</t>
+          <t>AF453 GRU 04/01 14:40 → CDG 05/01 06:05 · AF1138 CDG 10:00 → VIE 12:00 (conexão 3h55) · AF1383 PRG 10/01 12:10 → CDG 14:05 · AF454 CDG 12/01 23:20 → GRU 13/01 07:20 · econômica</t>
         </is>
       </c>
       <c r="E7" s="23" t="inlineStr">
         <is>
-          <t>10/01</t>
+          <t>04/01 e 12/01</t>
         </is>
       </c>
       <c r="F7" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="25" t="inlineStr"/>
+      <c r="G7" s="25" t="inlineStr">
+        <is>
+          <t>Air France (consolidador)</t>
+        </is>
+      </c>
       <c r="H7" s="25" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="I7" s="26" t="n"/>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="I7" s="26" t="n">
+        <v>12056.63</v>
+      </c>
       <c r="J7" s="25" t="n">
         <v>1</v>
       </c>
@@ -1398,7 +1398,7 @@
       <c r="L7" s="28" t="inlineStr"/>
       <c r="M7" s="25" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="N7" s="29">
@@ -1407,12 +1407,12 @@
       </c>
       <c r="O7" s="25" t="inlineStr">
         <is>
-          <t>Descartado</t>
+          <t>Cotado</t>
         </is>
       </c>
       <c r="P7" s="30" t="inlineStr">
         <is>
-          <t>Incluído no multitrecho do filho (AF1383). Não cotar à parte.</t>
+          <t>Recotação de 20/09: R$ 12.056,63 (USD 2.337,69). Com a Opção A dos 4, ele viaja separado em 10/01 e 12/01; com a Opção B, os cinco viajam juntos.</t>
         </is>
       </c>
     </row>
@@ -1427,31 +1427,31 @@
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>Opcional · upgrade de cabine</t>
+          <t>Voo Praga → Paris · filho · 1 pax</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
         <is>
-          <t>Diferença para Premium Economy ou Executiva no trecho internacional · 5 pax</t>
+          <t>PRG → CDG 10/01 · os 4 já estão no bilhete internacional (AF1183) · ideal: mesmo voo AF1183 09:50</t>
         </is>
       </c>
       <c r="E8" s="23" t="inlineStr">
         <is>
-          <t>29/12, 04/01 e 12/01</t>
+          <t>10/01</t>
         </is>
       </c>
       <c r="F8" s="23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G8" s="25" t="inlineStr"/>
       <c r="H8" s="25" t="inlineStr">
         <is>
-          <t>BRL</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="I8" s="26" t="n"/>
       <c r="J8" s="25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K8" s="27">
         <f>IF(I8="","",I8*J8)</f>
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O8" s="25" t="inlineStr">
         <is>
-          <t>A cotar</t>
+          <t>Descartado</t>
         </is>
       </c>
       <c r="P8" s="30" t="inlineStr">
         <is>
-          <t>Só entra no total se o cliente pedir.</t>
+          <t>Incluído no multitrecho do filho (AF1383). Não cotar à parte.</t>
         </is>
       </c>
     </row>
@@ -1484,52 +1484,42 @@
       </c>
       <c r="B9" s="23" t="inlineStr">
         <is>
-          <t>Hotel</t>
+          <t>Aéreo</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
         <is>
-          <t>Budapeste · Opção 1 · Barceló Budapest 4★</t>
+          <t>Opcional · upgrade de cabine</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
         <is>
-          <t>Király utca, Terézváros, a 5 min da Basílica · 2 quartos Superior Double · café da manhã · 4 noites</t>
+          <t>Diferença para Premium Economy ou Executiva no trecho internacional · 5 pax</t>
         </is>
       </c>
       <c r="E9" s="23" t="inlineStr">
         <is>
-          <t>30/12 → 03/01</t>
+          <t>29/12, 04/01 e 12/01</t>
         </is>
       </c>
       <c r="F9" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="G9" s="25" t="inlineStr">
-        <is>
-          <t>Consolidador (a nomear)</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="G9" s="25" t="inlineStr"/>
       <c r="H9" s="25" t="inlineStr">
         <is>
           <t>BRL</t>
         </is>
       </c>
-      <c r="I9" s="26" t="n">
-        <v>16800</v>
-      </c>
+      <c r="I9" s="26" t="n"/>
       <c r="J9" s="25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K9" s="27">
         <f>IF(I9="","",I9*J9)</f>
         <v/>
       </c>
-      <c r="L9" s="28" t="inlineStr">
-        <is>
-          <t>Booking 20/09: R$ 15.136 pelas 2 quartos/4 noites no mesmo hotel · InterContinental 5★ € 2.398 · Corinthia 5★ € 2.939</t>
-        </is>
-      </c>
+      <c r="L9" s="28" t="inlineStr"/>
       <c r="M9" s="25" t="inlineStr">
         <is>
           <t>Não</t>
@@ -1541,12 +1531,12 @@
       </c>
       <c r="O9" s="25" t="inlineStr">
         <is>
-          <t>Cotado</t>
+          <t>A cotar</t>
         </is>
       </c>
       <c r="P9" s="30" t="inlineStr">
         <is>
-          <t>Cotação de 21/09: R$ 16.800 por quarto pelas 4 noites (R$ 4.200/noite) = R$ 33.600. ALERTA: mais que o dobro do Booking para o mesmo hotel e datas (R$ 15.136 pelos 2 quartos). Confirmar se o valor é por quarto ou pelos dois, e o que a tarifa inclui (cancelamento flexível? pacote de Réveillon?).</t>
+          <t>Só entra no total se o cliente pedir.</t>
         </is>
       </c>
     </row>
@@ -1561,12 +1551,12 @@
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>Budapeste · Opção 2 · Mercure Budapest City Center 4★</t>
+          <t>Budapeste · Opção 1 · Barceló Budapest 4★</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
         <is>
-          <t>Váci utca, coração de Pest, pedestre · 2 quartos Superior · café da manhã · 4 noites</t>
+          <t>Király utca, Terézváros, a 5 min da Basílica · 2 quartos Superior Double · café da manhã · 4 noites</t>
         </is>
       </c>
       <c r="E10" s="23" t="inlineStr">
@@ -1588,7 +1578,7 @@
         </is>
       </c>
       <c r="I10" s="26" t="n">
-        <v>6700</v>
+        <v>8400</v>
       </c>
       <c r="J10" s="25" t="n">
         <v>2</v>
@@ -1599,7 +1589,7 @@
       </c>
       <c r="L10" s="28" t="inlineStr">
         <is>
-          <t>Booking 20/09: R$ 11.016 pelos 2 quartos/4 noites no mesmo hotel</t>
+          <t>Booking 20/09: R$ 15.136 pelas 2 quartos/4 noites no mesmo hotel · InterContinental 5★ € 2.398 · Corinthia 5★ € 2.939</t>
         </is>
       </c>
       <c r="M10" s="25" t="inlineStr">
@@ -1618,7 +1608,7 @@
       </c>
       <c r="P10" s="30" t="inlineStr">
         <is>
-          <t>Cotação de 21/09: '2x Superior Room 13.400' — lido como R$ 13.400 pelos 2 quartos (R$ 6.700 por quarto, R$ 1.675/noite). Se for por quarto, o total é R$ 26.800. Confirmar. Com café da manhã.</t>
+          <t>Cotação de 21/09: R$ 16.800 pelos 2 quartos (R$ 8.400 por quarto, R$ 2.100/noite). Alternativa: R$ 580 abaixo do InterContinental, que segue no total por ser 5★ à beira do rio.</t>
         </is>
       </c>
     </row>
@@ -1633,12 +1623,12 @@
       </c>
       <c r="C11" s="24" t="inlineStr">
         <is>
-          <t>Budapeste · Opção 3 · InterContinental Budapest 5★</t>
+          <t>Budapeste · Opção 2 · Mercure Budapest City Center 4★</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
         <is>
-          <t>Margem do Danúbio, vista para o Castelo e a Ponte das Correntes · 2 quartos Classic · café da manhã · 4 noites</t>
+          <t>Váci utca, coração de Pest, pedestre · 2 quartos Superior · café da manhã · 4 noites</t>
         </is>
       </c>
       <c r="E11" s="23" t="inlineStr">
@@ -1660,7 +1650,7 @@
         </is>
       </c>
       <c r="I11" s="26" t="n">
-        <v>8690</v>
+        <v>6700</v>
       </c>
       <c r="J11" s="25" t="n">
         <v>2</v>
@@ -1671,12 +1661,12 @@
       </c>
       <c r="L11" s="28" t="inlineStr">
         <is>
-          <t>Booking 20/09: € 2.398 (≈ R$ 14.172) pelos 2 quartos/4 noites no mesmo hotel, tarifa mais barata</t>
+          <t>Booking 20/09: R$ 11.016 pelos 2 quartos/4 noites no mesmo hotel</t>
         </is>
       </c>
       <c r="M11" s="25" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="N11" s="29">
@@ -1690,7 +1680,7 @@
       </c>
       <c r="P11" s="30" t="inlineStr">
         <is>
-          <t>Cotação de 21/09: '2x Classic Room 17.380' — R$ 17.380 pelos 2 quartos (R$ 8.690 por quarto, R$ 2.172/noite). Escolhida para o total: único 5★ das três, à beira do rio, por R$ 3.980 a mais que o Mercure.</t>
+          <t>Cotação de 21/09: '2x Superior Room 13.400' — lido como R$ 13.400 pelos 2 quartos (R$ 6.700 por quarto, R$ 1.675/noite). Se for por quarto, o total é R$ 26.800. Confirmar. Com café da manhã.</t>
         </is>
       </c>
     </row>
@@ -1705,17 +1695,17 @@
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>Viena · Opção 1 · Steigenberger Icon Herrenhof 5★</t>
+          <t>Budapeste · Opção 3 · InterContinental Budapest 5★</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
         <is>
-          <t>Herrengasse, Innere Stadt, a 5 min do Hofburg · 1 Junior Suite + 1 Superior Room · café da manhã · 4 noites</t>
+          <t>Margem do Danúbio, vista para o Castelo e a Ponte das Correntes · 2 quartos Classic · café da manhã · 4 noites</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">
         <is>
-          <t>03/01 → 07/01</t>
+          <t>30/12 → 03/01</t>
         </is>
       </c>
       <c r="F12" s="23" t="n">
@@ -1732,10 +1722,10 @@
         </is>
       </c>
       <c r="I12" s="26" t="n">
-        <v>5910</v>
+        <v>8690</v>
       </c>
       <c r="J12" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K12" s="27">
         <f>IF(I12="","",I12*J12)</f>
@@ -1743,7 +1733,7 @@
       </c>
       <c r="L12" s="28" t="inlineStr">
         <is>
-          <t>Booking 20/09: € 1.862 (≈ R$ 11.004) por 2 quartos standard/4 noites no mesmo hotel</t>
+          <t>Booking 20/09: € 2.398 (≈ R$ 14.172) pelos 2 quartos/4 noites no mesmo hotel, tarifa mais barata</t>
         </is>
       </c>
       <c r="M12" s="25" t="inlineStr">
@@ -1762,7 +1752,7 @@
       </c>
       <c r="P12" s="30" t="inlineStr">
         <is>
-          <t>Cotação de 21/09: Junior Suite R$ 15.300 + Superior Room R$ 8.340 = R$ 23.640 pelas 4 noites (R$ 5.910/noite). A Junior Suite custa quase o dobro do Superior: perguntar ao consolidador se ela comporta 3 pessoas (sofá-cama) — se sim, resolve o filho a partir de 05/01 e a linha de cama extra sai. Pedir também o preço com 2 Superior.</t>
+          <t>Cotação de 21/09: '2x Classic Room 17.380' — R$ 17.380 pelos 2 quartos (R$ 8.690 por quarto, R$ 2.172/noite). Escolhida para o total: único 5★ das três, à beira do rio, por R$ 3.980 a mais que o Mercure.</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1767,12 @@
       </c>
       <c r="C13" s="24" t="inlineStr">
         <is>
-          <t>Viena · Opção 2 · Radisson Blu Style Hotel 5★</t>
+          <t>Viena · Opção 1 · Steigenberger Icon Herrenhof 5★</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
         <is>
-          <t>Herrengasse 12, Innere Stadt, design, a 3 min do Hofburg · 1 Junior Suite + 1 Superior Room · café da manhã · 4 noites</t>
+          <t>Herrengasse, Innere Stadt, a 5 min do Hofburg · 1 Junior Suite + 1 Superior Room · café da manhã · 4 noites</t>
         </is>
       </c>
       <c r="E13" s="23" t="inlineStr">
@@ -1804,7 +1794,7 @@
         </is>
       </c>
       <c r="I13" s="26" t="n">
-        <v>4768</v>
+        <v>5910</v>
       </c>
       <c r="J13" s="25" t="n">
         <v>4</v>
@@ -1815,12 +1805,12 @@
       </c>
       <c r="L13" s="28" t="inlineStr">
         <is>
-          <t>Booking 20/09: R$ 12.034 por 2 quartos standard/4 noites no mesmo hotel</t>
+          <t>Booking 20/09: € 1.862 (≈ R$ 11.004) por 2 quartos standard/4 noites no mesmo hotel</t>
         </is>
       </c>
       <c r="M13" s="25" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="N13" s="29">
@@ -1834,7 +1824,7 @@
       </c>
       <c r="P13" s="30" t="inlineStr">
         <is>
-          <t>Cotação de 21/09: Junior Suite R$ 11.042 + Superior Room R$ 8.030 = R$ 19.072 pelas 4 noites (R$ 4.768/noite). R$ 4.568 mais barato que o Herrenhof na mesma configuração e na mesma rua. Mesma pergunta: a Junior Suite comporta 3?</t>
+          <t>Cotação de 21/09: Junior Suite R$ 15.300 + Superior Room R$ 8.340 = R$ 23.640 pelas 4 noites (R$ 5.910/noite). Junior Suite comporta 3: pais + filho a partir de 05/01, filhas no Superior. Sem cama extra.</t>
         </is>
       </c>
     </row>
@@ -1849,40 +1839,50 @@
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>Viena · cama extra ou 3º quarto para o filho</t>
+          <t>Viena · Opção 2 · Radisson Blu Style Hotel 5★</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
         <is>
-          <t>2 noites, a partir da chegada em 05/01, no hotel escolhido</t>
+          <t>Herrengasse 12, Innere Stadt, design, a 3 min do Hofburg · 1 Junior Suite + 1 Superior Room · café da manhã · 4 noites</t>
         </is>
       </c>
       <c r="E14" s="23" t="inlineStr">
         <is>
-          <t>05/01 → 07/01</t>
+          <t>03/01 → 07/01</t>
         </is>
       </c>
       <c r="F14" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="25" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G14" s="25" t="inlineStr">
+        <is>
+          <t>Consolidador (a nomear)</t>
+        </is>
+      </c>
       <c r="H14" s="25" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="I14" s="26" t="n"/>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="I14" s="26" t="n">
+        <v>4768</v>
+      </c>
       <c r="J14" s="25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K14" s="27">
         <f>IF(I14="","",I14*J14)</f>
         <v/>
       </c>
-      <c r="L14" s="28" t="inlineStr"/>
+      <c r="L14" s="28" t="inlineStr">
+        <is>
+          <t>Booking 20/09: R$ 12.034 por 2 quartos standard/4 noites no mesmo hotel</t>
+        </is>
+      </c>
       <c r="M14" s="25" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="N14" s="29">
@@ -1891,12 +1891,12 @@
       </c>
       <c r="O14" s="25" t="inlineStr">
         <is>
-          <t>A cotar</t>
+          <t>Cotado</t>
         </is>
       </c>
       <c r="P14" s="30" t="inlineStr">
         <is>
-          <t>Valor unitário = diária. Se o hotel oferecer triplo, ajustar a Opção escolhida em vez desta linha.</t>
+          <t>Cotação de 21/09: Junior Suite R$ 11.042 + Superior Room R$ 8.030 = R$ 19.072 pelas 4 noites (R$ 4.768/noite). Junior Suite comporta 3. R$ 4.568 mais barato que o Herrenhof, na mesma rua.</t>
         </is>
       </c>
     </row>
@@ -1911,50 +1911,40 @@
       </c>
       <c r="C15" s="24" t="inlineStr">
         <is>
-          <t>Praga · Opção 1 · The Emblem Prague Hotel 5★</t>
+          <t>Viena · cama extra ou 3º quarto para o filho</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
         <is>
-          <t>Platnéřská, Cidade Velha, a 2 min da Praça da Cidade Velha, spa na cobertura · 1 Suite Pretender + 1 Queen Room · café da manhã · 3 noites</t>
+          <t>2 noites, a partir da chegada em 05/01, no hotel escolhido</t>
         </is>
       </c>
       <c r="E15" s="23" t="inlineStr">
         <is>
-          <t>07/01 → 10/01</t>
+          <t>05/01 → 07/01</t>
         </is>
       </c>
       <c r="F15" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="G15" s="25" t="inlineStr">
-        <is>
-          <t>Consolidador (a nomear)</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G15" s="25" t="inlineStr"/>
       <c r="H15" s="25" t="inlineStr">
         <is>
-          <t>BRL</t>
-        </is>
-      </c>
-      <c r="I15" s="26" t="n">
-        <v>3335</v>
-      </c>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I15" s="26" t="n"/>
       <c r="J15" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K15" s="27">
         <f>IF(I15="","",I15*J15)</f>
         <v/>
       </c>
-      <c r="L15" s="28" t="inlineStr">
-        <is>
-          <t>Booking 20/09, outros hotéis: Art Nouveau Palace 5★ € 812 · Hilton Old Town 5★ € 1.041 por 2 quartos/3 noites (5 pax)</t>
-        </is>
-      </c>
+      <c r="L15" s="28" t="inlineStr"/>
       <c r="M15" s="25" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="N15" s="29">
@@ -1963,12 +1953,12 @@
       </c>
       <c r="O15" s="25" t="inlineStr">
         <is>
-          <t>Cotado</t>
+          <t>Descartado</t>
         </is>
       </c>
       <c r="P15" s="30" t="inlineStr">
         <is>
-          <t>Cotação de 21/09: Suite Pretender R$ 5.680 + Queen Room R$ 4.325 = R$ 10.005 pelas 3 noites (R$ 3.335/noite). Escolhida para o total: boutique 5★ no coração da Cidade Velha, R$ 1.980 acima da Opção 2. Confirmar que a suíte comporta 3 (pais + filho).</t>
+          <t>Desnecessária: a Junior Suite das duas opções comporta o filho.</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1973,12 @@
       </c>
       <c r="C16" s="24" t="inlineStr">
         <is>
-          <t>Praga · Opção 2 · Century Old Town Prague, MGallery 4★</t>
+          <t>Praga · Opção 1 · The Emblem Prague Hotel 5★</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
         <is>
-          <t>Na Poříčí, prédio onde Kafka trabalhou, a 8 min da Praça da Cidade Velha · 1 Executive + 1 Classic Room · café da manhã · 3 noites</t>
+          <t>Platnéřská, Cidade Velha, a 2 min da Praça da Cidade Velha, spa na cobertura · 1 Suite Pretender + 1 Queen Room · café da manhã · 3 noites</t>
         </is>
       </c>
       <c r="E16" s="23" t="inlineStr">
@@ -2010,7 +2000,7 @@
         </is>
       </c>
       <c r="I16" s="26" t="n">
-        <v>2675</v>
+        <v>3335</v>
       </c>
       <c r="J16" s="25" t="n">
         <v>3</v>
@@ -2019,10 +2009,14 @@
         <f>IF(I16="","",I16*J16)</f>
         <v/>
       </c>
-      <c r="L16" s="28" t="n"/>
+      <c r="L16" s="28" t="inlineStr">
+        <is>
+          <t>Booking 20/09, outros hotéis: Art Nouveau Palace 5★ € 812 · Hilton Old Town 5★ € 1.041 por 2 quartos/3 noites (5 pax)</t>
+        </is>
+      </c>
       <c r="M16" s="25" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="N16" s="29">
@@ -2036,7 +2030,7 @@
       </c>
       <c r="P16" s="30" t="inlineStr">
         <is>
-          <t>Cotação de 21/09: Executive R$ 4.645 + Classic R$ 3.380 = R$ 8.025 pelas 3 noites (R$ 2.675/noite).</t>
+          <t>Cotação de 21/09: Suite Pretender R$ 5.680 + Queen Room R$ 4.325 = R$ 10.005 pelas 3 noites (R$ 3.335/noite). Suíte comporta 3. Escolhida para o total: boutique 5★ no coração da Cidade Velha, R$ 1.980 acima da Opção 2.</t>
         </is>
       </c>
     </row>
@@ -2051,44 +2045,46 @@
       </c>
       <c r="C17" s="24" t="inlineStr">
         <is>
-          <t>Paris · Opção 1 · Castille Paris 5★</t>
+          <t>Praga · Opção 2 · Century Old Town Prague, MGallery 4★</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
         <is>
-          <t>Rue Cambon, 1º arr., entre Louvre e Madeleine · 2 quartos (5 pax) · café · 2 noites</t>
+          <t>Na Poříčí, prédio onde Kafka trabalhou, a 8 min da Praça da Cidade Velha · 1 Executive + 1 Classic Room · café da manhã · 3 noites</t>
         </is>
       </c>
       <c r="E17" s="23" t="inlineStr">
         <is>
-          <t>10/01 → 12/01</t>
+          <t>07/01 → 10/01</t>
         </is>
       </c>
       <c r="F17" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="G17" s="25" t="inlineStr"/>
+      <c r="G17" s="25" t="inlineStr">
+        <is>
+          <t>Consolidador (a nomear)</t>
+        </is>
+      </c>
       <c r="H17" s="25" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="I17" s="26" t="n"/>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="I17" s="26" t="n">
+        <v>2675</v>
+      </c>
       <c r="J17" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K17" s="27">
         <f>IF(I17="","",I17*J17)</f>
         <v/>
       </c>
-      <c r="L17" s="28" t="inlineStr">
-        <is>
-          <t>€ 1.509 · 2 noites · 2 quartos · 3 adultos + 2 crianças</t>
-        </is>
-      </c>
+      <c r="L17" s="28" t="n"/>
       <c r="M17" s="25" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="N17" s="29">
@@ -2097,12 +2093,12 @@
       </c>
       <c r="O17" s="25" t="inlineStr">
         <is>
-          <t>A cotar</t>
+          <t>Cotado</t>
         </is>
       </c>
       <c r="P17" s="30" t="inlineStr">
         <is>
-          <t>Valor unitário = diária dos 2 quartos somados.</t>
+          <t>Cotação de 21/09: Executive R$ 4.645 + Classic R$ 3.380 = R$ 8.025 pelas 3 noites (R$ 2.675/noite). Suíte comporta 3.</t>
         </is>
       </c>
     </row>
@@ -2117,12 +2113,12 @@
       </c>
       <c r="C18" s="24" t="inlineStr">
         <is>
-          <t>Paris · Opção 2 · Hôtel Napoleon Paris 5★</t>
+          <t>Paris · Opção 1 · Castille Paris 5★</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
         <is>
-          <t>Av. de Friedland, 8º arr., a 100 m do Arco do Triunfo · 2 quartos (5 pax) · café · 2 noites</t>
+          <t>Rue Cambon, 1º arr., entre Louvre e Madeleine · 2 quartos (5 pax) · café · 2 noites</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">
@@ -2149,12 +2145,12 @@
       </c>
       <c r="L18" s="28" t="inlineStr">
         <is>
-          <t>€ 1.593 · 2 noites · 2 quartos · 3 adultos + 2 crianças</t>
+          <t>€ 1.509 · 2 noites · 2 quartos · 3 adultos + 2 crianças</t>
         </is>
       </c>
       <c r="M18" s="25" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="N18" s="29">
@@ -2166,7 +2162,11 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P18" s="30" t="inlineStr"/>
+      <c r="P18" s="30" t="inlineStr">
+        <is>
+          <t>Valor unitário = diária dos 2 quartos somados.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="23" t="n">
@@ -2174,51 +2174,49 @@
       </c>
       <c r="B19" s="23" t="inlineStr">
         <is>
-          <t>Trem</t>
+          <t>Hotel</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
         <is>
-          <t>Railjet Budapeste → Viena · 4 pax</t>
+          <t>Paris · Opção 2 · Hôtel Napoleon Paris 5★</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
         <is>
-          <t>ÖBB RJX 62 · Budapest-Keleti 09:30 → Wien Hbf 12:20 · 2h50 · direto · assentos marcados</t>
+          <t>Av. de Friedland, 8º arr., a 100 m do Arco do Triunfo · 2 quartos (5 pax) · café · 2 noites</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
         <is>
-          <t>03/01</t>
+          <t>10/01 → 12/01</t>
         </is>
       </c>
       <c r="F19" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="G19" s="25" t="inlineStr">
-        <is>
-          <t>Consolidador (a nomear)</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="G19" s="25" t="inlineStr"/>
       <c r="H19" s="25" t="inlineStr">
         <is>
-          <t>BRL</t>
-        </is>
-      </c>
-      <c r="I19" s="26" t="n">
-        <v>302.5</v>
-      </c>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I19" s="26" t="n"/>
       <c r="J19" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K19" s="27">
         <f>IF(I19="","",I19*J19)</f>
         <v/>
       </c>
-      <c r="L19" s="28" t="inlineStr"/>
+      <c r="L19" s="28" t="inlineStr">
+        <is>
+          <t>€ 1.593 · 2 noites · 2 quartos · 3 adultos + 2 crianças</t>
+        </is>
+      </c>
       <c r="M19" s="25" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="N19" s="29">
@@ -2227,14 +2225,10 @@
       </c>
       <c r="O19" s="25" t="inlineStr">
         <is>
-          <t>Cotado</t>
-        </is>
-      </c>
-      <c r="P19" s="30" t="inlineStr">
-        <is>
-          <t>Cotação de 21/09: R$ 1.210 para 4 pax (R$ 302,50/pax). Confirmar classe (1ª ou 2ª) e se a tarifa permite alteração.</t>
-        </is>
-      </c>
+          <t>A cotar</t>
+        </is>
+      </c>
+      <c r="P19" s="30" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="23" t="n">
@@ -2247,21 +2241,21 @@
       </c>
       <c r="C20" s="24" t="inlineStr">
         <is>
-          <t>Railjet Viena → Praga · 5 pax</t>
+          <t>Railjet Budapeste → Viena · 4 pax</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
         <is>
-          <t>ÖBB RJ 252 · Wien Hbf 11:10 → Praha hlavní nádraží 15:23 · 4h13 · direto · assentos marcados</t>
+          <t>ÖBB RJX 62 · Budapest-Keleti 09:30 → Wien Hbf 12:20 · 2h50 · direto · 1ª classe · assentos marcados</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
         <is>
-          <t>07/01</t>
+          <t>03/01</t>
         </is>
       </c>
       <c r="F20" s="23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G20" s="25" t="inlineStr">
         <is>
@@ -2274,10 +2268,10 @@
         </is>
       </c>
       <c r="I20" s="26" t="n">
-        <v>381</v>
+        <v>302.5</v>
       </c>
       <c r="J20" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K20" s="27">
         <f>IF(I20="","",I20*J20)</f>
@@ -2300,7 +2294,7 @@
       </c>
       <c r="P20" s="30" t="inlineStr">
         <is>
-          <t>Cotação de 21/09: R$ 1.905 para 5 pax (R$ 381/pax). Confirmar classe (1ª ou 2ª) e se a tarifa permite alteração.</t>
+          <t>Cotação de 21/09: R$ 1.210 para 4 pax (R$ 302,50/pax), 1ª classe.</t>
         </is>
       </c>
     </row>
@@ -2310,36 +2304,42 @@
       </c>
       <c r="B21" s="23" t="inlineStr">
         <is>
-          <t>Transfer</t>
+          <t>Trem</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
         <is>
-          <t>Budapeste · aeroporto → hotel · 4 pax</t>
+          <t>Railjet Viena → Praga · 5 pax</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
         <is>
-          <t>Van privativa com recepção no desembarque</t>
+          <t>ÖBB RJ 252 · Wien Hbf 11:10 → Praha hlavní nádraží 15:23 · 4h13 · direto · 1ª classe · assentos marcados</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
         <is>
-          <t>30/12</t>
+          <t>07/01</t>
         </is>
       </c>
       <c r="F21" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="G21" s="25" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="G21" s="25" t="inlineStr">
+        <is>
+          <t>Consolidador (a nomear)</t>
+        </is>
+      </c>
       <c r="H21" s="25" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="I21" s="26" t="n"/>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="I21" s="26" t="n">
+        <v>381</v>
+      </c>
       <c r="J21" s="25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K21" s="27">
         <f>IF(I21="","",I21*J21)</f>
@@ -2357,12 +2357,12 @@
       </c>
       <c r="O21" s="25" t="inlineStr">
         <is>
-          <t>A cotar</t>
+          <t>Cotado</t>
         </is>
       </c>
       <c r="P21" s="30" t="inlineStr">
         <is>
-          <t>Valor unitário = por veículo.</t>
+          <t>Cotação de 21/09: R$ 1.905 para 5 pax (R$ 381/pax), 1ª classe.</t>
         </is>
       </c>
     </row>
@@ -2377,17 +2377,17 @@
       </c>
       <c r="C22" s="24" t="inlineStr">
         <is>
-          <t>Budapeste · hotel → estação Keleti · 4 pax</t>
+          <t>Budapeste · aeroporto → hotel · 4 pax</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
         <is>
-          <t>Carro ou van privativa</t>
+          <t>Van privativa com recepção no desembarque</t>
         </is>
       </c>
       <c r="E22" s="23" t="inlineStr">
         <is>
-          <t>03/01</t>
+          <t>30/12</t>
         </is>
       </c>
       <c r="F22" s="23" t="n">
@@ -2422,7 +2422,11 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P22" s="30" t="inlineStr"/>
+      <c r="P22" s="30" t="inlineStr">
+        <is>
+          <t>Valor unitário = por veículo.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="23" t="n">
@@ -2435,7 +2439,7 @@
       </c>
       <c r="C23" s="24" t="inlineStr">
         <is>
-          <t>Viena · estação Hbf → hotel · 4 pax</t>
+          <t>Budapeste · hotel → estação Keleti · 4 pax</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
@@ -2493,21 +2497,21 @@
       </c>
       <c r="C24" s="24" t="inlineStr">
         <is>
-          <t>Viena · aeroporto → hotel · filho · 1 pax</t>
+          <t>Viena · estação Hbf → hotel · 4 pax</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
         <is>
-          <t>Motorista com placa no desembarque · reforçar: menor viajando só</t>
+          <t>Carro ou van privativa</t>
         </is>
       </c>
       <c r="E24" s="23" t="inlineStr">
         <is>
-          <t>05/01</t>
+          <t>03/01</t>
         </is>
       </c>
       <c r="F24" s="23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G24" s="25" t="inlineStr"/>
       <c r="H24" s="25" t="inlineStr">
@@ -2551,21 +2555,21 @@
       </c>
       <c r="C25" s="24" t="inlineStr">
         <is>
-          <t>Viena · hotel → estação Hbf · 5 pax</t>
+          <t>Viena · aeroporto → hotel · filho · 1 pax</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
         <is>
-          <t>Van privativa</t>
+          <t>Motorista com placa no desembarque · reforçar: menor viajando só</t>
         </is>
       </c>
       <c r="E25" s="23" t="inlineStr">
         <is>
-          <t>07/01</t>
+          <t>05/01</t>
         </is>
       </c>
       <c r="F25" s="23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G25" s="25" t="inlineStr"/>
       <c r="H25" s="25" t="inlineStr">
@@ -2609,7 +2613,7 @@
       </c>
       <c r="C26" s="24" t="inlineStr">
         <is>
-          <t>Praga · estação hl.n. → hotel · 5 pax</t>
+          <t>Viena · hotel → estação Hbf · 5 pax</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
@@ -2667,7 +2671,7 @@
       </c>
       <c r="C27" s="24" t="inlineStr">
         <is>
-          <t>Praga · hotel → aeroporto · 5 pax</t>
+          <t>Praga · estação hl.n. → hotel · 5 pax</t>
         </is>
       </c>
       <c r="D27" s="23" t="inlineStr">
@@ -2677,7 +2681,7 @@
       </c>
       <c r="E27" s="23" t="inlineStr">
         <is>
-          <t>10/01</t>
+          <t>07/01</t>
         </is>
       </c>
       <c r="F27" s="23" t="n">
@@ -2725,7 +2729,7 @@
       </c>
       <c r="C28" s="24" t="inlineStr">
         <is>
-          <t>Paris · CDG → hotel · 5 pax</t>
+          <t>Praga · hotel → aeroporto · 5 pax</t>
         </is>
       </c>
       <c r="D28" s="23" t="inlineStr">
@@ -2783,7 +2787,7 @@
       </c>
       <c r="C29" s="24" t="inlineStr">
         <is>
-          <t>Paris · hotel → CDG · 5 pax</t>
+          <t>Paris · CDG → hotel · 5 pax</t>
         </is>
       </c>
       <c r="D29" s="23" t="inlineStr">
@@ -2793,7 +2797,7 @@
       </c>
       <c r="E29" s="23" t="inlineStr">
         <is>
-          <t>12/01</t>
+          <t>10/01</t>
         </is>
       </c>
       <c r="F29" s="23" t="n">
@@ -2836,52 +2840,42 @@
       </c>
       <c r="B30" s="23" t="inlineStr">
         <is>
-          <t>Experiência</t>
+          <t>Transfer</t>
         </is>
       </c>
       <c r="C30" s="24" t="inlineStr">
         <is>
-          <t>Réveillon · Opção 1 · Silverline · jantar de gala em catamarã · 4 pax</t>
+          <t>Paris · hotel → CDG · 5 pax</t>
         </is>
       </c>
       <c r="D30" s="23" t="inlineStr">
         <is>
-          <t>Cais 11, Ponte Elisabeth · welcome cocktail, jantar de 5 pratos, espumante, show de piano · passa pelo Parlamento iluminado, brinde e fogos à meia-noite</t>
+          <t>Van privativa</t>
         </is>
       </c>
       <c r="E30" s="23" t="inlineStr">
         <is>
-          <t>31/12</t>
+          <t>12/01</t>
         </is>
       </c>
       <c r="F30" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="G30" s="25" t="inlineStr">
-        <is>
-          <t>Silverline Cruises</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="G30" s="25" t="inlineStr"/>
       <c r="H30" s="25" t="inlineStr">
         <is>
-          <t>BRL</t>
-        </is>
-      </c>
-      <c r="I30" s="26" t="n">
-        <v>1092.24</v>
-      </c>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I30" s="26" t="n"/>
       <c r="J30" s="25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K30" s="27">
         <f>IF(I30="","",I30*J30)</f>
         <v/>
       </c>
-      <c r="L30" s="28" t="inlineStr">
-        <is>
-          <t>silver-line.hu/product/budapest-new-years-eve-dinner-cruise</t>
-        </is>
-      </c>
+      <c r="L30" s="28" t="inlineStr"/>
       <c r="M30" s="25" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2893,14 +2887,10 @@
       </c>
       <c r="O30" s="25" t="inlineStr">
         <is>
-          <t>Cotado</t>
-        </is>
-      </c>
-      <c r="P30" s="30" t="inlineStr">
-        <is>
-          <t>Valor por pessoa do pacote de bebidas básico (o site tem pacotes até quase o dobro). Preço de criança e horário de embarque a confirmar na página.</t>
-        </is>
-      </c>
+          <t>A cotar</t>
+        </is>
+      </c>
+      <c r="P30" s="30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="23" t="n">
@@ -2913,12 +2903,12 @@
       </c>
       <c r="C31" s="24" t="inlineStr">
         <is>
-          <t>Réveillon · Opção 2 · Budapest River Cruise · NYE Party Cruise · 4 pax</t>
+          <t>Réveillon · Opção 1 · Silverline · jantar de gala em catamarã · 4 pax</t>
         </is>
       </c>
       <c r="D31" s="23" t="inlineStr">
         <is>
-          <t>Cais 8/8A, Ponte Elisabeth · embarque 19h, retorno 1h · jantar, música ao vivo e virada a bordo</t>
+          <t>Cais 11, Ponte Elisabeth · welcome cocktail, jantar de 5 pratos, espumante, show de piano · passa pelo Parlamento iluminado, brinde e fogos à meia-noite</t>
         </is>
       </c>
       <c r="E31" s="23" t="inlineStr">
@@ -2931,7 +2921,7 @@
       </c>
       <c r="G31" s="25" t="inlineStr">
         <is>
-          <t>Budapest River Cruise</t>
+          <t>Silverline Cruises</t>
         </is>
       </c>
       <c r="H31" s="25" t="inlineStr">
@@ -2940,7 +2930,7 @@
         </is>
       </c>
       <c r="I31" s="26" t="n">
-        <v>2272.86</v>
+        <v>1092.24</v>
       </c>
       <c r="J31" s="25" t="n">
         <v>4</v>
@@ -2951,12 +2941,12 @@
       </c>
       <c r="L31" s="28" t="inlineStr">
         <is>
-          <t>budapestrivercruise.com/budapest-new-years-eve-cruise-party</t>
+          <t>silver-line.hu/product/budapest-new-years-eve-dinner-cruise</t>
         </is>
       </c>
       <c r="M31" s="25" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="N31" s="29">
@@ -2970,7 +2960,7 @@
       </c>
       <c r="P31" s="30" t="inlineStr">
         <is>
-          <t>Valor por pessoa, 6 horas a bordo (19h à 1h). Mais que o dobro da Opção 1 por pessoa. Confirmar preço de menor e o que o jantar inclui.</t>
+          <t>Valor por pessoa do pacote de bebidas básico (o site tem pacotes até quase o dobro). Preço de criança e horário de embarque a confirmar na página.</t>
         </is>
       </c>
     </row>
@@ -2985,40 +2975,50 @@
       </c>
       <c r="C32" s="24" t="inlineStr">
         <is>
-          <t>Tokaj · motorista-guia privativo · dia inteiro · 4 pax</t>
+          <t>Réveillon · Opção 2 · Budapest River Cruise · NYE Party Cruise · 4 pax</t>
         </is>
       </c>
       <c r="D32" s="23" t="inlineStr">
         <is>
-          <t>Saída 8h de Budapeste, Oremus (Tolcsva) + segunda vinícola + almoço em Mád/Tarcal, retorno ~19h</t>
+          <t>Cais 8/8A, Ponte Elisabeth · embarque 19h, retorno 1h · jantar, música ao vivo e virada a bordo</t>
         </is>
       </c>
       <c r="E32" s="23" t="inlineStr">
         <is>
-          <t>02/01</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="F32" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="G32" s="25" t="inlineStr"/>
+      <c r="G32" s="25" t="inlineStr">
+        <is>
+          <t>Budapest River Cruise</t>
+        </is>
+      </c>
       <c r="H32" s="25" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="I32" s="26" t="n"/>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="I32" s="26" t="n">
+        <v>2272.86</v>
+      </c>
       <c r="J32" s="25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K32" s="27">
         <f>IF(I32="","",I32*J32)</f>
         <v/>
       </c>
-      <c r="L32" s="28" t="inlineStr"/>
+      <c r="L32" s="28" t="inlineStr">
+        <is>
+          <t>budapestrivercruise.com/budapest-new-years-eve-cruise-party</t>
+        </is>
+      </c>
       <c r="M32" s="25" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="N32" s="29">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="O32" s="25" t="inlineStr">
         <is>
-          <t>A cotar</t>
+          <t>Cotado</t>
         </is>
       </c>
       <c r="P32" s="30" t="inlineStr">
         <is>
-          <t>Valor unitário = por veículo/dia. Motorista não bebe: tolerância zero na Hungria.</t>
+          <t>Valor por pessoa, 6 horas a bordo (19h à 1h). Mais que o dobro da Opção 1 por pessoa. Confirmar preço de menor e o que o jantar inclui.</t>
         </is>
       </c>
     </row>
@@ -3047,12 +3047,12 @@
       </c>
       <c r="C33" s="24" t="inlineStr">
         <is>
-          <t>Oremus · visita à adega e prova · 2 adultos + 2 filhas</t>
+          <t>Tokaj · motorista-guia privativo · dia inteiro · 4 pax</t>
         </is>
       </c>
       <c r="D33" s="23" t="inlineStr">
         <is>
-          <t>Tolcsva · agendamento por e-mail · ~1h · adegas do século XIII · adolescentes acompanham sem álcool</t>
+          <t>Saída 8h de Budapeste, Oremus (Tolcsva) + segunda vinícola + almoço em Mád/Tarcal, retorno ~19h</t>
         </is>
       </c>
       <c r="E33" s="23" t="inlineStr">
@@ -3063,19 +3063,13 @@
       <c r="F33" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="G33" s="25" t="inlineStr">
-        <is>
-          <t>Tokaj-Oremus</t>
-        </is>
-      </c>
+      <c r="G33" s="25" t="inlineStr"/>
       <c r="H33" s="25" t="inlineStr">
         <is>
-          <t>BRL</t>
-        </is>
-      </c>
-      <c r="I33" s="26" t="n">
-        <v>315.67</v>
-      </c>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I33" s="26" t="n"/>
       <c r="J33" s="25" t="n">
         <v>1</v>
       </c>
@@ -3095,12 +3089,12 @@
       </c>
       <c r="O33" s="25" t="inlineStr">
         <is>
-          <t>Cotado</t>
+          <t>A cotar</t>
         </is>
       </c>
       <c r="P33" s="30" t="inlineStr">
         <is>
-          <t>Cotação de 21/09 em reais para a família (2 adultos e 2 filhas). Confirmar recepção no sábado 02/01; plano B: segunda 04/01.</t>
+          <t>Valor unitário = por veículo/dia. Motorista não bebe: tolerância zero na Hungria.</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3109,12 @@
       </c>
       <c r="C34" s="24" t="inlineStr">
         <is>
-          <t>Almoço em vinícola ou restaurante em Tokaj · 4 pax</t>
+          <t>Oremus · visita à adega e prova · 2 adultos + 2 filhas</t>
         </is>
       </c>
       <c r="D34" s="23" t="inlineStr">
         <is>
-          <t>Mád ou Tarcal</t>
+          <t>Tolcsva · agendamento por e-mail · ~1h · adegas do século XIII · adolescentes acompanham sem álcool</t>
         </is>
       </c>
       <c r="E34" s="23" t="inlineStr">
@@ -3131,15 +3125,21 @@
       <c r="F34" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="G34" s="25" t="inlineStr"/>
+      <c r="G34" s="25" t="inlineStr">
+        <is>
+          <t>Tokaj-Oremus</t>
+        </is>
+      </c>
       <c r="H34" s="25" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="I34" s="26" t="n"/>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="I34" s="26" t="n">
+        <v>315.67</v>
+      </c>
       <c r="J34" s="25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K34" s="27">
         <f>IF(I34="","",I34*J34)</f>
@@ -3157,12 +3157,12 @@
       </c>
       <c r="O34" s="25" t="inlineStr">
         <is>
-          <t>A cotar</t>
+          <t>Cotado</t>
         </is>
       </c>
       <c r="P34" s="30" t="inlineStr">
         <is>
-          <t>Pode vir incluído no pacote do motorista-guia.</t>
+          <t>Cotação de 21/09 em reais para a família (2 adultos e 2 filhas). Confirmar recepção no sábado 02/01; plano B: segunda 04/01.</t>
         </is>
       </c>
     </row>
@@ -3177,17 +3177,17 @@
       </c>
       <c r="C35" s="24" t="inlineStr">
         <is>
-          <t>Termas Széchenyi · 4 pax</t>
+          <t>Almoço em vinícola ou restaurante em Tokaj · 4 pax</t>
         </is>
       </c>
       <c r="D35" s="23" t="inlineStr">
         <is>
-          <t>Ingresso dia inteiro com cabine · aberto em 01/01</t>
+          <t>Mád ou Tarcal</t>
         </is>
       </c>
       <c r="E35" s="23" t="inlineStr">
         <is>
-          <t>01/01</t>
+          <t>02/01</t>
         </is>
       </c>
       <c r="F35" s="23" t="n">
@@ -3222,7 +3222,11 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P35" s="30" t="inlineStr"/>
+      <c r="P35" s="30" t="inlineStr">
+        <is>
+          <t>Pode vir incluído no pacote do motorista-guia.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="23" t="n">
@@ -3235,17 +3239,17 @@
       </c>
       <c r="C36" s="24" t="inlineStr">
         <is>
-          <t>Schönbrunn · Grand Tour · 4 pax</t>
+          <t>Termas Széchenyi · 4 pax</t>
         </is>
       </c>
       <c r="D36" s="23" t="inlineStr">
         <is>
-          <t>Entrada com hora marcada · mercado de Ano Novo no pátio até 06/01</t>
+          <t>Ingresso dia inteiro com cabine · aberto em 01/01</t>
         </is>
       </c>
       <c r="E36" s="23" t="inlineStr">
         <is>
-          <t>04/01</t>
+          <t>01/01</t>
         </is>
       </c>
       <c r="F36" s="23" t="n">
@@ -3293,12 +3297,12 @@
       </c>
       <c r="C37" s="24" t="inlineStr">
         <is>
-          <t>Concerto Orquestra do Hofburg ou Musikverein · 4 pax</t>
+          <t>Schönbrunn · Grand Tour · 4 pax</t>
         </is>
       </c>
       <c r="D37" s="23" t="inlineStr">
         <is>
-          <t>Strauss e Mozart · categoria de assento a definir</t>
+          <t>Entrada com hora marcada · mercado de Ano Novo no pátio até 06/01</t>
         </is>
       </c>
       <c r="E37" s="23" t="inlineStr">
@@ -3338,11 +3342,7 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P37" s="30" t="inlineStr">
-        <is>
-          <t>Concerto de Ano Novo da Filarmônica (01/01) é por sorteio já encerrado.</t>
-        </is>
-      </c>
+      <c r="P37" s="30" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="23" t="n">
@@ -3355,21 +3355,21 @@
       </c>
       <c r="C38" s="24" t="inlineStr">
         <is>
-          <t>Prater · Roda Gigante · 5 pax</t>
+          <t>Concerto Orquestra do Hofburg ou Musikverein · 4 pax</t>
         </is>
       </c>
       <c r="D38" s="23" t="inlineStr">
         <is>
-          <t>Ingresso · mercado de inverno na praça até 06/01</t>
+          <t>Strauss e Mozart · categoria de assento a definir</t>
         </is>
       </c>
       <c r="E38" s="23" t="inlineStr">
         <is>
-          <t>05/01</t>
+          <t>04/01</t>
         </is>
       </c>
       <c r="F38" s="23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G38" s="25" t="inlineStr"/>
       <c r="H38" s="25" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="I38" s="26" t="n"/>
       <c r="J38" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K38" s="27">
         <f>IF(I38="","",I38*J38)</f>
@@ -3400,7 +3400,11 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P38" s="30" t="inlineStr"/>
+      <c r="P38" s="30" t="inlineStr">
+        <is>
+          <t>Concerto de Ano Novo da Filarmônica (01/01) é por sorteio já encerrado.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="23" t="n">
@@ -3413,17 +3417,17 @@
       </c>
       <c r="C39" s="24" t="inlineStr">
         <is>
-          <t>Belvedere Superior · 5 pax</t>
+          <t>Prater · Roda Gigante · 5 pax</t>
         </is>
       </c>
       <c r="D39" s="23" t="inlineStr">
         <is>
-          <t>Ingresso · O Beijo de Klimt</t>
+          <t>Ingresso · mercado de inverno na praça até 06/01</t>
         </is>
       </c>
       <c r="E39" s="23" t="inlineStr">
         <is>
-          <t>06/01</t>
+          <t>05/01</t>
         </is>
       </c>
       <c r="F39" s="23" t="n">
@@ -3471,12 +3475,12 @@
       </c>
       <c r="C40" s="24" t="inlineStr">
         <is>
-          <t>Opcional · Ópera Estatal de Viena · 5 pax</t>
+          <t>Belvedere Superior · 5 pax</t>
         </is>
       </c>
       <c r="D40" s="23" t="inlineStr">
         <is>
-          <t>Récita da noite · verificar programa de 06/01</t>
+          <t>Ingresso · O Beijo de Klimt</t>
         </is>
       </c>
       <c r="E40" s="23" t="inlineStr">
@@ -3504,7 +3508,7 @@
       <c r="L40" s="28" t="inlineStr"/>
       <c r="M40" s="25" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="N40" s="29">
@@ -3516,11 +3520,7 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P40" s="30" t="inlineStr">
-        <is>
-          <t>Só entra se o cliente pedir.</t>
-        </is>
-      </c>
+      <c r="P40" s="30" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="23" t="n">
@@ -3533,17 +3533,17 @@
       </c>
       <c r="C41" s="24" t="inlineStr">
         <is>
-          <t>Castelo de Praga · circuito B · 5 pax</t>
+          <t>Opcional · Ópera Estatal de Viena · 5 pax</t>
         </is>
       </c>
       <c r="D41" s="23" t="inlineStr">
         <is>
-          <t>Catedral de São Vito, Palácio Real Antigo, Ruela Dourada</t>
+          <t>Récita da noite · verificar programa de 06/01</t>
         </is>
       </c>
       <c r="E41" s="23" t="inlineStr">
         <is>
-          <t>08/01</t>
+          <t>06/01</t>
         </is>
       </c>
       <c r="F41" s="23" t="n">
@@ -3566,7 +3566,7 @@
       <c r="L41" s="28" t="inlineStr"/>
       <c r="M41" s="25" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="N41" s="29">
@@ -3578,7 +3578,11 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P41" s="30" t="inlineStr"/>
+      <c r="P41" s="30" t="inlineStr">
+        <is>
+          <t>Só entra se o cliente pedir.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="23" t="n">
@@ -3591,12 +3595,12 @@
       </c>
       <c r="C42" s="24" t="inlineStr">
         <is>
-          <t>Teatro de luz negra · 5 pax</t>
+          <t>Castelo de Praga · circuito B · 5 pax</t>
         </is>
       </c>
       <c r="D42" s="23" t="inlineStr">
         <is>
-          <t>Sessão da noite</t>
+          <t>Catedral de São Vito, Palácio Real Antigo, Ruela Dourada</t>
         </is>
       </c>
       <c r="E42" s="23" t="inlineStr">
@@ -3649,17 +3653,17 @@
       </c>
       <c r="C43" s="24" t="inlineStr">
         <is>
-          <t>Torre Eiffel · topo · 5 pax</t>
+          <t>Teatro de luz negra · 5 pax</t>
         </is>
       </c>
       <c r="D43" s="23" t="inlineStr">
         <is>
-          <t>Entrada com hora marcada · abre venda 60 dias antes</t>
+          <t>Sessão da noite</t>
         </is>
       </c>
       <c r="E43" s="23" t="inlineStr">
         <is>
-          <t>10/01</t>
+          <t>08/01</t>
         </is>
       </c>
       <c r="F43" s="23" t="n">
@@ -3694,11 +3698,7 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P43" s="30" t="inlineStr">
-        <is>
-          <t>Reservar exatamente em 11/11 para garantir horário.</t>
-        </is>
-      </c>
+      <c r="P43" s="30" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="23" t="n">
@@ -3711,17 +3711,17 @@
       </c>
       <c r="C44" s="24" t="inlineStr">
         <is>
-          <t>Louvre · 5 pax</t>
+          <t>Torre Eiffel · topo · 5 pax</t>
         </is>
       </c>
       <c r="D44" s="23" t="inlineStr">
         <is>
-          <t>Entrada com hora marcada · menores de 18 gratuitos</t>
+          <t>Entrada com hora marcada · abre venda 60 dias antes</t>
         </is>
       </c>
       <c r="E44" s="23" t="inlineStr">
         <is>
-          <t>11/01</t>
+          <t>10/01</t>
         </is>
       </c>
       <c r="F44" s="23" t="n">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="I44" s="26" t="n"/>
       <c r="J44" s="25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K44" s="27">
         <f>IF(I44="","",I44*J44)</f>
@@ -3758,7 +3758,7 @@
       </c>
       <c r="P44" s="30" t="inlineStr">
         <is>
-          <t>Qtd = 2 adultos pagantes.</t>
+          <t>Reservar exatamente em 11/11 para garantir horário.</t>
         </is>
       </c>
     </row>
@@ -3773,12 +3773,12 @@
       </c>
       <c r="C45" s="24" t="inlineStr">
         <is>
-          <t>Cruzeiro no Sena com jantar · 5 pax</t>
+          <t>Louvre · 5 pax</t>
         </is>
       </c>
       <c r="D45" s="23" t="inlineStr">
         <is>
-          <t>Bateaux Parisiens ou Bateaux-Mouches · jantar da noite</t>
+          <t>Entrada com hora marcada · menores de 18 gratuitos</t>
         </is>
       </c>
       <c r="E45" s="23" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="I45" s="26" t="n"/>
       <c r="J45" s="25" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K45" s="27">
         <f>IF(I45="","",I45*J45)</f>
@@ -3818,7 +3818,11 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P45" s="30" t="inlineStr"/>
+      <c r="P45" s="30" t="inlineStr">
+        <is>
+          <t>Qtd = 2 adultos pagantes.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="23" t="n">
@@ -3826,22 +3830,22 @@
       </c>
       <c r="B46" s="23" t="inlineStr">
         <is>
-          <t>Seguro/Docs</t>
+          <t>Experiência</t>
         </is>
       </c>
       <c r="C46" s="24" t="inlineStr">
         <is>
-          <t>Seguro viagem · 5 pax · 15 dias</t>
+          <t>Cruzeiro no Sena com jantar · 5 pax</t>
         </is>
       </c>
       <c r="D46" s="23" t="inlineStr">
         <is>
-          <t>Cobertura médica mínima € 30.000 (Schengen) · bagagem · cancelamento</t>
+          <t>Bateaux Parisiens ou Bateaux-Mouches · jantar da noite</t>
         </is>
       </c>
       <c r="E46" s="23" t="inlineStr">
         <is>
-          <t>29/12 → 12/01</t>
+          <t>11/01</t>
         </is>
       </c>
       <c r="F46" s="23" t="n">
@@ -3850,7 +3854,7 @@
       <c r="G46" s="25" t="inlineStr"/>
       <c r="H46" s="25" t="inlineStr">
         <is>
-          <t>BRL</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="I46" s="26" t="n"/>
@@ -3876,114 +3880,135 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P46" s="30" t="inlineStr">
+      <c r="P46" s="30" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="23" t="n">
+        <v>43</v>
+      </c>
+      <c r="B47" s="23" t="inlineStr">
+        <is>
+          <t>Seguro/Docs</t>
+        </is>
+      </c>
+      <c r="C47" s="24" t="inlineStr">
+        <is>
+          <t>Seguro viagem · 5 pax · 15 dias</t>
+        </is>
+      </c>
+      <c r="D47" s="23" t="inlineStr">
+        <is>
+          <t>Cobertura médica mínima € 30.000 (Schengen) · bagagem · cancelamento</t>
+        </is>
+      </c>
+      <c r="E47" s="23" t="inlineStr">
+        <is>
+          <t>29/12 → 12/01</t>
+        </is>
+      </c>
+      <c r="F47" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="G47" s="25" t="inlineStr"/>
+      <c r="H47" s="25" t="inlineStr">
+        <is>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="I47" s="26" t="n"/>
+      <c r="J47" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="K47" s="27">
+        <f>IF(I47="","",I47*J47)</f>
+        <v/>
+      </c>
+      <c r="L47" s="28" t="inlineStr"/>
+      <c r="M47" s="25" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="N47" s="29">
+        <f>IF(OR(M47&lt;&gt;"Sim",I47=""),0,K47*IF(H47="BRL",1,IF(H47="EUR",Parâmetros!$B$4,IF(H47="USD",Parâmetros!$B$5,1))))</f>
+        <v/>
+      </c>
+      <c r="O47" s="25" t="inlineStr">
+        <is>
+          <t>A cotar</t>
+        </is>
+      </c>
+      <c r="P47" s="30" t="inlineStr">
         <is>
           <t>Valor unitário = por pessoa. Filho com vigência a partir de 04/01 pode sair mais barato.</t>
         </is>
       </c>
     </row>
-    <row r="47"/>
-    <row r="48">
-      <c r="C48" s="21" t="inlineStr">
+    <row r="48"/>
+    <row r="49">
+      <c r="C49" s="21" t="inlineStr">
         <is>
           <t>SUBTOTAL EM R$ (itens marcados como Sim)</t>
         </is>
       </c>
-      <c r="N48" s="31">
-        <f>SUM(N5:N46)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="C49" s="12" t="inlineStr">
+      <c r="N49" s="31">
+        <f>SUM(N5:N47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" s="12" t="inlineStr">
         <is>
           <t>Taxa de serviço LusaTravel</t>
         </is>
       </c>
-      <c r="N49" s="13">
-        <f>N48*Parâmetros!$B$10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="32" t="n"/>
-      <c r="B50" s="32" t="n"/>
-      <c r="C50" s="33" t="inlineStr">
+      <c r="N50" s="13">
+        <f>N49*Parâmetros!$B$10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="32" t="n"/>
+      <c r="B51" s="32" t="n"/>
+      <c r="C51" s="33" t="inlineStr">
         <is>
           <t>TOTAL PARA O CLIENTE</t>
         </is>
       </c>
-      <c r="D50" s="32" t="n"/>
-      <c r="E50" s="32" t="n"/>
-      <c r="F50" s="32" t="n"/>
-      <c r="G50" s="32" t="n"/>
-      <c r="H50" s="32" t="n"/>
-      <c r="I50" s="32" t="n"/>
-      <c r="J50" s="32" t="n"/>
-      <c r="K50" s="32" t="n"/>
-      <c r="L50" s="32" t="n"/>
-      <c r="M50" s="32" t="n"/>
-      <c r="N50" s="34">
-        <f>N48+N49</f>
-        <v/>
-      </c>
-      <c r="O50" s="32" t="n"/>
-      <c r="P50" s="32" t="n"/>
-    </row>
-    <row r="51">
-      <c r="C51" s="2" t="inlineStr">
+      <c r="D51" s="32" t="n"/>
+      <c r="E51" s="32" t="n"/>
+      <c r="F51" s="32" t="n"/>
+      <c r="G51" s="32" t="n"/>
+      <c r="H51" s="32" t="n"/>
+      <c r="I51" s="32" t="n"/>
+      <c r="J51" s="32" t="n"/>
+      <c r="K51" s="32" t="n"/>
+      <c r="L51" s="32" t="n"/>
+      <c r="M51" s="32" t="n"/>
+      <c r="N51" s="34">
+        <f>N49+N50</f>
+        <v/>
+      </c>
+      <c r="O51" s="32" t="n"/>
+      <c r="P51" s="32" t="n"/>
+    </row>
+    <row r="52">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>*Nada reservado, apenas cotado.</t>
         </is>
       </c>
     </row>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
   </sheetData>
-  <autoFilter ref="A4:P46"/>
+  <autoFilter ref="A4:P47"/>
   <dataValidations count="3">
-    <dataValidation sqref="O5:O46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O5:O47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"A cotar,Cotado,Aprovado pelo cliente,Reservado,Descartado"</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="M5:M47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="H5:H47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"BRL,EUR,USD"</formula1>
     </dataValidation>
   </dataValidations>

--- a/cotacao-cristofer-reveillon.xlsx
+++ b/cotacao-cristofer-reveillon.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Cotação" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Cotação'!$A$4:$P$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Cotação'!$A$4:$P$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -625,19 +625,19 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$47,A5)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$36,A5)</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$47,A5,Cotação!$O$5:$O$47,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$36,A5,Cotação!$O$5:$O$36,"A cotar")</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$47,A5,Cotação!$O$5:$O$47,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$36,A5,Cotação!$O$5:$O$36,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E5" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$47,A5,Cotação!$N$5:$N$47)</f>
+        <f>SUMIF(Cotação!$B$5:$B$36,A5,Cotação!$N$5:$N$36)</f>
         <v/>
       </c>
     </row>
@@ -648,19 +648,19 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$47,A6)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$36,A6)</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$47,A6,Cotação!$O$5:$O$47,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$36,A6,Cotação!$O$5:$O$36,"A cotar")</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$47,A6,Cotação!$O$5:$O$47,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$36,A6,Cotação!$O$5:$O$36,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E6" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$47,A6,Cotação!$N$5:$N$47)</f>
+        <f>SUMIF(Cotação!$B$5:$B$36,A6,Cotação!$N$5:$N$36)</f>
         <v/>
       </c>
     </row>
@@ -671,19 +671,19 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$47,A7)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$36,A7)</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$47,A7,Cotação!$O$5:$O$47,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$36,A7,Cotação!$O$5:$O$36,"A cotar")</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$47,A7,Cotação!$O$5:$O$47,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$36,A7,Cotação!$O$5:$O$36,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E7" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$47,A7,Cotação!$N$5:$N$47)</f>
+        <f>SUMIF(Cotação!$B$5:$B$36,A7,Cotação!$N$5:$N$36)</f>
         <v/>
       </c>
     </row>
@@ -694,19 +694,19 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$47,A8)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$36,A8)</f>
         <v/>
       </c>
       <c r="C8" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$47,A8,Cotação!$O$5:$O$47,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$36,A8,Cotação!$O$5:$O$36,"A cotar")</f>
         <v/>
       </c>
       <c r="D8" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$47,A8,Cotação!$O$5:$O$47,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$36,A8,Cotação!$O$5:$O$36,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E8" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$47,A8,Cotação!$N$5:$N$47)</f>
+        <f>SUMIF(Cotação!$B$5:$B$36,A8,Cotação!$N$5:$N$36)</f>
         <v/>
       </c>
     </row>
@@ -717,19 +717,19 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$47,A9)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$36,A9)</f>
         <v/>
       </c>
       <c r="C9" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$47,A9,Cotação!$O$5:$O$47,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$36,A9,Cotação!$O$5:$O$36,"A cotar")</f>
         <v/>
       </c>
       <c r="D9" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$47,A9,Cotação!$O$5:$O$47,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$36,A9,Cotação!$O$5:$O$36,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E9" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$47,A9,Cotação!$N$5:$N$47)</f>
+        <f>SUMIF(Cotação!$B$5:$B$36,A9,Cotação!$N$5:$N$36)</f>
         <v/>
       </c>
     </row>
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$47,A10)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$36,A10)</f>
         <v/>
       </c>
       <c r="C10" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$47,A10,Cotação!$O$5:$O$47,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$36,A10,Cotação!$O$5:$O$36,"A cotar")</f>
         <v/>
       </c>
       <c r="D10" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$47,A10,Cotação!$O$5:$O$47,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$36,A10,Cotação!$O$5:$O$36,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$47,A10,Cotação!$N$5:$N$47)</f>
+        <f>SUMIF(Cotação!$B$5:$B$36,A10,Cotação!$N$5:$N$36)</f>
         <v/>
       </c>
     </row>
@@ -763,19 +763,19 @@
         </is>
       </c>
       <c r="B11" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$47,A11)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$36,A11)</f>
         <v/>
       </c>
       <c r="C11" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$47,A11,Cotação!$O$5:$O$47,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$36,A11,Cotação!$O$5:$O$36,"A cotar")</f>
         <v/>
       </c>
       <c r="D11" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$47,A11,Cotação!$O$5:$O$47,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$36,A11,Cotação!$O$5:$O$36,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E11" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$47,A11,Cotação!$N$5:$N$47)</f>
+        <f>SUMIF(Cotação!$B$5:$B$36,A11,Cotação!$N$5:$N$36)</f>
         <v/>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P52"/>
+  <dimension ref="A1:P41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="D31" s="23" t="inlineStr">
         <is>
-          <t>Cais 11, Ponte Elisabeth · welcome cocktail, jantar de 5 pratos, espumante, show de piano · passa pelo Parlamento iluminado, brinde e fogos à meia-noite</t>
+          <t>Cais 11, Ponte Elisabeth · embarque 20h, retorno 1h · welcome cocktail, jantar de 5 pratos, espumante, show de piano · Parlamento iluminado, brinde e fogos à meia-noite</t>
         </is>
       </c>
       <c r="E31" s="23" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="P31" s="30" t="inlineStr">
         <is>
-          <t>Valor por pessoa do pacote de bebidas básico (o site tem pacotes até quase o dobro). Preço de criança e horário de embarque a confirmar na página.</t>
+          <t>Valor por pessoa. Confirmar na página o preço vigente para 31/12 e se há tarifa de menor.</t>
         </is>
       </c>
     </row>
@@ -3234,36 +3234,36 @@
       </c>
       <c r="B36" s="23" t="inlineStr">
         <is>
-          <t>Experiência</t>
+          <t>Seguro/Docs</t>
         </is>
       </c>
       <c r="C36" s="24" t="inlineStr">
         <is>
-          <t>Termas Széchenyi · 4 pax</t>
+          <t>Seguro viagem · 5 pax · 15 dias</t>
         </is>
       </c>
       <c r="D36" s="23" t="inlineStr">
         <is>
-          <t>Ingresso dia inteiro com cabine · aberto em 01/01</t>
+          <t>Cobertura médica mínima € 30.000 (Schengen) · bagagem · cancelamento</t>
         </is>
       </c>
       <c r="E36" s="23" t="inlineStr">
         <is>
-          <t>01/01</t>
+          <t>29/12 → 12/01</t>
         </is>
       </c>
       <c r="F36" s="23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G36" s="25" t="inlineStr"/>
       <c r="H36" s="25" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>BRL</t>
         </is>
       </c>
       <c r="I36" s="26" t="n"/>
       <c r="J36" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K36" s="27">
         <f>IF(I36="","",I36*J36)</f>
@@ -3284,731 +3284,77 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P36" s="30" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="23" t="n">
-        <v>33</v>
-      </c>
-      <c r="B37" s="23" t="inlineStr">
-        <is>
-          <t>Experiência</t>
-        </is>
-      </c>
-      <c r="C37" s="24" t="inlineStr">
-        <is>
-          <t>Schönbrunn · Grand Tour · 4 pax</t>
-        </is>
-      </c>
-      <c r="D37" s="23" t="inlineStr">
-        <is>
-          <t>Entrada com hora marcada · mercado de Ano Novo no pátio até 06/01</t>
-        </is>
-      </c>
-      <c r="E37" s="23" t="inlineStr">
-        <is>
-          <t>04/01</t>
-        </is>
-      </c>
-      <c r="F37" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="G37" s="25" t="inlineStr"/>
-      <c r="H37" s="25" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="I37" s="26" t="n"/>
-      <c r="J37" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="K37" s="27">
-        <f>IF(I37="","",I37*J37)</f>
-        <v/>
-      </c>
-      <c r="L37" s="28" t="inlineStr"/>
-      <c r="M37" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="N37" s="29">
-        <f>IF(OR(M37&lt;&gt;"Sim",I37=""),0,K37*IF(H37="BRL",1,IF(H37="EUR",Parâmetros!$B$4,IF(H37="USD",Parâmetros!$B$5,1))))</f>
-        <v/>
-      </c>
-      <c r="O37" s="25" t="inlineStr">
-        <is>
-          <t>A cotar</t>
-        </is>
-      </c>
-      <c r="P37" s="30" t="inlineStr"/>
-    </row>
+      <c r="P36" s="30" t="inlineStr">
+        <is>
+          <t>Valor unitário = por pessoa. Filho com vigência a partir de 04/01 pode sair mais barato.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
     <row r="38">
-      <c r="A38" s="23" t="n">
-        <v>34</v>
-      </c>
-      <c r="B38" s="23" t="inlineStr">
-        <is>
-          <t>Experiência</t>
-        </is>
-      </c>
-      <c r="C38" s="24" t="inlineStr">
-        <is>
-          <t>Concerto Orquestra do Hofburg ou Musikverein · 4 pax</t>
-        </is>
-      </c>
-      <c r="D38" s="23" t="inlineStr">
-        <is>
-          <t>Strauss e Mozart · categoria de assento a definir</t>
-        </is>
-      </c>
-      <c r="E38" s="23" t="inlineStr">
-        <is>
-          <t>04/01</t>
-        </is>
-      </c>
-      <c r="F38" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="G38" s="25" t="inlineStr"/>
-      <c r="H38" s="25" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="I38" s="26" t="n"/>
-      <c r="J38" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="K38" s="27">
-        <f>IF(I38="","",I38*J38)</f>
-        <v/>
-      </c>
-      <c r="L38" s="28" t="inlineStr"/>
-      <c r="M38" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="N38" s="29">
-        <f>IF(OR(M38&lt;&gt;"Sim",I38=""),0,K38*IF(H38="BRL",1,IF(H38="EUR",Parâmetros!$B$4,IF(H38="USD",Parâmetros!$B$5,1))))</f>
-        <v/>
-      </c>
-      <c r="O38" s="25" t="inlineStr">
-        <is>
-          <t>A cotar</t>
-        </is>
-      </c>
-      <c r="P38" s="30" t="inlineStr">
-        <is>
-          <t>Concerto de Ano Novo da Filarmônica (01/01) é por sorteio já encerrado.</t>
-        </is>
+      <c r="C38" s="21" t="inlineStr">
+        <is>
+          <t>SUBTOTAL EM R$ (itens marcados como Sim)</t>
+        </is>
+      </c>
+      <c r="N38" s="31">
+        <f>SUM(N5:N36)</f>
+        <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="23" t="n">
-        <v>35</v>
-      </c>
-      <c r="B39" s="23" t="inlineStr">
-        <is>
-          <t>Experiência</t>
-        </is>
-      </c>
-      <c r="C39" s="24" t="inlineStr">
-        <is>
-          <t>Prater · Roda Gigante · 5 pax</t>
-        </is>
-      </c>
-      <c r="D39" s="23" t="inlineStr">
-        <is>
-          <t>Ingresso · mercado de inverno na praça até 06/01</t>
-        </is>
-      </c>
-      <c r="E39" s="23" t="inlineStr">
-        <is>
-          <t>05/01</t>
-        </is>
-      </c>
-      <c r="F39" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="G39" s="25" t="inlineStr"/>
-      <c r="H39" s="25" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="I39" s="26" t="n"/>
-      <c r="J39" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="K39" s="27">
-        <f>IF(I39="","",I39*J39)</f>
-        <v/>
-      </c>
-      <c r="L39" s="28" t="inlineStr"/>
-      <c r="M39" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="N39" s="29">
-        <f>IF(OR(M39&lt;&gt;"Sim",I39=""),0,K39*IF(H39="BRL",1,IF(H39="EUR",Parâmetros!$B$4,IF(H39="USD",Parâmetros!$B$5,1))))</f>
-        <v/>
-      </c>
-      <c r="O39" s="25" t="inlineStr">
-        <is>
-          <t>A cotar</t>
-        </is>
-      </c>
-      <c r="P39" s="30" t="inlineStr"/>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>Taxa de serviço LusaTravel</t>
+        </is>
+      </c>
+      <c r="N39" s="13">
+        <f>N38*Parâmetros!$B$10</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="23" t="n">
-        <v>36</v>
-      </c>
-      <c r="B40" s="23" t="inlineStr">
-        <is>
-          <t>Experiência</t>
-        </is>
-      </c>
-      <c r="C40" s="24" t="inlineStr">
-        <is>
-          <t>Belvedere Superior · 5 pax</t>
-        </is>
-      </c>
-      <c r="D40" s="23" t="inlineStr">
-        <is>
-          <t>Ingresso · O Beijo de Klimt</t>
-        </is>
-      </c>
-      <c r="E40" s="23" t="inlineStr">
-        <is>
-          <t>06/01</t>
-        </is>
-      </c>
-      <c r="F40" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="G40" s="25" t="inlineStr"/>
-      <c r="H40" s="25" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="I40" s="26" t="n"/>
-      <c r="J40" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="K40" s="27">
-        <f>IF(I40="","",I40*J40)</f>
-        <v/>
-      </c>
-      <c r="L40" s="28" t="inlineStr"/>
-      <c r="M40" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="N40" s="29">
-        <f>IF(OR(M40&lt;&gt;"Sim",I40=""),0,K40*IF(H40="BRL",1,IF(H40="EUR",Parâmetros!$B$4,IF(H40="USD",Parâmetros!$B$5,1))))</f>
-        <v/>
-      </c>
-      <c r="O40" s="25" t="inlineStr">
-        <is>
-          <t>A cotar</t>
-        </is>
-      </c>
-      <c r="P40" s="30" t="inlineStr"/>
+      <c r="A40" s="32" t="n"/>
+      <c r="B40" s="32" t="n"/>
+      <c r="C40" s="33" t="inlineStr">
+        <is>
+          <t>TOTAL PARA O CLIENTE</t>
+        </is>
+      </c>
+      <c r="D40" s="32" t="n"/>
+      <c r="E40" s="32" t="n"/>
+      <c r="F40" s="32" t="n"/>
+      <c r="G40" s="32" t="n"/>
+      <c r="H40" s="32" t="n"/>
+      <c r="I40" s="32" t="n"/>
+      <c r="J40" s="32" t="n"/>
+      <c r="K40" s="32" t="n"/>
+      <c r="L40" s="32" t="n"/>
+      <c r="M40" s="32" t="n"/>
+      <c r="N40" s="34">
+        <f>N38+N39</f>
+        <v/>
+      </c>
+      <c r="O40" s="32" t="n"/>
+      <c r="P40" s="32" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="23" t="n">
-        <v>37</v>
-      </c>
-      <c r="B41" s="23" t="inlineStr">
-        <is>
-          <t>Experiência</t>
-        </is>
-      </c>
-      <c r="C41" s="24" t="inlineStr">
-        <is>
-          <t>Opcional · Ópera Estatal de Viena · 5 pax</t>
-        </is>
-      </c>
-      <c r="D41" s="23" t="inlineStr">
-        <is>
-          <t>Récita da noite · verificar programa de 06/01</t>
-        </is>
-      </c>
-      <c r="E41" s="23" t="inlineStr">
-        <is>
-          <t>06/01</t>
-        </is>
-      </c>
-      <c r="F41" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="G41" s="25" t="inlineStr"/>
-      <c r="H41" s="25" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="I41" s="26" t="n"/>
-      <c r="J41" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="K41" s="27">
-        <f>IF(I41="","",I41*J41)</f>
-        <v/>
-      </c>
-      <c r="L41" s="28" t="inlineStr"/>
-      <c r="M41" s="25" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="N41" s="29">
-        <f>IF(OR(M41&lt;&gt;"Sim",I41=""),0,K41*IF(H41="BRL",1,IF(H41="EUR",Parâmetros!$B$4,IF(H41="USD",Parâmetros!$B$5,1))))</f>
-        <v/>
-      </c>
-      <c r="O41" s="25" t="inlineStr">
-        <is>
-          <t>A cotar</t>
-        </is>
-      </c>
-      <c r="P41" s="30" t="inlineStr">
-        <is>
-          <t>Só entra se o cliente pedir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="23" t="n">
-        <v>38</v>
-      </c>
-      <c r="B42" s="23" t="inlineStr">
-        <is>
-          <t>Experiência</t>
-        </is>
-      </c>
-      <c r="C42" s="24" t="inlineStr">
-        <is>
-          <t>Castelo de Praga · circuito B · 5 pax</t>
-        </is>
-      </c>
-      <c r="D42" s="23" t="inlineStr">
-        <is>
-          <t>Catedral de São Vito, Palácio Real Antigo, Ruela Dourada</t>
-        </is>
-      </c>
-      <c r="E42" s="23" t="inlineStr">
-        <is>
-          <t>08/01</t>
-        </is>
-      </c>
-      <c r="F42" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="G42" s="25" t="inlineStr"/>
-      <c r="H42" s="25" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="I42" s="26" t="n"/>
-      <c r="J42" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="K42" s="27">
-        <f>IF(I42="","",I42*J42)</f>
-        <v/>
-      </c>
-      <c r="L42" s="28" t="inlineStr"/>
-      <c r="M42" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="N42" s="29">
-        <f>IF(OR(M42&lt;&gt;"Sim",I42=""),0,K42*IF(H42="BRL",1,IF(H42="EUR",Parâmetros!$B$4,IF(H42="USD",Parâmetros!$B$5,1))))</f>
-        <v/>
-      </c>
-      <c r="O42" s="25" t="inlineStr">
-        <is>
-          <t>A cotar</t>
-        </is>
-      </c>
-      <c r="P42" s="30" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="23" t="n">
-        <v>39</v>
-      </c>
-      <c r="B43" s="23" t="inlineStr">
-        <is>
-          <t>Experiência</t>
-        </is>
-      </c>
-      <c r="C43" s="24" t="inlineStr">
-        <is>
-          <t>Teatro de luz negra · 5 pax</t>
-        </is>
-      </c>
-      <c r="D43" s="23" t="inlineStr">
-        <is>
-          <t>Sessão da noite</t>
-        </is>
-      </c>
-      <c r="E43" s="23" t="inlineStr">
-        <is>
-          <t>08/01</t>
-        </is>
-      </c>
-      <c r="F43" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="G43" s="25" t="inlineStr"/>
-      <c r="H43" s="25" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="I43" s="26" t="n"/>
-      <c r="J43" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="K43" s="27">
-        <f>IF(I43="","",I43*J43)</f>
-        <v/>
-      </c>
-      <c r="L43" s="28" t="inlineStr"/>
-      <c r="M43" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="N43" s="29">
-        <f>IF(OR(M43&lt;&gt;"Sim",I43=""),0,K43*IF(H43="BRL",1,IF(H43="EUR",Parâmetros!$B$4,IF(H43="USD",Parâmetros!$B$5,1))))</f>
-        <v/>
-      </c>
-      <c r="O43" s="25" t="inlineStr">
-        <is>
-          <t>A cotar</t>
-        </is>
-      </c>
-      <c r="P43" s="30" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="23" t="n">
-        <v>40</v>
-      </c>
-      <c r="B44" s="23" t="inlineStr">
-        <is>
-          <t>Experiência</t>
-        </is>
-      </c>
-      <c r="C44" s="24" t="inlineStr">
-        <is>
-          <t>Torre Eiffel · topo · 5 pax</t>
-        </is>
-      </c>
-      <c r="D44" s="23" t="inlineStr">
-        <is>
-          <t>Entrada com hora marcada · abre venda 60 dias antes</t>
-        </is>
-      </c>
-      <c r="E44" s="23" t="inlineStr">
-        <is>
-          <t>10/01</t>
-        </is>
-      </c>
-      <c r="F44" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="G44" s="25" t="inlineStr"/>
-      <c r="H44" s="25" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="I44" s="26" t="n"/>
-      <c r="J44" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="K44" s="27">
-        <f>IF(I44="","",I44*J44)</f>
-        <v/>
-      </c>
-      <c r="L44" s="28" t="inlineStr"/>
-      <c r="M44" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="N44" s="29">
-        <f>IF(OR(M44&lt;&gt;"Sim",I44=""),0,K44*IF(H44="BRL",1,IF(H44="EUR",Parâmetros!$B$4,IF(H44="USD",Parâmetros!$B$5,1))))</f>
-        <v/>
-      </c>
-      <c r="O44" s="25" t="inlineStr">
-        <is>
-          <t>A cotar</t>
-        </is>
-      </c>
-      <c r="P44" s="30" t="inlineStr">
-        <is>
-          <t>Reservar exatamente em 11/11 para garantir horário.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="23" t="n">
-        <v>41</v>
-      </c>
-      <c r="B45" s="23" t="inlineStr">
-        <is>
-          <t>Experiência</t>
-        </is>
-      </c>
-      <c r="C45" s="24" t="inlineStr">
-        <is>
-          <t>Louvre · 5 pax</t>
-        </is>
-      </c>
-      <c r="D45" s="23" t="inlineStr">
-        <is>
-          <t>Entrada com hora marcada · menores de 18 gratuitos</t>
-        </is>
-      </c>
-      <c r="E45" s="23" t="inlineStr">
-        <is>
-          <t>11/01</t>
-        </is>
-      </c>
-      <c r="F45" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="G45" s="25" t="inlineStr"/>
-      <c r="H45" s="25" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="I45" s="26" t="n"/>
-      <c r="J45" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="K45" s="27">
-        <f>IF(I45="","",I45*J45)</f>
-        <v/>
-      </c>
-      <c r="L45" s="28" t="inlineStr"/>
-      <c r="M45" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="N45" s="29">
-        <f>IF(OR(M45&lt;&gt;"Sim",I45=""),0,K45*IF(H45="BRL",1,IF(H45="EUR",Parâmetros!$B$4,IF(H45="USD",Parâmetros!$B$5,1))))</f>
-        <v/>
-      </c>
-      <c r="O45" s="25" t="inlineStr">
-        <is>
-          <t>A cotar</t>
-        </is>
-      </c>
-      <c r="P45" s="30" t="inlineStr">
-        <is>
-          <t>Qtd = 2 adultos pagantes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="23" t="n">
-        <v>42</v>
-      </c>
-      <c r="B46" s="23" t="inlineStr">
-        <is>
-          <t>Experiência</t>
-        </is>
-      </c>
-      <c r="C46" s="24" t="inlineStr">
-        <is>
-          <t>Cruzeiro no Sena com jantar · 5 pax</t>
-        </is>
-      </c>
-      <c r="D46" s="23" t="inlineStr">
-        <is>
-          <t>Bateaux Parisiens ou Bateaux-Mouches · jantar da noite</t>
-        </is>
-      </c>
-      <c r="E46" s="23" t="inlineStr">
-        <is>
-          <t>11/01</t>
-        </is>
-      </c>
-      <c r="F46" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="G46" s="25" t="inlineStr"/>
-      <c r="H46" s="25" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="I46" s="26" t="n"/>
-      <c r="J46" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="K46" s="27">
-        <f>IF(I46="","",I46*J46)</f>
-        <v/>
-      </c>
-      <c r="L46" s="28" t="inlineStr"/>
-      <c r="M46" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="N46" s="29">
-        <f>IF(OR(M46&lt;&gt;"Sim",I46=""),0,K46*IF(H46="BRL",1,IF(H46="EUR",Parâmetros!$B$4,IF(H46="USD",Parâmetros!$B$5,1))))</f>
-        <v/>
-      </c>
-      <c r="O46" s="25" t="inlineStr">
-        <is>
-          <t>A cotar</t>
-        </is>
-      </c>
-      <c r="P46" s="30" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="23" t="n">
-        <v>43</v>
-      </c>
-      <c r="B47" s="23" t="inlineStr">
-        <is>
-          <t>Seguro/Docs</t>
-        </is>
-      </c>
-      <c r="C47" s="24" t="inlineStr">
-        <is>
-          <t>Seguro viagem · 5 pax · 15 dias</t>
-        </is>
-      </c>
-      <c r="D47" s="23" t="inlineStr">
-        <is>
-          <t>Cobertura médica mínima € 30.000 (Schengen) · bagagem · cancelamento</t>
-        </is>
-      </c>
-      <c r="E47" s="23" t="inlineStr">
-        <is>
-          <t>29/12 → 12/01</t>
-        </is>
-      </c>
-      <c r="F47" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="G47" s="25" t="inlineStr"/>
-      <c r="H47" s="25" t="inlineStr">
-        <is>
-          <t>BRL</t>
-        </is>
-      </c>
-      <c r="I47" s="26" t="n"/>
-      <c r="J47" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="K47" s="27">
-        <f>IF(I47="","",I47*J47)</f>
-        <v/>
-      </c>
-      <c r="L47" s="28" t="inlineStr"/>
-      <c r="M47" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="N47" s="29">
-        <f>IF(OR(M47&lt;&gt;"Sim",I47=""),0,K47*IF(H47="BRL",1,IF(H47="EUR",Parâmetros!$B$4,IF(H47="USD",Parâmetros!$B$5,1))))</f>
-        <v/>
-      </c>
-      <c r="O47" s="25" t="inlineStr">
-        <is>
-          <t>A cotar</t>
-        </is>
-      </c>
-      <c r="P47" s="30" t="inlineStr">
-        <is>
-          <t>Valor unitário = por pessoa. Filho com vigência a partir de 04/01 pode sair mais barato.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48"/>
-    <row r="49">
-      <c r="C49" s="21" t="inlineStr">
-        <is>
-          <t>SUBTOTAL EM R$ (itens marcados como Sim)</t>
-        </is>
-      </c>
-      <c r="N49" s="31">
-        <f>SUM(N5:N47)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="C50" s="12" t="inlineStr">
-        <is>
-          <t>Taxa de serviço LusaTravel</t>
-        </is>
-      </c>
-      <c r="N50" s="13">
-        <f>N49*Parâmetros!$B$10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="32" t="n"/>
-      <c r="B51" s="32" t="n"/>
-      <c r="C51" s="33" t="inlineStr">
-        <is>
-          <t>TOTAL PARA O CLIENTE</t>
-        </is>
-      </c>
-      <c r="D51" s="32" t="n"/>
-      <c r="E51" s="32" t="n"/>
-      <c r="F51" s="32" t="n"/>
-      <c r="G51" s="32" t="n"/>
-      <c r="H51" s="32" t="n"/>
-      <c r="I51" s="32" t="n"/>
-      <c r="J51" s="32" t="n"/>
-      <c r="K51" s="32" t="n"/>
-      <c r="L51" s="32" t="n"/>
-      <c r="M51" s="32" t="n"/>
-      <c r="N51" s="34">
-        <f>N49+N50</f>
-        <v/>
-      </c>
-      <c r="O51" s="32" t="n"/>
-      <c r="P51" s="32" t="n"/>
-    </row>
-    <row r="52">
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>*Nada reservado, apenas cotado.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:P47"/>
+  <autoFilter ref="A4:P36"/>
   <dataValidations count="3">
-    <dataValidation sqref="O5:O47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O5:O36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"A cotar,Cotado,Aprovado pelo cliente,Reservado,Descartado"</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="M5:M36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="H5:H36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"BRL,EUR,USD"</formula1>
     </dataValidation>
   </dataValidations>

--- a/cotacao-cristofer-reveillon.xlsx
+++ b/cotacao-cristofer-reveillon.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Cotação" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Cotação'!$A$4:$P$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Cotação'!$A$4:$P$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -625,19 +625,19 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$36,A5)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$37,A5)</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$36,A5,Cotação!$O$5:$O$36,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$37,A5,Cotação!$O$5:$O$37,"A cotar")</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$36,A5,Cotação!$O$5:$O$36,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$37,A5,Cotação!$O$5:$O$37,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E5" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$36,A5,Cotação!$N$5:$N$36)</f>
+        <f>SUMIF(Cotação!$B$5:$B$37,A5,Cotação!$N$5:$N$37)</f>
         <v/>
       </c>
     </row>
@@ -648,19 +648,19 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$36,A6)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$37,A6)</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$36,A6,Cotação!$O$5:$O$36,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$37,A6,Cotação!$O$5:$O$37,"A cotar")</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$36,A6,Cotação!$O$5:$O$36,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$37,A6,Cotação!$O$5:$O$37,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E6" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$36,A6,Cotação!$N$5:$N$36)</f>
+        <f>SUMIF(Cotação!$B$5:$B$37,A6,Cotação!$N$5:$N$37)</f>
         <v/>
       </c>
     </row>
@@ -671,19 +671,19 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$36,A7)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$37,A7)</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$36,A7,Cotação!$O$5:$O$36,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$37,A7,Cotação!$O$5:$O$37,"A cotar")</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$36,A7,Cotação!$O$5:$O$36,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$37,A7,Cotação!$O$5:$O$37,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E7" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$36,A7,Cotação!$N$5:$N$36)</f>
+        <f>SUMIF(Cotação!$B$5:$B$37,A7,Cotação!$N$5:$N$37)</f>
         <v/>
       </c>
     </row>
@@ -694,19 +694,19 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$36,A8)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$37,A8)</f>
         <v/>
       </c>
       <c r="C8" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$36,A8,Cotação!$O$5:$O$36,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$37,A8,Cotação!$O$5:$O$37,"A cotar")</f>
         <v/>
       </c>
       <c r="D8" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$36,A8,Cotação!$O$5:$O$36,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$37,A8,Cotação!$O$5:$O$37,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E8" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$36,A8,Cotação!$N$5:$N$36)</f>
+        <f>SUMIF(Cotação!$B$5:$B$37,A8,Cotação!$N$5:$N$37)</f>
         <v/>
       </c>
     </row>
@@ -717,19 +717,19 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$36,A9)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$37,A9)</f>
         <v/>
       </c>
       <c r="C9" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$36,A9,Cotação!$O$5:$O$36,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$37,A9,Cotação!$O$5:$O$37,"A cotar")</f>
         <v/>
       </c>
       <c r="D9" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$36,A9,Cotação!$O$5:$O$36,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$37,A9,Cotação!$O$5:$O$37,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E9" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$36,A9,Cotação!$N$5:$N$36)</f>
+        <f>SUMIF(Cotação!$B$5:$B$37,A9,Cotação!$N$5:$N$37)</f>
         <v/>
       </c>
     </row>
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$36,A10)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$37,A10)</f>
         <v/>
       </c>
       <c r="C10" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$36,A10,Cotação!$O$5:$O$36,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$37,A10,Cotação!$O$5:$O$37,"A cotar")</f>
         <v/>
       </c>
       <c r="D10" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$36,A10,Cotação!$O$5:$O$36,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$37,A10,Cotação!$O$5:$O$37,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$36,A10,Cotação!$N$5:$N$36)</f>
+        <f>SUMIF(Cotação!$B$5:$B$37,A10,Cotação!$N$5:$N$37)</f>
         <v/>
       </c>
     </row>
@@ -763,19 +763,19 @@
         </is>
       </c>
       <c r="B11" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$36,A11)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$37,A11)</f>
         <v/>
       </c>
       <c r="C11" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$36,A11,Cotação!$O$5:$O$36,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$37,A11,Cotação!$O$5:$O$37,"A cotar")</f>
         <v/>
       </c>
       <c r="D11" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$36,A11,Cotação!$O$5:$O$36,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$37,A11,Cotação!$O$5:$O$37,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E11" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$36,A11,Cotação!$N$5:$N$36)</f>
+        <f>SUMIF(Cotação!$B$5:$B$37,A11,Cotação!$N$5:$N$37)</f>
         <v/>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P41"/>
+  <dimension ref="A1:P42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="I31" s="26" t="n">
-        <v>1092.24</v>
+        <v>2146.59</v>
       </c>
       <c r="J31" s="25" t="n">
         <v>4</v>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="P31" s="30" t="inlineStr">
         <is>
-          <t>Valor por pessoa. Confirmar na página o preço vigente para 31/12 e se há tarifa de menor.</t>
+          <t>Valor por pessoa, conforme a página da Silverline em 21/09.</t>
         </is>
       </c>
     </row>
@@ -3177,12 +3177,12 @@
       </c>
       <c r="C35" s="24" t="inlineStr">
         <is>
-          <t>Almoço em vinícola ou restaurante em Tokaj · 4 pax</t>
+          <t>Disznókő · visita e prova · 2 adultos + 2 filhas</t>
         </is>
       </c>
       <c r="D35" s="23" t="inlineStr">
         <is>
-          <t>Mád ou Tarcal</t>
+          <t>Mezőzombor, a 20 min de Tolcsva · vinícola do grupo AXA Millésimes · segunda parada da tarde</t>
         </is>
       </c>
       <c r="E35" s="23" t="inlineStr">
@@ -3193,21 +3193,25 @@
       <c r="F35" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="G35" s="25" t="inlineStr"/>
+      <c r="G35" s="25" t="inlineStr">
+        <is>
+          <t>Disznókő</t>
+        </is>
+      </c>
       <c r="H35" s="25" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>BRL</t>
         </is>
       </c>
       <c r="I35" s="26" t="n"/>
       <c r="J35" s="25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K35" s="27">
         <f>IF(I35="","",I35*J35)</f>
         <v/>
       </c>
-      <c r="L35" s="28" t="inlineStr"/>
+      <c r="L35" s="28" t="n"/>
       <c r="M35" s="25" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -3224,7 +3228,7 @@
       </c>
       <c r="P35" s="30" t="inlineStr">
         <is>
-          <t>Pode vir incluído no pacote do motorista-guia.</t>
+          <t>Aguardando valores da vinícola.</t>
         </is>
       </c>
     </row>
@@ -3234,36 +3238,36 @@
       </c>
       <c r="B36" s="23" t="inlineStr">
         <is>
-          <t>Seguro/Docs</t>
+          <t>Experiência</t>
         </is>
       </c>
       <c r="C36" s="24" t="inlineStr">
         <is>
-          <t>Seguro viagem · 5 pax · 15 dias</t>
+          <t>Almoço em vinícola ou restaurante em Tokaj · 4 pax</t>
         </is>
       </c>
       <c r="D36" s="23" t="inlineStr">
         <is>
-          <t>Cobertura médica mínima € 30.000 (Schengen) · bagagem · cancelamento</t>
+          <t>Mád ou Tarcal</t>
         </is>
       </c>
       <c r="E36" s="23" t="inlineStr">
         <is>
-          <t>29/12 → 12/01</t>
+          <t>02/01</t>
         </is>
       </c>
       <c r="F36" s="23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G36" s="25" t="inlineStr"/>
       <c r="H36" s="25" t="inlineStr">
         <is>
-          <t>BRL</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="I36" s="26" t="n"/>
       <c r="J36" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K36" s="27">
         <f>IF(I36="","",I36*J36)</f>
@@ -3286,75 +3290,137 @@
       </c>
       <c r="P36" s="30" t="inlineStr">
         <is>
+          <t>Pode vir incluído no pacote do motorista-guia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="23" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="23" t="inlineStr">
+        <is>
+          <t>Seguro/Docs</t>
+        </is>
+      </c>
+      <c r="C37" s="24" t="inlineStr">
+        <is>
+          <t>Seguro viagem · 5 pax · 15 dias</t>
+        </is>
+      </c>
+      <c r="D37" s="23" t="inlineStr">
+        <is>
+          <t>Cobertura médica mínima € 30.000 (Schengen) · bagagem · cancelamento</t>
+        </is>
+      </c>
+      <c r="E37" s="23" t="inlineStr">
+        <is>
+          <t>29/12 → 12/01</t>
+        </is>
+      </c>
+      <c r="F37" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="G37" s="25" t="inlineStr"/>
+      <c r="H37" s="25" t="inlineStr">
+        <is>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="I37" s="26" t="n"/>
+      <c r="J37" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="K37" s="27">
+        <f>IF(I37="","",I37*J37)</f>
+        <v/>
+      </c>
+      <c r="L37" s="28" t="inlineStr"/>
+      <c r="M37" s="25" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="N37" s="29">
+        <f>IF(OR(M37&lt;&gt;"Sim",I37=""),0,K37*IF(H37="BRL",1,IF(H37="EUR",Parâmetros!$B$4,IF(H37="USD",Parâmetros!$B$5,1))))</f>
+        <v/>
+      </c>
+      <c r="O37" s="25" t="inlineStr">
+        <is>
+          <t>A cotar</t>
+        </is>
+      </c>
+      <c r="P37" s="30" t="inlineStr">
+        <is>
           <t>Valor unitário = por pessoa. Filho com vigência a partir de 04/01 pode sair mais barato.</t>
         </is>
       </c>
     </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="C38" s="21" t="inlineStr">
+    <row r="38"/>
+    <row r="39">
+      <c r="C39" s="21" t="inlineStr">
         <is>
           <t>SUBTOTAL EM R$ (itens marcados como Sim)</t>
         </is>
       </c>
-      <c r="N38" s="31">
-        <f>SUM(N5:N36)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="C39" s="12" t="inlineStr">
+      <c r="N39" s="31">
+        <f>SUM(N5:N37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" s="12" t="inlineStr">
         <is>
           <t>Taxa de serviço LusaTravel</t>
         </is>
       </c>
-      <c r="N39" s="13">
-        <f>N38*Parâmetros!$B$10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="32" t="n"/>
-      <c r="B40" s="32" t="n"/>
-      <c r="C40" s="33" t="inlineStr">
+      <c r="N40" s="13">
+        <f>N39*Parâmetros!$B$10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="32" t="n"/>
+      <c r="B41" s="32" t="n"/>
+      <c r="C41" s="33" t="inlineStr">
         <is>
           <t>TOTAL PARA O CLIENTE</t>
         </is>
       </c>
-      <c r="D40" s="32" t="n"/>
-      <c r="E40" s="32" t="n"/>
-      <c r="F40" s="32" t="n"/>
-      <c r="G40" s="32" t="n"/>
-      <c r="H40" s="32" t="n"/>
-      <c r="I40" s="32" t="n"/>
-      <c r="J40" s="32" t="n"/>
-      <c r="K40" s="32" t="n"/>
-      <c r="L40" s="32" t="n"/>
-      <c r="M40" s="32" t="n"/>
-      <c r="N40" s="34">
-        <f>N38+N39</f>
-        <v/>
-      </c>
-      <c r="O40" s="32" t="n"/>
-      <c r="P40" s="32" t="n"/>
-    </row>
-    <row r="41">
-      <c r="C41" s="2" t="inlineStr">
+      <c r="D41" s="32" t="n"/>
+      <c r="E41" s="32" t="n"/>
+      <c r="F41" s="32" t="n"/>
+      <c r="G41" s="32" t="n"/>
+      <c r="H41" s="32" t="n"/>
+      <c r="I41" s="32" t="n"/>
+      <c r="J41" s="32" t="n"/>
+      <c r="K41" s="32" t="n"/>
+      <c r="L41" s="32" t="n"/>
+      <c r="M41" s="32" t="n"/>
+      <c r="N41" s="34">
+        <f>N39+N40</f>
+        <v/>
+      </c>
+      <c r="O41" s="32" t="n"/>
+      <c r="P41" s="32" t="n"/>
+    </row>
+    <row r="42">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>*Nada reservado, apenas cotado.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:P36"/>
+  <autoFilter ref="A4:P37"/>
   <dataValidations count="3">
-    <dataValidation sqref="O5:O36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O5:O37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"A cotar,Cotado,Aprovado pelo cliente,Reservado,Descartado"</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="M5:M37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="H5:H37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"BRL,EUR,USD"</formula1>
     </dataValidation>
   </dataValidations>

--- a/cotacao-cristofer-reveillon.xlsx
+++ b/cotacao-cristofer-reveillon.xlsx
@@ -3310,7 +3310,7 @@
       </c>
       <c r="D37" s="23" t="inlineStr">
         <is>
-          <t>Cobertura médica mínima € 30.000 (Schengen) · bagagem · cancelamento</t>
+          <t>Plano 90 Essential · cobertura médica de USD 90.000, acima do mínimo Schengen · 29/12 a 12/01</t>
         </is>
       </c>
       <c r="E37" s="23" t="inlineStr">
@@ -3321,13 +3321,19 @@
       <c r="F37" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="G37" s="25" t="inlineStr"/>
+      <c r="G37" s="25" t="inlineStr">
+        <is>
+          <t>31 Motivos</t>
+        </is>
+      </c>
       <c r="H37" s="25" t="inlineStr">
         <is>
           <t>BRL</t>
         </is>
       </c>
-      <c r="I37" s="26" t="n"/>
+      <c r="I37" s="26" t="n">
+        <v>300.6</v>
+      </c>
       <c r="J37" s="25" t="n">
         <v>5</v>
       </c>
@@ -3347,12 +3353,12 @@
       </c>
       <c r="O37" s="25" t="inlineStr">
         <is>
-          <t>A cotar</t>
+          <t>Cotado</t>
         </is>
       </c>
       <c r="P37" s="30" t="inlineStr">
         <is>
-          <t>Valor unitário = por pessoa. Filho com vigência a partir de 04/01 pode sair mais barato.</t>
+          <t>Cotação de 21/09: R$ 1.503,00 para os 5 (R$ 300,60 por pessoa). Confirmar se a apólice do filho cobre desde o embarque dele em 04/01.</t>
         </is>
       </c>
     </row>

--- a/cotacao-cristofer-reveillon.xlsx
+++ b/cotacao-cristofer-reveillon.xlsx
@@ -3310,7 +3310,7 @@
       </c>
       <c r="D37" s="23" t="inlineStr">
         <is>
-          <t>Plano 90 Essential · cobertura médica de USD 90.000, acima do mínimo Schengen · 29/12 a 12/01</t>
+          <t>Plano 90 Essential · DMH USD 90.000 · 29/12 a 12/01</t>
         </is>
       </c>
       <c r="E37" s="23" t="inlineStr">
@@ -3362,7 +3362,6 @@
         </is>
       </c>
     </row>
-    <row r="38"/>
     <row r="39">
       <c r="C39" s="21" t="inlineStr">
         <is>

--- a/cotacao-cristofer-reveillon.xlsx
+++ b/cotacao-cristofer-reveillon.xlsx
@@ -2113,12 +2113,12 @@
       </c>
       <c r="C18" s="24" t="inlineStr">
         <is>
-          <t>Paris · Opção 1 · Castille Paris 5★</t>
+          <t>Paris · Opção 1 · Hôtel François 1er 4★</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
         <is>
-          <t>Rue Cambon, 1º arr., entre Louvre e Madeleine · 2 quartos (5 pax) · café · 2 noites</t>
+          <t>Rue Magellan, 8º arr., a 2 min da Champs-Élysées · 1 Executive Room + 1 Classic Double · café da manhã · 2 noites</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">
@@ -2129,13 +2129,19 @@
       <c r="F18" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="G18" s="25" t="inlineStr"/>
+      <c r="G18" s="25" t="inlineStr">
+        <is>
+          <t>Consolidador (a nomear)</t>
+        </is>
+      </c>
       <c r="H18" s="25" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="I18" s="26" t="n"/>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="I18" s="26" t="n">
+        <v>5587.5</v>
+      </c>
       <c r="J18" s="25" t="n">
         <v>2</v>
       </c>
@@ -2143,11 +2149,7 @@
         <f>IF(I18="","",I18*J18)</f>
         <v/>
       </c>
-      <c r="L18" s="28" t="inlineStr">
-        <is>
-          <t>€ 1.509 · 2 noites · 2 quartos · 3 adultos + 2 crianças</t>
-        </is>
-      </c>
+      <c r="L18" s="28" t="n"/>
       <c r="M18" s="25" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2159,12 +2161,12 @@
       </c>
       <c r="O18" s="25" t="inlineStr">
         <is>
-          <t>A cotar</t>
+          <t>Cotado</t>
         </is>
       </c>
       <c r="P18" s="30" t="inlineStr">
         <is>
-          <t>Valor unitário = diária dos 2 quartos somados.</t>
+          <t>Cotação de 21/09: Executive R$ 6.420 + Classic Double R$ 4.755 = R$ 11.175 pelas 2 noites (R$ 5.587,50/noite). Confirmar que a Executive comporta 3 (pais + filho).</t>
         </is>
       </c>
     </row>
@@ -2179,12 +2181,12 @@
       </c>
       <c r="C19" s="24" t="inlineStr">
         <is>
-          <t>Paris · Opção 2 · Hôtel Napoleon Paris 5★</t>
+          <t xml:space="preserve">Paris · Opção 2 · (hotel a informar) </t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
         <is>
-          <t>Av. de Friedland, 8º arr., a 100 m do Arco do Triunfo · 2 quartos (5 pax) · café · 2 noites</t>
+          <t>1 Standard Queen triplo + 1 Standard Queen duplo · café da manhã · 2 noites</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
@@ -2195,13 +2197,19 @@
       <c r="F19" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="G19" s="25" t="inlineStr"/>
+      <c r="G19" s="25" t="inlineStr">
+        <is>
+          <t>Consolidador (a nomear)</t>
+        </is>
+      </c>
       <c r="H19" s="25" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="I19" s="26" t="n"/>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="I19" s="26" t="n">
+        <v>5715</v>
+      </c>
       <c r="J19" s="25" t="n">
         <v>2</v>
       </c>
@@ -2209,11 +2217,7 @@
         <f>IF(I19="","",I19*J19)</f>
         <v/>
       </c>
-      <c r="L19" s="28" t="inlineStr">
-        <is>
-          <t>€ 1.593 · 2 noites · 2 quartos · 3 adultos + 2 crianças</t>
-        </is>
-      </c>
+      <c r="L19" s="28" t="n"/>
       <c r="M19" s="25" t="inlineStr">
         <is>
           <t>Não</t>
@@ -2225,10 +2229,14 @@
       </c>
       <c r="O19" s="25" t="inlineStr">
         <is>
-          <t>A cotar</t>
-        </is>
-      </c>
-      <c r="P19" s="30" t="inlineStr"/>
+          <t>Cotado</t>
+        </is>
+      </c>
+      <c r="P19" s="30" t="inlineStr">
+        <is>
+          <t>Cotação de 21/09: triplo R$ 6.730 + duplo R$ 4.700 = R$ 11.430 pelas 2 noites (R$ 5.715/noite). Faltou o nome do hotel.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="23" t="n">
@@ -3362,6 +3370,7 @@
         </is>
       </c>
     </row>
+    <row r="38"/>
     <row r="39">
       <c r="C39" s="21" t="inlineStr">
         <is>

--- a/cotacao-cristofer-reveillon.xlsx
+++ b/cotacao-cristofer-reveillon.xlsx
@@ -2181,12 +2181,12 @@
       </c>
       <c r="C19" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paris · Opção 2 · (hotel a informar) </t>
+          <t>Paris · Opção 2 · Hotel Indigo Paris Opéra, IHG 4★</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
         <is>
-          <t>1 Standard Queen triplo + 1 Standard Queen duplo · café da manhã · 2 noites</t>
+          <t>Rue de Châteaudun, 9º arr., entre a Ópera Garnier e Montmartre · 1 Standard Queen triplo + 1 Standard Queen duplo · café da manhã · 2 noites</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="P19" s="30" t="inlineStr">
         <is>
-          <t>Cotação de 21/09: triplo R$ 6.730 + duplo R$ 4.700 = R$ 11.430 pelas 2 noites (R$ 5.715/noite). Faltou o nome do hotel.</t>
+          <t>Cotação de 21/09: triplo R$ 6.730 + duplo R$ 4.700 = R$ 11.430 pelas 2 noites (R$ 5.715/noite). Triplo resolve pais + filho sem depender de confirmação.</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,6 @@
         </is>
       </c>
     </row>
-    <row r="38"/>
     <row r="39">
       <c r="C39" s="21" t="inlineStr">
         <is>

--- a/cotacao-cristofer-reveillon.xlsx
+++ b/cotacao-cristofer-reveillon.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Cotação" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Cotação'!$A$4:$P$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Cotação'!$A$4:$P$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -625,19 +625,19 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$37,A5)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$40,A5)</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$37,A5,Cotação!$O$5:$O$37,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$40,A5,Cotação!$O$5:$O$40,"A cotar")</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$37,A5,Cotação!$O$5:$O$37,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$40,A5,Cotação!$O$5:$O$40,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E5" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$37,A5,Cotação!$N$5:$N$37)</f>
+        <f>SUMIF(Cotação!$B$5:$B$40,A5,Cotação!$N$5:$N$40)</f>
         <v/>
       </c>
     </row>
@@ -648,19 +648,19 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$37,A6)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$40,A6)</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$37,A6,Cotação!$O$5:$O$37,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$40,A6,Cotação!$O$5:$O$40,"A cotar")</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$37,A6,Cotação!$O$5:$O$37,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$40,A6,Cotação!$O$5:$O$40,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E6" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$37,A6,Cotação!$N$5:$N$37)</f>
+        <f>SUMIF(Cotação!$B$5:$B$40,A6,Cotação!$N$5:$N$40)</f>
         <v/>
       </c>
     </row>
@@ -671,19 +671,19 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$37,A7)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$40,A7)</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$37,A7,Cotação!$O$5:$O$37,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$40,A7,Cotação!$O$5:$O$40,"A cotar")</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$37,A7,Cotação!$O$5:$O$37,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$40,A7,Cotação!$O$5:$O$40,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E7" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$37,A7,Cotação!$N$5:$N$37)</f>
+        <f>SUMIF(Cotação!$B$5:$B$40,A7,Cotação!$N$5:$N$40)</f>
         <v/>
       </c>
     </row>
@@ -694,19 +694,19 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$37,A8)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$40,A8)</f>
         <v/>
       </c>
       <c r="C8" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$37,A8,Cotação!$O$5:$O$37,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$40,A8,Cotação!$O$5:$O$40,"A cotar")</f>
         <v/>
       </c>
       <c r="D8" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$37,A8,Cotação!$O$5:$O$37,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$40,A8,Cotação!$O$5:$O$40,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E8" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$37,A8,Cotação!$N$5:$N$37)</f>
+        <f>SUMIF(Cotação!$B$5:$B$40,A8,Cotação!$N$5:$N$40)</f>
         <v/>
       </c>
     </row>
@@ -717,19 +717,19 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$37,A9)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$40,A9)</f>
         <v/>
       </c>
       <c r="C9" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$37,A9,Cotação!$O$5:$O$37,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$40,A9,Cotação!$O$5:$O$40,"A cotar")</f>
         <v/>
       </c>
       <c r="D9" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$37,A9,Cotação!$O$5:$O$37,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$40,A9,Cotação!$O$5:$O$40,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E9" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$37,A9,Cotação!$N$5:$N$37)</f>
+        <f>SUMIF(Cotação!$B$5:$B$40,A9,Cotação!$N$5:$N$40)</f>
         <v/>
       </c>
     </row>
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$37,A10)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$40,A10)</f>
         <v/>
       </c>
       <c r="C10" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$37,A10,Cotação!$O$5:$O$37,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$40,A10,Cotação!$O$5:$O$40,"A cotar")</f>
         <v/>
       </c>
       <c r="D10" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$37,A10,Cotação!$O$5:$O$37,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$40,A10,Cotação!$O$5:$O$40,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$37,A10,Cotação!$N$5:$N$37)</f>
+        <f>SUMIF(Cotação!$B$5:$B$40,A10,Cotação!$N$5:$N$40)</f>
         <v/>
       </c>
     </row>
@@ -763,19 +763,19 @@
         </is>
       </c>
       <c r="B11" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$37,A11)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$40,A11)</f>
         <v/>
       </c>
       <c r="C11" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$37,A11,Cotação!$O$5:$O$37,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$40,A11,Cotação!$O$5:$O$40,"A cotar")</f>
         <v/>
       </c>
       <c r="D11" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$37,A11,Cotação!$O$5:$O$37,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$40,A11,Cotação!$O$5:$O$40,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E11" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$37,A11,Cotação!$N$5:$N$37)</f>
+        <f>SUMIF(Cotação!$B$5:$B$40,A11,Cotação!$N$5:$N$40)</f>
         <v/>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P42"/>
+  <dimension ref="A1:P45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="D10" s="23" t="inlineStr">
         <is>
-          <t>Király utca, Terézváros, a 5 min da Basílica · 2 quartos Superior Double · café da manhã · 4 noites</t>
+          <t>Király utca, Terézváros, a 5 min da Basílica · 2 quartos Superior Double · café da manhã · 3 noites</t>
         </is>
       </c>
       <c r="E10" s="23" t="inlineStr">
         <is>
-          <t>30/12 → 03/01</t>
+          <t>30/12 → 02/01</t>
         </is>
       </c>
       <c r="F10" s="23" t="n">
@@ -1603,12 +1603,12 @@
       </c>
       <c r="O10" s="25" t="inlineStr">
         <is>
-          <t>Cotado</t>
+          <t>A cotar</t>
         </is>
       </c>
       <c r="P10" s="30" t="inlineStr">
         <is>
-          <t>Cotação de 21/09: R$ 16.800 pelos 2 quartos (R$ 8.400 por quarto, R$ 2.100/noite). Alternativa: R$ 580 abaixo do InterContinental, que segue no total por ser 5★ à beira do rio.</t>
+          <t>Valor lançado é o das 4 noites. Pedir recotação para 3 noites (30/12 → 02/01); tarifa de Réveillon não é proporcional.</t>
         </is>
       </c>
     </row>
@@ -1628,12 +1628,12 @@
       </c>
       <c r="D11" s="23" t="inlineStr">
         <is>
-          <t>Váci utca, coração de Pest, pedestre · 2 quartos Superior · café da manhã · 4 noites</t>
+          <t>Váci utca, coração de Pest, pedestre · 2 quartos Superior · café da manhã · 3 noites</t>
         </is>
       </c>
       <c r="E11" s="23" t="inlineStr">
         <is>
-          <t>30/12 → 03/01</t>
+          <t>30/12 → 02/01</t>
         </is>
       </c>
       <c r="F11" s="23" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="O11" s="25" t="inlineStr">
         <is>
-          <t>Cotado</t>
+          <t>A cotar</t>
         </is>
       </c>
       <c r="P11" s="30" t="inlineStr">
         <is>
-          <t>Cotação de 21/09: '2x Superior Room 13.400' — lido como R$ 13.400 pelos 2 quartos (R$ 6.700 por quarto, R$ 1.675/noite). Se for por quarto, o total é R$ 26.800. Confirmar. Com café da manhã.</t>
+          <t>Valor lançado é o das 4 noites. Pedir recotação para 3 noites (30/12 → 02/01); tarifa de Réveillon não é proporcional.</t>
         </is>
       </c>
     </row>
@@ -1700,12 +1700,12 @@
       </c>
       <c r="D12" s="23" t="inlineStr">
         <is>
-          <t>Margem do Danúbio, vista para o Castelo e a Ponte das Correntes · 2 quartos Classic · café da manhã · 4 noites</t>
+          <t>Margem do Danúbio, vista para o Castelo e a Ponte das Correntes · 2 quartos Classic · café da manhã · 3 noites</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">
         <is>
-          <t>30/12 → 03/01</t>
+          <t>30/12 → 02/01</t>
         </is>
       </c>
       <c r="F12" s="23" t="n">
@@ -1747,12 +1747,12 @@
       </c>
       <c r="O12" s="25" t="inlineStr">
         <is>
-          <t>Cotado</t>
+          <t>A cotar</t>
         </is>
       </c>
       <c r="P12" s="30" t="inlineStr">
         <is>
-          <t>Cotação de 21/09: '2x Classic Room 17.380' — R$ 17.380 pelos 2 quartos (R$ 8.690 por quarto, R$ 2.172/noite). Escolhida para o total: único 5★ das três, à beira do rio, por R$ 3.980 a mais que o Mercure.</t>
+          <t>Valor lançado é o das 4 noites. Pedir recotação para 3 noites (30/12 → 02/01); tarifa de Réveillon não é proporcional.</t>
         </is>
       </c>
     </row>
@@ -1767,17 +1767,17 @@
       </c>
       <c r="C13" s="24" t="inlineStr">
         <is>
-          <t>Viena · Opção 1 · Steigenberger Icon Herrenhof 5★</t>
+          <t>Tokaj · Minaro Hotel Tokaj, MGallery 5★</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
         <is>
-          <t>Herrengasse, Innere Stadt, a 5 min do Hofburg · 1 Junior Suite + 1 Superior Room · café da manhã · 4 noites</t>
+          <t>Tokaj, à beira do rio Bodrog, a 5 min da estação · 2 quartos duplos · café da manhã · 1 noite</t>
         </is>
       </c>
       <c r="E13" s="23" t="inlineStr">
         <is>
-          <t>03/01 → 07/01</t>
+          <t>02/01 → 03/01</t>
         </is>
       </c>
       <c r="F13" s="23" t="n">
@@ -1793,21 +1793,15 @@
           <t>BRL</t>
         </is>
       </c>
-      <c r="I13" s="26" t="n">
-        <v>5910</v>
-      </c>
+      <c r="I13" s="26" t="n"/>
       <c r="J13" s="25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K13" s="27">
         <f>IF(I13="","",I13*J13)</f>
         <v/>
       </c>
-      <c r="L13" s="28" t="inlineStr">
-        <is>
-          <t>Booking 20/09: € 1.862 (≈ R$ 11.004) por 2 quartos standard/4 noites no mesmo hotel</t>
-        </is>
-      </c>
+      <c r="L13" s="28" t="n"/>
       <c r="M13" s="25" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1819,12 +1813,12 @@
       </c>
       <c r="O13" s="25" t="inlineStr">
         <is>
-          <t>Cotado</t>
+          <t>A cotar</t>
         </is>
       </c>
       <c r="P13" s="30" t="inlineStr">
         <is>
-          <t>Cotação de 21/09: Junior Suite R$ 15.300 + Superior Room R$ 8.340 = R$ 23.640 pelas 4 noites (R$ 5.910/noite). Junior Suite comporta 3: pais + filho a partir de 05/01, filhas no Superior. Sem cama extra.</t>
+          <t>Substitui a 4ª noite de Budapeste. Valor unitário = diária dos 2 quartos somados.</t>
         </is>
       </c>
     </row>
@@ -1839,12 +1833,12 @@
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>Viena · Opção 2 · Radisson Blu Style Hotel 5★</t>
+          <t>Viena · Opção 1 · Steigenberger Icon Herrenhof 5★</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
         <is>
-          <t>Herrengasse 12, Innere Stadt, design, a 3 min do Hofburg · 1 Junior Suite + 1 Superior Room · café da manhã · 4 noites</t>
+          <t>Herrengasse, Innere Stadt, a 5 min do Hofburg · 1 Junior Suite + 1 Superior Room · café da manhã · 4 noites</t>
         </is>
       </c>
       <c r="E14" s="23" t="inlineStr">
@@ -1866,7 +1860,7 @@
         </is>
       </c>
       <c r="I14" s="26" t="n">
-        <v>4768</v>
+        <v>5910</v>
       </c>
       <c r="J14" s="25" t="n">
         <v>4</v>
@@ -1877,12 +1871,12 @@
       </c>
       <c r="L14" s="28" t="inlineStr">
         <is>
-          <t>Booking 20/09: R$ 12.034 por 2 quartos standard/4 noites no mesmo hotel</t>
+          <t>Booking 20/09: € 1.862 (≈ R$ 11.004) por 2 quartos standard/4 noites no mesmo hotel</t>
         </is>
       </c>
       <c r="M14" s="25" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="N14" s="29">
@@ -1896,7 +1890,7 @@
       </c>
       <c r="P14" s="30" t="inlineStr">
         <is>
-          <t>Cotação de 21/09: Junior Suite R$ 11.042 + Superior Room R$ 8.030 = R$ 19.072 pelas 4 noites (R$ 4.768/noite). Junior Suite comporta 3. R$ 4.568 mais barato que o Herrenhof, na mesma rua.</t>
+          <t>Cotação de 21/09: Junior Suite R$ 15.300 + Superior Room R$ 8.340 = R$ 23.640 pelas 4 noites (R$ 5.910/noite). Junior Suite comporta 3: pais + filho a partir de 05/01, filhas no Superior. Sem cama extra.</t>
         </is>
       </c>
     </row>
@@ -1911,37 +1905,47 @@
       </c>
       <c r="C15" s="24" t="inlineStr">
         <is>
-          <t>Viena · cama extra ou 3º quarto para o filho</t>
+          <t>Viena · Opção 2 · Radisson Blu Style Hotel 5★</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
         <is>
-          <t>2 noites, a partir da chegada em 05/01, no hotel escolhido</t>
+          <t>Herrengasse 12, Innere Stadt, design, a 3 min do Hofburg · 1 Junior Suite + 1 Superior Room · café da manhã · 4 noites</t>
         </is>
       </c>
       <c r="E15" s="23" t="inlineStr">
         <is>
-          <t>05/01 → 07/01</t>
+          <t>03/01 → 07/01</t>
         </is>
       </c>
       <c r="F15" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="25" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G15" s="25" t="inlineStr">
+        <is>
+          <t>Consolidador (a nomear)</t>
+        </is>
+      </c>
       <c r="H15" s="25" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="I15" s="26" t="n"/>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="I15" s="26" t="n">
+        <v>4768</v>
+      </c>
       <c r="J15" s="25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K15" s="27">
         <f>IF(I15="","",I15*J15)</f>
         <v/>
       </c>
-      <c r="L15" s="28" t="inlineStr"/>
+      <c r="L15" s="28" t="inlineStr">
+        <is>
+          <t>Booking 20/09: R$ 12.034 por 2 quartos standard/4 noites no mesmo hotel</t>
+        </is>
+      </c>
       <c r="M15" s="25" t="inlineStr">
         <is>
           <t>Não</t>
@@ -1953,12 +1957,12 @@
       </c>
       <c r="O15" s="25" t="inlineStr">
         <is>
-          <t>Descartado</t>
+          <t>Cotado</t>
         </is>
       </c>
       <c r="P15" s="30" t="inlineStr">
         <is>
-          <t>Desnecessária: a Junior Suite das duas opções comporta o filho.</t>
+          <t>Cotação de 21/09: Junior Suite R$ 11.042 + Superior Room R$ 8.030 = R$ 19.072 pelas 4 noites (R$ 4.768/noite). Junior Suite comporta 3. R$ 4.568 mais barato que o Herrenhof, na mesma rua.</t>
         </is>
       </c>
     </row>
@@ -1973,50 +1977,40 @@
       </c>
       <c r="C16" s="24" t="inlineStr">
         <is>
-          <t>Praga · Opção 1 · The Emblem Prague Hotel 5★</t>
+          <t>Viena · cama extra ou 3º quarto para o filho</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
         <is>
-          <t>Platnéřská, Cidade Velha, a 2 min da Praça da Cidade Velha, spa na cobertura · 1 Suite Pretender + 1 Queen Room · café da manhã · 3 noites</t>
+          <t>2 noites, a partir da chegada em 05/01, no hotel escolhido</t>
         </is>
       </c>
       <c r="E16" s="23" t="inlineStr">
         <is>
-          <t>07/01 → 10/01</t>
+          <t>05/01 → 07/01</t>
         </is>
       </c>
       <c r="F16" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="G16" s="25" t="inlineStr">
-        <is>
-          <t>Consolidador (a nomear)</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G16" s="25" t="inlineStr"/>
       <c r="H16" s="25" t="inlineStr">
         <is>
-          <t>BRL</t>
-        </is>
-      </c>
-      <c r="I16" s="26" t="n">
-        <v>3335</v>
-      </c>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I16" s="26" t="n"/>
       <c r="J16" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K16" s="27">
         <f>IF(I16="","",I16*J16)</f>
         <v/>
       </c>
-      <c r="L16" s="28" t="inlineStr">
-        <is>
-          <t>Booking 20/09, outros hotéis: Art Nouveau Palace 5★ € 812 · Hilton Old Town 5★ € 1.041 por 2 quartos/3 noites (5 pax)</t>
-        </is>
-      </c>
+      <c r="L16" s="28" t="inlineStr"/>
       <c r="M16" s="25" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="N16" s="29">
@@ -2025,12 +2019,12 @@
       </c>
       <c r="O16" s="25" t="inlineStr">
         <is>
-          <t>Cotado</t>
+          <t>Descartado</t>
         </is>
       </c>
       <c r="P16" s="30" t="inlineStr">
         <is>
-          <t>Cotação de 21/09: Suite Pretender R$ 5.680 + Queen Room R$ 4.325 = R$ 10.005 pelas 3 noites (R$ 3.335/noite). Suíte comporta 3. Escolhida para o total: boutique 5★ no coração da Cidade Velha, R$ 1.980 acima da Opção 2.</t>
+          <t>Desnecessária: a Junior Suite das duas opções comporta o filho.</t>
         </is>
       </c>
     </row>
@@ -2045,12 +2039,12 @@
       </c>
       <c r="C17" s="24" t="inlineStr">
         <is>
-          <t>Praga · Opção 2 · Century Old Town Prague, MGallery 4★</t>
+          <t>Praga · Opção 1 · The Emblem Prague Hotel 5★</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
         <is>
-          <t>Na Poříčí, prédio onde Kafka trabalhou, a 8 min da Praça da Cidade Velha · 1 Executive + 1 Classic Room · café da manhã · 3 noites</t>
+          <t>Platnéřská, Cidade Velha, a 2 min da Praça da Cidade Velha, spa na cobertura · 1 Suite Pretender + 1 Queen Room · café da manhã · 3 noites</t>
         </is>
       </c>
       <c r="E17" s="23" t="inlineStr">
@@ -2072,7 +2066,7 @@
         </is>
       </c>
       <c r="I17" s="26" t="n">
-        <v>2675</v>
+        <v>3335</v>
       </c>
       <c r="J17" s="25" t="n">
         <v>3</v>
@@ -2081,10 +2075,14 @@
         <f>IF(I17="","",I17*J17)</f>
         <v/>
       </c>
-      <c r="L17" s="28" t="n"/>
+      <c r="L17" s="28" t="inlineStr">
+        <is>
+          <t>Booking 20/09, outros hotéis: Art Nouveau Palace 5★ € 812 · Hilton Old Town 5★ € 1.041 por 2 quartos/3 noites (5 pax)</t>
+        </is>
+      </c>
       <c r="M17" s="25" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="N17" s="29">
@@ -2098,7 +2096,7 @@
       </c>
       <c r="P17" s="30" t="inlineStr">
         <is>
-          <t>Cotação de 21/09: Executive R$ 4.645 + Classic R$ 3.380 = R$ 8.025 pelas 3 noites (R$ 2.675/noite). Suíte comporta 3.</t>
+          <t>Cotação de 21/09: Suite Pretender R$ 5.680 + Queen Room R$ 4.325 = R$ 10.005 pelas 3 noites (R$ 3.335/noite). Suíte comporta 3. Escolhida para o total: boutique 5★ no coração da Cidade Velha, R$ 1.980 acima da Opção 2.</t>
         </is>
       </c>
     </row>
@@ -2113,17 +2111,17 @@
       </c>
       <c r="C18" s="24" t="inlineStr">
         <is>
-          <t>Paris · Opção 1 · Hôtel François 1er 4★</t>
+          <t>Praga · Opção 2 · Century Old Town Prague, MGallery 4★</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
         <is>
-          <t>Rue Magellan, 8º arr., a 2 min da Champs-Élysées · 1 Executive Room + 1 Classic Double · café da manhã · 2 noites</t>
+          <t>Na Poříčí, prédio onde Kafka trabalhou, a 8 min da Praça da Cidade Velha · 1 Executive + 1 Classic Room · café da manhã · 3 noites</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">
         <is>
-          <t>10/01 → 12/01</t>
+          <t>07/01 → 10/01</t>
         </is>
       </c>
       <c r="F18" s="23" t="n">
@@ -2140,10 +2138,10 @@
         </is>
       </c>
       <c r="I18" s="26" t="n">
-        <v>5587.5</v>
+        <v>2675</v>
       </c>
       <c r="J18" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K18" s="27">
         <f>IF(I18="","",I18*J18)</f>
@@ -2152,7 +2150,7 @@
       <c r="L18" s="28" t="n"/>
       <c r="M18" s="25" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="N18" s="29">
@@ -2166,7 +2164,7 @@
       </c>
       <c r="P18" s="30" t="inlineStr">
         <is>
-          <t>Cotação de 21/09: Executive R$ 6.420 + Classic Double R$ 4.755 = R$ 11.175 pelas 2 noites (R$ 5.587,50/noite). Confirmar que a Executive comporta 3 (pais + filho).</t>
+          <t>Cotação de 21/09: Executive R$ 4.645 + Classic R$ 3.380 = R$ 8.025 pelas 3 noites (R$ 2.675/noite). Suíte comporta 3.</t>
         </is>
       </c>
     </row>
@@ -2181,12 +2179,12 @@
       </c>
       <c r="C19" s="24" t="inlineStr">
         <is>
-          <t>Paris · Opção 2 · Hotel Indigo Paris Opéra, IHG 4★</t>
+          <t>Paris · Opção 1 · Hôtel François 1er 4★</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
         <is>
-          <t>Rue de Châteaudun, 9º arr., entre a Ópera Garnier e Montmartre · 1 Standard Queen triplo + 1 Standard Queen duplo · café da manhã · 2 noites</t>
+          <t>Rue Magellan, 8º arr., a 2 min da Champs-Élysées · 1 Executive Room + 1 Classic Double · café da manhã · 2 noites</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
@@ -2208,7 +2206,7 @@
         </is>
       </c>
       <c r="I19" s="26" t="n">
-        <v>5715</v>
+        <v>5587.5</v>
       </c>
       <c r="J19" s="25" t="n">
         <v>2</v>
@@ -2220,7 +2218,7 @@
       <c r="L19" s="28" t="n"/>
       <c r="M19" s="25" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="N19" s="29">
@@ -2234,7 +2232,7 @@
       </c>
       <c r="P19" s="30" t="inlineStr">
         <is>
-          <t>Cotação de 21/09: triplo R$ 6.730 + duplo R$ 4.700 = R$ 11.430 pelas 2 noites (R$ 5.715/noite). Triplo resolve pais + filho sem depender de confirmação.</t>
+          <t>Cotação de 21/09: Executive R$ 6.420 + Classic Double R$ 4.755 = R$ 11.175 pelas 2 noites (R$ 5.587,50/noite). Confirmar que a Executive comporta 3 (pais + filho).</t>
         </is>
       </c>
     </row>
@@ -2244,26 +2242,26 @@
       </c>
       <c r="B20" s="23" t="inlineStr">
         <is>
-          <t>Trem</t>
+          <t>Hotel</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
         <is>
-          <t>Railjet Budapeste → Viena · 4 pax</t>
+          <t>Paris · Opção 2 · Hotel Indigo Paris Opéra, IHG 4★</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
         <is>
-          <t>ÖBB RJX 62 · Budapest-Keleti 09:30 → Wien Hbf 12:20 · 2h50 · direto · 1ª classe · assentos marcados</t>
+          <t>Rue de Châteaudun, 9º arr., entre a Ópera Garnier e Montmartre · 1 Standard Queen triplo + 1 Standard Queen duplo · café da manhã · 2 noites</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
         <is>
-          <t>03/01</t>
+          <t>10/01 → 12/01</t>
         </is>
       </c>
       <c r="F20" s="23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G20" s="25" t="inlineStr">
         <is>
@@ -2276,19 +2274,19 @@
         </is>
       </c>
       <c r="I20" s="26" t="n">
-        <v>302.5</v>
+        <v>5715</v>
       </c>
       <c r="J20" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K20" s="27">
         <f>IF(I20="","",I20*J20)</f>
         <v/>
       </c>
-      <c r="L20" s="28" t="inlineStr"/>
+      <c r="L20" s="28" t="n"/>
       <c r="M20" s="25" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="N20" s="29">
@@ -2302,7 +2300,7 @@
       </c>
       <c r="P20" s="30" t="inlineStr">
         <is>
-          <t>Cotação de 21/09: R$ 1.210 para 4 pax (R$ 302,50/pax), 1ª classe.</t>
+          <t>Cotação de 21/09: triplo R$ 6.730 + duplo R$ 4.700 = R$ 11.430 pelas 2 noites (R$ 5.715/noite). Triplo resolve pais + filho sem depender de confirmação.</t>
         </is>
       </c>
     </row>
@@ -2317,21 +2315,21 @@
       </c>
       <c r="C21" s="24" t="inlineStr">
         <is>
-          <t>Railjet Viena → Praga · 5 pax</t>
+          <t>Railjet Budapeste → Viena · 4 pax</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
         <is>
-          <t>ÖBB RJ 252 · Wien Hbf 11:10 → Praha hlavní nádraží 15:23 · 4h13 · direto · 1ª classe · assentos marcados</t>
+          <t>ÖBB RJX 62 · Budapest-Keleti 09:30 → Wien Hbf 12:20 · 2h50 · direto · 1ª classe · assentos marcados</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
         <is>
-          <t>07/01</t>
+          <t>03/01</t>
         </is>
       </c>
       <c r="F21" s="23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G21" s="25" t="inlineStr">
         <is>
@@ -2344,10 +2342,10 @@
         </is>
       </c>
       <c r="I21" s="26" t="n">
-        <v>381</v>
+        <v>302.5</v>
       </c>
       <c r="J21" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K21" s="27">
         <f>IF(I21="","",I21*J21)</f>
@@ -2356,7 +2354,7 @@
       <c r="L21" s="28" t="inlineStr"/>
       <c r="M21" s="25" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="N21" s="29">
@@ -2365,12 +2363,12 @@
       </c>
       <c r="O21" s="25" t="inlineStr">
         <is>
-          <t>Cotado</t>
+          <t>Descartado</t>
         </is>
       </c>
       <c r="P21" s="30" t="inlineStr">
         <is>
-          <t>Cotação de 21/09: R$ 1.905 para 5 pax (R$ 381/pax), 1ª classe.</t>
+          <t>Substituído pelo trajeto via Tokaj (02 e 03/01). Valor de referência: R$ 1.210 para 4 pax em 1ª classe.</t>
         </is>
       </c>
     </row>
@@ -2380,42 +2378,46 @@
       </c>
       <c r="B22" s="23" t="inlineStr">
         <is>
-          <t>Transfer</t>
+          <t>Trem</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
         <is>
-          <t>Budapeste · aeroporto → hotel · 4 pax</t>
+          <t>Trem Budapeste → Tokaj · 4 pax</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
         <is>
-          <t>Van privativa com recepção no desembarque</t>
+          <t>MÁV InterCity · Budapest-Keleti → Tokaj · ~2h30 · 1ª classe · com bagagem</t>
         </is>
       </c>
       <c r="E22" s="23" t="inlineStr">
         <is>
-          <t>30/12</t>
+          <t>02/01</t>
         </is>
       </c>
       <c r="F22" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="G22" s="25" t="inlineStr"/>
+      <c r="G22" s="25" t="inlineStr">
+        <is>
+          <t>Consolidador (a nomear)</t>
+        </is>
+      </c>
       <c r="H22" s="25" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>BRL</t>
         </is>
       </c>
       <c r="I22" s="26" t="n"/>
       <c r="J22" s="25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K22" s="27">
         <f>IF(I22="","",I22*J22)</f>
         <v/>
       </c>
-      <c r="L22" s="28" t="inlineStr"/>
+      <c r="L22" s="28" t="n"/>
       <c r="M22" s="25" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2432,7 +2434,7 @@
       </c>
       <c r="P22" s="30" t="inlineStr">
         <is>
-          <t>Valor unitário = por veículo.</t>
+          <t>Sábado: conferir grade reduzida da MÁV. Ideal saída ~07:30 para chegar às 10h.</t>
         </is>
       </c>
     </row>
@@ -2442,17 +2444,17 @@
       </c>
       <c r="B23" s="23" t="inlineStr">
         <is>
-          <t>Transfer</t>
+          <t>Trem</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
         <is>
-          <t>Budapeste · hotel → estação Keleti · 4 pax</t>
+          <t>Trem Tokaj → Budapeste → Viena · 4 pax</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
         <is>
-          <t>Carro ou van privativa</t>
+          <t>MÁV InterCity Tokaj → Budapest-Keleti + Railjet Keleti → Wien Hbf · ~6h com conexão · 1ª classe</t>
         </is>
       </c>
       <c r="E23" s="23" t="inlineStr">
@@ -2463,21 +2465,25 @@
       <c r="F23" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="G23" s="25" t="inlineStr"/>
+      <c r="G23" s="25" t="inlineStr">
+        <is>
+          <t>Consolidador (a nomear)</t>
+        </is>
+      </c>
       <c r="H23" s="25" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>BRL</t>
         </is>
       </c>
       <c r="I23" s="26" t="n"/>
       <c r="J23" s="25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K23" s="27">
         <f>IF(I23="","",I23*J23)</f>
         <v/>
       </c>
-      <c r="L23" s="28" t="inlineStr"/>
+      <c r="L23" s="28" t="n"/>
       <c r="M23" s="25" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2492,7 +2498,11 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P23" s="30" t="inlineStr"/>
+      <c r="P23" s="30" t="inlineStr">
+        <is>
+          <t>Chegada em Viena no meio da tarde. Deixar folga de ≥ 40 min na conexão em Keleti.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="23" t="n">
@@ -2500,36 +2510,42 @@
       </c>
       <c r="B24" s="23" t="inlineStr">
         <is>
-          <t>Transfer</t>
+          <t>Trem</t>
         </is>
       </c>
       <c r="C24" s="24" t="inlineStr">
         <is>
-          <t>Viena · estação Hbf → hotel · 4 pax</t>
+          <t>Railjet Viena → Praga · 5 pax</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
         <is>
-          <t>Carro ou van privativa</t>
+          <t>ÖBB RJ 252 · Wien Hbf 11:10 → Praha hlavní nádraží 15:23 · 4h13 · direto · 1ª classe · assentos marcados</t>
         </is>
       </c>
       <c r="E24" s="23" t="inlineStr">
         <is>
-          <t>03/01</t>
+          <t>07/01</t>
         </is>
       </c>
       <c r="F24" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="G24" s="25" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="G24" s="25" t="inlineStr">
+        <is>
+          <t>Consolidador (a nomear)</t>
+        </is>
+      </c>
       <c r="H24" s="25" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="I24" s="26" t="n"/>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="I24" s="26" t="n">
+        <v>381</v>
+      </c>
       <c r="J24" s="25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K24" s="27">
         <f>IF(I24="","",I24*J24)</f>
@@ -2547,10 +2563,14 @@
       </c>
       <c r="O24" s="25" t="inlineStr">
         <is>
-          <t>A cotar</t>
-        </is>
-      </c>
-      <c r="P24" s="30" t="inlineStr"/>
+          <t>Cotado</t>
+        </is>
+      </c>
+      <c r="P24" s="30" t="inlineStr">
+        <is>
+          <t>Cotação de 21/09: R$ 1.905 para 5 pax (R$ 381/pax), 1ª classe.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="23" t="n">
@@ -2563,21 +2583,21 @@
       </c>
       <c r="C25" s="24" t="inlineStr">
         <is>
-          <t>Viena · aeroporto → hotel · filho · 1 pax</t>
+          <t>Budapeste · aeroporto → hotel · 4 pax</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
         <is>
-          <t>Motorista com placa no desembarque · reforçar: menor viajando só</t>
+          <t>Van privativa com recepção no desembarque</t>
         </is>
       </c>
       <c r="E25" s="23" t="inlineStr">
         <is>
-          <t>05/01</t>
+          <t>30/12</t>
         </is>
       </c>
       <c r="F25" s="23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G25" s="25" t="inlineStr"/>
       <c r="H25" s="25" t="inlineStr">
@@ -2608,7 +2628,11 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P25" s="30" t="inlineStr"/>
+      <c r="P25" s="30" t="inlineStr">
+        <is>
+          <t>Valor unitário = por veículo.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="23" t="n">
@@ -2621,21 +2645,21 @@
       </c>
       <c r="C26" s="24" t="inlineStr">
         <is>
-          <t>Viena · hotel → estação Hbf · 5 pax</t>
+          <t>Budapeste · hotel → estação Keleti · 4 pax</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
         <is>
-          <t>Van privativa</t>
+          <t>Carro ou van privativa, com bagagem</t>
         </is>
       </c>
       <c r="E26" s="23" t="inlineStr">
         <is>
-          <t>07/01</t>
+          <t>02/01</t>
         </is>
       </c>
       <c r="F26" s="23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G26" s="25" t="inlineStr"/>
       <c r="H26" s="25" t="inlineStr">
@@ -2679,21 +2703,21 @@
       </c>
       <c r="C27" s="24" t="inlineStr">
         <is>
-          <t>Praga · estação hl.n. → hotel · 5 pax</t>
+          <t>Viena · estação Hbf → hotel · 4 pax</t>
         </is>
       </c>
       <c r="D27" s="23" t="inlineStr">
         <is>
-          <t>Van privativa</t>
+          <t>Carro ou van privativa</t>
         </is>
       </c>
       <c r="E27" s="23" t="inlineStr">
         <is>
-          <t>07/01</t>
+          <t>03/01</t>
         </is>
       </c>
       <c r="F27" s="23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G27" s="25" t="inlineStr"/>
       <c r="H27" s="25" t="inlineStr">
@@ -2737,21 +2761,21 @@
       </c>
       <c r="C28" s="24" t="inlineStr">
         <is>
-          <t>Praga · hotel → aeroporto · 5 pax</t>
+          <t>Viena · aeroporto → hotel · filho · 1 pax</t>
         </is>
       </c>
       <c r="D28" s="23" t="inlineStr">
         <is>
-          <t>Van privativa</t>
+          <t>Motorista com placa no desembarque · reforçar: menor viajando só</t>
         </is>
       </c>
       <c r="E28" s="23" t="inlineStr">
         <is>
-          <t>10/01</t>
+          <t>05/01</t>
         </is>
       </c>
       <c r="F28" s="23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G28" s="25" t="inlineStr"/>
       <c r="H28" s="25" t="inlineStr">
@@ -2795,7 +2819,7 @@
       </c>
       <c r="C29" s="24" t="inlineStr">
         <is>
-          <t>Paris · CDG → hotel · 5 pax</t>
+          <t>Viena · hotel → estação Hbf · 5 pax</t>
         </is>
       </c>
       <c r="D29" s="23" t="inlineStr">
@@ -2805,7 +2829,7 @@
       </c>
       <c r="E29" s="23" t="inlineStr">
         <is>
-          <t>10/01</t>
+          <t>07/01</t>
         </is>
       </c>
       <c r="F29" s="23" t="n">
@@ -2853,7 +2877,7 @@
       </c>
       <c r="C30" s="24" t="inlineStr">
         <is>
-          <t>Paris · hotel → CDG · 5 pax</t>
+          <t>Praga · estação hl.n. → hotel · 5 pax</t>
         </is>
       </c>
       <c r="D30" s="23" t="inlineStr">
@@ -2863,7 +2887,7 @@
       </c>
       <c r="E30" s="23" t="inlineStr">
         <is>
-          <t>12/01</t>
+          <t>07/01</t>
         </is>
       </c>
       <c r="F30" s="23" t="n">
@@ -2906,52 +2930,42 @@
       </c>
       <c r="B31" s="23" t="inlineStr">
         <is>
-          <t>Experiência</t>
+          <t>Transfer</t>
         </is>
       </c>
       <c r="C31" s="24" t="inlineStr">
         <is>
-          <t>Réveillon · Opção 1 · Silverline · jantar de gala em catamarã · 4 pax</t>
+          <t>Praga · hotel → aeroporto · 5 pax</t>
         </is>
       </c>
       <c r="D31" s="23" t="inlineStr">
         <is>
-          <t>Cais 11, Ponte Elisabeth · embarque 20h, retorno 1h · welcome cocktail, jantar de 5 pratos, espumante, show de piano · Parlamento iluminado, brinde e fogos à meia-noite</t>
+          <t>Van privativa</t>
         </is>
       </c>
       <c r="E31" s="23" t="inlineStr">
         <is>
-          <t>31/12</t>
+          <t>10/01</t>
         </is>
       </c>
       <c r="F31" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="G31" s="25" t="inlineStr">
-        <is>
-          <t>Silverline Cruises</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="G31" s="25" t="inlineStr"/>
       <c r="H31" s="25" t="inlineStr">
         <is>
-          <t>BRL</t>
-        </is>
-      </c>
-      <c r="I31" s="26" t="n">
-        <v>2146.59</v>
-      </c>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I31" s="26" t="n"/>
       <c r="J31" s="25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K31" s="27">
         <f>IF(I31="","",I31*J31)</f>
         <v/>
       </c>
-      <c r="L31" s="28" t="inlineStr">
-        <is>
-          <t>silver-line.hu/product/budapest-new-years-eve-dinner-cruise</t>
-        </is>
-      </c>
+      <c r="L31" s="28" t="inlineStr"/>
       <c r="M31" s="25" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2963,14 +2977,10 @@
       </c>
       <c r="O31" s="25" t="inlineStr">
         <is>
-          <t>Cotado</t>
-        </is>
-      </c>
-      <c r="P31" s="30" t="inlineStr">
-        <is>
-          <t>Valor por pessoa, conforme a página da Silverline em 21/09.</t>
-        </is>
-      </c>
+          <t>A cotar</t>
+        </is>
+      </c>
+      <c r="P31" s="30" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="23" t="n">
@@ -2978,55 +2988,45 @@
       </c>
       <c r="B32" s="23" t="inlineStr">
         <is>
-          <t>Experiência</t>
+          <t>Transfer</t>
         </is>
       </c>
       <c r="C32" s="24" t="inlineStr">
         <is>
-          <t>Réveillon · Opção 2 · Budapest River Cruise · NYE Party Cruise · 4 pax</t>
+          <t>Paris · CDG → hotel · 5 pax</t>
         </is>
       </c>
       <c r="D32" s="23" t="inlineStr">
         <is>
-          <t>Cais 8/8A, Ponte Elisabeth · embarque 19h, retorno 1h · jantar, música ao vivo e virada a bordo</t>
+          <t>Van privativa</t>
         </is>
       </c>
       <c r="E32" s="23" t="inlineStr">
         <is>
-          <t>31/12</t>
+          <t>10/01</t>
         </is>
       </c>
       <c r="F32" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="G32" s="25" t="inlineStr">
-        <is>
-          <t>Budapest River Cruise</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="G32" s="25" t="inlineStr"/>
       <c r="H32" s="25" t="inlineStr">
         <is>
-          <t>BRL</t>
-        </is>
-      </c>
-      <c r="I32" s="26" t="n">
-        <v>2272.86</v>
-      </c>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I32" s="26" t="n"/>
       <c r="J32" s="25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K32" s="27">
         <f>IF(I32="","",I32*J32)</f>
         <v/>
       </c>
-      <c r="L32" s="28" t="inlineStr">
-        <is>
-          <t>budapestrivercruise.com/budapest-new-years-eve-cruise-party</t>
-        </is>
-      </c>
+      <c r="L32" s="28" t="inlineStr"/>
       <c r="M32" s="25" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="N32" s="29">
@@ -3035,14 +3035,10 @@
       </c>
       <c r="O32" s="25" t="inlineStr">
         <is>
-          <t>Cotado</t>
-        </is>
-      </c>
-      <c r="P32" s="30" t="inlineStr">
-        <is>
-          <t>Valor por pessoa, 6 horas a bordo (19h à 1h). Mais que o dobro da Opção 1 por pessoa. Confirmar preço de menor e o que o jantar inclui.</t>
-        </is>
-      </c>
+          <t>A cotar</t>
+        </is>
+      </c>
+      <c r="P32" s="30" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="23" t="n">
@@ -3050,26 +3046,26 @@
       </c>
       <c r="B33" s="23" t="inlineStr">
         <is>
-          <t>Experiência</t>
+          <t>Transfer</t>
         </is>
       </c>
       <c r="C33" s="24" t="inlineStr">
         <is>
-          <t>Tokaj · motorista-guia privativo · dia inteiro · 4 pax</t>
+          <t>Paris · hotel → CDG · 5 pax</t>
         </is>
       </c>
       <c r="D33" s="23" t="inlineStr">
         <is>
-          <t>Saída 8h de Budapeste, Oremus (Tolcsva) + segunda vinícola + almoço em Mád/Tarcal, retorno ~19h</t>
+          <t>Van privativa</t>
         </is>
       </c>
       <c r="E33" s="23" t="inlineStr">
         <is>
-          <t>02/01</t>
+          <t>12/01</t>
         </is>
       </c>
       <c r="F33" s="23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G33" s="25" t="inlineStr"/>
       <c r="H33" s="25" t="inlineStr">
@@ -3100,11 +3096,7 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P33" s="30" t="inlineStr">
-        <is>
-          <t>Valor unitário = por veículo/dia. Motorista não bebe: tolerância zero na Hungria.</t>
-        </is>
-      </c>
+      <c r="P33" s="30" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="23" t="n">
@@ -3117,17 +3109,17 @@
       </c>
       <c r="C34" s="24" t="inlineStr">
         <is>
-          <t>Oremus · visita à adega e prova · 2 adultos + 2 filhas</t>
+          <t>Réveillon · Opção 1 · Silverline · jantar de gala em catamarã · 4 pax</t>
         </is>
       </c>
       <c r="D34" s="23" t="inlineStr">
         <is>
-          <t>Tolcsva · agendamento por e-mail · ~1h · adegas do século XIII · adolescentes acompanham sem álcool</t>
+          <t>Cais 11, Ponte Elisabeth · embarque 20h, retorno 1h · welcome cocktail, jantar de 5 pratos, espumante, show de piano · Parlamento iluminado, brinde e fogos à meia-noite</t>
         </is>
       </c>
       <c r="E34" s="23" t="inlineStr">
         <is>
-          <t>02/01</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="F34" s="23" t="n">
@@ -3135,7 +3127,7 @@
       </c>
       <c r="G34" s="25" t="inlineStr">
         <is>
-          <t>Tokaj-Oremus</t>
+          <t>Silverline Cruises</t>
         </is>
       </c>
       <c r="H34" s="25" t="inlineStr">
@@ -3144,16 +3136,20 @@
         </is>
       </c>
       <c r="I34" s="26" t="n">
-        <v>315.67</v>
+        <v>2146.59</v>
       </c>
       <c r="J34" s="25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K34" s="27">
         <f>IF(I34="","",I34*J34)</f>
         <v/>
       </c>
-      <c r="L34" s="28" t="inlineStr"/>
+      <c r="L34" s="28" t="inlineStr">
+        <is>
+          <t>silver-line.hu/product/budapest-new-years-eve-dinner-cruise</t>
+        </is>
+      </c>
       <c r="M34" s="25" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -3170,7 +3166,7 @@
       </c>
       <c r="P34" s="30" t="inlineStr">
         <is>
-          <t>Cotação de 21/09 em reais para a família (2 adultos e 2 filhas). Confirmar recepção no sábado 02/01; plano B: segunda 04/01.</t>
+          <t>Valor por pessoa, conforme a página da Silverline em 21/09.</t>
         </is>
       </c>
     </row>
@@ -3185,17 +3181,17 @@
       </c>
       <c r="C35" s="24" t="inlineStr">
         <is>
-          <t>Disznókő · visita e prova · 2 adultos + 2 filhas</t>
+          <t>Réveillon · Opção 2 · Budapest River Cruise · NYE Party Cruise · 4 pax</t>
         </is>
       </c>
       <c r="D35" s="23" t="inlineStr">
         <is>
-          <t>Mezőzombor, a 20 min de Tolcsva · vinícola do grupo AXA Millésimes · segunda parada da tarde</t>
+          <t>Cais 8/8A, Ponte Elisabeth · embarque 19h, retorno 1h · jantar, música ao vivo e virada a bordo</t>
         </is>
       </c>
       <c r="E35" s="23" t="inlineStr">
         <is>
-          <t>02/01</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="F35" s="23" t="n">
@@ -3203,7 +3199,7 @@
       </c>
       <c r="G35" s="25" t="inlineStr">
         <is>
-          <t>Disznókő</t>
+          <t>Budapest River Cruise</t>
         </is>
       </c>
       <c r="H35" s="25" t="inlineStr">
@@ -3211,18 +3207,24 @@
           <t>BRL</t>
         </is>
       </c>
-      <c r="I35" s="26" t="n"/>
+      <c r="I35" s="26" t="n">
+        <v>2272.86</v>
+      </c>
       <c r="J35" s="25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K35" s="27">
         <f>IF(I35="","",I35*J35)</f>
         <v/>
       </c>
-      <c r="L35" s="28" t="n"/>
+      <c r="L35" s="28" t="inlineStr">
+        <is>
+          <t>budapestrivercruise.com/budapest-new-years-eve-cruise-party</t>
+        </is>
+      </c>
       <c r="M35" s="25" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="N35" s="29">
@@ -3231,12 +3233,12 @@
       </c>
       <c r="O35" s="25" t="inlineStr">
         <is>
-          <t>A cotar</t>
+          <t>Cotado</t>
         </is>
       </c>
       <c r="P35" s="30" t="inlineStr">
         <is>
-          <t>Aguardando valores da vinícola.</t>
+          <t>Valor por pessoa, 6 horas a bordo (19h à 1h). Mais que o dobro da Opção 1 por pessoa. Confirmar preço de menor e o que o jantar inclui.</t>
         </is>
       </c>
     </row>
@@ -3251,12 +3253,12 @@
       </c>
       <c r="C36" s="24" t="inlineStr">
         <is>
-          <t>Almoço em vinícola ou restaurante em Tokaj · 4 pax</t>
+          <t>Tokaj · táxi local contratado pelo dia · 4 pax</t>
         </is>
       </c>
       <c r="D36" s="23" t="inlineStr">
         <is>
-          <t>Mád ou Tarcal</t>
+          <t>Estação de Tokaj → Oremus (Tolcsva) → almoço → Disznókő (Mezőzombor) → Minaro Hotel · 03/01 hotel → estação</t>
         </is>
       </c>
       <c r="E36" s="23" t="inlineStr">
@@ -3267,15 +3269,19 @@
       <c r="F36" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="G36" s="25" t="inlineStr"/>
+      <c r="G36" s="25" t="inlineStr">
+        <is>
+          <t>Motorista local (indicação da Oremus)</t>
+        </is>
+      </c>
       <c r="H36" s="25" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>BRL</t>
         </is>
       </c>
       <c r="I36" s="26" t="n"/>
       <c r="J36" s="25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K36" s="27">
         <f>IF(I36="","",I36*J36)</f>
@@ -3298,7 +3304,7 @@
       </c>
       <c r="P36" s="30" t="inlineStr">
         <is>
-          <t>Pode vir incluído no pacote do motorista-guia.</t>
+          <t>Substitui o motorista-guia de Budapeste, que veio muito caro. Referência: € 120 a 180 pelo dia.</t>
         </is>
       </c>
     </row>
@@ -3308,30 +3314,30 @@
       </c>
       <c r="B37" s="23" t="inlineStr">
         <is>
-          <t>Seguro/Docs</t>
+          <t>Experiência</t>
         </is>
       </c>
       <c r="C37" s="24" t="inlineStr">
         <is>
-          <t>Seguro viagem · 5 pax · 15 dias</t>
+          <t>Oremus · visita à adega e prova · 2 adultos + 2 filhas</t>
         </is>
       </c>
       <c r="D37" s="23" t="inlineStr">
         <is>
-          <t>Plano 90 Essential · DMH USD 90.000 · 29/12 a 12/01</t>
+          <t>Tolcsva · agendamento por e-mail · ~1h · adegas do século XIII · adolescentes acompanham sem álcool</t>
         </is>
       </c>
       <c r="E37" s="23" t="inlineStr">
         <is>
-          <t>29/12 → 12/01</t>
+          <t>02/01</t>
         </is>
       </c>
       <c r="F37" s="23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G37" s="25" t="inlineStr">
         <is>
-          <t>31 Motivos</t>
+          <t>Tokaj-Oremus</t>
         </is>
       </c>
       <c r="H37" s="25" t="inlineStr">
@@ -3340,10 +3346,10 @@
         </is>
       </c>
       <c r="I37" s="26" t="n">
-        <v>300.6</v>
+        <v>315.67</v>
       </c>
       <c r="J37" s="25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K37" s="27">
         <f>IF(I37="","",I37*J37)</f>
@@ -3366,74 +3372,271 @@
       </c>
       <c r="P37" s="30" t="inlineStr">
         <is>
+          <t>Cotação de 21/09 em reais para a família (2 adultos e 2 filhas). Confirmar recepção no sábado 02/01; plano B: segunda 04/01.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="23" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="23" t="inlineStr">
+        <is>
+          <t>Experiência</t>
+        </is>
+      </c>
+      <c r="C38" s="24" t="inlineStr">
+        <is>
+          <t>Disznókő · visita e prova · 2 adultos + 2 filhas</t>
+        </is>
+      </c>
+      <c r="D38" s="23" t="inlineStr">
+        <is>
+          <t>Mezőzombor, a 20 min de Tolcsva · vinícola do grupo AXA Millésimes · segunda parada da tarde</t>
+        </is>
+      </c>
+      <c r="E38" s="23" t="inlineStr">
+        <is>
+          <t>02/01</t>
+        </is>
+      </c>
+      <c r="F38" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="G38" s="25" t="inlineStr">
+        <is>
+          <t>Disznókő</t>
+        </is>
+      </c>
+      <c r="H38" s="25" t="inlineStr">
+        <is>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="I38" s="26" t="n"/>
+      <c r="J38" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" s="27">
+        <f>IF(I38="","",I38*J38)</f>
+        <v/>
+      </c>
+      <c r="L38" s="28" t="n"/>
+      <c r="M38" s="25" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="N38" s="29">
+        <f>IF(OR(M38&lt;&gt;"Sim",I38=""),0,K38*IF(H38="BRL",1,IF(H38="EUR",Parâmetros!$B$4,IF(H38="USD",Parâmetros!$B$5,1))))</f>
+        <v/>
+      </c>
+      <c r="O38" s="25" t="inlineStr">
+        <is>
+          <t>A cotar</t>
+        </is>
+      </c>
+      <c r="P38" s="30" t="inlineStr">
+        <is>
+          <t>Aguardando valores da vinícola.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="23" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="23" t="inlineStr">
+        <is>
+          <t>Experiência</t>
+        </is>
+      </c>
+      <c r="C39" s="24" t="inlineStr">
+        <is>
+          <t>Almoço em vinícola ou restaurante em Tokaj · 4 pax</t>
+        </is>
+      </c>
+      <c r="D39" s="23" t="inlineStr">
+        <is>
+          <t>Mád ou Tarcal</t>
+        </is>
+      </c>
+      <c r="E39" s="23" t="inlineStr">
+        <is>
+          <t>02/01</t>
+        </is>
+      </c>
+      <c r="F39" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="G39" s="25" t="inlineStr"/>
+      <c r="H39" s="25" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I39" s="26" t="n"/>
+      <c r="J39" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="K39" s="27">
+        <f>IF(I39="","",I39*J39)</f>
+        <v/>
+      </c>
+      <c r="L39" s="28" t="inlineStr"/>
+      <c r="M39" s="25" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="N39" s="29">
+        <f>IF(OR(M39&lt;&gt;"Sim",I39=""),0,K39*IF(H39="BRL",1,IF(H39="EUR",Parâmetros!$B$4,IF(H39="USD",Parâmetros!$B$5,1))))</f>
+        <v/>
+      </c>
+      <c r="O39" s="25" t="inlineStr">
+        <is>
+          <t>A cotar</t>
+        </is>
+      </c>
+      <c r="P39" s="30" t="inlineStr">
+        <is>
+          <t>Pode vir incluído no pacote do motorista-guia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="23" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="23" t="inlineStr">
+        <is>
+          <t>Seguro/Docs</t>
+        </is>
+      </c>
+      <c r="C40" s="24" t="inlineStr">
+        <is>
+          <t>Seguro viagem · 5 pax · 15 dias</t>
+        </is>
+      </c>
+      <c r="D40" s="23" t="inlineStr">
+        <is>
+          <t>Plano 90 Essential · DMH USD 90.000 · 29/12 a 12/01</t>
+        </is>
+      </c>
+      <c r="E40" s="23" t="inlineStr">
+        <is>
+          <t>29/12 → 12/01</t>
+        </is>
+      </c>
+      <c r="F40" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="G40" s="25" t="inlineStr">
+        <is>
+          <t>31 Motivos</t>
+        </is>
+      </c>
+      <c r="H40" s="25" t="inlineStr">
+        <is>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="I40" s="26" t="n">
+        <v>300.6</v>
+      </c>
+      <c r="J40" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="K40" s="27">
+        <f>IF(I40="","",I40*J40)</f>
+        <v/>
+      </c>
+      <c r="L40" s="28" t="inlineStr"/>
+      <c r="M40" s="25" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="N40" s="29">
+        <f>IF(OR(M40&lt;&gt;"Sim",I40=""),0,K40*IF(H40="BRL",1,IF(H40="EUR",Parâmetros!$B$4,IF(H40="USD",Parâmetros!$B$5,1))))</f>
+        <v/>
+      </c>
+      <c r="O40" s="25" t="inlineStr">
+        <is>
+          <t>Cotado</t>
+        </is>
+      </c>
+      <c r="P40" s="30" t="inlineStr">
+        <is>
           <t>Cotação de 21/09: R$ 1.503,00 para os 5 (R$ 300,60 por pessoa). Confirmar se a apólice do filho cobre desde o embarque dele em 04/01.</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="C39" s="21" t="inlineStr">
+    <row r="41"/>
+    <row r="42">
+      <c r="C42" s="21" t="inlineStr">
         <is>
           <t>SUBTOTAL EM R$ (itens marcados como Sim)</t>
         </is>
       </c>
-      <c r="N39" s="31">
-        <f>SUM(N5:N37)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="C40" s="12" t="inlineStr">
+      <c r="N42" s="31">
+        <f>SUM(N5:N40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" s="12" t="inlineStr">
         <is>
           <t>Taxa de serviço LusaTravel</t>
         </is>
       </c>
-      <c r="N40" s="13">
-        <f>N39*Parâmetros!$B$10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="32" t="n"/>
-      <c r="B41" s="32" t="n"/>
-      <c r="C41" s="33" t="inlineStr">
+      <c r="N43" s="13">
+        <f>N42*Parâmetros!$B$10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="32" t="n"/>
+      <c r="B44" s="32" t="n"/>
+      <c r="C44" s="33" t="inlineStr">
         <is>
           <t>TOTAL PARA O CLIENTE</t>
         </is>
       </c>
-      <c r="D41" s="32" t="n"/>
-      <c r="E41" s="32" t="n"/>
-      <c r="F41" s="32" t="n"/>
-      <c r="G41" s="32" t="n"/>
-      <c r="H41" s="32" t="n"/>
-      <c r="I41" s="32" t="n"/>
-      <c r="J41" s="32" t="n"/>
-      <c r="K41" s="32" t="n"/>
-      <c r="L41" s="32" t="n"/>
-      <c r="M41" s="32" t="n"/>
-      <c r="N41" s="34">
-        <f>N39+N40</f>
-        <v/>
-      </c>
-      <c r="O41" s="32" t="n"/>
-      <c r="P41" s="32" t="n"/>
-    </row>
-    <row r="42">
-      <c r="C42" s="2" t="inlineStr">
+      <c r="D44" s="32" t="n"/>
+      <c r="E44" s="32" t="n"/>
+      <c r="F44" s="32" t="n"/>
+      <c r="G44" s="32" t="n"/>
+      <c r="H44" s="32" t="n"/>
+      <c r="I44" s="32" t="n"/>
+      <c r="J44" s="32" t="n"/>
+      <c r="K44" s="32" t="n"/>
+      <c r="L44" s="32" t="n"/>
+      <c r="M44" s="32" t="n"/>
+      <c r="N44" s="34">
+        <f>N42+N43</f>
+        <v/>
+      </c>
+      <c r="O44" s="32" t="n"/>
+      <c r="P44" s="32" t="n"/>
+    </row>
+    <row r="45">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>*Nada reservado, apenas cotado.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:P37"/>
+  <autoFilter ref="A4:P40"/>
   <dataValidations count="3">
-    <dataValidation sqref="O5:O37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O5:O40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"A cotar,Cotado,Aprovado pelo cliente,Reservado,Descartado"</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="M5:M40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="H5:H40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"BRL,EUR,USD"</formula1>
     </dataValidation>
   </dataValidations>

--- a/cotacao-cristofer-reveillon.xlsx
+++ b/cotacao-cristofer-reveillon.xlsx
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="I10" s="26" t="n">
-        <v>8400</v>
+        <v>6300</v>
       </c>
       <c r="J10" s="25" t="n">
         <v>2</v>
@@ -1603,12 +1603,12 @@
       </c>
       <c r="O10" s="25" t="inlineStr">
         <is>
-          <t>A cotar</t>
+          <t>Cotado</t>
         </is>
       </c>
       <c r="P10" s="30" t="inlineStr">
         <is>
-          <t>Valor lançado é o das 4 noites. Pedir recotação para 3 noites (30/12 → 02/01); tarifa de Réveillon não é proporcional.</t>
+          <t>3 noites calculadas proporcionalmente a partir da cotação de 4 noites (R$ 16.800 → R$ 12.600). Confirmar com o hotel na reserva.</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="I11" s="26" t="n">
-        <v>6700</v>
+        <v>5025</v>
       </c>
       <c r="J11" s="25" t="n">
         <v>2</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="O11" s="25" t="inlineStr">
         <is>
-          <t>A cotar</t>
+          <t>Cotado</t>
         </is>
       </c>
       <c r="P11" s="30" t="inlineStr">
         <is>
-          <t>Valor lançado é o das 4 noites. Pedir recotação para 3 noites (30/12 → 02/01); tarifa de Réveillon não é proporcional.</t>
+          <t>3 noites calculadas proporcionalmente a partir da cotação de 4 noites (R$ 13.400 → R$ 10.050). Confirmar com o hotel na reserva.</t>
         </is>
       </c>
     </row>
@@ -1722,7 +1722,7 @@
         </is>
       </c>
       <c r="I12" s="26" t="n">
-        <v>8690</v>
+        <v>6517.5</v>
       </c>
       <c r="J12" s="25" t="n">
         <v>2</v>
@@ -1747,12 +1747,12 @@
       </c>
       <c r="O12" s="25" t="inlineStr">
         <is>
-          <t>A cotar</t>
+          <t>Cotado</t>
         </is>
       </c>
       <c r="P12" s="30" t="inlineStr">
         <is>
-          <t>Valor lançado é o das 4 noites. Pedir recotação para 3 noites (30/12 → 02/01); tarifa de Réveillon não é proporcional.</t>
+          <t>3 noites calculadas proporcionalmente a partir da cotação de 4 noites (R$ 17.380 → R$ 13.035). Confirmar com o hotel na reserva.</t>
         </is>
       </c>
     </row>
@@ -3572,7 +3572,6 @@
         </is>
       </c>
     </row>
-    <row r="41"/>
     <row r="42">
       <c r="C42" s="21" t="inlineStr">
         <is>

--- a/cotacao-cristofer-reveillon.xlsx
+++ b/cotacao-cristofer-reveillon.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Cotação" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Cotação'!$A$4:$P$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Cotação'!$A$4:$P$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -625,19 +625,19 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$40,A5)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$39,A5)</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$40,A5,Cotação!$O$5:$O$40,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$39,A5,Cotação!$O$5:$O$39,"A cotar")</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$40,A5,Cotação!$O$5:$O$40,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$39,A5,Cotação!$O$5:$O$39,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E5" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$40,A5,Cotação!$N$5:$N$40)</f>
+        <f>SUMIF(Cotação!$B$5:$B$39,A5,Cotação!$N$5:$N$39)</f>
         <v/>
       </c>
     </row>
@@ -648,19 +648,19 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$40,A6)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$39,A6)</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$40,A6,Cotação!$O$5:$O$40,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$39,A6,Cotação!$O$5:$O$39,"A cotar")</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$40,A6,Cotação!$O$5:$O$40,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$39,A6,Cotação!$O$5:$O$39,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E6" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$40,A6,Cotação!$N$5:$N$40)</f>
+        <f>SUMIF(Cotação!$B$5:$B$39,A6,Cotação!$N$5:$N$39)</f>
         <v/>
       </c>
     </row>
@@ -671,19 +671,19 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$40,A7)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$39,A7)</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$40,A7,Cotação!$O$5:$O$40,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$39,A7,Cotação!$O$5:$O$39,"A cotar")</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$40,A7,Cotação!$O$5:$O$40,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$39,A7,Cotação!$O$5:$O$39,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E7" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$40,A7,Cotação!$N$5:$N$40)</f>
+        <f>SUMIF(Cotação!$B$5:$B$39,A7,Cotação!$N$5:$N$39)</f>
         <v/>
       </c>
     </row>
@@ -694,19 +694,19 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$40,A8)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$39,A8)</f>
         <v/>
       </c>
       <c r="C8" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$40,A8,Cotação!$O$5:$O$40,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$39,A8,Cotação!$O$5:$O$39,"A cotar")</f>
         <v/>
       </c>
       <c r="D8" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$40,A8,Cotação!$O$5:$O$40,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$39,A8,Cotação!$O$5:$O$39,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E8" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$40,A8,Cotação!$N$5:$N$40)</f>
+        <f>SUMIF(Cotação!$B$5:$B$39,A8,Cotação!$N$5:$N$39)</f>
         <v/>
       </c>
     </row>
@@ -717,19 +717,19 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$40,A9)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$39,A9)</f>
         <v/>
       </c>
       <c r="C9" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$40,A9,Cotação!$O$5:$O$40,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$39,A9,Cotação!$O$5:$O$39,"A cotar")</f>
         <v/>
       </c>
       <c r="D9" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$40,A9,Cotação!$O$5:$O$40,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$39,A9,Cotação!$O$5:$O$39,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E9" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$40,A9,Cotação!$N$5:$N$40)</f>
+        <f>SUMIF(Cotação!$B$5:$B$39,A9,Cotação!$N$5:$N$39)</f>
         <v/>
       </c>
     </row>
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$40,A10)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$39,A10)</f>
         <v/>
       </c>
       <c r="C10" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$40,A10,Cotação!$O$5:$O$40,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$39,A10,Cotação!$O$5:$O$39,"A cotar")</f>
         <v/>
       </c>
       <c r="D10" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$40,A10,Cotação!$O$5:$O$40,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$39,A10,Cotação!$O$5:$O$39,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$40,A10,Cotação!$N$5:$N$40)</f>
+        <f>SUMIF(Cotação!$B$5:$B$39,A10,Cotação!$N$5:$N$39)</f>
         <v/>
       </c>
     </row>
@@ -763,19 +763,19 @@
         </is>
       </c>
       <c r="B11" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$40,A11)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$39,A11)</f>
         <v/>
       </c>
       <c r="C11" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$40,A11,Cotação!$O$5:$O$40,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$39,A11,Cotação!$O$5:$O$39,"A cotar")</f>
         <v/>
       </c>
       <c r="D11" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$40,A11,Cotação!$O$5:$O$40,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$39,A11,Cotação!$O$5:$O$39,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E11" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$40,A11,Cotação!$N$5:$N$40)</f>
+        <f>SUMIF(Cotação!$B$5:$B$39,A11,Cotação!$N$5:$N$39)</f>
         <v/>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P45"/>
+  <dimension ref="A1:P44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="C5" s="24" t="inlineStr">
         <is>
-          <t>Aéreo internacional · 4 pax · Opção A · volta 12/01 12:05</t>
+          <t>Aéreo internacional · 4 pax</t>
         </is>
       </c>
       <c r="D5" s="23" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="P5" s="30" t="inlineStr">
         <is>
-          <t>Cotação de 20/09: R$ 41.637,56 total (USD 8.073,20) = R$ 10.409,39 por pax. Inclui Praga → Paris. Nesta opção o filho viaja em voos diferentes em 10/01 e 12/01 (chega ao Brasil em 13/01 de manhã).</t>
+          <t>Cotação de 20/09: R$ 41.637,56 total (USD 8.073,20) = R$ 10.409,39 por pax. Inclui Praga → Paris.</t>
         </is>
       </c>
     </row>
@@ -1297,40 +1297,46 @@
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>Aéreo internacional · 4 pax · Opção B · volta 12/01 23:20, junto com o filho</t>
+          <t>Aéreo do filho · 1 pax</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
         <is>
-          <t>Mesma ida (LA1579 + IB869) · AF1383 PRG 10/01 12:10 → CDG 14:05 · AF454 CDG 12/01 23:20 → GRU 13/01 07:20 · os cinco nos mesmos voos em 10/01 e 12/01 · dia 12 inteiro em Paris</t>
+          <t>AF453 GRU 04/01 14:40 → CDG 05/01 06:05 · AF1138 CDG 10:00 → VIE 12:00 (conexão 3h55) · AF1383 PRG 10/01 12:10 → CDG 14:05 · AF454 CDG 12/01 23:20 → GRU 13/01 07:20 · econômica</t>
         </is>
       </c>
       <c r="E6" s="23" t="inlineStr">
         <is>
-          <t>29/12 e 12/01</t>
+          <t>04/01 e 12/01</t>
         </is>
       </c>
       <c r="F6" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="G6" s="25" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G6" s="25" t="inlineStr">
+        <is>
+          <t>Air France (consolidador)</t>
+        </is>
+      </c>
       <c r="H6" s="25" t="inlineStr">
         <is>
           <t>BRL</t>
         </is>
       </c>
-      <c r="I6" s="26" t="n"/>
+      <c r="I6" s="26" t="n">
+        <v>12056.63</v>
+      </c>
       <c r="J6" s="25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K6" s="27">
         <f>IF(I6="","",I6*J6)</f>
         <v/>
       </c>
-      <c r="L6" s="28" t="n"/>
+      <c r="L6" s="28" t="inlineStr"/>
       <c r="M6" s="25" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="N6" s="29">
@@ -1339,12 +1345,12 @@
       </c>
       <c r="O6" s="25" t="inlineStr">
         <is>
-          <t>A cotar</t>
+          <t>Cotado</t>
         </is>
       </c>
       <c r="P6" s="30" t="inlineStr">
         <is>
-          <t>A recotar com o consolidador. Decisão do cliente: chegar ao Brasil na noite de 12/01 separado do filho, ou na manhã de 13/01 com ele.</t>
+          <t>Recotação de 20/09: R$ 12.056,63 (USD 2.337,69).</t>
         </is>
       </c>
     </row>
@@ -1359,35 +1365,29 @@
       </c>
       <c r="C7" s="24" t="inlineStr">
         <is>
-          <t>Aéreo do filho · 1 pax</t>
+          <t>Voo Praga → Paris · filho · 1 pax</t>
         </is>
       </c>
       <c r="D7" s="23" t="inlineStr">
         <is>
-          <t>AF453 GRU 04/01 14:40 → CDG 05/01 06:05 · AF1138 CDG 10:00 → VIE 12:00 (conexão 3h55) · AF1383 PRG 10/01 12:10 → CDG 14:05 · AF454 CDG 12/01 23:20 → GRU 13/01 07:20 · econômica</t>
+          <t>PRG → CDG 10/01 · os 4 já estão no bilhete internacional (AF1183) · ideal: mesmo voo AF1183 09:50</t>
         </is>
       </c>
       <c r="E7" s="23" t="inlineStr">
         <is>
-          <t>04/01 e 12/01</t>
+          <t>10/01</t>
         </is>
       </c>
       <c r="F7" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="25" t="inlineStr">
-        <is>
-          <t>Air France (consolidador)</t>
-        </is>
-      </c>
+      <c r="G7" s="25" t="inlineStr"/>
       <c r="H7" s="25" t="inlineStr">
         <is>
-          <t>BRL</t>
-        </is>
-      </c>
-      <c r="I7" s="26" t="n">
-        <v>12056.63</v>
-      </c>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I7" s="26" t="n"/>
       <c r="J7" s="25" t="n">
         <v>1</v>
       </c>
@@ -1398,7 +1398,7 @@
       <c r="L7" s="28" t="inlineStr"/>
       <c r="M7" s="25" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="N7" s="29">
@@ -1407,12 +1407,12 @@
       </c>
       <c r="O7" s="25" t="inlineStr">
         <is>
-          <t>Cotado</t>
+          <t>Descartado</t>
         </is>
       </c>
       <c r="P7" s="30" t="inlineStr">
         <is>
-          <t>Recotação de 20/09: R$ 12.056,63 (USD 2.337,69). Com a Opção A dos 4, ele viaja separado em 10/01 e 12/01; com a Opção B, os cinco viajam juntos.</t>
+          <t>Incluído no multitrecho do filho (AF1383). Não cotar à parte.</t>
         </is>
       </c>
     </row>
@@ -1427,31 +1427,31 @@
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>Voo Praga → Paris · filho · 1 pax</t>
+          <t>Opcional · upgrade de cabine</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
         <is>
-          <t>PRG → CDG 10/01 · os 4 já estão no bilhete internacional (AF1183) · ideal: mesmo voo AF1183 09:50</t>
+          <t>Diferença para Premium Economy ou Executiva no trecho internacional · 5 pax</t>
         </is>
       </c>
       <c r="E8" s="23" t="inlineStr">
         <is>
-          <t>10/01</t>
+          <t>29/12, 04/01 e 12/01</t>
         </is>
       </c>
       <c r="F8" s="23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G8" s="25" t="inlineStr"/>
       <c r="H8" s="25" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>BRL</t>
         </is>
       </c>
       <c r="I8" s="26" t="n"/>
       <c r="J8" s="25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K8" s="27">
         <f>IF(I8="","",I8*J8)</f>
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O8" s="25" t="inlineStr">
         <is>
-          <t>Descartado</t>
+          <t>A cotar</t>
         </is>
       </c>
       <c r="P8" s="30" t="inlineStr">
         <is>
-          <t>Incluído no multitrecho do filho (AF1383). Não cotar à parte.</t>
+          <t>Só entra no total se o cliente pedir.</t>
         </is>
       </c>
     </row>
@@ -1484,42 +1484,52 @@
       </c>
       <c r="B9" s="23" t="inlineStr">
         <is>
-          <t>Aéreo</t>
+          <t>Hotel</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
         <is>
-          <t>Opcional · upgrade de cabine</t>
+          <t>Budapeste · Opção 1 · Barceló Budapest 4★</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
         <is>
-          <t>Diferença para Premium Economy ou Executiva no trecho internacional · 5 pax</t>
+          <t>Király utca, Terézváros, a 5 min da Basílica · 2 quartos Superior Double · café da manhã · 3 noites</t>
         </is>
       </c>
       <c r="E9" s="23" t="inlineStr">
         <is>
-          <t>29/12, 04/01 e 12/01</t>
+          <t>30/12 → 02/01</t>
         </is>
       </c>
       <c r="F9" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="G9" s="25" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G9" s="25" t="inlineStr">
+        <is>
+          <t>Consolidador (a nomear)</t>
+        </is>
+      </c>
       <c r="H9" s="25" t="inlineStr">
         <is>
           <t>BRL</t>
         </is>
       </c>
-      <c r="I9" s="26" t="n"/>
+      <c r="I9" s="26" t="n">
+        <v>6300</v>
+      </c>
       <c r="J9" s="25" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K9" s="27">
         <f>IF(I9="","",I9*J9)</f>
         <v/>
       </c>
-      <c r="L9" s="28" t="inlineStr"/>
+      <c r="L9" s="28" t="inlineStr">
+        <is>
+          <t>Booking 20/09: R$ 15.136 pelas 2 quartos/4 noites no mesmo hotel · InterContinental 5★ € 2.398 · Corinthia 5★ € 2.939</t>
+        </is>
+      </c>
       <c r="M9" s="25" t="inlineStr">
         <is>
           <t>Não</t>
@@ -1531,12 +1541,12 @@
       </c>
       <c r="O9" s="25" t="inlineStr">
         <is>
-          <t>A cotar</t>
+          <t>Cotado</t>
         </is>
       </c>
       <c r="P9" s="30" t="inlineStr">
         <is>
-          <t>Só entra no total se o cliente pedir.</t>
+          <t>3 noites calculadas proporcionalmente a partir da cotação de 4 noites (R$ 16.800 → R$ 12.600). Confirmar com o hotel na reserva.</t>
         </is>
       </c>
     </row>
@@ -1551,12 +1561,12 @@
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>Budapeste · Opção 1 · Barceló Budapest 4★</t>
+          <t>Budapeste · Opção 2 · Mercure Budapest City Center 4★</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
         <is>
-          <t>Király utca, Terézváros, a 5 min da Basílica · 2 quartos Superior Double · café da manhã · 3 noites</t>
+          <t>Váci utca, coração de Pest, pedestre · 2 quartos Superior · café da manhã · 3 noites</t>
         </is>
       </c>
       <c r="E10" s="23" t="inlineStr">
@@ -1578,7 +1588,7 @@
         </is>
       </c>
       <c r="I10" s="26" t="n">
-        <v>6300</v>
+        <v>5025</v>
       </c>
       <c r="J10" s="25" t="n">
         <v>2</v>
@@ -1589,7 +1599,7 @@
       </c>
       <c r="L10" s="28" t="inlineStr">
         <is>
-          <t>Booking 20/09: R$ 15.136 pelas 2 quartos/4 noites no mesmo hotel · InterContinental 5★ € 2.398 · Corinthia 5★ € 2.939</t>
+          <t>Booking 20/09: R$ 11.016 pelos 2 quartos/4 noites no mesmo hotel</t>
         </is>
       </c>
       <c r="M10" s="25" t="inlineStr">
@@ -1608,7 +1618,7 @@
       </c>
       <c r="P10" s="30" t="inlineStr">
         <is>
-          <t>3 noites calculadas proporcionalmente a partir da cotação de 4 noites (R$ 16.800 → R$ 12.600). Confirmar com o hotel na reserva.</t>
+          <t>3 noites calculadas proporcionalmente a partir da cotação de 4 noites (R$ 13.400 → R$ 10.050). Confirmar com o hotel na reserva.</t>
         </is>
       </c>
     </row>
@@ -1623,12 +1633,12 @@
       </c>
       <c r="C11" s="24" t="inlineStr">
         <is>
-          <t>Budapeste · Opção 2 · Mercure Budapest City Center 4★</t>
+          <t>Budapeste · Opção 3 · InterContinental Budapest 5★</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
         <is>
-          <t>Váci utca, coração de Pest, pedestre · 2 quartos Superior · café da manhã · 3 noites</t>
+          <t>Margem do Danúbio, vista para o Castelo e a Ponte das Correntes · 2 quartos Classic · café da manhã · 3 noites</t>
         </is>
       </c>
       <c r="E11" s="23" t="inlineStr">
@@ -1650,7 +1660,7 @@
         </is>
       </c>
       <c r="I11" s="26" t="n">
-        <v>5025</v>
+        <v>6517.5</v>
       </c>
       <c r="J11" s="25" t="n">
         <v>2</v>
@@ -1661,12 +1671,12 @@
       </c>
       <c r="L11" s="28" t="inlineStr">
         <is>
-          <t>Booking 20/09: R$ 11.016 pelos 2 quartos/4 noites no mesmo hotel</t>
+          <t>Booking 20/09: € 2.398 (≈ R$ 14.172) pelos 2 quartos/4 noites no mesmo hotel, tarifa mais barata</t>
         </is>
       </c>
       <c r="M11" s="25" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="N11" s="29">
@@ -1680,7 +1690,7 @@
       </c>
       <c r="P11" s="30" t="inlineStr">
         <is>
-          <t>3 noites calculadas proporcionalmente a partir da cotação de 4 noites (R$ 13.400 → R$ 10.050). Confirmar com o hotel na reserva.</t>
+          <t>3 noites calculadas proporcionalmente a partir da cotação de 4 noites (R$ 17.380 → R$ 13.035). Confirmar com o hotel na reserva.</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1705,17 @@
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>Budapeste · Opção 3 · InterContinental Budapest 5★</t>
+          <t>Tokaj · Minaro Hotel Tokaj, MGallery 5★</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
         <is>
-          <t>Margem do Danúbio, vista para o Castelo e a Ponte das Correntes · 2 quartos Classic · café da manhã · 3 noites</t>
+          <t>Tokaj, à beira do rio Bodrog, a 5 min da estação · 2 quartos duplos · café da manhã · 1 noite</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">
         <is>
-          <t>30/12 → 02/01</t>
+          <t>02/01 → 03/01</t>
         </is>
       </c>
       <c r="F12" s="23" t="n">
@@ -1721,21 +1731,15 @@
           <t>BRL</t>
         </is>
       </c>
-      <c r="I12" s="26" t="n">
-        <v>6517.5</v>
-      </c>
+      <c r="I12" s="26" t="n"/>
       <c r="J12" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K12" s="27">
         <f>IF(I12="","",I12*J12)</f>
         <v/>
       </c>
-      <c r="L12" s="28" t="inlineStr">
-        <is>
-          <t>Booking 20/09: € 2.398 (≈ R$ 14.172) pelos 2 quartos/4 noites no mesmo hotel, tarifa mais barata</t>
-        </is>
-      </c>
+      <c r="L12" s="28" t="n"/>
       <c r="M12" s="25" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1747,12 +1751,12 @@
       </c>
       <c r="O12" s="25" t="inlineStr">
         <is>
-          <t>Cotado</t>
+          <t>A cotar</t>
         </is>
       </c>
       <c r="P12" s="30" t="inlineStr">
         <is>
-          <t>3 noites calculadas proporcionalmente a partir da cotação de 4 noites (R$ 17.380 → R$ 13.035). Confirmar com o hotel na reserva.</t>
+          <t>Substitui a 4ª noite de Budapeste. Valor unitário = diária dos 2 quartos somados.</t>
         </is>
       </c>
     </row>
@@ -1767,17 +1771,17 @@
       </c>
       <c r="C13" s="24" t="inlineStr">
         <is>
-          <t>Tokaj · Minaro Hotel Tokaj, MGallery 5★</t>
+          <t>Viena · Opção 1 · Steigenberger Icon Herrenhof 5★</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
         <is>
-          <t>Tokaj, à beira do rio Bodrog, a 5 min da estação · 2 quartos duplos · café da manhã · 1 noite</t>
+          <t>Herrengasse, Innere Stadt, a 5 min do Hofburg · 1 Junior Suite + 1 Superior Room · café da manhã · 4 noites</t>
         </is>
       </c>
       <c r="E13" s="23" t="inlineStr">
         <is>
-          <t>02/01 → 03/01</t>
+          <t>03/01 → 07/01</t>
         </is>
       </c>
       <c r="F13" s="23" t="n">
@@ -1793,15 +1797,21 @@
           <t>BRL</t>
         </is>
       </c>
-      <c r="I13" s="26" t="n"/>
+      <c r="I13" s="26" t="n">
+        <v>5910</v>
+      </c>
       <c r="J13" s="25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K13" s="27">
         <f>IF(I13="","",I13*J13)</f>
         <v/>
       </c>
-      <c r="L13" s="28" t="n"/>
+      <c r="L13" s="28" t="inlineStr">
+        <is>
+          <t>Booking 20/09: € 1.862 (≈ R$ 11.004) por 2 quartos standard/4 noites no mesmo hotel</t>
+        </is>
+      </c>
       <c r="M13" s="25" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1813,12 +1823,12 @@
       </c>
       <c r="O13" s="25" t="inlineStr">
         <is>
-          <t>A cotar</t>
+          <t>Cotado</t>
         </is>
       </c>
       <c r="P13" s="30" t="inlineStr">
         <is>
-          <t>Substitui a 4ª noite de Budapeste. Valor unitário = diária dos 2 quartos somados.</t>
+          <t>Cotação de 21/09: Junior Suite R$ 15.300 + Superior Room R$ 8.340 = R$ 23.640 pelas 4 noites (R$ 5.910/noite). Junior Suite comporta 3: pais + filho a partir de 05/01, filhas no Superior. Sem cama extra.</t>
         </is>
       </c>
     </row>
@@ -1833,12 +1843,12 @@
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>Viena · Opção 1 · Steigenberger Icon Herrenhof 5★</t>
+          <t>Viena · Opção 2 · Radisson Blu Style Hotel 5★</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
         <is>
-          <t>Herrengasse, Innere Stadt, a 5 min do Hofburg · 1 Junior Suite + 1 Superior Room · café da manhã · 4 noites</t>
+          <t>Herrengasse 12, Innere Stadt, design, a 3 min do Hofburg · 1 Junior Suite + 1 Superior Room · café da manhã · 4 noites</t>
         </is>
       </c>
       <c r="E14" s="23" t="inlineStr">
@@ -1860,7 +1870,7 @@
         </is>
       </c>
       <c r="I14" s="26" t="n">
-        <v>5910</v>
+        <v>4768</v>
       </c>
       <c r="J14" s="25" t="n">
         <v>4</v>
@@ -1871,12 +1881,12 @@
       </c>
       <c r="L14" s="28" t="inlineStr">
         <is>
-          <t>Booking 20/09: € 1.862 (≈ R$ 11.004) por 2 quartos standard/4 noites no mesmo hotel</t>
+          <t>Booking 20/09: R$ 12.034 por 2 quartos standard/4 noites no mesmo hotel</t>
         </is>
       </c>
       <c r="M14" s="25" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="N14" s="29">
@@ -1890,7 +1900,7 @@
       </c>
       <c r="P14" s="30" t="inlineStr">
         <is>
-          <t>Cotação de 21/09: Junior Suite R$ 15.300 + Superior Room R$ 8.340 = R$ 23.640 pelas 4 noites (R$ 5.910/noite). Junior Suite comporta 3: pais + filho a partir de 05/01, filhas no Superior. Sem cama extra.</t>
+          <t>Cotação de 21/09: Junior Suite R$ 11.042 + Superior Room R$ 8.030 = R$ 19.072 pelas 4 noites (R$ 4.768/noite). Junior Suite comporta 3. R$ 4.568 mais barato que o Herrenhof, na mesma rua.</t>
         </is>
       </c>
     </row>
@@ -1905,47 +1915,37 @@
       </c>
       <c r="C15" s="24" t="inlineStr">
         <is>
-          <t>Viena · Opção 2 · Radisson Blu Style Hotel 5★</t>
+          <t>Viena · cama extra ou 3º quarto para o filho</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
         <is>
-          <t>Herrengasse 12, Innere Stadt, design, a 3 min do Hofburg · 1 Junior Suite + 1 Superior Room · café da manhã · 4 noites</t>
+          <t>2 noites, a partir da chegada em 05/01, no hotel escolhido</t>
         </is>
       </c>
       <c r="E15" s="23" t="inlineStr">
         <is>
-          <t>03/01 → 07/01</t>
+          <t>05/01 → 07/01</t>
         </is>
       </c>
       <c r="F15" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="G15" s="25" t="inlineStr">
-        <is>
-          <t>Consolidador (a nomear)</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G15" s="25" t="inlineStr"/>
       <c r="H15" s="25" t="inlineStr">
         <is>
-          <t>BRL</t>
-        </is>
-      </c>
-      <c r="I15" s="26" t="n">
-        <v>4768</v>
-      </c>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I15" s="26" t="n"/>
       <c r="J15" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K15" s="27">
         <f>IF(I15="","",I15*J15)</f>
         <v/>
       </c>
-      <c r="L15" s="28" t="inlineStr">
-        <is>
-          <t>Booking 20/09: R$ 12.034 por 2 quartos standard/4 noites no mesmo hotel</t>
-        </is>
-      </c>
+      <c r="L15" s="28" t="inlineStr"/>
       <c r="M15" s="25" t="inlineStr">
         <is>
           <t>Não</t>
@@ -1957,12 +1957,12 @@
       </c>
       <c r="O15" s="25" t="inlineStr">
         <is>
-          <t>Cotado</t>
+          <t>Descartado</t>
         </is>
       </c>
       <c r="P15" s="30" t="inlineStr">
         <is>
-          <t>Cotação de 21/09: Junior Suite R$ 11.042 + Superior Room R$ 8.030 = R$ 19.072 pelas 4 noites (R$ 4.768/noite). Junior Suite comporta 3. R$ 4.568 mais barato que o Herrenhof, na mesma rua.</t>
+          <t>Desnecessária: a Junior Suite das duas opções comporta o filho.</t>
         </is>
       </c>
     </row>
@@ -1977,40 +1977,50 @@
       </c>
       <c r="C16" s="24" t="inlineStr">
         <is>
-          <t>Viena · cama extra ou 3º quarto para o filho</t>
+          <t>Praga · Opção 1 · The Emblem Prague Hotel 5★</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
         <is>
-          <t>2 noites, a partir da chegada em 05/01, no hotel escolhido</t>
+          <t>Platnéřská, Cidade Velha, a 2 min da Praça da Cidade Velha, spa na cobertura · 1 Suite Pretender + 1 Queen Room · café da manhã · 3 noites</t>
         </is>
       </c>
       <c r="E16" s="23" t="inlineStr">
         <is>
-          <t>05/01 → 07/01</t>
+          <t>07/01 → 10/01</t>
         </is>
       </c>
       <c r="F16" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" s="25" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="G16" s="25" t="inlineStr">
+        <is>
+          <t>Consolidador (a nomear)</t>
+        </is>
+      </c>
       <c r="H16" s="25" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="I16" s="26" t="n"/>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="I16" s="26" t="n">
+        <v>3335</v>
+      </c>
       <c r="J16" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K16" s="27">
         <f>IF(I16="","",I16*J16)</f>
         <v/>
       </c>
-      <c r="L16" s="28" t="inlineStr"/>
+      <c r="L16" s="28" t="inlineStr">
+        <is>
+          <t>Booking 20/09, outros hotéis: Art Nouveau Palace 5★ € 812 · Hilton Old Town 5★ € 1.041 por 2 quartos/3 noites (5 pax)</t>
+        </is>
+      </c>
       <c r="M16" s="25" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="N16" s="29">
@@ -2019,12 +2029,12 @@
       </c>
       <c r="O16" s="25" t="inlineStr">
         <is>
-          <t>Descartado</t>
+          <t>Cotado</t>
         </is>
       </c>
       <c r="P16" s="30" t="inlineStr">
         <is>
-          <t>Desnecessária: a Junior Suite das duas opções comporta o filho.</t>
+          <t>Cotação de 21/09: Suite Pretender R$ 5.680 + Queen Room R$ 4.325 = R$ 10.005 pelas 3 noites (R$ 3.335/noite). Suíte comporta 3. Escolhida para o total: boutique 5★ no coração da Cidade Velha, R$ 1.980 acima da Opção 2.</t>
         </is>
       </c>
     </row>
@@ -2039,12 +2049,12 @@
       </c>
       <c r="C17" s="24" t="inlineStr">
         <is>
-          <t>Praga · Opção 1 · The Emblem Prague Hotel 5★</t>
+          <t>Praga · Opção 2 · Century Old Town Prague, MGallery 4★</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
         <is>
-          <t>Platnéřská, Cidade Velha, a 2 min da Praça da Cidade Velha, spa na cobertura · 1 Suite Pretender + 1 Queen Room · café da manhã · 3 noites</t>
+          <t>Na Poříčí, prédio onde Kafka trabalhou, a 8 min da Praça da Cidade Velha · 1 Executive + 1 Classic Room · café da manhã · 3 noites</t>
         </is>
       </c>
       <c r="E17" s="23" t="inlineStr">
@@ -2066,7 +2076,7 @@
         </is>
       </c>
       <c r="I17" s="26" t="n">
-        <v>3335</v>
+        <v>2675</v>
       </c>
       <c r="J17" s="25" t="n">
         <v>3</v>
@@ -2075,14 +2085,10 @@
         <f>IF(I17="","",I17*J17)</f>
         <v/>
       </c>
-      <c r="L17" s="28" t="inlineStr">
-        <is>
-          <t>Booking 20/09, outros hotéis: Art Nouveau Palace 5★ € 812 · Hilton Old Town 5★ € 1.041 por 2 quartos/3 noites (5 pax)</t>
-        </is>
-      </c>
+      <c r="L17" s="28" t="n"/>
       <c r="M17" s="25" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="N17" s="29">
@@ -2096,7 +2102,7 @@
       </c>
       <c r="P17" s="30" t="inlineStr">
         <is>
-          <t>Cotação de 21/09: Suite Pretender R$ 5.680 + Queen Room R$ 4.325 = R$ 10.005 pelas 3 noites (R$ 3.335/noite). Suíte comporta 3. Escolhida para o total: boutique 5★ no coração da Cidade Velha, R$ 1.980 acima da Opção 2.</t>
+          <t>Cotação de 21/09: Executive R$ 4.645 + Classic R$ 3.380 = R$ 8.025 pelas 3 noites (R$ 2.675/noite). Suíte comporta 3.</t>
         </is>
       </c>
     </row>
@@ -2111,17 +2117,17 @@
       </c>
       <c r="C18" s="24" t="inlineStr">
         <is>
-          <t>Praga · Opção 2 · Century Old Town Prague, MGallery 4★</t>
+          <t>Paris · Opção 1 · Hôtel François 1er 4★</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
         <is>
-          <t>Na Poříčí, prédio onde Kafka trabalhou, a 8 min da Praça da Cidade Velha · 1 Executive + 1 Classic Room · café da manhã · 3 noites</t>
+          <t>Rue Magellan, 8º arr., a 2 min da Champs-Élysées · 1 Executive Room + 1 Classic Double · café da manhã · 2 noites</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">
         <is>
-          <t>07/01 → 10/01</t>
+          <t>10/01 → 12/01</t>
         </is>
       </c>
       <c r="F18" s="23" t="n">
@@ -2138,10 +2144,10 @@
         </is>
       </c>
       <c r="I18" s="26" t="n">
-        <v>2675</v>
+        <v>5587.5</v>
       </c>
       <c r="J18" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K18" s="27">
         <f>IF(I18="","",I18*J18)</f>
@@ -2150,7 +2156,7 @@
       <c r="L18" s="28" t="n"/>
       <c r="M18" s="25" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="N18" s="29">
@@ -2164,7 +2170,7 @@
       </c>
       <c r="P18" s="30" t="inlineStr">
         <is>
-          <t>Cotação de 21/09: Executive R$ 4.645 + Classic R$ 3.380 = R$ 8.025 pelas 3 noites (R$ 2.675/noite). Suíte comporta 3.</t>
+          <t>Cotação de 21/09: Executive R$ 6.420 + Classic Double R$ 4.755 = R$ 11.175 pelas 2 noites (R$ 5.587,50/noite). Executive comporta 3: pais + filho, filhas no Classic.</t>
         </is>
       </c>
     </row>
@@ -2179,12 +2185,12 @@
       </c>
       <c r="C19" s="24" t="inlineStr">
         <is>
-          <t>Paris · Opção 1 · Hôtel François 1er 4★</t>
+          <t>Paris · Opção 2 · Hotel Indigo Paris Opéra, IHG 4★</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
         <is>
-          <t>Rue Magellan, 8º arr., a 2 min da Champs-Élysées · 1 Executive Room + 1 Classic Double · café da manhã · 2 noites</t>
+          <t>Rue de Châteaudun, 9º arr., entre a Ópera Garnier e Montmartre · 1 Standard Queen triplo + 1 Standard Queen duplo · café da manhã · 2 noites</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
@@ -2206,7 +2212,7 @@
         </is>
       </c>
       <c r="I19" s="26" t="n">
-        <v>5587.5</v>
+        <v>5715</v>
       </c>
       <c r="J19" s="25" t="n">
         <v>2</v>
@@ -2218,7 +2224,7 @@
       <c r="L19" s="28" t="n"/>
       <c r="M19" s="25" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="N19" s="29">
@@ -2232,7 +2238,7 @@
       </c>
       <c r="P19" s="30" t="inlineStr">
         <is>
-          <t>Cotação de 21/09: Executive R$ 6.420 + Classic Double R$ 4.755 = R$ 11.175 pelas 2 noites (R$ 5.587,50/noite). Confirmar que a Executive comporta 3 (pais + filho).</t>
+          <t>Cotação de 21/09: triplo R$ 6.730 + duplo R$ 4.700 = R$ 11.430 pelas 2 noites (R$ 5.715/noite). Triplo resolve pais + filho sem depender de confirmação.</t>
         </is>
       </c>
     </row>
@@ -2242,26 +2248,26 @@
       </c>
       <c r="B20" s="23" t="inlineStr">
         <is>
-          <t>Hotel</t>
+          <t>Trem</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
         <is>
-          <t>Paris · Opção 2 · Hotel Indigo Paris Opéra, IHG 4★</t>
+          <t>Railjet Budapeste → Viena · 4 pax</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
         <is>
-          <t>Rue de Châteaudun, 9º arr., entre a Ópera Garnier e Montmartre · 1 Standard Queen triplo + 1 Standard Queen duplo · café da manhã · 2 noites</t>
+          <t>ÖBB RJX 62 · Budapest-Keleti 09:30 → Wien Hbf 12:20 · 2h50 · direto · 1ª classe · assentos marcados</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
         <is>
-          <t>10/01 → 12/01</t>
+          <t>03/01</t>
         </is>
       </c>
       <c r="F20" s="23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G20" s="25" t="inlineStr">
         <is>
@@ -2274,16 +2280,16 @@
         </is>
       </c>
       <c r="I20" s="26" t="n">
-        <v>5715</v>
+        <v>302.5</v>
       </c>
       <c r="J20" s="25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K20" s="27">
         <f>IF(I20="","",I20*J20)</f>
         <v/>
       </c>
-      <c r="L20" s="28" t="n"/>
+      <c r="L20" s="28" t="inlineStr"/>
       <c r="M20" s="25" t="inlineStr">
         <is>
           <t>Não</t>
@@ -2295,12 +2301,12 @@
       </c>
       <c r="O20" s="25" t="inlineStr">
         <is>
-          <t>Cotado</t>
+          <t>Descartado</t>
         </is>
       </c>
       <c r="P20" s="30" t="inlineStr">
         <is>
-          <t>Cotação de 21/09: triplo R$ 6.730 + duplo R$ 4.700 = R$ 11.430 pelas 2 noites (R$ 5.715/noite). Triplo resolve pais + filho sem depender de confirmação.</t>
+          <t>Substituído pelo trajeto via Tokaj (02 e 03/01). Valor de referência: R$ 1.210 para 4 pax em 1ª classe.</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2321,17 @@
       </c>
       <c r="C21" s="24" t="inlineStr">
         <is>
-          <t>Railjet Budapeste → Viena · 4 pax</t>
+          <t>Trem Budapeste → Tokaj · 4 pax</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
         <is>
-          <t>ÖBB RJX 62 · Budapest-Keleti 09:30 → Wien Hbf 12:20 · 2h50 · direto · 1ª classe · assentos marcados</t>
+          <t>MÁV InterCity · Budapest-Keleti → Tokaj · ~2h30 · 1ª classe · com bagagem</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
         <is>
-          <t>03/01</t>
+          <t>02/01</t>
         </is>
       </c>
       <c r="F21" s="23" t="n">
@@ -2341,9 +2347,7 @@
           <t>BRL</t>
         </is>
       </c>
-      <c r="I21" s="26" t="n">
-        <v>302.5</v>
-      </c>
+      <c r="I21" s="26" t="n"/>
       <c r="J21" s="25" t="n">
         <v>4</v>
       </c>
@@ -2351,10 +2355,10 @@
         <f>IF(I21="","",I21*J21)</f>
         <v/>
       </c>
-      <c r="L21" s="28" t="inlineStr"/>
+      <c r="L21" s="28" t="n"/>
       <c r="M21" s="25" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="N21" s="29">
@@ -2363,12 +2367,12 @@
       </c>
       <c r="O21" s="25" t="inlineStr">
         <is>
-          <t>Descartado</t>
+          <t>A cotar</t>
         </is>
       </c>
       <c r="P21" s="30" t="inlineStr">
         <is>
-          <t>Substituído pelo trajeto via Tokaj (02 e 03/01). Valor de referência: R$ 1.210 para 4 pax em 1ª classe.</t>
+          <t>Sábado: conferir grade reduzida da MÁV. Ideal saída ~07:30 para chegar às 10h.</t>
         </is>
       </c>
     </row>
@@ -2383,17 +2387,17 @@
       </c>
       <c r="C22" s="24" t="inlineStr">
         <is>
-          <t>Trem Budapeste → Tokaj · 4 pax</t>
+          <t>Trem Tokaj → Budapeste → Viena · 4 pax</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
         <is>
-          <t>MÁV InterCity · Budapest-Keleti → Tokaj · ~2h30 · 1ª classe · com bagagem</t>
+          <t>MÁV InterCity Tokaj → Budapest-Keleti + Railjet Keleti → Wien Hbf · ~6h com conexão · 1ª classe</t>
         </is>
       </c>
       <c r="E22" s="23" t="inlineStr">
         <is>
-          <t>02/01</t>
+          <t>03/01</t>
         </is>
       </c>
       <c r="F22" s="23" t="n">
@@ -2434,7 +2438,7 @@
       </c>
       <c r="P22" s="30" t="inlineStr">
         <is>
-          <t>Sábado: conferir grade reduzida da MÁV. Ideal saída ~07:30 para chegar às 10h.</t>
+          <t>Chegada em Viena no meio da tarde. Deixar folga de ≥ 40 min na conexão em Keleti.</t>
         </is>
       </c>
     </row>
@@ -2449,21 +2453,21 @@
       </c>
       <c r="C23" s="24" t="inlineStr">
         <is>
-          <t>Trem Tokaj → Budapeste → Viena · 4 pax</t>
+          <t>Railjet Viena → Praga · 5 pax</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
         <is>
-          <t>MÁV InterCity Tokaj → Budapest-Keleti + Railjet Keleti → Wien Hbf · ~6h com conexão · 1ª classe</t>
+          <t>ÖBB RJ 252 · Wien Hbf 11:10 → Praha hlavní nádraží 15:23 · 4h13 · direto · 1ª classe · assentos marcados</t>
         </is>
       </c>
       <c r="E23" s="23" t="inlineStr">
         <is>
-          <t>03/01</t>
+          <t>07/01</t>
         </is>
       </c>
       <c r="F23" s="23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G23" s="25" t="inlineStr">
         <is>
@@ -2475,15 +2479,17 @@
           <t>BRL</t>
         </is>
       </c>
-      <c r="I23" s="26" t="n"/>
+      <c r="I23" s="26" t="n">
+        <v>381</v>
+      </c>
       <c r="J23" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K23" s="27">
         <f>IF(I23="","",I23*J23)</f>
         <v/>
       </c>
-      <c r="L23" s="28" t="n"/>
+      <c r="L23" s="28" t="inlineStr"/>
       <c r="M23" s="25" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2495,12 +2501,12 @@
       </c>
       <c r="O23" s="25" t="inlineStr">
         <is>
-          <t>A cotar</t>
+          <t>Cotado</t>
         </is>
       </c>
       <c r="P23" s="30" t="inlineStr">
         <is>
-          <t>Chegada em Viena no meio da tarde. Deixar folga de ≥ 40 min na conexão em Keleti.</t>
+          <t>Cotação de 21/09: R$ 1.905 para 5 pax (R$ 381/pax), 1ª classe.</t>
         </is>
       </c>
     </row>
@@ -2510,42 +2516,36 @@
       </c>
       <c r="B24" s="23" t="inlineStr">
         <is>
-          <t>Trem</t>
+          <t>Transfer</t>
         </is>
       </c>
       <c r="C24" s="24" t="inlineStr">
         <is>
-          <t>Railjet Viena → Praga · 5 pax</t>
+          <t>Budapeste · aeroporto → hotel · 4 pax</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
         <is>
-          <t>ÖBB RJ 252 · Wien Hbf 11:10 → Praha hlavní nádraží 15:23 · 4h13 · direto · 1ª classe · assentos marcados</t>
+          <t>Van privativa com recepção no desembarque</t>
         </is>
       </c>
       <c r="E24" s="23" t="inlineStr">
         <is>
-          <t>07/01</t>
+          <t>30/12</t>
         </is>
       </c>
       <c r="F24" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="G24" s="25" t="inlineStr">
-        <is>
-          <t>Consolidador (a nomear)</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G24" s="25" t="inlineStr"/>
       <c r="H24" s="25" t="inlineStr">
         <is>
-          <t>BRL</t>
-        </is>
-      </c>
-      <c r="I24" s="26" t="n">
-        <v>381</v>
-      </c>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I24" s="26" t="n"/>
       <c r="J24" s="25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K24" s="27">
         <f>IF(I24="","",I24*J24)</f>
@@ -2563,12 +2563,12 @@
       </c>
       <c r="O24" s="25" t="inlineStr">
         <is>
-          <t>Cotado</t>
+          <t>A cotar</t>
         </is>
       </c>
       <c r="P24" s="30" t="inlineStr">
         <is>
-          <t>Cotação de 21/09: R$ 1.905 para 5 pax (R$ 381/pax), 1ª classe.</t>
+          <t>Valor unitário = por veículo.</t>
         </is>
       </c>
     </row>
@@ -2583,17 +2583,17 @@
       </c>
       <c r="C25" s="24" t="inlineStr">
         <is>
-          <t>Budapeste · aeroporto → hotel · 4 pax</t>
+          <t>Budapeste · hotel → estação Keleti · 4 pax</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
         <is>
-          <t>Van privativa com recepção no desembarque</t>
+          <t>Carro ou van privativa, com bagagem</t>
         </is>
       </c>
       <c r="E25" s="23" t="inlineStr">
         <is>
-          <t>30/12</t>
+          <t>02/01</t>
         </is>
       </c>
       <c r="F25" s="23" t="n">
@@ -2628,11 +2628,7 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P25" s="30" t="inlineStr">
-        <is>
-          <t>Valor unitário = por veículo.</t>
-        </is>
-      </c>
+      <c r="P25" s="30" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="23" t="n">
@@ -2645,17 +2641,17 @@
       </c>
       <c r="C26" s="24" t="inlineStr">
         <is>
-          <t>Budapeste · hotel → estação Keleti · 4 pax</t>
+          <t>Viena · estação Hbf → hotel · 4 pax</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
         <is>
-          <t>Carro ou van privativa, com bagagem</t>
+          <t>Carro ou van privativa</t>
         </is>
       </c>
       <c r="E26" s="23" t="inlineStr">
         <is>
-          <t>02/01</t>
+          <t>03/01</t>
         </is>
       </c>
       <c r="F26" s="23" t="n">
@@ -2703,21 +2699,21 @@
       </c>
       <c r="C27" s="24" t="inlineStr">
         <is>
-          <t>Viena · estação Hbf → hotel · 4 pax</t>
+          <t>Viena · aeroporto → hotel · filho · 1 pax</t>
         </is>
       </c>
       <c r="D27" s="23" t="inlineStr">
         <is>
-          <t>Carro ou van privativa</t>
+          <t>Motorista com placa no desembarque · reforçar: menor viajando só</t>
         </is>
       </c>
       <c r="E27" s="23" t="inlineStr">
         <is>
-          <t>03/01</t>
+          <t>05/01</t>
         </is>
       </c>
       <c r="F27" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G27" s="25" t="inlineStr"/>
       <c r="H27" s="25" t="inlineStr">
@@ -2761,21 +2757,21 @@
       </c>
       <c r="C28" s="24" t="inlineStr">
         <is>
-          <t>Viena · aeroporto → hotel · filho · 1 pax</t>
+          <t>Viena · hotel → estação Hbf · 5 pax</t>
         </is>
       </c>
       <c r="D28" s="23" t="inlineStr">
         <is>
-          <t>Motorista com placa no desembarque · reforçar: menor viajando só</t>
+          <t>Van privativa</t>
         </is>
       </c>
       <c r="E28" s="23" t="inlineStr">
         <is>
-          <t>05/01</t>
+          <t>07/01</t>
         </is>
       </c>
       <c r="F28" s="23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G28" s="25" t="inlineStr"/>
       <c r="H28" s="25" t="inlineStr">
@@ -2819,7 +2815,7 @@
       </c>
       <c r="C29" s="24" t="inlineStr">
         <is>
-          <t>Viena · hotel → estação Hbf · 5 pax</t>
+          <t>Praga · estação hl.n. → hotel · 5 pax</t>
         </is>
       </c>
       <c r="D29" s="23" t="inlineStr">
@@ -2877,7 +2873,7 @@
       </c>
       <c r="C30" s="24" t="inlineStr">
         <is>
-          <t>Praga · estação hl.n. → hotel · 5 pax</t>
+          <t>Praga · hotel → aeroporto · 5 pax</t>
         </is>
       </c>
       <c r="D30" s="23" t="inlineStr">
@@ -2887,7 +2883,7 @@
       </c>
       <c r="E30" s="23" t="inlineStr">
         <is>
-          <t>07/01</t>
+          <t>10/01</t>
         </is>
       </c>
       <c r="F30" s="23" t="n">
@@ -2935,7 +2931,7 @@
       </c>
       <c r="C31" s="24" t="inlineStr">
         <is>
-          <t>Praga · hotel → aeroporto · 5 pax</t>
+          <t>Paris · CDG → hotel · 5 pax</t>
         </is>
       </c>
       <c r="D31" s="23" t="inlineStr">
@@ -2993,7 +2989,7 @@
       </c>
       <c r="C32" s="24" t="inlineStr">
         <is>
-          <t>Paris · CDG → hotel · 5 pax</t>
+          <t>Paris · hotel → CDG · 5 pax</t>
         </is>
       </c>
       <c r="D32" s="23" t="inlineStr">
@@ -3003,7 +2999,7 @@
       </c>
       <c r="E32" s="23" t="inlineStr">
         <is>
-          <t>10/01</t>
+          <t>12/01</t>
         </is>
       </c>
       <c r="F32" s="23" t="n">
@@ -3046,42 +3042,52 @@
       </c>
       <c r="B33" s="23" t="inlineStr">
         <is>
-          <t>Transfer</t>
+          <t>Experiência</t>
         </is>
       </c>
       <c r="C33" s="24" t="inlineStr">
         <is>
-          <t>Paris · hotel → CDG · 5 pax</t>
+          <t>Réveillon · Opção 1 · Silverline · jantar de gala em catamarã · 4 pax</t>
         </is>
       </c>
       <c r="D33" s="23" t="inlineStr">
         <is>
-          <t>Van privativa</t>
+          <t>Cais 11, Ponte Elisabeth · embarque 20h, retorno 1h · welcome cocktail, jantar de 5 pratos, espumante, show de piano · Parlamento iluminado, brinde e fogos à meia-noite</t>
         </is>
       </c>
       <c r="E33" s="23" t="inlineStr">
         <is>
-          <t>12/01</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="F33" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="G33" s="25" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G33" s="25" t="inlineStr">
+        <is>
+          <t>Silverline Cruises</t>
+        </is>
+      </c>
       <c r="H33" s="25" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="I33" s="26" t="n"/>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="I33" s="26" t="n">
+        <v>2146.59</v>
+      </c>
       <c r="J33" s="25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K33" s="27">
         <f>IF(I33="","",I33*J33)</f>
         <v/>
       </c>
-      <c r="L33" s="28" t="inlineStr"/>
+      <c r="L33" s="28" t="inlineStr">
+        <is>
+          <t>silver-line.hu/product/budapest-new-years-eve-dinner-cruise</t>
+        </is>
+      </c>
       <c r="M33" s="25" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -3093,10 +3099,14 @@
       </c>
       <c r="O33" s="25" t="inlineStr">
         <is>
-          <t>A cotar</t>
-        </is>
-      </c>
-      <c r="P33" s="30" t="inlineStr"/>
+          <t>Cotado</t>
+        </is>
+      </c>
+      <c r="P33" s="30" t="inlineStr">
+        <is>
+          <t>Valor por pessoa, conforme a página da Silverline em 21/09.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="23" t="n">
@@ -3109,12 +3119,12 @@
       </c>
       <c r="C34" s="24" t="inlineStr">
         <is>
-          <t>Réveillon · Opção 1 · Silverline · jantar de gala em catamarã · 4 pax</t>
+          <t>Réveillon · Opção 2 · Budapest River Cruise · NYE Party Cruise · 4 pax</t>
         </is>
       </c>
       <c r="D34" s="23" t="inlineStr">
         <is>
-          <t>Cais 11, Ponte Elisabeth · embarque 20h, retorno 1h · welcome cocktail, jantar de 5 pratos, espumante, show de piano · Parlamento iluminado, brinde e fogos à meia-noite</t>
+          <t>Cais 8/8A, Ponte Elisabeth · embarque 19h, retorno 1h · jantar, música ao vivo e virada a bordo</t>
         </is>
       </c>
       <c r="E34" s="23" t="inlineStr">
@@ -3127,7 +3137,7 @@
       </c>
       <c r="G34" s="25" t="inlineStr">
         <is>
-          <t>Silverline Cruises</t>
+          <t>Budapest River Cruise</t>
         </is>
       </c>
       <c r="H34" s="25" t="inlineStr">
@@ -3136,7 +3146,7 @@
         </is>
       </c>
       <c r="I34" s="26" t="n">
-        <v>2146.59</v>
+        <v>2272.86</v>
       </c>
       <c r="J34" s="25" t="n">
         <v>4</v>
@@ -3147,12 +3157,12 @@
       </c>
       <c r="L34" s="28" t="inlineStr">
         <is>
-          <t>silver-line.hu/product/budapest-new-years-eve-dinner-cruise</t>
+          <t>budapestrivercruise.com/budapest-new-years-eve-cruise-party</t>
         </is>
       </c>
       <c r="M34" s="25" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="N34" s="29">
@@ -3166,7 +3176,7 @@
       </c>
       <c r="P34" s="30" t="inlineStr">
         <is>
-          <t>Valor por pessoa, conforme a página da Silverline em 21/09.</t>
+          <t>Valor por pessoa, 6 horas a bordo (19h à 1h). Mais que o dobro da Opção 1 por pessoa. Confirmar preço de menor e o que o jantar inclui.</t>
         </is>
       </c>
     </row>
@@ -3181,17 +3191,17 @@
       </c>
       <c r="C35" s="24" t="inlineStr">
         <is>
-          <t>Réveillon · Opção 2 · Budapest River Cruise · NYE Party Cruise · 4 pax</t>
+          <t>Tokaj · táxi local contratado pelo dia · 4 pax</t>
         </is>
       </c>
       <c r="D35" s="23" t="inlineStr">
         <is>
-          <t>Cais 8/8A, Ponte Elisabeth · embarque 19h, retorno 1h · jantar, música ao vivo e virada a bordo</t>
+          <t>Estação de Tokaj → Oremus (Tolcsva) → almoço → Disznókő (Mezőzombor) → Minaro Hotel · 03/01 hotel → estação</t>
         </is>
       </c>
       <c r="E35" s="23" t="inlineStr">
         <is>
-          <t>31/12</t>
+          <t>02/01</t>
         </is>
       </c>
       <c r="F35" s="23" t="n">
@@ -3199,7 +3209,7 @@
       </c>
       <c r="G35" s="25" t="inlineStr">
         <is>
-          <t>Budapest River Cruise</t>
+          <t>Motorista local (indicação da Oremus)</t>
         </is>
       </c>
       <c r="H35" s="25" t="inlineStr">
@@ -3207,24 +3217,18 @@
           <t>BRL</t>
         </is>
       </c>
-      <c r="I35" s="26" t="n">
-        <v>2272.86</v>
-      </c>
+      <c r="I35" s="26" t="n"/>
       <c r="J35" s="25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K35" s="27">
         <f>IF(I35="","",I35*J35)</f>
         <v/>
       </c>
-      <c r="L35" s="28" t="inlineStr">
-        <is>
-          <t>budapestrivercruise.com/budapest-new-years-eve-cruise-party</t>
-        </is>
-      </c>
+      <c r="L35" s="28" t="inlineStr"/>
       <c r="M35" s="25" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="N35" s="29">
@@ -3233,12 +3237,12 @@
       </c>
       <c r="O35" s="25" t="inlineStr">
         <is>
-          <t>Cotado</t>
+          <t>A cotar</t>
         </is>
       </c>
       <c r="P35" s="30" t="inlineStr">
         <is>
-          <t>Valor por pessoa, 6 horas a bordo (19h à 1h). Mais que o dobro da Opção 1 por pessoa. Confirmar preço de menor e o que o jantar inclui.</t>
+          <t>Substitui o motorista-guia de Budapeste, que veio muito caro. Referência: € 120 a 180 pelo dia.</t>
         </is>
       </c>
     </row>
@@ -3253,12 +3257,12 @@
       </c>
       <c r="C36" s="24" t="inlineStr">
         <is>
-          <t>Tokaj · táxi local contratado pelo dia · 4 pax</t>
+          <t>Oremus · visita à adega e prova · 2 adultos + 2 filhas</t>
         </is>
       </c>
       <c r="D36" s="23" t="inlineStr">
         <is>
-          <t>Estação de Tokaj → Oremus (Tolcsva) → almoço → Disznókő (Mezőzombor) → Minaro Hotel · 03/01 hotel → estação</t>
+          <t>Tolcsva · agendamento por e-mail · ~1h · adegas do século XIII · adolescentes acompanham sem álcool</t>
         </is>
       </c>
       <c r="E36" s="23" t="inlineStr">
@@ -3271,7 +3275,7 @@
       </c>
       <c r="G36" s="25" t="inlineStr">
         <is>
-          <t>Motorista local (indicação da Oremus)</t>
+          <t>Tokaj-Oremus</t>
         </is>
       </c>
       <c r="H36" s="25" t="inlineStr">
@@ -3279,7 +3283,9 @@
           <t>BRL</t>
         </is>
       </c>
-      <c r="I36" s="26" t="n"/>
+      <c r="I36" s="26" t="n">
+        <v>315.67</v>
+      </c>
       <c r="J36" s="25" t="n">
         <v>1</v>
       </c>
@@ -3299,12 +3305,12 @@
       </c>
       <c r="O36" s="25" t="inlineStr">
         <is>
-          <t>A cotar</t>
+          <t>Cotado</t>
         </is>
       </c>
       <c r="P36" s="30" t="inlineStr">
         <is>
-          <t>Substitui o motorista-guia de Budapeste, que veio muito caro. Referência: € 120 a 180 pelo dia.</t>
+          <t>Cotação de 21/09 em reais para a família (2 adultos e 2 filhas). Confirmar recepção no sábado 02/01; plano B: segunda 04/01.</t>
         </is>
       </c>
     </row>
@@ -3319,12 +3325,12 @@
       </c>
       <c r="C37" s="24" t="inlineStr">
         <is>
-          <t>Oremus · visita à adega e prova · 2 adultos + 2 filhas</t>
+          <t>Disznókő · visita e prova · 2 adultos + 2 filhas</t>
         </is>
       </c>
       <c r="D37" s="23" t="inlineStr">
         <is>
-          <t>Tolcsva · agendamento por e-mail · ~1h · adegas do século XIII · adolescentes acompanham sem álcool</t>
+          <t>Mezőzombor, a 20 min de Tolcsva · vinícola do grupo AXA Millésimes · segunda parada da tarde</t>
         </is>
       </c>
       <c r="E37" s="23" t="inlineStr">
@@ -3337,7 +3343,7 @@
       </c>
       <c r="G37" s="25" t="inlineStr">
         <is>
-          <t>Tokaj-Oremus</t>
+          <t>Disznókő</t>
         </is>
       </c>
       <c r="H37" s="25" t="inlineStr">
@@ -3345,9 +3351,7 @@
           <t>BRL</t>
         </is>
       </c>
-      <c r="I37" s="26" t="n">
-        <v>315.67</v>
-      </c>
+      <c r="I37" s="26" t="n"/>
       <c r="J37" s="25" t="n">
         <v>1</v>
       </c>
@@ -3355,7 +3359,7 @@
         <f>IF(I37="","",I37*J37)</f>
         <v/>
       </c>
-      <c r="L37" s="28" t="inlineStr"/>
+      <c r="L37" s="28" t="n"/>
       <c r="M37" s="25" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -3367,12 +3371,12 @@
       </c>
       <c r="O37" s="25" t="inlineStr">
         <is>
-          <t>Cotado</t>
+          <t>A cotar</t>
         </is>
       </c>
       <c r="P37" s="30" t="inlineStr">
         <is>
-          <t>Cotação de 21/09 em reais para a família (2 adultos e 2 filhas). Confirmar recepção no sábado 02/01; plano B: segunda 04/01.</t>
+          <t>Aguardando valores da vinícola.</t>
         </is>
       </c>
     </row>
@@ -3387,12 +3391,12 @@
       </c>
       <c r="C38" s="24" t="inlineStr">
         <is>
-          <t>Disznókő · visita e prova · 2 adultos + 2 filhas</t>
+          <t>Almoço em vinícola ou restaurante em Tokaj · 4 pax</t>
         </is>
       </c>
       <c r="D38" s="23" t="inlineStr">
         <is>
-          <t>Mezőzombor, a 20 min de Tolcsva · vinícola do grupo AXA Millésimes · segunda parada da tarde</t>
+          <t>Mád ou Tarcal</t>
         </is>
       </c>
       <c r="E38" s="23" t="inlineStr">
@@ -3403,25 +3407,21 @@
       <c r="F38" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="G38" s="25" t="inlineStr">
-        <is>
-          <t>Disznókő</t>
-        </is>
-      </c>
+      <c r="G38" s="25" t="inlineStr"/>
       <c r="H38" s="25" t="inlineStr">
         <is>
-          <t>BRL</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="I38" s="26" t="n"/>
       <c r="J38" s="25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K38" s="27">
         <f>IF(I38="","",I38*J38)</f>
         <v/>
       </c>
-      <c r="L38" s="28" t="n"/>
+      <c r="L38" s="28" t="inlineStr"/>
       <c r="M38" s="25" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -3438,7 +3438,7 @@
       </c>
       <c r="P38" s="30" t="inlineStr">
         <is>
-          <t>Aguardando valores da vinícola.</t>
+          <t>Pode vir incluído no pacote do motorista-guia.</t>
         </is>
       </c>
     </row>
@@ -3448,36 +3448,42 @@
       </c>
       <c r="B39" s="23" t="inlineStr">
         <is>
-          <t>Experiência</t>
+          <t>Seguro/Docs</t>
         </is>
       </c>
       <c r="C39" s="24" t="inlineStr">
         <is>
-          <t>Almoço em vinícola ou restaurante em Tokaj · 4 pax</t>
+          <t>Seguro viagem · 5 pax · 15 dias</t>
         </is>
       </c>
       <c r="D39" s="23" t="inlineStr">
         <is>
-          <t>Mád ou Tarcal</t>
+          <t>Plano 90 Essential · DMH USD 90.000 · 29/12 a 12/01</t>
         </is>
       </c>
       <c r="E39" s="23" t="inlineStr">
         <is>
-          <t>02/01</t>
+          <t>29/12 → 12/01</t>
         </is>
       </c>
       <c r="F39" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="G39" s="25" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="G39" s="25" t="inlineStr">
+        <is>
+          <t>31 Motivos</t>
+        </is>
+      </c>
       <c r="H39" s="25" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="I39" s="26" t="n"/>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="I39" s="26" t="n">
+        <v>300.6</v>
+      </c>
       <c r="J39" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K39" s="27">
         <f>IF(I39="","",I39*J39)</f>
@@ -3495,147 +3501,80 @@
       </c>
       <c r="O39" s="25" t="inlineStr">
         <is>
-          <t>A cotar</t>
+          <t>Cotado</t>
         </is>
       </c>
       <c r="P39" s="30" t="inlineStr">
         <is>
-          <t>Pode vir incluído no pacote do motorista-guia.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="23" t="n">
-        <v>36</v>
-      </c>
-      <c r="B40" s="23" t="inlineStr">
-        <is>
-          <t>Seguro/Docs</t>
-        </is>
-      </c>
-      <c r="C40" s="24" t="inlineStr">
-        <is>
-          <t>Seguro viagem · 5 pax · 15 dias</t>
-        </is>
-      </c>
-      <c r="D40" s="23" t="inlineStr">
-        <is>
-          <t>Plano 90 Essential · DMH USD 90.000 · 29/12 a 12/01</t>
-        </is>
-      </c>
-      <c r="E40" s="23" t="inlineStr">
-        <is>
-          <t>29/12 → 12/01</t>
-        </is>
-      </c>
-      <c r="F40" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="G40" s="25" t="inlineStr">
-        <is>
-          <t>31 Motivos</t>
-        </is>
-      </c>
-      <c r="H40" s="25" t="inlineStr">
-        <is>
-          <t>BRL</t>
-        </is>
-      </c>
-      <c r="I40" s="26" t="n">
-        <v>300.6</v>
-      </c>
-      <c r="J40" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="K40" s="27">
-        <f>IF(I40="","",I40*J40)</f>
-        <v/>
-      </c>
-      <c r="L40" s="28" t="inlineStr"/>
-      <c r="M40" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="N40" s="29">
-        <f>IF(OR(M40&lt;&gt;"Sim",I40=""),0,K40*IF(H40="BRL",1,IF(H40="EUR",Parâmetros!$B$4,IF(H40="USD",Parâmetros!$B$5,1))))</f>
-        <v/>
-      </c>
-      <c r="O40" s="25" t="inlineStr">
-        <is>
-          <t>Cotado</t>
-        </is>
-      </c>
-      <c r="P40" s="30" t="inlineStr">
-        <is>
           <t>Cotação de 21/09: R$ 1.503,00 para os 5 (R$ 300,60 por pessoa). Confirmar se a apólice do filho cobre desde o embarque dele em 04/01.</t>
         </is>
       </c>
     </row>
+    <row r="40"/>
+    <row r="41">
+      <c r="C41" s="21" t="inlineStr">
+        <is>
+          <t>SUBTOTAL EM R$ (itens marcados como Sim)</t>
+        </is>
+      </c>
+      <c r="N41" s="31">
+        <f>SUM(N5:N39)</f>
+        <v/>
+      </c>
+    </row>
     <row r="42">
-      <c r="C42" s="21" t="inlineStr">
-        <is>
-          <t>SUBTOTAL EM R$ (itens marcados como Sim)</t>
-        </is>
-      </c>
-      <c r="N42" s="31">
-        <f>SUM(N5:N40)</f>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>Taxa de serviço LusaTravel</t>
+        </is>
+      </c>
+      <c r="N42" s="13">
+        <f>N41*Parâmetros!$B$10</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="C43" s="12" t="inlineStr">
-        <is>
-          <t>Taxa de serviço LusaTravel</t>
-        </is>
-      </c>
-      <c r="N43" s="13">
-        <f>N42*Parâmetros!$B$10</f>
-        <v/>
-      </c>
+      <c r="A43" s="32" t="n"/>
+      <c r="B43" s="32" t="n"/>
+      <c r="C43" s="33" t="inlineStr">
+        <is>
+          <t>TOTAL PARA O CLIENTE</t>
+        </is>
+      </c>
+      <c r="D43" s="32" t="n"/>
+      <c r="E43" s="32" t="n"/>
+      <c r="F43" s="32" t="n"/>
+      <c r="G43" s="32" t="n"/>
+      <c r="H43" s="32" t="n"/>
+      <c r="I43" s="32" t="n"/>
+      <c r="J43" s="32" t="n"/>
+      <c r="K43" s="32" t="n"/>
+      <c r="L43" s="32" t="n"/>
+      <c r="M43" s="32" t="n"/>
+      <c r="N43" s="34">
+        <f>N41+N42</f>
+        <v/>
+      </c>
+      <c r="O43" s="32" t="n"/>
+      <c r="P43" s="32" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="32" t="n"/>
-      <c r="B44" s="32" t="n"/>
-      <c r="C44" s="33" t="inlineStr">
-        <is>
-          <t>TOTAL PARA O CLIENTE</t>
-        </is>
-      </c>
-      <c r="D44" s="32" t="n"/>
-      <c r="E44" s="32" t="n"/>
-      <c r="F44" s="32" t="n"/>
-      <c r="G44" s="32" t="n"/>
-      <c r="H44" s="32" t="n"/>
-      <c r="I44" s="32" t="n"/>
-      <c r="J44" s="32" t="n"/>
-      <c r="K44" s="32" t="n"/>
-      <c r="L44" s="32" t="n"/>
-      <c r="M44" s="32" t="n"/>
-      <c r="N44" s="34">
-        <f>N42+N43</f>
-        <v/>
-      </c>
-      <c r="O44" s="32" t="n"/>
-      <c r="P44" s="32" t="n"/>
-    </row>
-    <row r="45">
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>*Nada reservado, apenas cotado.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:P40"/>
+  <autoFilter ref="A4:P39"/>
   <dataValidations count="3">
-    <dataValidation sqref="O5:O40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O5:O39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"A cotar,Cotado,Aprovado pelo cliente,Reservado,Descartado"</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="M5:M39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="H5:H39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"BRL,EUR,USD"</formula1>
     </dataValidation>
   </dataValidations>

--- a/cotacao-cristofer-reveillon.xlsx
+++ b/cotacao-cristofer-reveillon.xlsx
@@ -1710,7 +1710,7 @@
       </c>
       <c r="D12" s="23" t="inlineStr">
         <is>
-          <t>Tokaj, à beira do rio Bodrog, a 5 min da estação · 2 quartos duplos · café da manhã · 1 noite</t>
+          <t>Tokaj, à beira do rio Bodrog, a 5 min da estação · 2 quartos Superior King duplos · café da manhã · 1 noite</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">
@@ -1731,7 +1731,9 @@
           <t>BRL</t>
         </is>
       </c>
-      <c r="I12" s="26" t="n"/>
+      <c r="I12" s="26" t="n">
+        <v>3330</v>
+      </c>
       <c r="J12" s="25" t="n">
         <v>1</v>
       </c>
@@ -1751,12 +1753,12 @@
       </c>
       <c r="O12" s="25" t="inlineStr">
         <is>
-          <t>A cotar</t>
+          <t>Cotado</t>
         </is>
       </c>
       <c r="P12" s="30" t="inlineStr">
         <is>
-          <t>Substitui a 4ª noite de Budapeste. Valor unitário = diária dos 2 quartos somados.</t>
+          <t>Cotação de 21/09: R$ 3.330 pelos 2 quartos, 1 noite. Substitui a 4ª noite de Budapeste (R$ 4.345 no InterContinental): a troca economiza R$ 1.015.</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3512,6 @@
         </is>
       </c>
     </row>
-    <row r="40"/>
     <row r="41">
       <c r="C41" s="21" t="inlineStr">
         <is>

--- a/cotacao-cristofer-reveillon.xlsx
+++ b/cotacao-cristofer-reveillon.xlsx
@@ -2328,7 +2328,7 @@
       </c>
       <c r="D21" s="23" t="inlineStr">
         <is>
-          <t>MÁV InterCity · Budapest-Keleti → Tokaj · ~2h30 · 1ª classe · com bagagem</t>
+          <t>MÁV IC 562 Tokaj InterCity · Budapest-Keleti 09:25 → Tokaj 12:08 · 2h43 · direto · com bagagem</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
@@ -2349,7 +2349,9 @@
           <t>BRL</t>
         </is>
       </c>
-      <c r="I21" s="26" t="n"/>
+      <c r="I21" s="26" t="n">
+        <v>100</v>
+      </c>
       <c r="J21" s="25" t="n">
         <v>4</v>
       </c>
@@ -2369,12 +2371,12 @@
       </c>
       <c r="O21" s="25" t="inlineStr">
         <is>
-          <t>A cotar</t>
+          <t>Cotado</t>
         </is>
       </c>
       <c r="P21" s="30" t="inlineStr">
         <is>
-          <t>Sábado: conferir grade reduzida da MÁV. Ideal saída ~07:30 para chegar às 10h.</t>
+          <t>Cotação de 21/09: R$ 400 para 2 adultos e 2 adolescentes (R$ 100/pax). Confirmar classe. Chegada ao meio-dia: fazer Disznókő (descer em Mezőzombor, 12:00) e almoço primeiro, Oremus às 15h30, hotel às 17h. Há um alerta (⚠) em Hatvan no sistema da MÁV: conferir se é obra na linha.</t>
         </is>
       </c>
     </row>

--- a/cotacao-cristofer-reveillon.xlsx
+++ b/cotacao-cristofer-reveillon.xlsx
@@ -2396,7 +2396,7 @@
       </c>
       <c r="D22" s="23" t="inlineStr">
         <is>
-          <t>MÁV InterCity Tokaj → Budapest-Keleti + Railjet Keleti → Wien Hbf · ~6h com conexão · 1ª classe</t>
+          <t>IC 650 Tokaj 09:50 → Budapest-Keleti 12:47 · conexão 43 min · RJX 66 Keleti 13:30 → Wien Hbf 16:20 · 1ª classe · com bagagem</t>
         </is>
       </c>
       <c r="E22" s="23" t="inlineStr">
@@ -2417,7 +2417,9 @@
           <t>BRL</t>
         </is>
       </c>
-      <c r="I22" s="26" t="n"/>
+      <c r="I22" s="26" t="n">
+        <v>925</v>
+      </c>
       <c r="J22" s="25" t="n">
         <v>4</v>
       </c>
@@ -2437,12 +2439,12 @@
       </c>
       <c r="O22" s="25" t="inlineStr">
         <is>
-          <t>A cotar</t>
+          <t>Cotado</t>
         </is>
       </c>
       <c r="P22" s="30" t="inlineStr">
         <is>
-          <t>Chegada em Viena no meio da tarde. Deixar folga de ≥ 40 min na conexão em Keleti.</t>
+          <t>Cotação de 21/09 para 2 adultos e 2 adolescentes: R$ 3.700 em 1ª classe (R$ 925/pax) ou R$ 2.530 em 2ª. ALERTA: o RJX 62 sozinho havia sido cotado a R$ 1.210 em 1ª classe para os 4. Pedir o mesmo trecho como duas passagens separadas (MÁV Tokaj → Keleti + ÖBB Sparschiene Keleti → Wien): deve cair para perto de R$ 1.600.</t>
         </is>
       </c>
     </row>

--- a/cotacao-cristofer-reveillon.xlsx
+++ b/cotacao-cristofer-reveillon.xlsx
@@ -1008,11 +1008,11 @@
         </is>
       </c>
       <c r="B10" s="19" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>Sobre o subtotal em R$. Ajustar conforme política da agência.</t>
+          <t>Zero: a margem já está embutida nos valores dos fornecedores.</t>
         </is>
       </c>
     </row>

--- a/cotacao-cristofer-reveillon.xlsx
+++ b/cotacao-cristofer-reveillon.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Cotação" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Cotação'!$A$4:$P$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Cotação'!$A$4:$P$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -625,19 +625,19 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$39,A5)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$36,A5)</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$39,A5,Cotação!$O$5:$O$39,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$36,A5,Cotação!$O$5:$O$36,"A cotar")</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$39,A5,Cotação!$O$5:$O$39,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$36,A5,Cotação!$O$5:$O$36,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E5" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$39,A5,Cotação!$N$5:$N$39)</f>
+        <f>SUMIF(Cotação!$B$5:$B$36,A5,Cotação!$N$5:$N$36)</f>
         <v/>
       </c>
     </row>
@@ -648,19 +648,19 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$39,A6)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$36,A6)</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$39,A6,Cotação!$O$5:$O$39,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$36,A6,Cotação!$O$5:$O$36,"A cotar")</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$39,A6,Cotação!$O$5:$O$39,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$36,A6,Cotação!$O$5:$O$36,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E6" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$39,A6,Cotação!$N$5:$N$39)</f>
+        <f>SUMIF(Cotação!$B$5:$B$36,A6,Cotação!$N$5:$N$36)</f>
         <v/>
       </c>
     </row>
@@ -671,19 +671,19 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$39,A7)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$36,A7)</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$39,A7,Cotação!$O$5:$O$39,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$36,A7,Cotação!$O$5:$O$36,"A cotar")</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$39,A7,Cotação!$O$5:$O$39,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$36,A7,Cotação!$O$5:$O$36,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E7" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$39,A7,Cotação!$N$5:$N$39)</f>
+        <f>SUMIF(Cotação!$B$5:$B$36,A7,Cotação!$N$5:$N$36)</f>
         <v/>
       </c>
     </row>
@@ -694,19 +694,19 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$39,A8)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$36,A8)</f>
         <v/>
       </c>
       <c r="C8" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$39,A8,Cotação!$O$5:$O$39,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$36,A8,Cotação!$O$5:$O$36,"A cotar")</f>
         <v/>
       </c>
       <c r="D8" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$39,A8,Cotação!$O$5:$O$39,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$36,A8,Cotação!$O$5:$O$36,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E8" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$39,A8,Cotação!$N$5:$N$39)</f>
+        <f>SUMIF(Cotação!$B$5:$B$36,A8,Cotação!$N$5:$N$36)</f>
         <v/>
       </c>
     </row>
@@ -717,19 +717,19 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$39,A9)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$36,A9)</f>
         <v/>
       </c>
       <c r="C9" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$39,A9,Cotação!$O$5:$O$39,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$36,A9,Cotação!$O$5:$O$36,"A cotar")</f>
         <v/>
       </c>
       <c r="D9" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$39,A9,Cotação!$O$5:$O$39,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$36,A9,Cotação!$O$5:$O$36,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E9" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$39,A9,Cotação!$N$5:$N$39)</f>
+        <f>SUMIF(Cotação!$B$5:$B$36,A9,Cotação!$N$5:$N$36)</f>
         <v/>
       </c>
     </row>
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$39,A10)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$36,A10)</f>
         <v/>
       </c>
       <c r="C10" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$39,A10,Cotação!$O$5:$O$39,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$36,A10,Cotação!$O$5:$O$36,"A cotar")</f>
         <v/>
       </c>
       <c r="D10" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$39,A10,Cotação!$O$5:$O$39,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$36,A10,Cotação!$O$5:$O$36,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$39,A10,Cotação!$N$5:$N$39)</f>
+        <f>SUMIF(Cotação!$B$5:$B$36,A10,Cotação!$N$5:$N$36)</f>
         <v/>
       </c>
     </row>
@@ -763,19 +763,19 @@
         </is>
       </c>
       <c r="B11" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$39,A11)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$36,A11)</f>
         <v/>
       </c>
       <c r="C11" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$39,A11,Cotação!$O$5:$O$39,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$36,A11,Cotação!$O$5:$O$36,"A cotar")</f>
         <v/>
       </c>
       <c r="D11" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$39,A11,Cotação!$O$5:$O$39,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$36,A11,Cotação!$O$5:$O$36,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E11" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$39,A11,Cotação!$N$5:$N$39)</f>
+        <f>SUMIF(Cotação!$B$5:$B$36,A11,Cotação!$N$5:$N$36)</f>
         <v/>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P44"/>
+  <dimension ref="A1:P41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1494,12 +1494,12 @@
       </c>
       <c r="D9" s="23" t="inlineStr">
         <is>
-          <t>Király utca, Terézváros, a 5 min da Basílica · 2 quartos Superior Double · café da manhã · 3 noites</t>
+          <t>Király utca, Terézváros, a 5 min da Basílica · 2 quartos Superior Double · café da manhã · 4 noites</t>
         </is>
       </c>
       <c r="E9" s="23" t="inlineStr">
         <is>
-          <t>30/12 → 02/01</t>
+          <t>30/12 → 03/01</t>
         </is>
       </c>
       <c r="F9" s="23" t="n">
@@ -1516,7 +1516,7 @@
         </is>
       </c>
       <c r="I9" s="26" t="n">
-        <v>6300</v>
+        <v>8400</v>
       </c>
       <c r="J9" s="25" t="n">
         <v>2</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="P9" s="30" t="inlineStr">
         <is>
-          <t>3 noites calculadas proporcionalmente a partir da cotação de 4 noites (R$ 16.800 → R$ 12.600). Confirmar com o hotel na reserva.</t>
+          <t>Cotação de 21/09: R$ 16.800 pelos 2 quartos. 4 noites.</t>
         </is>
       </c>
     </row>
@@ -1566,12 +1566,12 @@
       </c>
       <c r="D10" s="23" t="inlineStr">
         <is>
-          <t>Váci utca, coração de Pest, pedestre · 2 quartos Superior · café da manhã · 3 noites</t>
+          <t>Váci utca, coração de Pest, pedestre · 2 quartos Superior · café da manhã · 4 noites</t>
         </is>
       </c>
       <c r="E10" s="23" t="inlineStr">
         <is>
-          <t>30/12 → 02/01</t>
+          <t>30/12 → 03/01</t>
         </is>
       </c>
       <c r="F10" s="23" t="n">
@@ -1588,7 +1588,7 @@
         </is>
       </c>
       <c r="I10" s="26" t="n">
-        <v>5025</v>
+        <v>6700</v>
       </c>
       <c r="J10" s="25" t="n">
         <v>2</v>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="P10" s="30" t="inlineStr">
         <is>
-          <t>3 noites calculadas proporcionalmente a partir da cotação de 4 noites (R$ 13.400 → R$ 10.050). Confirmar com o hotel na reserva.</t>
+          <t>Cotação de 21/09: R$ 13.400 pelos 2 quartos. 4 noites.</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="D11" s="23" t="inlineStr">
         <is>
-          <t>Margem do Danúbio, vista para o Castelo e a Ponte das Correntes · 2 quartos Classic · café da manhã · 3 noites</t>
+          <t>Margem do Danúbio, vista para o Castelo e a Ponte das Correntes · 2 quartos Classic · café da manhã · 4 noites</t>
         </is>
       </c>
       <c r="E11" s="23" t="inlineStr">
         <is>
-          <t>30/12 → 02/01</t>
+          <t>30/12 → 03/01</t>
         </is>
       </c>
       <c r="F11" s="23" t="n">
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="I11" s="26" t="n">
-        <v>6517.5</v>
+        <v>8690</v>
       </c>
       <c r="J11" s="25" t="n">
         <v>2</v>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="P11" s="30" t="inlineStr">
         <is>
-          <t>3 noites calculadas proporcionalmente a partir da cotação de 4 noites (R$ 17.380 → R$ 13.035). Confirmar com o hotel na reserva.</t>
+          <t>Cotação de 21/09: R$ 17.380 pelos 2 quartos. 4 noites. Escolhido para o total: único 5★ das três, à beira do rio.</t>
         </is>
       </c>
     </row>
@@ -1705,17 +1705,17 @@
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>Tokaj · Minaro Hotel Tokaj, MGallery 5★</t>
+          <t>Viena · Opção 1 · Steigenberger Icon Herrenhof 5★</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
         <is>
-          <t>Tokaj, à beira do rio Bodrog, a 5 min da estação · 2 quartos Superior King duplos · café da manhã · 1 noite</t>
+          <t>Herrengasse, Innere Stadt, a 5 min do Hofburg · 1 Junior Suite + 1 Superior Room · café da manhã · 4 noites</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">
         <is>
-          <t>02/01 → 03/01</t>
+          <t>03/01 → 07/01</t>
         </is>
       </c>
       <c r="F12" s="23" t="n">
@@ -1732,16 +1732,20 @@
         </is>
       </c>
       <c r="I12" s="26" t="n">
-        <v>3330</v>
+        <v>5910</v>
       </c>
       <c r="J12" s="25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K12" s="27">
         <f>IF(I12="","",I12*J12)</f>
         <v/>
       </c>
-      <c r="L12" s="28" t="n"/>
+      <c r="L12" s="28" t="inlineStr">
+        <is>
+          <t>Booking 20/09: € 1.862 (≈ R$ 11.004) por 2 quartos standard/4 noites no mesmo hotel</t>
+        </is>
+      </c>
       <c r="M12" s="25" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1758,7 +1762,7 @@
       </c>
       <c r="P12" s="30" t="inlineStr">
         <is>
-          <t>Cotação de 21/09: R$ 3.330 pelos 2 quartos, 1 noite. Substitui a 4ª noite de Budapeste (R$ 4.345 no InterContinental): a troca economiza R$ 1.015.</t>
+          <t>Cotação de 21/09: Junior Suite R$ 15.300 + Superior Room R$ 8.340 = R$ 23.640 pelas 4 noites (R$ 5.910/noite). Junior Suite comporta 3: pais + filho a partir de 05/01, filhas no Superior. Sem cama extra.</t>
         </is>
       </c>
     </row>
@@ -1773,12 +1777,12 @@
       </c>
       <c r="C13" s="24" t="inlineStr">
         <is>
-          <t>Viena · Opção 1 · Steigenberger Icon Herrenhof 5★</t>
+          <t>Viena · Opção 2 · Radisson Blu Style Hotel 5★</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
         <is>
-          <t>Herrengasse, Innere Stadt, a 5 min do Hofburg · 1 Junior Suite + 1 Superior Room · café da manhã · 4 noites</t>
+          <t>Herrengasse 12, Innere Stadt, design, a 3 min do Hofburg · 1 Junior Suite + 1 Superior Room · café da manhã · 4 noites</t>
         </is>
       </c>
       <c r="E13" s="23" t="inlineStr">
@@ -1800,7 +1804,7 @@
         </is>
       </c>
       <c r="I13" s="26" t="n">
-        <v>5910</v>
+        <v>4768</v>
       </c>
       <c r="J13" s="25" t="n">
         <v>4</v>
@@ -1811,12 +1815,12 @@
       </c>
       <c r="L13" s="28" t="inlineStr">
         <is>
-          <t>Booking 20/09: € 1.862 (≈ R$ 11.004) por 2 quartos standard/4 noites no mesmo hotel</t>
+          <t>Booking 20/09: R$ 12.034 por 2 quartos standard/4 noites no mesmo hotel</t>
         </is>
       </c>
       <c r="M13" s="25" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="N13" s="29">
@@ -1830,7 +1834,7 @@
       </c>
       <c r="P13" s="30" t="inlineStr">
         <is>
-          <t>Cotação de 21/09: Junior Suite R$ 15.300 + Superior Room R$ 8.340 = R$ 23.640 pelas 4 noites (R$ 5.910/noite). Junior Suite comporta 3: pais + filho a partir de 05/01, filhas no Superior. Sem cama extra.</t>
+          <t>Cotação de 21/09: Junior Suite R$ 11.042 + Superior Room R$ 8.030 = R$ 19.072 pelas 4 noites (R$ 4.768/noite). Junior Suite comporta 3. R$ 4.568 mais barato que o Herrenhof, na mesma rua.</t>
         </is>
       </c>
     </row>
@@ -1845,47 +1849,37 @@
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>Viena · Opção 2 · Radisson Blu Style Hotel 5★</t>
+          <t>Viena · cama extra ou 3º quarto para o filho</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
         <is>
-          <t>Herrengasse 12, Innere Stadt, design, a 3 min do Hofburg · 1 Junior Suite + 1 Superior Room · café da manhã · 4 noites</t>
+          <t>2 noites, a partir da chegada em 05/01, no hotel escolhido</t>
         </is>
       </c>
       <c r="E14" s="23" t="inlineStr">
         <is>
-          <t>03/01 → 07/01</t>
+          <t>05/01 → 07/01</t>
         </is>
       </c>
       <c r="F14" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="G14" s="25" t="inlineStr">
-        <is>
-          <t>Consolidador (a nomear)</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G14" s="25" t="inlineStr"/>
       <c r="H14" s="25" t="inlineStr">
         <is>
-          <t>BRL</t>
-        </is>
-      </c>
-      <c r="I14" s="26" t="n">
-        <v>4768</v>
-      </c>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I14" s="26" t="n"/>
       <c r="J14" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K14" s="27">
         <f>IF(I14="","",I14*J14)</f>
         <v/>
       </c>
-      <c r="L14" s="28" t="inlineStr">
-        <is>
-          <t>Booking 20/09: R$ 12.034 por 2 quartos standard/4 noites no mesmo hotel</t>
-        </is>
-      </c>
+      <c r="L14" s="28" t="inlineStr"/>
       <c r="M14" s="25" t="inlineStr">
         <is>
           <t>Não</t>
@@ -1897,12 +1891,12 @@
       </c>
       <c r="O14" s="25" t="inlineStr">
         <is>
-          <t>Cotado</t>
+          <t>Descartado</t>
         </is>
       </c>
       <c r="P14" s="30" t="inlineStr">
         <is>
-          <t>Cotação de 21/09: Junior Suite R$ 11.042 + Superior Room R$ 8.030 = R$ 19.072 pelas 4 noites (R$ 4.768/noite). Junior Suite comporta 3. R$ 4.568 mais barato que o Herrenhof, na mesma rua.</t>
+          <t>Desnecessária: a Junior Suite das duas opções comporta o filho.</t>
         </is>
       </c>
     </row>
@@ -1917,40 +1911,50 @@
       </c>
       <c r="C15" s="24" t="inlineStr">
         <is>
-          <t>Viena · cama extra ou 3º quarto para o filho</t>
+          <t>Praga · Opção 1 · The Emblem Prague Hotel 5★</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
         <is>
-          <t>2 noites, a partir da chegada em 05/01, no hotel escolhido</t>
+          <t>Platnéřská, Cidade Velha, a 2 min da Praça da Cidade Velha, spa na cobertura · 1 Suite Pretender + 1 Queen Room · café da manhã · 3 noites</t>
         </is>
       </c>
       <c r="E15" s="23" t="inlineStr">
         <is>
-          <t>05/01 → 07/01</t>
+          <t>07/01 → 10/01</t>
         </is>
       </c>
       <c r="F15" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="25" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="G15" s="25" t="inlineStr">
+        <is>
+          <t>Consolidador (a nomear)</t>
+        </is>
+      </c>
       <c r="H15" s="25" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="I15" s="26" t="n"/>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="I15" s="26" t="n">
+        <v>3335</v>
+      </c>
       <c r="J15" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15" s="27">
         <f>IF(I15="","",I15*J15)</f>
         <v/>
       </c>
-      <c r="L15" s="28" t="inlineStr"/>
+      <c r="L15" s="28" t="inlineStr">
+        <is>
+          <t>Booking 20/09, outros hotéis: Art Nouveau Palace 5★ € 812 · Hilton Old Town 5★ € 1.041 por 2 quartos/3 noites (5 pax)</t>
+        </is>
+      </c>
       <c r="M15" s="25" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="N15" s="29">
@@ -1959,12 +1963,12 @@
       </c>
       <c r="O15" s="25" t="inlineStr">
         <is>
-          <t>Descartado</t>
+          <t>Cotado</t>
         </is>
       </c>
       <c r="P15" s="30" t="inlineStr">
         <is>
-          <t>Desnecessária: a Junior Suite das duas opções comporta o filho.</t>
+          <t>Cotação de 21/09: Suite Pretender R$ 5.680 + Queen Room R$ 4.325 = R$ 10.005 pelas 3 noites (R$ 3.335/noite). Suíte comporta 3. Escolhida para o total: boutique 5★ no coração da Cidade Velha, R$ 1.980 acima da Opção 2.</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1983,12 @@
       </c>
       <c r="C16" s="24" t="inlineStr">
         <is>
-          <t>Praga · Opção 1 · The Emblem Prague Hotel 5★</t>
+          <t>Praga · Opção 2 · Century Old Town Prague, MGallery 4★</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
         <is>
-          <t>Platnéřská, Cidade Velha, a 2 min da Praça da Cidade Velha, spa na cobertura · 1 Suite Pretender + 1 Queen Room · café da manhã · 3 noites</t>
+          <t>Na Poříčí, prédio onde Kafka trabalhou, a 8 min da Praça da Cidade Velha · 1 Executive + 1 Classic Room · café da manhã · 3 noites</t>
         </is>
       </c>
       <c r="E16" s="23" t="inlineStr">
@@ -2006,7 +2010,7 @@
         </is>
       </c>
       <c r="I16" s="26" t="n">
-        <v>3335</v>
+        <v>2675</v>
       </c>
       <c r="J16" s="25" t="n">
         <v>3</v>
@@ -2015,14 +2019,10 @@
         <f>IF(I16="","",I16*J16)</f>
         <v/>
       </c>
-      <c r="L16" s="28" t="inlineStr">
-        <is>
-          <t>Booking 20/09, outros hotéis: Art Nouveau Palace 5★ € 812 · Hilton Old Town 5★ € 1.041 por 2 quartos/3 noites (5 pax)</t>
-        </is>
-      </c>
+      <c r="L16" s="28" t="n"/>
       <c r="M16" s="25" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="N16" s="29">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="P16" s="30" t="inlineStr">
         <is>
-          <t>Cotação de 21/09: Suite Pretender R$ 5.680 + Queen Room R$ 4.325 = R$ 10.005 pelas 3 noites (R$ 3.335/noite). Suíte comporta 3. Escolhida para o total: boutique 5★ no coração da Cidade Velha, R$ 1.980 acima da Opção 2.</t>
+          <t>Cotação de 21/09: Executive R$ 4.645 + Classic R$ 3.380 = R$ 8.025 pelas 3 noites (R$ 2.675/noite). Suíte comporta 3.</t>
         </is>
       </c>
     </row>
@@ -2051,17 +2051,17 @@
       </c>
       <c r="C17" s="24" t="inlineStr">
         <is>
-          <t>Praga · Opção 2 · Century Old Town Prague, MGallery 4★</t>
+          <t>Paris · Opção 1 · Hôtel François 1er 4★</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
         <is>
-          <t>Na Poříčí, prédio onde Kafka trabalhou, a 8 min da Praça da Cidade Velha · 1 Executive + 1 Classic Room · café da manhã · 3 noites</t>
+          <t>Rue Magellan, 8º arr., a 2 min da Champs-Élysées · 1 Executive Room + 1 Classic Double · café da manhã · 2 noites</t>
         </is>
       </c>
       <c r="E17" s="23" t="inlineStr">
         <is>
-          <t>07/01 → 10/01</t>
+          <t>10/01 → 12/01</t>
         </is>
       </c>
       <c r="F17" s="23" t="n">
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="I17" s="26" t="n">
-        <v>2675</v>
+        <v>5587.5</v>
       </c>
       <c r="J17" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K17" s="27">
         <f>IF(I17="","",I17*J17)</f>
@@ -2090,7 +2090,7 @@
       <c r="L17" s="28" t="n"/>
       <c r="M17" s="25" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="N17" s="29">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="P17" s="30" t="inlineStr">
         <is>
-          <t>Cotação de 21/09: Executive R$ 4.645 + Classic R$ 3.380 = R$ 8.025 pelas 3 noites (R$ 2.675/noite). Suíte comporta 3.</t>
+          <t>Cotação de 21/09: Executive R$ 6.420 + Classic Double R$ 4.755 = R$ 11.175 pelas 2 noites (R$ 5.587,50/noite). Executive comporta 3: pais + filho, filhas no Classic.</t>
         </is>
       </c>
     </row>
@@ -2119,12 +2119,12 @@
       </c>
       <c r="C18" s="24" t="inlineStr">
         <is>
-          <t>Paris · Opção 1 · Hôtel François 1er 4★</t>
+          <t>Paris · Opção 2 · Hotel Indigo Paris Opéra, IHG 4★</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
         <is>
-          <t>Rue Magellan, 8º arr., a 2 min da Champs-Élysées · 1 Executive Room + 1 Classic Double · café da manhã · 2 noites</t>
+          <t>Rue de Châteaudun, 9º arr., entre a Ópera Garnier e Montmartre · 1 Standard Queen triplo + 1 Standard Queen duplo · café da manhã · 2 noites</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">
@@ -2146,7 +2146,7 @@
         </is>
       </c>
       <c r="I18" s="26" t="n">
-        <v>5587.5</v>
+        <v>5715</v>
       </c>
       <c r="J18" s="25" t="n">
         <v>2</v>
@@ -2158,7 +2158,7 @@
       <c r="L18" s="28" t="n"/>
       <c r="M18" s="25" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="N18" s="29">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="P18" s="30" t="inlineStr">
         <is>
-          <t>Cotação de 21/09: Executive R$ 6.420 + Classic Double R$ 4.755 = R$ 11.175 pelas 2 noites (R$ 5.587,50/noite). Executive comporta 3: pais + filho, filhas no Classic.</t>
+          <t>Cotação de 21/09: triplo R$ 6.730 + duplo R$ 4.700 = R$ 11.430 pelas 2 noites (R$ 5.715/noite). Triplo resolve pais + filho sem depender de confirmação.</t>
         </is>
       </c>
     </row>
@@ -2182,26 +2182,26 @@
       </c>
       <c r="B19" s="23" t="inlineStr">
         <is>
-          <t>Hotel</t>
+          <t>Trem</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
         <is>
-          <t>Paris · Opção 2 · Hotel Indigo Paris Opéra, IHG 4★</t>
+          <t>Railjet Budapeste → Viena · 4 pax</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
         <is>
-          <t>Rue de Châteaudun, 9º arr., entre a Ópera Garnier e Montmartre · 1 Standard Queen triplo + 1 Standard Queen duplo · café da manhã · 2 noites</t>
+          <t>ÖBB RJX 62 · Budapest-Keleti 09:30 → Wien Hbf 12:20 · 2h50 · direto · 1ª classe · assentos marcados</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
         <is>
-          <t>10/01 → 12/01</t>
+          <t>03/01</t>
         </is>
       </c>
       <c r="F19" s="23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G19" s="25" t="inlineStr">
         <is>
@@ -2214,19 +2214,19 @@
         </is>
       </c>
       <c r="I19" s="26" t="n">
-        <v>5715</v>
+        <v>302.5</v>
       </c>
       <c r="J19" s="25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K19" s="27">
         <f>IF(I19="","",I19*J19)</f>
         <v/>
       </c>
-      <c r="L19" s="28" t="n"/>
+      <c r="L19" s="28" t="inlineStr"/>
       <c r="M19" s="25" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="N19" s="29">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="P19" s="30" t="inlineStr">
         <is>
-          <t>Cotação de 21/09: triplo R$ 6.730 + duplo R$ 4.700 = R$ 11.430 pelas 2 noites (R$ 5.715/noite). Triplo resolve pais + filho sem depender de confirmação.</t>
+          <t>Cotação de 21/09: R$ 1.210 para 4 pax (R$ 302,50/pax), 1ª classe.</t>
         </is>
       </c>
     </row>
@@ -2255,21 +2255,21 @@
       </c>
       <c r="C20" s="24" t="inlineStr">
         <is>
-          <t>Railjet Budapeste → Viena · 4 pax</t>
+          <t>Railjet Viena → Praga · 5 pax</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
         <is>
-          <t>ÖBB RJX 62 · Budapest-Keleti 09:30 → Wien Hbf 12:20 · 2h50 · direto · 1ª classe · assentos marcados</t>
+          <t>ÖBB RJ 252 · Wien Hbf 11:10 → Praha hlavní nádraží 15:23 · 4h13 · direto · 1ª classe · assentos marcados</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
         <is>
-          <t>03/01</t>
+          <t>07/01</t>
         </is>
       </c>
       <c r="F20" s="23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G20" s="25" t="inlineStr">
         <is>
@@ -2282,10 +2282,10 @@
         </is>
       </c>
       <c r="I20" s="26" t="n">
-        <v>302.5</v>
+        <v>381</v>
       </c>
       <c r="J20" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K20" s="27">
         <f>IF(I20="","",I20*J20)</f>
@@ -2294,7 +2294,7 @@
       <c r="L20" s="28" t="inlineStr"/>
       <c r="M20" s="25" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="N20" s="29">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="O20" s="25" t="inlineStr">
         <is>
-          <t>Descartado</t>
+          <t>Cotado</t>
         </is>
       </c>
       <c r="P20" s="30" t="inlineStr">
         <is>
-          <t>Substituído pelo trajeto via Tokaj (02 e 03/01). Valor de referência: R$ 1.210 para 4 pax em 1ª classe.</t>
+          <t>Cotação de 21/09: R$ 1.905 para 5 pax (R$ 381/pax), 1ª classe.</t>
         </is>
       </c>
     </row>
@@ -2318,48 +2318,42 @@
       </c>
       <c r="B21" s="23" t="inlineStr">
         <is>
-          <t>Trem</t>
+          <t>Transfer</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
         <is>
-          <t>Trem Budapeste → Tokaj · 4 pax</t>
+          <t>Budapeste · aeroporto → hotel · 4 pax</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
         <is>
-          <t>MÁV IC 562 Tokaj InterCity · Budapest-Keleti 09:25 → Tokaj 12:08 · 2h43 · direto · com bagagem</t>
+          <t>Van privativa com recepção no desembarque</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
         <is>
-          <t>02/01</t>
+          <t>30/12</t>
         </is>
       </c>
       <c r="F21" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="G21" s="25" t="inlineStr">
-        <is>
-          <t>Consolidador (a nomear)</t>
-        </is>
-      </c>
+      <c r="G21" s="25" t="inlineStr"/>
       <c r="H21" s="25" t="inlineStr">
         <is>
-          <t>BRL</t>
-        </is>
-      </c>
-      <c r="I21" s="26" t="n">
-        <v>100</v>
-      </c>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I21" s="26" t="n"/>
       <c r="J21" s="25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K21" s="27">
         <f>IF(I21="","",I21*J21)</f>
         <v/>
       </c>
-      <c r="L21" s="28" t="n"/>
+      <c r="L21" s="28" t="inlineStr"/>
       <c r="M21" s="25" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2371,12 +2365,12 @@
       </c>
       <c r="O21" s="25" t="inlineStr">
         <is>
-          <t>Cotado</t>
+          <t>A cotar</t>
         </is>
       </c>
       <c r="P21" s="30" t="inlineStr">
         <is>
-          <t>Cotação de 21/09: R$ 400 para 2 adultos e 2 adolescentes (R$ 100/pax). Confirmar classe. Chegada ao meio-dia: fazer Disznókő (descer em Mezőzombor, 12:00) e almoço primeiro, Oremus às 15h30, hotel às 17h. Há um alerta (⚠) em Hatvan no sistema da MÁV: conferir se é obra na linha.</t>
+          <t>Valor unitário = por veículo.</t>
         </is>
       </c>
     </row>
@@ -2386,17 +2380,17 @@
       </c>
       <c r="B22" s="23" t="inlineStr">
         <is>
-          <t>Trem</t>
+          <t>Transfer</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
         <is>
-          <t>Trem Tokaj → Budapeste → Viena · 4 pax</t>
+          <t>Budapeste · hotel → estação Keleti · 4 pax</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
         <is>
-          <t>IC 650 Tokaj 09:50 → Budapest-Keleti 12:47 · conexão 43 min · RJX 66 Keleti 13:30 → Wien Hbf 16:20 · 1ª classe · com bagagem</t>
+          <t>Carro ou van privativa</t>
         </is>
       </c>
       <c r="E22" s="23" t="inlineStr">
@@ -2407,27 +2401,21 @@
       <c r="F22" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="G22" s="25" t="inlineStr">
-        <is>
-          <t>Consolidador (a nomear)</t>
-        </is>
-      </c>
+      <c r="G22" s="25" t="inlineStr"/>
       <c r="H22" s="25" t="inlineStr">
         <is>
-          <t>BRL</t>
-        </is>
-      </c>
-      <c r="I22" s="26" t="n">
-        <v>925</v>
-      </c>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I22" s="26" t="n"/>
       <c r="J22" s="25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K22" s="27">
         <f>IF(I22="","",I22*J22)</f>
         <v/>
       </c>
-      <c r="L22" s="28" t="n"/>
+      <c r="L22" s="28" t="inlineStr"/>
       <c r="M22" s="25" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2439,14 +2427,10 @@
       </c>
       <c r="O22" s="25" t="inlineStr">
         <is>
-          <t>Cotado</t>
-        </is>
-      </c>
-      <c r="P22" s="30" t="inlineStr">
-        <is>
-          <t>Cotação de 21/09 para 2 adultos e 2 adolescentes: R$ 3.700 em 1ª classe (R$ 925/pax) ou R$ 2.530 em 2ª. ALERTA: o RJX 62 sozinho havia sido cotado a R$ 1.210 em 1ª classe para os 4. Pedir o mesmo trecho como duas passagens separadas (MÁV Tokaj → Keleti + ÖBB Sparschiene Keleti → Wien): deve cair para perto de R$ 1.600.</t>
-        </is>
-      </c>
+          <t>A cotar</t>
+        </is>
+      </c>
+      <c r="P22" s="30" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="23" t="n">
@@ -2454,42 +2438,36 @@
       </c>
       <c r="B23" s="23" t="inlineStr">
         <is>
-          <t>Trem</t>
+          <t>Transfer</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
         <is>
-          <t>Railjet Viena → Praga · 5 pax</t>
+          <t>Viena · estação Hbf → hotel · 4 pax</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
         <is>
-          <t>ÖBB RJ 252 · Wien Hbf 11:10 → Praha hlavní nádraží 15:23 · 4h13 · direto · 1ª classe · assentos marcados</t>
+          <t>Carro ou van privativa</t>
         </is>
       </c>
       <c r="E23" s="23" t="inlineStr">
         <is>
-          <t>07/01</t>
+          <t>03/01</t>
         </is>
       </c>
       <c r="F23" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="G23" s="25" t="inlineStr">
-        <is>
-          <t>Consolidador (a nomear)</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G23" s="25" t="inlineStr"/>
       <c r="H23" s="25" t="inlineStr">
         <is>
-          <t>BRL</t>
-        </is>
-      </c>
-      <c r="I23" s="26" t="n">
-        <v>381</v>
-      </c>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I23" s="26" t="n"/>
       <c r="J23" s="25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K23" s="27">
         <f>IF(I23="","",I23*J23)</f>
@@ -2507,14 +2485,10 @@
       </c>
       <c r="O23" s="25" t="inlineStr">
         <is>
-          <t>Cotado</t>
-        </is>
-      </c>
-      <c r="P23" s="30" t="inlineStr">
-        <is>
-          <t>Cotação de 21/09: R$ 1.905 para 5 pax (R$ 381/pax), 1ª classe.</t>
-        </is>
-      </c>
+          <t>A cotar</t>
+        </is>
+      </c>
+      <c r="P23" s="30" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="23" t="n">
@@ -2527,21 +2501,21 @@
       </c>
       <c r="C24" s="24" t="inlineStr">
         <is>
-          <t>Budapeste · aeroporto → hotel · 4 pax</t>
+          <t>Viena · aeroporto → hotel · filho · 1 pax</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
         <is>
-          <t>Van privativa com recepção no desembarque</t>
+          <t>Motorista com placa no desembarque · reforçar: menor viajando só</t>
         </is>
       </c>
       <c r="E24" s="23" t="inlineStr">
         <is>
-          <t>30/12</t>
+          <t>05/01</t>
         </is>
       </c>
       <c r="F24" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G24" s="25" t="inlineStr"/>
       <c r="H24" s="25" t="inlineStr">
@@ -2572,11 +2546,7 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P24" s="30" t="inlineStr">
-        <is>
-          <t>Valor unitário = por veículo.</t>
-        </is>
-      </c>
+      <c r="P24" s="30" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="23" t="n">
@@ -2589,21 +2559,21 @@
       </c>
       <c r="C25" s="24" t="inlineStr">
         <is>
-          <t>Budapeste · hotel → estação Keleti · 4 pax</t>
+          <t>Viena · hotel → estação Hbf · 5 pax</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
         <is>
-          <t>Carro ou van privativa, com bagagem</t>
+          <t>Van privativa</t>
         </is>
       </c>
       <c r="E25" s="23" t="inlineStr">
         <is>
-          <t>02/01</t>
+          <t>07/01</t>
         </is>
       </c>
       <c r="F25" s="23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G25" s="25" t="inlineStr"/>
       <c r="H25" s="25" t="inlineStr">
@@ -2647,21 +2617,21 @@
       </c>
       <c r="C26" s="24" t="inlineStr">
         <is>
-          <t>Viena · estação Hbf → hotel · 4 pax</t>
+          <t>Praga · estação hl.n. → hotel · 5 pax</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
         <is>
-          <t>Carro ou van privativa</t>
+          <t>Van privativa</t>
         </is>
       </c>
       <c r="E26" s="23" t="inlineStr">
         <is>
-          <t>03/01</t>
+          <t>07/01</t>
         </is>
       </c>
       <c r="F26" s="23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G26" s="25" t="inlineStr"/>
       <c r="H26" s="25" t="inlineStr">
@@ -2705,21 +2675,21 @@
       </c>
       <c r="C27" s="24" t="inlineStr">
         <is>
-          <t>Viena · aeroporto → hotel · filho · 1 pax</t>
+          <t>Praga · hotel → aeroporto · 5 pax</t>
         </is>
       </c>
       <c r="D27" s="23" t="inlineStr">
         <is>
-          <t>Motorista com placa no desembarque · reforçar: menor viajando só</t>
+          <t>Van privativa</t>
         </is>
       </c>
       <c r="E27" s="23" t="inlineStr">
         <is>
-          <t>05/01</t>
+          <t>10/01</t>
         </is>
       </c>
       <c r="F27" s="23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G27" s="25" t="inlineStr"/>
       <c r="H27" s="25" t="inlineStr">
@@ -2763,7 +2733,7 @@
       </c>
       <c r="C28" s="24" t="inlineStr">
         <is>
-          <t>Viena · hotel → estação Hbf · 5 pax</t>
+          <t>Paris · CDG → hotel · 5 pax</t>
         </is>
       </c>
       <c r="D28" s="23" t="inlineStr">
@@ -2773,7 +2743,7 @@
       </c>
       <c r="E28" s="23" t="inlineStr">
         <is>
-          <t>07/01</t>
+          <t>10/01</t>
         </is>
       </c>
       <c r="F28" s="23" t="n">
@@ -2821,7 +2791,7 @@
       </c>
       <c r="C29" s="24" t="inlineStr">
         <is>
-          <t>Praga · estação hl.n. → hotel · 5 pax</t>
+          <t>Paris · hotel → CDG · 5 pax</t>
         </is>
       </c>
       <c r="D29" s="23" t="inlineStr">
@@ -2831,7 +2801,7 @@
       </c>
       <c r="E29" s="23" t="inlineStr">
         <is>
-          <t>07/01</t>
+          <t>12/01</t>
         </is>
       </c>
       <c r="F29" s="23" t="n">
@@ -2874,42 +2844,52 @@
       </c>
       <c r="B30" s="23" t="inlineStr">
         <is>
-          <t>Transfer</t>
+          <t>Experiência</t>
         </is>
       </c>
       <c r="C30" s="24" t="inlineStr">
         <is>
-          <t>Praga · hotel → aeroporto · 5 pax</t>
+          <t>Réveillon · Opção 1 · Silverline · jantar de gala em catamarã · 4 pax</t>
         </is>
       </c>
       <c r="D30" s="23" t="inlineStr">
         <is>
-          <t>Van privativa</t>
+          <t>Cais 11, Ponte Elisabeth · embarque 20h, retorno 1h · welcome cocktail, jantar de 5 pratos, espumante, show de piano · Parlamento iluminado, brinde e fogos à meia-noite</t>
         </is>
       </c>
       <c r="E30" s="23" t="inlineStr">
         <is>
-          <t>10/01</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="F30" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="G30" s="25" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G30" s="25" t="inlineStr">
+        <is>
+          <t>Silverline Cruises</t>
+        </is>
+      </c>
       <c r="H30" s="25" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="I30" s="26" t="n"/>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="I30" s="26" t="n">
+        <v>2146.59</v>
+      </c>
       <c r="J30" s="25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K30" s="27">
         <f>IF(I30="","",I30*J30)</f>
         <v/>
       </c>
-      <c r="L30" s="28" t="inlineStr"/>
+      <c r="L30" s="28" t="inlineStr">
+        <is>
+          <t>silver-line.hu/product/budapest-new-years-eve-dinner-cruise</t>
+        </is>
+      </c>
       <c r="M30" s="25" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2921,10 +2901,14 @@
       </c>
       <c r="O30" s="25" t="inlineStr">
         <is>
-          <t>A cotar</t>
-        </is>
-      </c>
-      <c r="P30" s="30" t="inlineStr"/>
+          <t>Cotado</t>
+        </is>
+      </c>
+      <c r="P30" s="30" t="inlineStr">
+        <is>
+          <t>Valor por pessoa, conforme a página da Silverline em 21/09.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="23" t="n">
@@ -2932,45 +2916,55 @@
       </c>
       <c r="B31" s="23" t="inlineStr">
         <is>
-          <t>Transfer</t>
+          <t>Experiência</t>
         </is>
       </c>
       <c r="C31" s="24" t="inlineStr">
         <is>
-          <t>Paris · CDG → hotel · 5 pax</t>
+          <t>Réveillon · Opção 2 · Budapest River Cruise · NYE Party Cruise · 4 pax</t>
         </is>
       </c>
       <c r="D31" s="23" t="inlineStr">
         <is>
-          <t>Van privativa</t>
+          <t>Cais 8/8A, Ponte Elisabeth · embarque 19h, retorno 1h · jantar, música ao vivo e virada a bordo</t>
         </is>
       </c>
       <c r="E31" s="23" t="inlineStr">
         <is>
-          <t>10/01</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="F31" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="G31" s="25" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G31" s="25" t="inlineStr">
+        <is>
+          <t>Budapest River Cruise</t>
+        </is>
+      </c>
       <c r="H31" s="25" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="I31" s="26" t="n"/>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="I31" s="26" t="n">
+        <v>2272.86</v>
+      </c>
       <c r="J31" s="25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K31" s="27">
         <f>IF(I31="","",I31*J31)</f>
         <v/>
       </c>
-      <c r="L31" s="28" t="inlineStr"/>
+      <c r="L31" s="28" t="inlineStr">
+        <is>
+          <t>budapestrivercruise.com/budapest-new-years-eve-cruise-party</t>
+        </is>
+      </c>
       <c r="M31" s="25" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="N31" s="29">
@@ -2979,10 +2973,14 @@
       </c>
       <c r="O31" s="25" t="inlineStr">
         <is>
-          <t>A cotar</t>
-        </is>
-      </c>
-      <c r="P31" s="30" t="inlineStr"/>
+          <t>Cotado</t>
+        </is>
+      </c>
+      <c r="P31" s="30" t="inlineStr">
+        <is>
+          <t>Valor por pessoa, 6 horas a bordo (19h à 1h). Mais que o dobro da Opção 1 por pessoa. Confirmar preço de menor e o que o jantar inclui.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="23" t="n">
@@ -2990,31 +2988,35 @@
       </c>
       <c r="B32" s="23" t="inlineStr">
         <is>
-          <t>Transfer</t>
+          <t>Experiência</t>
         </is>
       </c>
       <c r="C32" s="24" t="inlineStr">
         <is>
-          <t>Paris · hotel → CDG · 5 pax</t>
+          <t>Tokaj · motorista privativo · dia inteiro · 4 pax</t>
         </is>
       </c>
       <c r="D32" s="23" t="inlineStr">
         <is>
-          <t>Van privativa</t>
+          <t>Saída 07:30 do InterContinental · Oremus (Tolcsva) · almoço · Disznókő (Mezőzombor) · retorno ~18:30 · ~11 horas, ~500 km</t>
         </is>
       </c>
       <c r="E32" s="23" t="inlineStr">
         <is>
-          <t>12/01</t>
+          <t>02/01</t>
         </is>
       </c>
       <c r="F32" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="G32" s="25" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G32" s="25" t="inlineStr">
+        <is>
+          <t>A definir (Pickup Hungary, MoveFlow, Sweet Travel, Taste Hungary)</t>
+        </is>
+      </c>
       <c r="H32" s="25" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>BRL</t>
         </is>
       </c>
       <c r="I32" s="26" t="n"/>
@@ -3040,7 +3042,11 @@
           <t>A cotar</t>
         </is>
       </c>
-      <c r="P32" s="30" t="inlineStr"/>
+      <c r="P32" s="30" t="inlineStr">
+        <is>
+          <t>Bate-volta. Motorista sem guia costuma sair bem abaixo do motorista-guia que veio caro. Referência: € 350 a 500 pelo dia.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="23" t="n">
@@ -3053,17 +3059,17 @@
       </c>
       <c r="C33" s="24" t="inlineStr">
         <is>
-          <t>Réveillon · Opção 1 · Silverline · jantar de gala em catamarã · 4 pax</t>
+          <t>Oremus · visita à adega e prova · 2 adultos + 2 filhas</t>
         </is>
       </c>
       <c r="D33" s="23" t="inlineStr">
         <is>
-          <t>Cais 11, Ponte Elisabeth · embarque 20h, retorno 1h · welcome cocktail, jantar de 5 pratos, espumante, show de piano · Parlamento iluminado, brinde e fogos à meia-noite</t>
+          <t>Tolcsva · agendamento por e-mail · ~1h · adegas do século XIII · adolescentes acompanham sem álcool</t>
         </is>
       </c>
       <c r="E33" s="23" t="inlineStr">
         <is>
-          <t>31/12</t>
+          <t>02/01</t>
         </is>
       </c>
       <c r="F33" s="23" t="n">
@@ -3071,7 +3077,7 @@
       </c>
       <c r="G33" s="25" t="inlineStr">
         <is>
-          <t>Silverline Cruises</t>
+          <t>Tokaj-Oremus</t>
         </is>
       </c>
       <c r="H33" s="25" t="inlineStr">
@@ -3080,20 +3086,16 @@
         </is>
       </c>
       <c r="I33" s="26" t="n">
-        <v>2146.59</v>
+        <v>315.67</v>
       </c>
       <c r="J33" s="25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K33" s="27">
         <f>IF(I33="","",I33*J33)</f>
         <v/>
       </c>
-      <c r="L33" s="28" t="inlineStr">
-        <is>
-          <t>silver-line.hu/product/budapest-new-years-eve-dinner-cruise</t>
-        </is>
-      </c>
+      <c r="L33" s="28" t="inlineStr"/>
       <c r="M33" s="25" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -3110,7 +3112,7 @@
       </c>
       <c r="P33" s="30" t="inlineStr">
         <is>
-          <t>Valor por pessoa, conforme a página da Silverline em 21/09.</t>
+          <t>Cotação de 21/09 em reais para a família (2 adultos e 2 filhas). Confirmar recepção no sábado 02/01; plano B: segunda 04/01.</t>
         </is>
       </c>
     </row>
@@ -3125,17 +3127,17 @@
       </c>
       <c r="C34" s="24" t="inlineStr">
         <is>
-          <t>Réveillon · Opção 2 · Budapest River Cruise · NYE Party Cruise · 4 pax</t>
+          <t>Disznókő · visita e prova · 2 adultos + 2 filhas</t>
         </is>
       </c>
       <c r="D34" s="23" t="inlineStr">
         <is>
-          <t>Cais 8/8A, Ponte Elisabeth · embarque 19h, retorno 1h · jantar, música ao vivo e virada a bordo</t>
+          <t>Mezőzombor, a 20 min de Tolcsva · vinícola do grupo AXA Millésimes · segunda parada da tarde</t>
         </is>
       </c>
       <c r="E34" s="23" t="inlineStr">
         <is>
-          <t>31/12</t>
+          <t>02/01</t>
         </is>
       </c>
       <c r="F34" s="23" t="n">
@@ -3143,7 +3145,7 @@
       </c>
       <c r="G34" s="25" t="inlineStr">
         <is>
-          <t>Budapest River Cruise</t>
+          <t>Disznókő</t>
         </is>
       </c>
       <c r="H34" s="25" t="inlineStr">
@@ -3151,24 +3153,18 @@
           <t>BRL</t>
         </is>
       </c>
-      <c r="I34" s="26" t="n">
-        <v>2272.86</v>
-      </c>
+      <c r="I34" s="26" t="n"/>
       <c r="J34" s="25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K34" s="27">
         <f>IF(I34="","",I34*J34)</f>
         <v/>
       </c>
-      <c r="L34" s="28" t="inlineStr">
-        <is>
-          <t>budapestrivercruise.com/budapest-new-years-eve-cruise-party</t>
-        </is>
-      </c>
+      <c r="L34" s="28" t="n"/>
       <c r="M34" s="25" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="N34" s="29">
@@ -3177,12 +3173,12 @@
       </c>
       <c r="O34" s="25" t="inlineStr">
         <is>
-          <t>Cotado</t>
+          <t>A cotar</t>
         </is>
       </c>
       <c r="P34" s="30" t="inlineStr">
         <is>
-          <t>Valor por pessoa, 6 horas a bordo (19h à 1h). Mais que o dobro da Opção 1 por pessoa. Confirmar preço de menor e o que o jantar inclui.</t>
+          <t>Aguardando valores da vinícola.</t>
         </is>
       </c>
     </row>
@@ -3197,12 +3193,12 @@
       </c>
       <c r="C35" s="24" t="inlineStr">
         <is>
-          <t>Tokaj · táxi local contratado pelo dia · 4 pax</t>
+          <t>Almoço em vinícola ou restaurante em Tokaj · 4 pax</t>
         </is>
       </c>
       <c r="D35" s="23" t="inlineStr">
         <is>
-          <t>Estação de Tokaj → Oremus (Tolcsva) → almoço → Disznókő (Mezőzombor) → Minaro Hotel · 03/01 hotel → estação</t>
+          <t>Mád ou Tarcal</t>
         </is>
       </c>
       <c r="E35" s="23" t="inlineStr">
@@ -3213,19 +3209,15 @@
       <c r="F35" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="G35" s="25" t="inlineStr">
-        <is>
-          <t>Motorista local (indicação da Oremus)</t>
-        </is>
-      </c>
+      <c r="G35" s="25" t="inlineStr"/>
       <c r="H35" s="25" t="inlineStr">
         <is>
-          <t>BRL</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="I35" s="26" t="n"/>
       <c r="J35" s="25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K35" s="27">
         <f>IF(I35="","",I35*J35)</f>
@@ -3248,7 +3240,7 @@
       </c>
       <c r="P35" s="30" t="inlineStr">
         <is>
-          <t>Substitui o motorista-guia de Budapeste, que veio muito caro. Referência: € 120 a 180 pelo dia.</t>
+          <t>Pode vir incluído no pacote do motorista-guia.</t>
         </is>
       </c>
     </row>
@@ -3258,30 +3250,30 @@
       </c>
       <c r="B36" s="23" t="inlineStr">
         <is>
-          <t>Experiência</t>
+          <t>Seguro/Docs</t>
         </is>
       </c>
       <c r="C36" s="24" t="inlineStr">
         <is>
-          <t>Oremus · visita à adega e prova · 2 adultos + 2 filhas</t>
+          <t>Seguro viagem · 5 pax · 15 dias</t>
         </is>
       </c>
       <c r="D36" s="23" t="inlineStr">
         <is>
-          <t>Tolcsva · agendamento por e-mail · ~1h · adegas do século XIII · adolescentes acompanham sem álcool</t>
+          <t>Plano 90 Essential · DMH USD 90.000 · 29/12 a 12/01</t>
         </is>
       </c>
       <c r="E36" s="23" t="inlineStr">
         <is>
-          <t>02/01</t>
+          <t>29/12 → 12/01</t>
         </is>
       </c>
       <c r="F36" s="23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G36" s="25" t="inlineStr">
         <is>
-          <t>Tokaj-Oremus</t>
+          <t>31 Motivos</t>
         </is>
       </c>
       <c r="H36" s="25" t="inlineStr">
@@ -3290,10 +3282,10 @@
         </is>
       </c>
       <c r="I36" s="26" t="n">
-        <v>315.67</v>
+        <v>300.6</v>
       </c>
       <c r="J36" s="25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K36" s="27">
         <f>IF(I36="","",I36*J36)</f>
@@ -3316,270 +3308,75 @@
       </c>
       <c r="P36" s="30" t="inlineStr">
         <is>
-          <t>Cotação de 21/09 em reais para a família (2 adultos e 2 filhas). Confirmar recepção no sábado 02/01; plano B: segunda 04/01.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="23" t="n">
-        <v>33</v>
-      </c>
-      <c r="B37" s="23" t="inlineStr">
-        <is>
-          <t>Experiência</t>
-        </is>
-      </c>
-      <c r="C37" s="24" t="inlineStr">
-        <is>
-          <t>Disznókő · visita e prova · 2 adultos + 2 filhas</t>
-        </is>
-      </c>
-      <c r="D37" s="23" t="inlineStr">
-        <is>
-          <t>Mezőzombor, a 20 min de Tolcsva · vinícola do grupo AXA Millésimes · segunda parada da tarde</t>
-        </is>
-      </c>
-      <c r="E37" s="23" t="inlineStr">
-        <is>
-          <t>02/01</t>
-        </is>
-      </c>
-      <c r="F37" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="G37" s="25" t="inlineStr">
-        <is>
-          <t>Disznókő</t>
-        </is>
-      </c>
-      <c r="H37" s="25" t="inlineStr">
-        <is>
-          <t>BRL</t>
-        </is>
-      </c>
-      <c r="I37" s="26" t="n"/>
-      <c r="J37" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="K37" s="27">
-        <f>IF(I37="","",I37*J37)</f>
-        <v/>
-      </c>
-      <c r="L37" s="28" t="n"/>
-      <c r="M37" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="N37" s="29">
-        <f>IF(OR(M37&lt;&gt;"Sim",I37=""),0,K37*IF(H37="BRL",1,IF(H37="EUR",Parâmetros!$B$4,IF(H37="USD",Parâmetros!$B$5,1))))</f>
-        <v/>
-      </c>
-      <c r="O37" s="25" t="inlineStr">
-        <is>
-          <t>A cotar</t>
-        </is>
-      </c>
-      <c r="P37" s="30" t="inlineStr">
-        <is>
-          <t>Aguardando valores da vinícola.</t>
-        </is>
-      </c>
-    </row>
+          <t>Cotação de 21/09: R$ 1.503,00 para os 5 (R$ 300,60 por pessoa). Confirmar se a apólice do filho cobre desde o embarque dele em 04/01.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
     <row r="38">
-      <c r="A38" s="23" t="n">
-        <v>34</v>
-      </c>
-      <c r="B38" s="23" t="inlineStr">
-        <is>
-          <t>Experiência</t>
-        </is>
-      </c>
-      <c r="C38" s="24" t="inlineStr">
-        <is>
-          <t>Almoço em vinícola ou restaurante em Tokaj · 4 pax</t>
-        </is>
-      </c>
-      <c r="D38" s="23" t="inlineStr">
-        <is>
-          <t>Mád ou Tarcal</t>
-        </is>
-      </c>
-      <c r="E38" s="23" t="inlineStr">
-        <is>
-          <t>02/01</t>
-        </is>
-      </c>
-      <c r="F38" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="G38" s="25" t="inlineStr"/>
-      <c r="H38" s="25" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="I38" s="26" t="n"/>
-      <c r="J38" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="K38" s="27">
-        <f>IF(I38="","",I38*J38)</f>
-        <v/>
-      </c>
-      <c r="L38" s="28" t="inlineStr"/>
-      <c r="M38" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="N38" s="29">
-        <f>IF(OR(M38&lt;&gt;"Sim",I38=""),0,K38*IF(H38="BRL",1,IF(H38="EUR",Parâmetros!$B$4,IF(H38="USD",Parâmetros!$B$5,1))))</f>
-        <v/>
-      </c>
-      <c r="O38" s="25" t="inlineStr">
-        <is>
-          <t>A cotar</t>
-        </is>
-      </c>
-      <c r="P38" s="30" t="inlineStr">
-        <is>
-          <t>Pode vir incluído no pacote do motorista-guia.</t>
-        </is>
+      <c r="C38" s="21" t="inlineStr">
+        <is>
+          <t>SUBTOTAL EM R$ (itens marcados como Sim)</t>
+        </is>
+      </c>
+      <c r="N38" s="31">
+        <f>SUM(N5:N36)</f>
+        <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="23" t="n">
-        <v>35</v>
-      </c>
-      <c r="B39" s="23" t="inlineStr">
-        <is>
-          <t>Seguro/Docs</t>
-        </is>
-      </c>
-      <c r="C39" s="24" t="inlineStr">
-        <is>
-          <t>Seguro viagem · 5 pax · 15 dias</t>
-        </is>
-      </c>
-      <c r="D39" s="23" t="inlineStr">
-        <is>
-          <t>Plano 90 Essential · DMH USD 90.000 · 29/12 a 12/01</t>
-        </is>
-      </c>
-      <c r="E39" s="23" t="inlineStr">
-        <is>
-          <t>29/12 → 12/01</t>
-        </is>
-      </c>
-      <c r="F39" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="G39" s="25" t="inlineStr">
-        <is>
-          <t>31 Motivos</t>
-        </is>
-      </c>
-      <c r="H39" s="25" t="inlineStr">
-        <is>
-          <t>BRL</t>
-        </is>
-      </c>
-      <c r="I39" s="26" t="n">
-        <v>300.6</v>
-      </c>
-      <c r="J39" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="K39" s="27">
-        <f>IF(I39="","",I39*J39)</f>
-        <v/>
-      </c>
-      <c r="L39" s="28" t="inlineStr"/>
-      <c r="M39" s="25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="N39" s="29">
-        <f>IF(OR(M39&lt;&gt;"Sim",I39=""),0,K39*IF(H39="BRL",1,IF(H39="EUR",Parâmetros!$B$4,IF(H39="USD",Parâmetros!$B$5,1))))</f>
-        <v/>
-      </c>
-      <c r="O39" s="25" t="inlineStr">
-        <is>
-          <t>Cotado</t>
-        </is>
-      </c>
-      <c r="P39" s="30" t="inlineStr">
-        <is>
-          <t>Cotação de 21/09: R$ 1.503,00 para os 5 (R$ 300,60 por pessoa). Confirmar se a apólice do filho cobre desde o embarque dele em 04/01.</t>
-        </is>
-      </c>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>Taxa de serviço LusaTravel</t>
+        </is>
+      </c>
+      <c r="N39" s="13">
+        <f>N38*Parâmetros!$B$10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="32" t="n"/>
+      <c r="B40" s="32" t="n"/>
+      <c r="C40" s="33" t="inlineStr">
+        <is>
+          <t>TOTAL PARA O CLIENTE</t>
+        </is>
+      </c>
+      <c r="D40" s="32" t="n"/>
+      <c r="E40" s="32" t="n"/>
+      <c r="F40" s="32" t="n"/>
+      <c r="G40" s="32" t="n"/>
+      <c r="H40" s="32" t="n"/>
+      <c r="I40" s="32" t="n"/>
+      <c r="J40" s="32" t="n"/>
+      <c r="K40" s="32" t="n"/>
+      <c r="L40" s="32" t="n"/>
+      <c r="M40" s="32" t="n"/>
+      <c r="N40" s="34">
+        <f>N38+N39</f>
+        <v/>
+      </c>
+      <c r="O40" s="32" t="n"/>
+      <c r="P40" s="32" t="n"/>
     </row>
     <row r="41">
-      <c r="C41" s="21" t="inlineStr">
-        <is>
-          <t>SUBTOTAL EM R$ (itens marcados como Sim)</t>
-        </is>
-      </c>
-      <c r="N41" s="31">
-        <f>SUM(N5:N39)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="C42" s="12" t="inlineStr">
-        <is>
-          <t>Taxa de serviço LusaTravel</t>
-        </is>
-      </c>
-      <c r="N42" s="13">
-        <f>N41*Parâmetros!$B$10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="32" t="n"/>
-      <c r="B43" s="32" t="n"/>
-      <c r="C43" s="33" t="inlineStr">
-        <is>
-          <t>TOTAL PARA O CLIENTE</t>
-        </is>
-      </c>
-      <c r="D43" s="32" t="n"/>
-      <c r="E43" s="32" t="n"/>
-      <c r="F43" s="32" t="n"/>
-      <c r="G43" s="32" t="n"/>
-      <c r="H43" s="32" t="n"/>
-      <c r="I43" s="32" t="n"/>
-      <c r="J43" s="32" t="n"/>
-      <c r="K43" s="32" t="n"/>
-      <c r="L43" s="32" t="n"/>
-      <c r="M43" s="32" t="n"/>
-      <c r="N43" s="34">
-        <f>N41+N42</f>
-        <v/>
-      </c>
-      <c r="O43" s="32" t="n"/>
-      <c r="P43" s="32" t="n"/>
-    </row>
-    <row r="44">
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>*Nada reservado, apenas cotado.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:P39"/>
+  <autoFilter ref="A4:P36"/>
   <dataValidations count="3">
-    <dataValidation sqref="O5:O39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O5:O36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"A cotar,Cotado,Aprovado pelo cliente,Reservado,Descartado"</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="M5:M36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="H5:H36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"BRL,EUR,USD"</formula1>
     </dataValidation>
   </dataValidations>

--- a/cotacao-cristofer-reveillon.xlsx
+++ b/cotacao-cristofer-reveillon.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Cotação" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Cotação'!$A$4:$P$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Cotação'!$A$4:$P$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -625,19 +625,19 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$36,A5)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$37,A5)</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$36,A5,Cotação!$O$5:$O$36,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$37,A5,Cotação!$O$5:$O$37,"A cotar")</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$36,A5,Cotação!$O$5:$O$36,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$37,A5,Cotação!$O$5:$O$37,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E5" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$36,A5,Cotação!$N$5:$N$36)</f>
+        <f>SUMIF(Cotação!$B$5:$B$37,A5,Cotação!$N$5:$N$37)</f>
         <v/>
       </c>
     </row>
@@ -648,19 +648,19 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$36,A6)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$37,A6)</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$36,A6,Cotação!$O$5:$O$36,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$37,A6,Cotação!$O$5:$O$37,"A cotar")</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$36,A6,Cotação!$O$5:$O$36,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$37,A6,Cotação!$O$5:$O$37,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E6" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$36,A6,Cotação!$N$5:$N$36)</f>
+        <f>SUMIF(Cotação!$B$5:$B$37,A6,Cotação!$N$5:$N$37)</f>
         <v/>
       </c>
     </row>
@@ -671,19 +671,19 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$36,A7)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$37,A7)</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$36,A7,Cotação!$O$5:$O$36,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$37,A7,Cotação!$O$5:$O$37,"A cotar")</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$36,A7,Cotação!$O$5:$O$36,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$37,A7,Cotação!$O$5:$O$37,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E7" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$36,A7,Cotação!$N$5:$N$36)</f>
+        <f>SUMIF(Cotação!$B$5:$B$37,A7,Cotação!$N$5:$N$37)</f>
         <v/>
       </c>
     </row>
@@ -694,19 +694,19 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$36,A8)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$37,A8)</f>
         <v/>
       </c>
       <c r="C8" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$36,A8,Cotação!$O$5:$O$36,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$37,A8,Cotação!$O$5:$O$37,"A cotar")</f>
         <v/>
       </c>
       <c r="D8" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$36,A8,Cotação!$O$5:$O$36,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$37,A8,Cotação!$O$5:$O$37,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E8" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$36,A8,Cotação!$N$5:$N$36)</f>
+        <f>SUMIF(Cotação!$B$5:$B$37,A8,Cotação!$N$5:$N$37)</f>
         <v/>
       </c>
     </row>
@@ -717,19 +717,19 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$36,A9)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$37,A9)</f>
         <v/>
       </c>
       <c r="C9" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$36,A9,Cotação!$O$5:$O$36,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$37,A9,Cotação!$O$5:$O$37,"A cotar")</f>
         <v/>
       </c>
       <c r="D9" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$36,A9,Cotação!$O$5:$O$36,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$37,A9,Cotação!$O$5:$O$37,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E9" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$36,A9,Cotação!$N$5:$N$36)</f>
+        <f>SUMIF(Cotação!$B$5:$B$37,A9,Cotação!$N$5:$N$37)</f>
         <v/>
       </c>
     </row>
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$36,A10)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$37,A10)</f>
         <v/>
       </c>
       <c r="C10" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$36,A10,Cotação!$O$5:$O$36,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$37,A10,Cotação!$O$5:$O$37,"A cotar")</f>
         <v/>
       </c>
       <c r="D10" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$36,A10,Cotação!$O$5:$O$36,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$37,A10,Cotação!$O$5:$O$37,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$36,A10,Cotação!$N$5:$N$36)</f>
+        <f>SUMIF(Cotação!$B$5:$B$37,A10,Cotação!$N$5:$N$37)</f>
         <v/>
       </c>
     </row>
@@ -763,19 +763,19 @@
         </is>
       </c>
       <c r="B11" s="5">
-        <f>COUNTIF(Cotação!$B$5:$B$36,A11)</f>
+        <f>COUNTIF(Cotação!$B$5:$B$37,A11)</f>
         <v/>
       </c>
       <c r="C11" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$36,A11,Cotação!$O$5:$O$36,"A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$37,A11,Cotação!$O$5:$O$37,"A cotar")</f>
         <v/>
       </c>
       <c r="D11" s="5">
-        <f>COUNTIFS(Cotação!$B$5:$B$36,A11,Cotação!$O$5:$O$36,"&lt;&gt;A cotar")</f>
+        <f>COUNTIFS(Cotação!$B$5:$B$37,A11,Cotação!$O$5:$O$37,"&lt;&gt;A cotar")</f>
         <v/>
       </c>
       <c r="E11" s="6">
-        <f>SUMIF(Cotação!$B$5:$B$36,A11,Cotação!$N$5:$N$36)</f>
+        <f>SUMIF(Cotação!$B$5:$B$37,A11,Cotação!$N$5:$N$37)</f>
         <v/>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P41"/>
+  <dimension ref="A1:P42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2849,12 +2849,12 @@
       </c>
       <c r="C30" s="24" t="inlineStr">
         <is>
-          <t>Réveillon · Opção 1 · Silverline · jantar de gala em catamarã · 4 pax</t>
+          <t>Réveillon · Opção 1 · jantar no Bairro do Castelo + fogos do Bastião dos Pescadores · 4 pax</t>
         </is>
       </c>
       <c r="D30" s="23" t="inlineStr">
         <is>
-          <t>Cais 11, Ponte Elisabeth · embarque 20h, retorno 1h · welcome cocktail, jantar de 5 pratos, espumante, show de piano · Parlamento iluminado, brinde e fogos à meia-noite</t>
+          <t>Jantar de Réveillon no Pierrot ou no Alabárdos, Bairro do Castelo, lado de Buda · à meia-noite, 5 min a pé até os terraços do Bastião, vista de toda a margem de Pest e do Danúbio · retorno de carro ao hotel</t>
         </is>
       </c>
       <c r="E30" s="23" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="G30" s="25" t="inlineStr">
         <is>
-          <t>Silverline Cruises</t>
+          <t>Pierrot / Alabárdos</t>
         </is>
       </c>
       <c r="H30" s="25" t="inlineStr">
@@ -2875,9 +2875,7 @@
           <t>BRL</t>
         </is>
       </c>
-      <c r="I30" s="26" t="n">
-        <v>2146.59</v>
-      </c>
+      <c r="I30" s="26" t="n"/>
       <c r="J30" s="25" t="n">
         <v>4</v>
       </c>
@@ -2885,11 +2883,7 @@
         <f>IF(I30="","",I30*J30)</f>
         <v/>
       </c>
-      <c r="L30" s="28" t="inlineStr">
-        <is>
-          <t>silver-line.hu/product/budapest-new-years-eve-dinner-cruise</t>
-        </is>
-      </c>
+      <c r="L30" s="28" t="n"/>
       <c r="M30" s="25" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2901,12 +2895,12 @@
       </c>
       <c r="O30" s="25" t="inlineStr">
         <is>
-          <t>Cotado</t>
+          <t>A cotar</t>
         </is>
       </c>
       <c r="P30" s="30" t="inlineStr">
         <is>
-          <t>Valor por pessoa, conforme a página da Silverline em 21/09.</t>
+          <t>Escolha do cliente: jantar tranquilo e fogos vistos de longe, sem barco. Menu de Réveillon costuma ficar entre € 120 e 200 por pessoa. Reservar em outubro.</t>
         </is>
       </c>
     </row>
@@ -2921,12 +2915,12 @@
       </c>
       <c r="C31" s="24" t="inlineStr">
         <is>
-          <t>Réveillon · Opção 2 · Budapest River Cruise · NYE Party Cruise · 4 pax</t>
+          <t>Réveillon · Opção 2 · Silverline · jantar de gala em catamarã · 4 pax</t>
         </is>
       </c>
       <c r="D31" s="23" t="inlineStr">
         <is>
-          <t>Cais 8/8A, Ponte Elisabeth · embarque 19h, retorno 1h · jantar, música ao vivo e virada a bordo</t>
+          <t>Cais 11, Ponte Elisabeth · embarque 20h, retorno 1h · welcome cocktail, jantar de 5 pratos, espumante, show de piano · Parlamento iluminado, brinde e fogos à meia-noite</t>
         </is>
       </c>
       <c r="E31" s="23" t="inlineStr">
@@ -2939,7 +2933,7 @@
       </c>
       <c r="G31" s="25" t="inlineStr">
         <is>
-          <t>Budapest River Cruise</t>
+          <t>Silverline Cruises</t>
         </is>
       </c>
       <c r="H31" s="25" t="inlineStr">
@@ -2948,7 +2942,7 @@
         </is>
       </c>
       <c r="I31" s="26" t="n">
-        <v>2272.86</v>
+        <v>2146.59</v>
       </c>
       <c r="J31" s="25" t="n">
         <v>4</v>
@@ -2959,7 +2953,7 @@
       </c>
       <c r="L31" s="28" t="inlineStr">
         <is>
-          <t>budapestrivercruise.com/budapest-new-years-eve-cruise-party</t>
+          <t>silver-line.hu/product/budapest-new-years-eve-dinner-cruise</t>
         </is>
       </c>
       <c r="M31" s="25" t="inlineStr">
@@ -2978,7 +2972,7 @@
       </c>
       <c r="P31" s="30" t="inlineStr">
         <is>
-          <t>Valor por pessoa, 6 horas a bordo (19h à 1h). Mais que o dobro da Opção 1 por pessoa. Confirmar preço de menor e o que o jantar inclui.</t>
+          <t>Valor por pessoa, conforme a página da Silverline em 21/09.</t>
         </is>
       </c>
     </row>
@@ -2993,17 +2987,17 @@
       </c>
       <c r="C32" s="24" t="inlineStr">
         <is>
-          <t>Tokaj · motorista privativo · dia inteiro · 4 pax</t>
+          <t>Réveillon · Opção 3 · Budapest River Cruise · NYE Party Cruise · 4 pax</t>
         </is>
       </c>
       <c r="D32" s="23" t="inlineStr">
         <is>
-          <t>Saída 07:30 do InterContinental · Oremus (Tolcsva) · almoço · Disznókő (Mezőzombor) · retorno ~18:30 · ~11 horas, ~500 km</t>
+          <t>Cais 8/8A, Ponte Elisabeth · embarque 19h, retorno 1h · jantar, música ao vivo e virada a bordo</t>
         </is>
       </c>
       <c r="E32" s="23" t="inlineStr">
         <is>
-          <t>02/01</t>
+          <t>31/12</t>
         </is>
       </c>
       <c r="F32" s="23" t="n">
@@ -3011,7 +3005,7 @@
       </c>
       <c r="G32" s="25" t="inlineStr">
         <is>
-          <t>A definir (Pickup Hungary, MoveFlow, Sweet Travel, Taste Hungary)</t>
+          <t>Budapest River Cruise</t>
         </is>
       </c>
       <c r="H32" s="25" t="inlineStr">
@@ -3019,18 +3013,24 @@
           <t>BRL</t>
         </is>
       </c>
-      <c r="I32" s="26" t="n"/>
+      <c r="I32" s="26" t="n">
+        <v>2272.86</v>
+      </c>
       <c r="J32" s="25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K32" s="27">
         <f>IF(I32="","",I32*J32)</f>
         <v/>
       </c>
-      <c r="L32" s="28" t="inlineStr"/>
+      <c r="L32" s="28" t="inlineStr">
+        <is>
+          <t>budapestrivercruise.com/budapest-new-years-eve-cruise-party</t>
+        </is>
+      </c>
       <c r="M32" s="25" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="N32" s="29">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="O32" s="25" t="inlineStr">
         <is>
-          <t>A cotar</t>
+          <t>Cotado</t>
         </is>
       </c>
       <c r="P32" s="30" t="inlineStr">
         <is>
-          <t>Bate-volta. Motorista sem guia costuma sair bem abaixo do motorista-guia que veio caro. Referência: € 350 a 500 pelo dia.</t>
+          <t>Valor por pessoa, 6 horas a bordo (19h à 1h). Mais que o dobro da Opção 1 por pessoa. Confirmar preço de menor e o que o jantar inclui.</t>
         </is>
       </c>
     </row>
@@ -3059,12 +3059,12 @@
       </c>
       <c r="C33" s="24" t="inlineStr">
         <is>
-          <t>Oremus · visita à adega e prova · 2 adultos + 2 filhas</t>
+          <t>Tokaj · motorista privativo · dia inteiro · 4 pax</t>
         </is>
       </c>
       <c r="D33" s="23" t="inlineStr">
         <is>
-          <t>Tolcsva · agendamento por e-mail · ~1h · adegas do século XIII · adolescentes acompanham sem álcool</t>
+          <t>Saída 07:30 do InterContinental · Oremus (Tolcsva) · almoço · Disznókő (Mezőzombor) · retorno ~18:30 · ~11 horas, ~500 km</t>
         </is>
       </c>
       <c r="E33" s="23" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="G33" s="25" t="inlineStr">
         <is>
-          <t>Tokaj-Oremus</t>
+          <t>A definir (Pickup Hungary, MoveFlow, Sweet Travel, Taste Hungary)</t>
         </is>
       </c>
       <c r="H33" s="25" t="inlineStr">
@@ -3085,9 +3085,7 @@
           <t>BRL</t>
         </is>
       </c>
-      <c r="I33" s="26" t="n">
-        <v>315.67</v>
-      </c>
+      <c r="I33" s="26" t="n"/>
       <c r="J33" s="25" t="n">
         <v>1</v>
       </c>
@@ -3107,12 +3105,12 @@
       </c>
       <c r="O33" s="25" t="inlineStr">
         <is>
-          <t>Cotado</t>
+          <t>A cotar</t>
         </is>
       </c>
       <c r="P33" s="30" t="inlineStr">
         <is>
-          <t>Cotação de 21/09 em reais para a família (2 adultos e 2 filhas). Confirmar recepção no sábado 02/01; plano B: segunda 04/01.</t>
+          <t>Bate-volta. Motorista sem guia costuma sair bem abaixo do motorista-guia que veio caro. Referência: € 350 a 500 pelo dia.</t>
         </is>
       </c>
     </row>
@@ -3127,12 +3125,12 @@
       </c>
       <c r="C34" s="24" t="inlineStr">
         <is>
-          <t>Disznókő · visita e prova · 2 adultos + 2 filhas</t>
+          <t>Oremus · visita à adega e prova · 2 adultos + 2 filhas</t>
         </is>
       </c>
       <c r="D34" s="23" t="inlineStr">
         <is>
-          <t>Mezőzombor, a 20 min de Tolcsva · vinícola do grupo AXA Millésimes · segunda parada da tarde</t>
+          <t>Tolcsva · agendamento por e-mail · ~1h · adegas do século XIII · adolescentes acompanham sem álcool</t>
         </is>
       </c>
       <c r="E34" s="23" t="inlineStr">
@@ -3145,7 +3143,7 @@
       </c>
       <c r="G34" s="25" t="inlineStr">
         <is>
-          <t>Disznókő</t>
+          <t>Tokaj-Oremus</t>
         </is>
       </c>
       <c r="H34" s="25" t="inlineStr">
@@ -3153,7 +3151,9 @@
           <t>BRL</t>
         </is>
       </c>
-      <c r="I34" s="26" t="n"/>
+      <c r="I34" s="26" t="n">
+        <v>315.67</v>
+      </c>
       <c r="J34" s="25" t="n">
         <v>1</v>
       </c>
@@ -3161,7 +3161,7 @@
         <f>IF(I34="","",I34*J34)</f>
         <v/>
       </c>
-      <c r="L34" s="28" t="n"/>
+      <c r="L34" s="28" t="inlineStr"/>
       <c r="M34" s="25" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -3173,12 +3173,12 @@
       </c>
       <c r="O34" s="25" t="inlineStr">
         <is>
-          <t>A cotar</t>
+          <t>Cotado</t>
         </is>
       </c>
       <c r="P34" s="30" t="inlineStr">
         <is>
-          <t>Aguardando valores da vinícola.</t>
+          <t>Cotação de 21/09 em reais para a família (2 adultos e 2 filhas). Confirmar recepção no sábado 02/01; plano B: segunda 04/01.</t>
         </is>
       </c>
     </row>
@@ -3193,12 +3193,12 @@
       </c>
       <c r="C35" s="24" t="inlineStr">
         <is>
-          <t>Almoço em vinícola ou restaurante em Tokaj · 4 pax</t>
+          <t>Disznókő · visita e prova · 2 adultos + 2 filhas</t>
         </is>
       </c>
       <c r="D35" s="23" t="inlineStr">
         <is>
-          <t>Mád ou Tarcal</t>
+          <t>Mezőzombor, a 20 min de Tolcsva · vinícola do grupo AXA Millésimes · segunda parada da tarde</t>
         </is>
       </c>
       <c r="E35" s="23" t="inlineStr">
@@ -3209,21 +3209,25 @@
       <c r="F35" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="G35" s="25" t="inlineStr"/>
+      <c r="G35" s="25" t="inlineStr">
+        <is>
+          <t>Disznókő</t>
+        </is>
+      </c>
       <c r="H35" s="25" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>BRL</t>
         </is>
       </c>
       <c r="I35" s="26" t="n"/>
       <c r="J35" s="25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K35" s="27">
         <f>IF(I35="","",I35*J35)</f>
         <v/>
       </c>
-      <c r="L35" s="28" t="inlineStr"/>
+      <c r="L35" s="28" t="n"/>
       <c r="M35" s="25" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -3240,7 +3244,7 @@
       </c>
       <c r="P35" s="30" t="inlineStr">
         <is>
-          <t>Pode vir incluído no pacote do motorista-guia.</t>
+          <t>Aguardando valores da vinícola.</t>
         </is>
       </c>
     </row>
@@ -3250,42 +3254,36 @@
       </c>
       <c r="B36" s="23" t="inlineStr">
         <is>
-          <t>Seguro/Docs</t>
+          <t>Experiência</t>
         </is>
       </c>
       <c r="C36" s="24" t="inlineStr">
         <is>
-          <t>Seguro viagem · 5 pax · 15 dias</t>
+          <t>Almoço em vinícola ou restaurante em Tokaj · 4 pax</t>
         </is>
       </c>
       <c r="D36" s="23" t="inlineStr">
         <is>
-          <t>Plano 90 Essential · DMH USD 90.000 · 29/12 a 12/01</t>
+          <t>Mád ou Tarcal</t>
         </is>
       </c>
       <c r="E36" s="23" t="inlineStr">
         <is>
-          <t>29/12 → 12/01</t>
+          <t>02/01</t>
         </is>
       </c>
       <c r="F36" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="G36" s="25" t="inlineStr">
-        <is>
-          <t>31 Motivos</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G36" s="25" t="inlineStr"/>
       <c r="H36" s="25" t="inlineStr">
         <is>
-          <t>BRL</t>
-        </is>
-      </c>
-      <c r="I36" s="26" t="n">
-        <v>300.6</v>
-      </c>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I36" s="26" t="n"/>
       <c r="J36" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K36" s="27">
         <f>IF(I36="","",I36*J36)</f>
@@ -3303,80 +3301,148 @@
       </c>
       <c r="O36" s="25" t="inlineStr">
         <is>
+          <t>A cotar</t>
+        </is>
+      </c>
+      <c r="P36" s="30" t="inlineStr">
+        <is>
+          <t>Pode vir incluído no pacote do motorista-guia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="23" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="23" t="inlineStr">
+        <is>
+          <t>Seguro/Docs</t>
+        </is>
+      </c>
+      <c r="C37" s="24" t="inlineStr">
+        <is>
+          <t>Seguro viagem · 5 pax · 15 dias</t>
+        </is>
+      </c>
+      <c r="D37" s="23" t="inlineStr">
+        <is>
+          <t>Plano 90 Essential · DMH USD 90.000 · 29/12 a 12/01</t>
+        </is>
+      </c>
+      <c r="E37" s="23" t="inlineStr">
+        <is>
+          <t>29/12 → 12/01</t>
+        </is>
+      </c>
+      <c r="F37" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="G37" s="25" t="inlineStr">
+        <is>
+          <t>31 Motivos</t>
+        </is>
+      </c>
+      <c r="H37" s="25" t="inlineStr">
+        <is>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="I37" s="26" t="n">
+        <v>300.6</v>
+      </c>
+      <c r="J37" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="K37" s="27">
+        <f>IF(I37="","",I37*J37)</f>
+        <v/>
+      </c>
+      <c r="L37" s="28" t="inlineStr"/>
+      <c r="M37" s="25" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="N37" s="29">
+        <f>IF(OR(M37&lt;&gt;"Sim",I37=""),0,K37*IF(H37="BRL",1,IF(H37="EUR",Parâmetros!$B$4,IF(H37="USD",Parâmetros!$B$5,1))))</f>
+        <v/>
+      </c>
+      <c r="O37" s="25" t="inlineStr">
+        <is>
           <t>Cotado</t>
         </is>
       </c>
-      <c r="P36" s="30" t="inlineStr">
+      <c r="P37" s="30" t="inlineStr">
         <is>
           <t>Cotação de 21/09: R$ 1.503,00 para os 5 (R$ 300,60 por pessoa). Confirmar se a apólice do filho cobre desde o embarque dele em 04/01.</t>
         </is>
       </c>
     </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="C38" s="21" t="inlineStr">
+    <row r="38"/>
+    <row r="39">
+      <c r="C39" s="21" t="inlineStr">
         <is>
           <t>SUBTOTAL EM R$ (itens marcados como Sim)</t>
         </is>
       </c>
-      <c r="N38" s="31">
-        <f>SUM(N5:N36)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="C39" s="12" t="inlineStr">
+      <c r="N39" s="31">
+        <f>SUM(N5:N37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" s="12" t="inlineStr">
         <is>
           <t>Taxa de serviço LusaTravel</t>
         </is>
       </c>
-      <c r="N39" s="13">
-        <f>N38*Parâmetros!$B$10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="32" t="n"/>
-      <c r="B40" s="32" t="n"/>
-      <c r="C40" s="33" t="inlineStr">
+      <c r="N40" s="13">
+        <f>N39*Parâmetros!$B$10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="32" t="n"/>
+      <c r="B41" s="32" t="n"/>
+      <c r="C41" s="33" t="inlineStr">
         <is>
           <t>TOTAL PARA O CLIENTE</t>
         </is>
       </c>
-      <c r="D40" s="32" t="n"/>
-      <c r="E40" s="32" t="n"/>
-      <c r="F40" s="32" t="n"/>
-      <c r="G40" s="32" t="n"/>
-      <c r="H40" s="32" t="n"/>
-      <c r="I40" s="32" t="n"/>
-      <c r="J40" s="32" t="n"/>
-      <c r="K40" s="32" t="n"/>
-      <c r="L40" s="32" t="n"/>
-      <c r="M40" s="32" t="n"/>
-      <c r="N40" s="34">
-        <f>N38+N39</f>
-        <v/>
-      </c>
-      <c r="O40" s="32" t="n"/>
-      <c r="P40" s="32" t="n"/>
-    </row>
-    <row r="41">
-      <c r="C41" s="2" t="inlineStr">
+      <c r="D41" s="32" t="n"/>
+      <c r="E41" s="32" t="n"/>
+      <c r="F41" s="32" t="n"/>
+      <c r="G41" s="32" t="n"/>
+      <c r="H41" s="32" t="n"/>
+      <c r="I41" s="32" t="n"/>
+      <c r="J41" s="32" t="n"/>
+      <c r="K41" s="32" t="n"/>
+      <c r="L41" s="32" t="n"/>
+      <c r="M41" s="32" t="n"/>
+      <c r="N41" s="34">
+        <f>N39+N40</f>
+        <v/>
+      </c>
+      <c r="O41" s="32" t="n"/>
+      <c r="P41" s="32" t="n"/>
+    </row>
+    <row r="42">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>*Nada reservado, apenas cotado.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:P36"/>
+  <autoFilter ref="A4:P37"/>
   <dataValidations count="3">
-    <dataValidation sqref="O5:O36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O5:O37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"A cotar,Cotado,Aprovado pelo cliente,Reservado,Descartado"</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="M5:M37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="H5:H37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"BRL,EUR,USD"</formula1>
     </dataValidation>
   </dataValidations>
